--- a/appliances_usage.xlsx
+++ b/appliances_usage.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26502"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dianadanilenko/Desktop/appliances_analysis/usage/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dand\Documents\GitHub\appliances_interventions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{A782A198-7060-E74C-8FE1-2C3C27FE7D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F017B1AD-04C9-40FD-9354-749AAD4D5BBC}"/>
   <bookViews>
-    <workbookView xWindow="-4480" yWindow="-21100" windowWidth="38400" windowHeight="19400" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4485" yWindow="-21105" windowWidth="38400" windowHeight="19395" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Usage" sheetId="5" state="hidden" r:id="rId1"/>
@@ -22,9 +21,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Appliances!$AR$1:$AR$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Usage!$A$1:$BN$53</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="29452" r:id="rId5"/>
+    <pivotCache cacheId="22" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -46,35 +45,62 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={73C2226C-6106-4DC2-88CF-9C0A06F48311}</author>
     <author>tc={CEE78422-255C-40DC-AFED-5AA185CC03E1}</author>
     <author>tc={C7CEED71-5EFE-4791-84D8-7010C40A69F0}</author>
   </authors>
   <commentList>
-    <comment ref="AQ1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="AQ1" authorId="0" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     is this supposed to capture mean difference between control and treatment or ?</t>
+        </r>
       </text>
     </comment>
-    <comment ref="AZ1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="AZ1" authorId="1" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     daily kWh</t>
+        </r>
       </text>
     </comment>
-    <comment ref="AQ22" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="AQ22" authorId="2" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     in kWh</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -82,17 +108,26 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={1DD52412-77C6-1E43-B8CC-07AD562D2C6E}</author>
   </authors>
   <commentList>
-    <comment ref="AA1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="AA1" authorId="0" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     check label studies from srmt for label type</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -100,19 +135,28 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={CF36070F-7893-4948-8AB8-1CADF6EBBFD9}</author>
   </authors>
   <commentList>
-    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="D6" authorId="0" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     a bit confused as of where it’s correlation and where - quasi-experimental
 Reply:
     the way i reassessed this was - market statistics - correlation, whereas hypothetical choice - quasi-experimental</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -2221,7 +2265,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="9">
     <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
@@ -2842,9 +2886,9 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Link" xfId="2" builtinId="8"/>
+    <cellStyle name="Prozent" xfId="1" builtinId="5"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -2878,7 +2922,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="45057.552441087966" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="334" xr:uid="{D639B32B-9019-CA48-8E24-1BEF7DE87CE6}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="45057.552441087966" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="334">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:CD1048576" sheet="Appliances"/>
   </cacheSource>
@@ -34683,7 +34727,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1E95B189-0291-5F4C-AF42-581998D9F62B}" name="PivotTable2" cacheId="29452" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="22" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:BJ18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="92">
     <pivotField showAll="0"/>
@@ -35535,9 +35579,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BP53"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="4" max="4" width="20.625" customWidth="1"/>
     <col min="5" max="5" width="14.125" customWidth="1"/>
@@ -35585,7 +35629,7 @@
     <col min="67" max="67" width="25.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="48">
+    <row r="1" spans="1:68" ht="45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -43383,7 +43427,7 @@
         <v>6.7567567567567571E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:66" s="41" customFormat="1" ht="17.100000000000001">
+    <row r="39" spans="1:66" s="41" customFormat="1" ht="16.5">
       <c r="A39" s="45" t="s">
         <v>68</v>
       </c>
@@ -43588,7 +43632,7 @@
       </c>
       <c r="BN39" s="43"/>
     </row>
-    <row r="40" spans="1:66" s="41" customFormat="1" ht="17.100000000000001">
+    <row r="40" spans="1:66" s="41" customFormat="1" ht="16.5">
       <c r="A40" s="45" t="s">
         <v>68</v>
       </c>
@@ -43793,7 +43837,7 @@
       </c>
       <c r="BN40" s="43"/>
     </row>
-    <row r="41" spans="1:66" s="41" customFormat="1" ht="17.100000000000001">
+    <row r="41" spans="1:66" s="41" customFormat="1" ht="16.5">
       <c r="A41" s="45" t="s">
         <v>68</v>
       </c>
@@ -44002,7 +44046,7 @@
         <v>2.0421052631578922</v>
       </c>
     </row>
-    <row r="42" spans="1:66" s="41" customFormat="1" ht="17.100000000000001">
+    <row r="42" spans="1:66" s="41" customFormat="1" ht="16.5">
       <c r="A42" s="45" t="s">
         <v>68</v>
       </c>
@@ -46399,34 +46443,34 @@
   </sheetData>
   <dataConsolidate/>
   <dataValidations count="10">
-    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="M11:M12 N29:N32 M14:M16 L1:L1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="M11:M12 N29:N32 M14:M16 L1:L1048576">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="R1:W1 R2:Y9 X10:X12 BB43:BB52 BC29:BC32 S23:Y28 BB39:BC42 BC43:BC51 BC17:BC22 BB54:BB1048576 BB13:BC16 R33:Y1048576 BB17:BB38 BB1:BB12" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="R1:W1 R2:Y9 X10:X12 BB43:BB52 BC29:BC32 S23:Y28 BB39:BC42 BC43:BC51 BC17:BC22 BB54:BB1048576 BB13:BC16 R33:Y1048576 BB17:BB38 BB1:BB12">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="M1:Q9 M10 Y10:Y12 N10:W12 O29:Y32 P23:R28 N17:O28 P17:Y22 M13 N13:Y16 M17:M32 M33:Q1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="M1:Q9 M10 Y10:Y12 N10:W12 O29:Y32 P23:R28 N17:O28 P17:Y22 M13 N13:Y16 M17:M32 M33:Q1048576">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AO54:AO1048576 AO43:AO52 AO1:AO38" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AO54:AO1048576 AO43:AO52 AO1:AO38">
       <formula1>0</formula1>
       <formula2>3</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="X1" xr:uid="{00000000-0002-0000-0000-000004000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA53 AR53" xr:uid="{00000000-0002-0000-0000-000005000000}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J23:J37 J1:J12" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="X1"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA53 AR53"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J23:J37 J1:J12">
       <formula1>$F$2:$F$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K23:K37 K1:K12" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K23:K37 K1:K12">
       <formula1>$D$2:$D$6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K43:K51" xr:uid="{00000000-0002-0000-0000-000008000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K43:K51">
       <formula1>$D$2:$D$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J43:J51" xr:uid="{00000000-0002-0000-0000-000009000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J43:J51">
       <formula1>$F$2:$F$10</formula1>
     </dataValidation>
   </dataValidations>
@@ -46435,43 +46479,43 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Option to Opt/in - 1_x000a_No Option to Opt/in - 0_x000a_NA_x000a__x000a_" xr:uid="{00000000-0002-0000-0000-00000A000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Option to Opt/in - 1_x000a_No Option to Opt/in - 0_x000a_NA_x000a__x000a_">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B$2:$B$4</xm:f>
           </x14:formula1>
           <xm:sqref>BC23:BC28 BC54:BC1048576 BC33:BC38 BC1:BC12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000B000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$F$2:$F$9</xm:f>
           </x14:formula1>
           <xm:sqref>J54:J1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000C000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$A$2:$A$4</xm:f>
           </x14:formula1>
           <xm:sqref>AS43:AX51 AS54:AX1048576 AS23:AX38 AS2:AX12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000D000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$F$2:$F$10</xm:f>
           </x14:formula1>
           <xm:sqref>J38</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000E000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$E$2:$E$4</xm:f>
           </x14:formula1>
           <xm:sqref>AO43:AO51</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000F000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D$2:$D$6</xm:f>
           </x14:formula1>
           <xm:sqref>K54:K1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000010000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D$2:$D$7</xm:f>
           </x14:formula1>
@@ -46484,9 +46528,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:CH51"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="5" max="5" width="24.625" customWidth="1"/>
     <col min="6" max="6" width="17.625" customWidth="1"/>
@@ -46957,11 +47001,11 @@
         <v>1</v>
       </c>
       <c r="AZ2">
-        <f>AU2/AW2</f>
+        <f t="shared" ref="AZ2:AZ17" si="0">AU2/AW2</f>
         <v>2.7619047619047619</v>
       </c>
       <c r="BA2" s="102">
-        <f>EXP(AU2) - 1</f>
+        <f t="shared" ref="BA2:BA13" si="1">EXP(AU2) - 1</f>
         <v>5.9714995710287599E-2</v>
       </c>
       <c r="BB2" s="102"/>
@@ -47029,19 +47073,19 @@
         <v>1</v>
       </c>
       <c r="BX2" s="30">
-        <f>((AZ2^2)/(AZ2^2+BI2))^(1/2)</f>
+        <f t="shared" ref="BX2:BX37" si="2">((AZ2^2)/(AZ2^2+BI2))^(1/2)</f>
         <v>0.11481772350402021</v>
       </c>
       <c r="BY2" s="30">
-        <f>0.5*LN((1+BX2)/(1-BX2))</f>
+        <f t="shared" ref="BY2:BY37" si="3">0.5*LN((1+BX2)/(1-BX2))</f>
         <v>0.11532630395472614</v>
       </c>
       <c r="BZ2" s="30">
-        <f>((1-(BY2^2)^2)/(BI2-1))</f>
+        <f t="shared" ref="BZ2:BZ37" si="4">((1-(BY2^2)^2)/(BI2-1))</f>
         <v>1.754075624280991E-3</v>
       </c>
       <c r="CA2" s="30">
-        <f>1/(BI2-3)</f>
+        <f t="shared" ref="CA2:CA37" si="5">1/(BI2-3)</f>
         <v>1.7605633802816902E-3</v>
       </c>
       <c r="CE2" s="30">
@@ -47214,11 +47258,11 @@
         <v>1</v>
       </c>
       <c r="AZ3">
-        <f>AU3/AW3</f>
+        <f t="shared" si="0"/>
         <v>2.5714285714285712</v>
       </c>
       <c r="BA3" s="102">
-        <f>EXP(AU3) - 1</f>
+        <f t="shared" si="1"/>
         <v>5.5484602155080109E-2</v>
       </c>
       <c r="BB3" s="102"/>
@@ -47286,31 +47330,31 @@
         <v>1</v>
       </c>
       <c r="BX3" s="30">
-        <f>((AZ3^2)/(AZ3^2+BI3))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>0.10699322282140411</v>
       </c>
       <c r="BY3" s="30">
-        <f>0.5*LN((1+BX3)/(1-BX3))</f>
+        <f t="shared" si="3"/>
         <v>0.10740432025194586</v>
       </c>
       <c r="BZ3" s="30">
-        <f>((1-(BY3^2)^2)/(BI3-1))</f>
+        <f t="shared" si="4"/>
         <v>1.7541525050915158E-3</v>
       </c>
       <c r="CA3" s="30">
-        <f>1/(BI3-3)</f>
+        <f t="shared" si="5"/>
         <v>1.7605633802816902E-3</v>
       </c>
       <c r="CE3" s="30">
-        <f t="shared" ref="CE3:CE37" si="0">((AZ3^2)/(AZ3^2+BJ3))^(1/2)</f>
+        <f t="shared" ref="CE3:CE37" si="6">((AZ3^2)/(AZ3^2+BJ3))^(1/2)</f>
         <v>1.604274888962573E-2</v>
       </c>
       <c r="CF3" s="30">
-        <f t="shared" ref="CF3:CF37" si="1">0.5*LN((1+CE3)/(1-CE3))</f>
+        <f t="shared" ref="CF3:CF37" si="7">0.5*LN((1+CE3)/(1-CE3))</f>
         <v>1.6044125408511214E-2</v>
       </c>
       <c r="CG3" s="30">
-        <f t="shared" ref="CG3:CG37" si="2">((1-(CF3^2)^2)/(BJ3-1))</f>
+        <f t="shared" ref="CG3:CG37" si="8">((1-(CF3^2)^2)/(BJ3-1))</f>
         <v>3.8934742786873272E-5</v>
       </c>
       <c r="CH3" s="30">
@@ -47471,11 +47515,11 @@
         <v>1</v>
       </c>
       <c r="AZ4">
-        <f>AU4/AW4</f>
+        <f t="shared" si="0"/>
         <v>2.5714285714285712</v>
       </c>
       <c r="BA4" s="102">
-        <f>EXP(AU4) - 1</f>
+        <f t="shared" si="1"/>
         <v>5.5484602155080109E-2</v>
       </c>
       <c r="BB4" s="102"/>
@@ -47543,32 +47587,36 @@
         <v>1</v>
       </c>
       <c r="BX4" s="30">
-        <f>((AZ4^2)/(AZ4^2+BI4))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>0.10699322282140411</v>
       </c>
       <c r="BY4" s="30">
-        <f>0.5*LN((1+BX4)/(1-BX4))</f>
+        <f t="shared" si="3"/>
         <v>0.10740432025194586</v>
       </c>
       <c r="BZ4" s="30">
-        <f>((1-(BY4^2)^2)/(BI4-1))</f>
+        <f t="shared" si="4"/>
         <v>1.7541525050915158E-3</v>
       </c>
       <c r="CA4" s="30">
-        <f>1/(BI4-3)</f>
+        <f t="shared" si="5"/>
         <v>1.7605633802816902E-3</v>
       </c>
       <c r="CE4" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>1.604274888962573E-2</v>
       </c>
       <c r="CF4" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>1.6044125408511214E-2</v>
       </c>
       <c r="CG4" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>3.8934742786873272E-5</v>
+      </c>
+      <c r="CH4" s="30">
+        <f t="shared" ref="CH4:CH37" si="9">1/(BJ4-3)</f>
+        <v>3.8937777431664201E-5</v>
       </c>
     </row>
     <row r="5" spans="1:86">
@@ -47724,11 +47772,11 @@
         <v>1</v>
       </c>
       <c r="AZ5">
-        <f>AU5/AW5</f>
+        <f t="shared" si="0"/>
         <v>2.4761904761904758</v>
       </c>
       <c r="BA5" s="102">
-        <f>EXP(AU5) - 1</f>
+        <f t="shared" si="1"/>
         <v>5.3375742513364743E-2</v>
       </c>
       <c r="BB5" s="102"/>
@@ -47796,32 +47844,36 @@
         <v>1</v>
       </c>
       <c r="BX5" s="30">
-        <f>((AZ5^2)/(AZ5^2+BI5))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>0.10307341191556092</v>
       </c>
       <c r="BY5" s="30">
-        <f>0.5*LN((1+BX5)/(1-BX5))</f>
+        <f t="shared" si="3"/>
         <v>0.10344077825830729</v>
       </c>
       <c r="BZ5" s="30">
-        <f>((1-(BY5^2)^2)/(BI5-1))</f>
+        <f t="shared" si="4"/>
         <v>1.7541851054656437E-3</v>
       </c>
       <c r="CA5" s="30">
-        <f>1/(BI5-3)</f>
+        <f t="shared" si="5"/>
         <v>1.7605633802816902E-3</v>
       </c>
       <c r="CE5" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>1.5448717538944366E-2</v>
       </c>
       <c r="CF5" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>1.5449946726739888E-2</v>
       </c>
       <c r="CG5" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>3.8934743148337576E-5</v>
+      </c>
+      <c r="CH5" s="30">
+        <f t="shared" si="9"/>
+        <v>3.8937777431664201E-5</v>
       </c>
     </row>
     <row r="6" spans="1:86">
@@ -47977,11 +48029,11 @@
         <v>1</v>
       </c>
       <c r="AZ6">
-        <f>AU6/AW6</f>
+        <f t="shared" si="0"/>
         <v>2.6666666666666665</v>
       </c>
       <c r="BA6" s="102">
-        <f>EXP(AU6) - 1</f>
+        <f t="shared" si="1"/>
         <v>5.7597683736611227E-2</v>
       </c>
       <c r="BB6" s="102"/>
@@ -48049,32 +48101,36 @@
         <v>1</v>
       </c>
       <c r="BX6" s="30">
-        <f>((AZ6^2)/(AZ6^2+BI6))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>0.1109080511509852</v>
       </c>
       <c r="BY6" s="30">
-        <f>0.5*LN((1+BX6)/(1-BX6))</f>
+        <f t="shared" si="3"/>
         <v>0.11136618214120936</v>
       </c>
       <c r="BZ6" s="30">
-        <f>((1-(BY6^2)^2)/(BI6-1))</f>
+        <f t="shared" si="4"/>
         <v>1.7541161049408759E-3</v>
       </c>
       <c r="CA6" s="30">
-        <f>1/(BI6-3)</f>
+        <f t="shared" si="5"/>
         <v>1.7605633802816902E-3</v>
       </c>
       <c r="CE6" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>1.6890120870043275E-2</v>
       </c>
       <c r="CF6" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>1.6891727261415537E-2</v>
       </c>
       <c r="CG6" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>4.0130018001787165E-5</v>
+      </c>
+      <c r="CH6" s="30">
+        <f t="shared" si="9"/>
+        <v>4.0133242364650637E-5</v>
       </c>
     </row>
     <row r="7" spans="1:86">
@@ -48230,11 +48286,11 @@
         <v>1</v>
       </c>
       <c r="AZ7">
-        <f>AU7/AW7</f>
+        <f t="shared" si="0"/>
         <v>2.0454545454545454</v>
       </c>
       <c r="BA7" s="102">
-        <f>EXP(AU7) - 1</f>
+        <f t="shared" si="1"/>
         <v>4.6027859908716939E-2</v>
       </c>
       <c r="BB7" s="102"/>
@@ -48302,32 +48358,36 @@
         <v>1</v>
       </c>
       <c r="BX7" s="30">
-        <f>((AZ7^2)/(AZ7^2+BI7))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>8.5287714841797826E-2</v>
       </c>
       <c r="BY7" s="30">
-        <f>0.5*LN((1+BX7)/(1-BX7))</f>
+        <f t="shared" si="3"/>
         <v>8.5495416206607486E-2</v>
       </c>
       <c r="BZ7" s="30">
-        <f>((1-(BY7^2)^2)/(BI7-1))</f>
+        <f t="shared" si="4"/>
         <v>1.7542922310596193E-3</v>
       </c>
       <c r="CA7" s="30">
-        <f>1/(BI7-3)</f>
+        <f t="shared" si="5"/>
         <v>1.7605633802816902E-3</v>
       </c>
       <c r="CE7" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>1.3597084343537518E-2</v>
       </c>
       <c r="CF7" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>1.3597922382671032E-2</v>
       </c>
       <c r="CG7" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>4.419889351649495E-5</v>
+      </c>
+      <c r="CH7" s="30">
+        <f t="shared" si="9"/>
+        <v>4.4202802457675817E-5</v>
       </c>
     </row>
     <row r="8" spans="1:86" s="105" customFormat="1">
@@ -48483,11 +48543,11 @@
         <v>1</v>
       </c>
       <c r="AZ8">
-        <f>AU8/AW8</f>
+        <f t="shared" si="0"/>
         <v>1.9655172413793103</v>
       </c>
       <c r="BA8" s="102">
-        <f>EXP(AU8) - 1</f>
+        <f t="shared" si="1"/>
         <v>5.8655810395500163E-2</v>
       </c>
       <c r="BB8" s="102"/>
@@ -48555,35 +48615,39 @@
         <v>1</v>
       </c>
       <c r="BX8" s="30">
-        <f>((AZ8^2)/(AZ8^2+BI8))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>8.1977483380554009E-2</v>
       </c>
       <c r="BY8" s="30">
-        <f>0.5*LN((1+BX8)/(1-BX8))</f>
+        <f t="shared" si="3"/>
         <v>8.2161865388990771E-2</v>
       </c>
       <c r="BZ8" s="30">
-        <f>((1-(BY8^2)^2)/(BI8-1))</f>
+        <f t="shared" si="4"/>
         <v>1.7543060171508703E-3</v>
       </c>
       <c r="CA8" s="30">
-        <f>1/(BI8-3)</f>
+        <f t="shared" si="5"/>
         <v>1.7605633802816902E-3</v>
       </c>
       <c r="CB8"/>
       <c r="CC8"/>
       <c r="CD8"/>
       <c r="CE8" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>1.2263217028804526E-2</v>
       </c>
       <c r="CF8" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>1.2263831825009192E-2</v>
       </c>
       <c r="CG8" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>3.8934744486036733E-5</v>
+      </c>
+      <c r="CH8" s="30">
+        <f t="shared" si="9"/>
+        <v>3.8937777431664201E-5</v>
       </c>
     </row>
     <row r="9" spans="1:86" s="105" customFormat="1">
@@ -48739,11 +48803,11 @@
         <v>1</v>
       </c>
       <c r="AZ9">
-        <f>AU9/AW9</f>
+        <f t="shared" si="0"/>
         <v>3.0476190476190474</v>
       </c>
       <c r="BA9" s="102">
-        <f>EXP(AU9) - 1</f>
+        <f t="shared" si="1"/>
         <v>6.6092398761505189E-2</v>
       </c>
       <c r="BB9" s="102"/>
@@ -48811,35 +48875,39 @@
         <v>1</v>
       </c>
       <c r="BX9" s="30">
-        <f>((AZ9^2)/(AZ9^2+BI9))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>0.12651408859229724</v>
       </c>
       <c r="BY9" s="30">
-        <f>0.5*LN((1+BX9)/(1-BX9))</f>
+        <f t="shared" si="3"/>
         <v>0.12719563288286462</v>
       </c>
       <c r="BZ9" s="30">
-        <f>((1-(BY9^2)^2)/(BI9-1))</f>
+        <f t="shared" si="4"/>
         <v>1.7539267521528995E-3</v>
       </c>
       <c r="CA9" s="30">
-        <f>1/(BI9-3)</f>
+        <f t="shared" si="5"/>
         <v>1.7605633802816902E-3</v>
       </c>
       <c r="CB9"/>
       <c r="CC9"/>
       <c r="CD9"/>
       <c r="CE9" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>1.901263827271819E-2</v>
       </c>
       <c r="CF9" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>1.9014929668500848E-2</v>
       </c>
       <c r="CG9" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>3.8934740276783467E-5</v>
+      </c>
+      <c r="CH9" s="30">
+        <f t="shared" si="9"/>
+        <v>3.8937777431664201E-5</v>
       </c>
     </row>
     <row r="10" spans="1:86" s="105" customFormat="1">
@@ -48995,11 +49063,11 @@
         <v>1</v>
       </c>
       <c r="AZ10">
-        <f>AU10/AW10</f>
+        <f t="shared" si="0"/>
         <v>3.0952380952380953</v>
       </c>
       <c r="BA10" s="102">
-        <f>EXP(AU10) - 1</f>
+        <f t="shared" si="1"/>
         <v>6.7159024384192634E-2</v>
       </c>
       <c r="BB10" s="102"/>
@@ -49067,35 +49135,39 @@
         <v>1</v>
       </c>
       <c r="BX10" s="30">
-        <f>((AZ10^2)/(AZ10^2+BI10))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>0.12845849802371542</v>
       </c>
       <c r="BY10" s="30">
-        <f>0.5*LN((1+BX10)/(1-BX10))</f>
+        <f t="shared" si="3"/>
         <v>0.12917216710458213</v>
       </c>
       <c r="BZ10" s="30">
-        <f>((1-(BY10^2)^2)/(BI10-1))</f>
+        <f t="shared" si="4"/>
         <v>1.7538975364909846E-3</v>
       </c>
       <c r="CA10" s="30">
-        <f>1/(BI10-3)</f>
+        <f t="shared" si="5"/>
         <v>1.7605633802816902E-3</v>
       </c>
       <c r="CB10"/>
       <c r="CC10"/>
       <c r="CD10"/>
       <c r="CE10" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>1.9603633594857048E-2</v>
       </c>
       <c r="CF10" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>1.960614541553575E-2</v>
       </c>
       <c r="CG10" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>4.0130015339135551E-5</v>
+      </c>
+      <c r="CH10" s="30">
+        <f t="shared" si="9"/>
+        <v>4.0133242364650637E-5</v>
       </c>
     </row>
     <row r="11" spans="1:86" s="105" customFormat="1">
@@ -49251,11 +49323,11 @@
         <v>1</v>
       </c>
       <c r="AZ11">
-        <f>AU11/AW11</f>
+        <f t="shared" si="0"/>
         <v>3.5454545454545459</v>
       </c>
       <c r="BA11" s="102">
-        <f>EXP(AU11) - 1</f>
+        <f t="shared" si="1"/>
         <v>8.1122658670083059E-2</v>
       </c>
       <c r="BB11" s="102"/>
@@ -49323,35 +49395,39 @@
         <v>1</v>
       </c>
       <c r="BX11" s="30">
-        <f>((AZ11^2)/(AZ11^2+BI11))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>0.14676596375341069</v>
       </c>
       <c r="BY11" s="30">
-        <f>0.5*LN((1+BX11)/(1-BX11))</f>
+        <f t="shared" si="3"/>
         <v>0.14783358799274471</v>
       </c>
       <c r="BZ11" s="30">
-        <f>((1-(BY11^2)^2)/(BI11-1))</f>
+        <f t="shared" si="4"/>
         <v>1.753548015859059E-3</v>
       </c>
       <c r="CA11" s="30">
-        <f>1/(BI11-3)</f>
+        <f t="shared" si="5"/>
         <v>1.7605633802816902E-3</v>
       </c>
       <c r="CB11"/>
       <c r="CC11"/>
       <c r="CD11"/>
       <c r="CE11" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>2.4694819007967089E-2</v>
       </c>
       <c r="CF11" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>2.4699840759681221E-2</v>
       </c>
       <c r="CG11" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>4.8546027855710976E-5</v>
+      </c>
+      <c r="CH11" s="30">
+        <f t="shared" si="9"/>
+        <v>4.8550759819391176E-5</v>
       </c>
     </row>
     <row r="12" spans="1:86">
@@ -49507,11 +49583,11 @@
         <v>1</v>
       </c>
       <c r="AZ12">
-        <f>AU12/AW12</f>
+        <f t="shared" si="0"/>
         <v>3.5454545454545459</v>
       </c>
       <c r="BA12" s="102">
-        <f>EXP(AU12) - 1</f>
+        <f t="shared" si="1"/>
         <v>8.1122658670083059E-2</v>
       </c>
       <c r="BB12" s="102"/>
@@ -49579,32 +49655,36 @@
         <v>1</v>
       </c>
       <c r="BX12" s="30">
-        <f>((AZ12^2)/(AZ12^2+BI12))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>0.14676596375341069</v>
       </c>
       <c r="BY12" s="30">
-        <f>0.5*LN((1+BX12)/(1-BX12))</f>
+        <f t="shared" si="3"/>
         <v>0.14783358799274471</v>
       </c>
       <c r="BZ12" s="30">
-        <f>((1-(BY12^2)^2)/(BI12-1))</f>
+        <f t="shared" si="4"/>
         <v>1.753548015859059E-3</v>
       </c>
       <c r="CA12" s="30">
-        <f>1/(BI12-3)</f>
+        <f t="shared" si="5"/>
         <v>1.7605633802816902E-3</v>
       </c>
       <c r="CE12" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>2.4694819007967089E-2</v>
       </c>
       <c r="CF12" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>2.4699840759681221E-2</v>
       </c>
       <c r="CG12" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>4.8546027855710976E-5</v>
+      </c>
+      <c r="CH12" s="30">
+        <f t="shared" si="9"/>
+        <v>4.8550759819391176E-5</v>
       </c>
     </row>
     <row r="13" spans="1:86" s="107" customFormat="1">
@@ -49760,11 +49840,11 @@
         <v>1</v>
       </c>
       <c r="AZ13">
-        <f>AU13/AW13</f>
+        <f t="shared" si="0"/>
         <v>2.6538461538461542</v>
       </c>
       <c r="BA13" s="102">
-        <f>EXP(AU13) - 1</f>
+        <f t="shared" si="1"/>
         <v>7.1436209148346252E-2</v>
       </c>
       <c r="BB13" s="102"/>
@@ -49832,35 +49912,39 @@
         <v>1</v>
       </c>
       <c r="BX13" s="30">
-        <f>((AZ13^2)/(AZ13^2+BI13))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>0.11038135154213211</v>
       </c>
       <c r="BY13" s="30">
-        <f>0.5*LN((1+BX13)/(1-BX13))</f>
+        <f t="shared" si="3"/>
         <v>0.11083295461476669</v>
       </c>
       <c r="BZ13" s="30">
-        <f>((1-(BY13^2)^2)/(BI13-1))</f>
+        <f t="shared" si="4"/>
         <v>1.7541212363579208E-3</v>
       </c>
       <c r="CA13" s="30">
-        <f>1/(BI13-3)</f>
+        <f t="shared" si="5"/>
         <v>1.7605633802816902E-3</v>
       </c>
       <c r="CB13"/>
       <c r="CC13"/>
       <c r="CD13"/>
       <c r="CE13" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>1.8487062317075937E-2</v>
       </c>
       <c r="CF13" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>1.8489168865908314E-2</v>
       </c>
       <c r="CG13" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>4.8546040251420529E-5</v>
+      </c>
+      <c r="CH13" s="30">
+        <f t="shared" si="9"/>
+        <v>4.8550759819391176E-5</v>
       </c>
     </row>
     <row r="14" spans="1:86">
@@ -50015,7 +50099,7 @@
         <v>1</v>
       </c>
       <c r="AZ14">
-        <f>AU14/AW14</f>
+        <f t="shared" si="0"/>
         <v>1.8213567929369965</v>
       </c>
       <c r="BA14" s="41" t="s">
@@ -50086,32 +50170,36 @@
         <v>1</v>
       </c>
       <c r="BX14" s="30">
-        <f>((AZ14^2)/(AZ14^2+BI14))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>4.336173775143707E-2</v>
       </c>
       <c r="BY14" s="30">
-        <f>0.5*LN((1+BX14)/(1-BX14))</f>
+        <f t="shared" si="3"/>
         <v>4.3388945280999909E-2</v>
       </c>
       <c r="BZ14" s="30">
-        <f>((1-(BY14^2)^2)/(BI14-1))</f>
+        <f t="shared" si="4"/>
         <v>5.6817980444038869E-4</v>
       </c>
       <c r="CA14" s="30">
-        <f>1/(BI14-3)</f>
+        <f t="shared" si="5"/>
         <v>5.6882821387940839E-4</v>
       </c>
       <c r="CE14" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>4.336173775143707E-2</v>
       </c>
       <c r="CF14" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>4.3388945280999909E-2</v>
       </c>
       <c r="CG14" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>5.6817980444038869E-4</v>
+      </c>
+      <c r="CH14" s="30">
+        <f t="shared" si="9"/>
+        <v>5.6882821387940839E-4</v>
       </c>
     </row>
     <row r="15" spans="1:86">
@@ -50266,7 +50354,7 @@
         <v>1</v>
       </c>
       <c r="AZ15">
-        <f>AU15/AW15</f>
+        <f t="shared" si="0"/>
         <v>1.7220426989123607</v>
       </c>
       <c r="BA15" s="41" t="s">
@@ -50337,32 +50425,36 @@
         <v>1</v>
       </c>
       <c r="BX15" s="30">
-        <f>((AZ15^2)/(AZ15^2+BI15))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>4.1001418393220745E-2</v>
       </c>
       <c r="BY15" s="30">
-        <f>0.5*LN((1+BX15)/(1-BX15))</f>
+        <f t="shared" si="3"/>
         <v>4.1024417647402674E-2</v>
       </c>
       <c r="BZ15" s="30">
-        <f>((1-(BY15^2)^2)/(BI15-1))</f>
+        <f t="shared" si="4"/>
         <v>5.6818020880763031E-4</v>
       </c>
       <c r="CA15" s="30">
-        <f>1/(BI15-3)</f>
+        <f t="shared" si="5"/>
         <v>5.6882821387940839E-4</v>
       </c>
       <c r="CE15" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>4.1001418393220745E-2</v>
       </c>
       <c r="CF15" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>4.1024417647402674E-2</v>
       </c>
       <c r="CG15" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>5.6818020880763031E-4</v>
+      </c>
+      <c r="CH15" s="30">
+        <f t="shared" si="9"/>
+        <v>5.6882821387940839E-4</v>
       </c>
     </row>
     <row r="16" spans="1:86">
@@ -50517,7 +50609,7 @@
         <v>1</v>
       </c>
       <c r="AZ16">
-        <f>AU16/AW16</f>
+        <f t="shared" si="0"/>
         <v>2.2952440645363477</v>
       </c>
       <c r="BA16" s="41" t="s">
@@ -50588,35 +50680,39 @@
         <v>1</v>
       </c>
       <c r="BX16" s="30">
-        <f>((AZ16^2)/(AZ16^2+BI16))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>7.5991955053229768E-2</v>
       </c>
       <c r="BY16" s="30">
-        <f>0.5*LN((1+BX16)/(1-BX16))</f>
+        <f t="shared" si="3"/>
         <v>7.6138742860659789E-2</v>
       </c>
       <c r="BZ16" s="30">
-        <f>((1-(BY16^2)^2)/(BI16-1))</f>
+        <f t="shared" si="4"/>
         <v>1.1037156661555521E-3</v>
       </c>
       <c r="CA16" s="30">
-        <f>1/(BI16-3)</f>
+        <f t="shared" si="5"/>
         <v>1.1061946902654867E-3</v>
       </c>
       <c r="CE16" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>7.5991955053229768E-2</v>
       </c>
       <c r="CF16" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>7.6138742860659789E-2</v>
       </c>
       <c r="CG16" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.1037156661555521E-3</v>
       </c>
+      <c r="CH16" s="30">
+        <f t="shared" si="9"/>
+        <v>1.1061946902654867E-3</v>
+      </c>
     </row>
-    <row r="17" spans="1:85">
+    <row r="17" spans="1:86">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -50768,7 +50864,7 @@
         <v>2</v>
       </c>
       <c r="AZ17">
-        <f>AU17/AW17</f>
+        <f t="shared" si="0"/>
         <v>0.4628137059347513</v>
       </c>
       <c r="BA17" s="41" t="s">
@@ -50839,35 +50935,39 @@
         <v>1</v>
       </c>
       <c r="BX17" s="30">
-        <f>((AZ17^2)/(AZ17^2+BI17))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>1.5365662610743538E-2</v>
       </c>
       <c r="BY17" s="30">
-        <f>0.5*LN((1+BX17)/(1-BX17))</f>
+        <f t="shared" si="3"/>
         <v>1.5366872078105973E-2</v>
       </c>
       <c r="BZ17" s="30">
-        <f>((1-(BY17^2)^2)/(BI17-1))</f>
+        <f t="shared" si="4"/>
         <v>1.1037526978339323E-3</v>
       </c>
       <c r="CA17" s="30">
-        <f>1/(BI17-3)</f>
+        <f t="shared" si="5"/>
         <v>1.1061946902654867E-3</v>
       </c>
       <c r="CE17" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>1.5365662610743538E-2</v>
       </c>
       <c r="CF17" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>1.5366872078105973E-2</v>
       </c>
       <c r="CG17" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.1037526978339323E-3</v>
       </c>
+      <c r="CH17" s="30">
+        <f t="shared" si="9"/>
+        <v>1.1061946902654867E-3</v>
+      </c>
     </row>
-    <row r="18" spans="1:85" s="107" customFormat="1">
+    <row r="18" spans="1:86" s="107" customFormat="1">
       <c r="A18" s="11" t="s">
         <v>68</v>
       </c>
@@ -51011,7 +51111,7 @@
         <v>86</v>
       </c>
       <c r="AW18">
-        <f>AU18/AZ18</f>
+        <f t="shared" ref="AW18:AW23" si="10">AU18/AZ18</f>
         <v>1.3627450980392156E-2</v>
       </c>
       <c r="AX18">
@@ -51024,7 +51124,7 @@
         <v>2.04</v>
       </c>
       <c r="BA18" s="102">
-        <f>EXP(AU18) - 1</f>
+        <f t="shared" ref="BA18:BA27" si="11">EXP(AU18) - 1</f>
         <v>2.8190025851083211E-2</v>
       </c>
       <c r="BB18" s="102"/>
@@ -51093,38 +51193,42 @@
         <v>1</v>
       </c>
       <c r="BX18" s="30">
-        <f>((AZ18^2)/(AZ18^2+BI18))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>1.9399418017388252E-2</v>
       </c>
       <c r="BY18" s="30">
-        <f>0.5*LN((1+BX18)/(1-BX18))</f>
+        <f t="shared" si="3"/>
         <v>1.9401852142681517E-2</v>
       </c>
       <c r="BZ18" s="30">
-        <f>((1-(BY18^2)^2)/(BI18-1))</f>
+        <f t="shared" si="4"/>
         <v>9.0473161883565525E-5</v>
       </c>
       <c r="CA18" s="30">
-        <f>1/(BI18-3)</f>
+        <f t="shared" si="5"/>
         <v>9.0489548457153195E-5</v>
       </c>
       <c r="CB18"/>
       <c r="CC18"/>
       <c r="CD18"/>
       <c r="CE18" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>6.1963113535979377E-3</v>
       </c>
       <c r="CF18" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>6.1963906563842173E-3</v>
       </c>
       <c r="CG18" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>9.2262838237946257E-6</v>
       </c>
+      <c r="CH18" s="30">
+        <f t="shared" si="9"/>
+        <v>9.2264540891644526E-6</v>
+      </c>
     </row>
-    <row r="19" spans="1:85" s="107" customFormat="1" ht="17.100000000000001" customHeight="1">
+    <row r="19" spans="1:86" s="107" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A19" s="11" t="s">
         <v>68</v>
       </c>
@@ -51268,7 +51372,7 @@
         <v>86</v>
       </c>
       <c r="AW19">
-        <f>AU19/AZ19</f>
+        <f t="shared" si="10"/>
         <v>1.4986225895316804E-2</v>
       </c>
       <c r="AX19">
@@ -51281,7 +51385,7 @@
         <v>3.63</v>
       </c>
       <c r="BA19" s="102">
-        <f>EXP(AU19) - 1</f>
+        <f t="shared" si="11"/>
         <v>5.590688044596992E-2</v>
       </c>
       <c r="BB19" s="102"/>
@@ -51350,38 +51454,42 @@
         <v>1</v>
       </c>
       <c r="BX19" s="30">
-        <f>((AZ19^2)/(AZ19^2+BI19))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>3.4505490005142594E-2</v>
       </c>
       <c r="BY19" s="30">
-        <f>0.5*LN((1+BX19)/(1-BX19))</f>
+        <f t="shared" si="3"/>
         <v>3.4519194206964816E-2</v>
       </c>
       <c r="BZ19" s="30">
-        <f>((1-(BY19^2)^2)/(BI19-1))</f>
+        <f t="shared" si="4"/>
         <v>9.0473046245324396E-5</v>
       </c>
       <c r="CA19" s="30">
-        <f>1/(BI19-3)</f>
+        <f t="shared" si="5"/>
         <v>9.0489548457153195E-5</v>
       </c>
       <c r="CB19"/>
       <c r="CC19"/>
       <c r="CD19"/>
       <c r="CE19" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>1.8739199625567457E-2</v>
       </c>
       <c r="CF19" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>1.8741393558640896E-2</v>
       </c>
       <c r="CG19" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.6659554162372169E-5</v>
       </c>
+      <c r="CH19" s="30">
+        <f t="shared" si="9"/>
+        <v>2.6660978991148553E-5</v>
+      </c>
     </row>
-    <row r="20" spans="1:85" s="107" customFormat="1">
+    <row r="20" spans="1:86" s="107" customFormat="1">
       <c r="A20" s="11" t="s">
         <v>68</v>
       </c>
@@ -51525,7 +51633,7 @@
         <v>86</v>
       </c>
       <c r="AW20">
-        <f>AU20/AZ20</f>
+        <f t="shared" si="10"/>
         <v>1.7333333333333336E-2</v>
       </c>
       <c r="AX20">
@@ -51538,7 +51646,7 @@
         <v>3.15</v>
       </c>
       <c r="BA20" s="102">
-        <f>EXP(AU20) - 1</f>
+        <f t="shared" si="11"/>
         <v>5.6118082941604586E-2</v>
       </c>
       <c r="BB20" s="102"/>
@@ -51607,38 +51715,42 @@
         <v>1</v>
       </c>
       <c r="BX20" s="30">
-        <f>((AZ20^2)/(AZ20^2+BI20))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>2.9877055832671907E-2</v>
       </c>
       <c r="BY20" s="30">
-        <f>0.5*LN((1+BX20)/(1-BX20))</f>
+        <f t="shared" si="3"/>
         <v>2.9885950400025899E-2</v>
       </c>
       <c r="BZ20" s="30">
-        <f>((1-(BY20^2)^2)/(BI20-1))</f>
+        <f t="shared" si="4"/>
         <v>9.0049455402728065E-5</v>
       </c>
       <c r="CA20" s="30">
-        <f>1/(BI20-3)</f>
+        <f t="shared" si="5"/>
         <v>9.0065747996037111E-5</v>
       </c>
       <c r="CB20"/>
       <c r="CC20"/>
       <c r="CD20"/>
       <c r="CE20" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>1.2012412374711942E-2</v>
       </c>
       <c r="CF20" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>1.2012990213972756E-2</v>
       </c>
       <c r="CG20" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.4544819559496541E-5</v>
       </c>
+      <c r="CH20" s="30">
+        <f t="shared" si="9"/>
+        <v>1.4545242978283952E-5</v>
+      </c>
     </row>
-    <row r="21" spans="1:85">
+    <row r="21" spans="1:86">
       <c r="A21" s="11" t="s">
         <v>68</v>
       </c>
@@ -51782,7 +51894,7 @@
         <v>86</v>
       </c>
       <c r="AW21">
-        <f>AU21/AZ21</f>
+        <f t="shared" si="10"/>
         <v>1.682730923694779E-2</v>
       </c>
       <c r="AX21">
@@ -51795,7 +51907,7 @@
         <v>2.4900000000000002</v>
       </c>
       <c r="BA21" s="102">
-        <f>EXP(AU21) - 1</f>
+        <f t="shared" si="11"/>
         <v>4.2790194517186686E-2</v>
       </c>
       <c r="BB21" s="102"/>
@@ -51864,35 +51976,39 @@
         <v>1</v>
       </c>
       <c r="BX21" s="30">
-        <f>((AZ21^2)/(AZ21^2+BI21))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>2.3621056611749961E-2</v>
       </c>
       <c r="BY21" s="30">
-        <f>0.5*LN((1+BX21)/(1-BX21))</f>
+        <f t="shared" si="3"/>
         <v>2.3625451239868967E-2</v>
       </c>
       <c r="BZ21" s="30">
-        <f>((1-(BY21^2)^2)/(BI21-1))</f>
+        <f t="shared" si="4"/>
         <v>9.0049499185523786E-5</v>
       </c>
       <c r="CA21" s="30">
-        <f>1/(BI21-3)</f>
+        <f t="shared" si="5"/>
         <v>9.0065747996037111E-5</v>
       </c>
       <c r="CE21" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>1.3650404945197309E-2</v>
       </c>
       <c r="CF21" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>1.3651252882826532E-2</v>
       </c>
       <c r="CG21" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>3.0059817995947289E-5</v>
       </c>
+      <c r="CH21" s="30">
+        <f t="shared" si="9"/>
+        <v>3.0061626333984669E-5</v>
+      </c>
     </row>
-    <row r="22" spans="1:85">
+    <row r="22" spans="1:86">
       <c r="A22" s="11" t="s">
         <v>68</v>
       </c>
@@ -52036,7 +52152,7 @@
         <v>86</v>
       </c>
       <c r="AW22">
-        <f>AU22/AZ22</f>
+        <f t="shared" si="10"/>
         <v>4.3478260869565216E-2</v>
       </c>
       <c r="AX22">
@@ -52049,7 +52165,7 @@
         <v>0.23</v>
       </c>
       <c r="BA22" s="102">
-        <f>EXP(AU22) - 1</f>
+        <f t="shared" si="11"/>
         <v>1.0050167084167949E-2</v>
       </c>
       <c r="BB22" s="102"/>
@@ -52119,35 +52235,39 @@
         <v>1</v>
       </c>
       <c r="BX22" s="30">
-        <f>((AZ22^2)/(AZ22^2+BI22))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>1.0134490446309997E-2</v>
       </c>
       <c r="BY22" s="30">
-        <f>0.5*LN((1+BX22)/(1-BX22))</f>
+        <f t="shared" si="3"/>
         <v>1.0134837431758794E-2</v>
       </c>
       <c r="BZ22" s="30">
-        <f>((1-(BY22^2)^2)/(BI22-1))</f>
+        <f t="shared" si="4"/>
         <v>1.9455252713028077E-3</v>
       </c>
       <c r="CA22" s="30">
-        <f>1/(BI22-3)</f>
+        <f t="shared" si="5"/>
         <v>1.953125E-3</v>
       </c>
       <c r="CE22" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>1.0134490446309997E-2</v>
       </c>
       <c r="CF22" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>1.0134837431758794E-2</v>
       </c>
       <c r="CG22" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.9455252713028077E-3</v>
       </c>
+      <c r="CH22" s="30">
+        <f t="shared" si="9"/>
+        <v>1.953125E-3</v>
+      </c>
     </row>
-    <row r="23" spans="1:85">
+    <row r="23" spans="1:86">
       <c r="A23" s="11" t="s">
         <v>68</v>
       </c>
@@ -52291,7 +52411,7 @@
         <v>86</v>
       </c>
       <c r="AW23">
-        <f>AU23/AZ23</f>
+        <f t="shared" si="10"/>
         <v>2.4844720496894408E-2</v>
       </c>
       <c r="AX23">
@@ -52304,7 +52424,7 @@
         <v>4.83</v>
       </c>
       <c r="BA23" s="102">
-        <f>EXP(AU23) - 1</f>
+        <f t="shared" si="11"/>
         <v>0.12749685157937574</v>
       </c>
       <c r="BB23" s="102"/>
@@ -52374,35 +52494,39 @@
         <v>1</v>
       </c>
       <c r="BX23" s="30">
-        <f>((AZ23^2)/(AZ23^2+BI23))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>0.20817246417215696</v>
       </c>
       <c r="BY23" s="30">
-        <f>0.5*LN((1+BX23)/(1-BX23))</f>
+        <f t="shared" si="3"/>
         <v>0.21126026317506777</v>
       </c>
       <c r="BZ23" s="30">
-        <f>((1-(BY23^2)^2)/(BI23-1))</f>
+        <f t="shared" si="4"/>
         <v>1.9416499666781906E-3</v>
       </c>
       <c r="CA23" s="30">
-        <f>1/(BI23-3)</f>
+        <f t="shared" si="5"/>
         <v>1.953125E-3</v>
       </c>
       <c r="CE23" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>0.20817246417215696</v>
       </c>
       <c r="CF23" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0.21126026317506777</v>
       </c>
       <c r="CG23" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.9416499666781906E-3</v>
       </c>
+      <c r="CH23" s="30">
+        <f t="shared" si="9"/>
+        <v>1.953125E-3</v>
+      </c>
     </row>
-    <row r="24" spans="1:85">
+    <row r="24" spans="1:86">
       <c r="A24" s="11" t="s">
         <v>68</v>
       </c>
@@ -52555,11 +52679,11 @@
         <v>1</v>
       </c>
       <c r="AZ24">
-        <f>AU24/AW24</f>
+        <f t="shared" ref="AZ24:AZ30" si="12">AU24/AW24</f>
         <v>20.342105263157897</v>
       </c>
       <c r="BA24" s="109">
-        <f>EXP(AU24) - 1</f>
+        <f t="shared" si="11"/>
         <v>1.1662552812206535</v>
       </c>
       <c r="BB24" s="109"/>
@@ -52627,35 +52751,39 @@
         <v>0</v>
       </c>
       <c r="BX24" s="30">
-        <f>((AZ24^2)/(AZ24^2+BI24))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>0.38045554301813767</v>
       </c>
       <c r="BY24" s="30">
-        <f>0.5*LN((1+BX24)/(1-BX24))</f>
+        <f t="shared" si="3"/>
         <v>0.40059218306919919</v>
       </c>
       <c r="BZ24" s="30">
-        <f>((1-(BY24^2)^2)/(BI24-1))</f>
+        <f t="shared" si="4"/>
         <v>3.9862850415234801E-4</v>
       </c>
       <c r="CA24" s="30">
-        <f>1/(BI24-3)</f>
+        <f t="shared" si="5"/>
         <v>4.0950040950040953E-4</v>
       </c>
       <c r="CE24" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>0.38045554301813767</v>
       </c>
       <c r="CF24" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0.40059218306919919</v>
       </c>
       <c r="CG24" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>3.9862850415234801E-4</v>
       </c>
+      <c r="CH24" s="30">
+        <f t="shared" si="9"/>
+        <v>4.0950040950040953E-4</v>
+      </c>
     </row>
-    <row r="25" spans="1:85" ht="14.25" customHeight="1">
+    <row r="25" spans="1:86" ht="14.25" customHeight="1">
       <c r="A25" s="11" t="s">
         <v>68</v>
       </c>
@@ -52808,11 +52936,11 @@
         <v>1</v>
       </c>
       <c r="AZ25">
-        <f>AU25/AW25</f>
+        <f t="shared" si="12"/>
         <v>13.770491803278688</v>
       </c>
       <c r="BA25" s="109">
-        <f>EXP(AU25) - 1</f>
+        <f t="shared" si="11"/>
         <v>1.3163669767810915</v>
       </c>
       <c r="BB25" s="109"/>
@@ -52880,35 +53008,39 @@
         <v>1</v>
       </c>
       <c r="BX25" s="30">
-        <f>((AZ25^2)/(AZ25^2+BI25))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>0.26889407517381664</v>
       </c>
       <c r="BY25" s="30">
-        <f>0.5*LN((1+BX25)/(1-BX25))</f>
+        <f t="shared" si="3"/>
         <v>0.27567131993753202</v>
       </c>
       <c r="BZ25" s="30">
-        <f>((1-(BY25^2)^2)/(BI25-1))</f>
+        <f t="shared" si="4"/>
         <v>4.0880954322490722E-4</v>
       </c>
       <c r="CA25" s="30">
-        <f>1/(BI25-3)</f>
+        <f t="shared" si="5"/>
         <v>4.1152263374485596E-4</v>
       </c>
       <c r="CE25" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>0.26889407517381664</v>
       </c>
       <c r="CF25" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0.27567131993753202</v>
       </c>
       <c r="CG25" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>4.0880954322490722E-4</v>
       </c>
+      <c r="CH25" s="30">
+        <f t="shared" si="9"/>
+        <v>4.1152263374485596E-4</v>
+      </c>
     </row>
-    <row r="26" spans="1:85">
+    <row r="26" spans="1:86">
       <c r="A26" s="11" t="s">
         <v>68</v>
       </c>
@@ -53061,11 +53193,11 @@
         <v>2</v>
       </c>
       <c r="AZ26">
-        <f>AU26/AW26</f>
+        <f t="shared" si="12"/>
         <v>0.36666666666666664</v>
       </c>
       <c r="BA26" s="102">
-        <f>EXP(AU26) - 1</f>
+        <f t="shared" si="11"/>
         <v>1.1060722444719451E-2</v>
       </c>
       <c r="BB26" s="102"/>
@@ -53133,35 +53265,39 @@
         <v>0</v>
       </c>
       <c r="BX26" s="30">
-        <f>((AZ26^2)/(AZ26^2+BI26))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>7.4151520133472265E-3</v>
       </c>
       <c r="BY26" s="30">
-        <f>0.5*LN((1+BX26)/(1-BX26))</f>
+        <f t="shared" si="3"/>
         <v>7.4152879239220478E-3</v>
       </c>
       <c r="BZ26" s="30">
-        <f>((1-(BY26^2)^2)/(BI26-1))</f>
+        <f t="shared" si="4"/>
         <v>4.0916530154520679E-4</v>
       </c>
       <c r="CA26" s="30">
-        <f>1/(BI26-3)</f>
+        <f t="shared" si="5"/>
         <v>4.0950040950040953E-4</v>
       </c>
       <c r="CE26" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>7.4151520133472265E-3</v>
       </c>
       <c r="CF26" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>7.4152879239220478E-3</v>
       </c>
       <c r="CG26" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>4.0916530154520679E-4</v>
       </c>
+      <c r="CH26" s="30">
+        <f t="shared" si="9"/>
+        <v>4.0950040950040953E-4</v>
+      </c>
     </row>
-    <row r="27" spans="1:85">
+    <row r="27" spans="1:86">
       <c r="A27" s="11" t="s">
         <v>68</v>
       </c>
@@ -53314,11 +53450,11 @@
         <v>1</v>
       </c>
       <c r="AZ27">
-        <f>AU27/AW27</f>
+        <f t="shared" si="12"/>
         <v>1.6964285714285714</v>
       </c>
       <c r="BA27" s="102">
-        <f>EXP(AU27) - 1</f>
+        <f t="shared" si="11"/>
         <v>9.9658855126102841E-2</v>
       </c>
       <c r="BB27" s="102"/>
@@ -53386,35 +53522,39 @@
         <v>1</v>
       </c>
       <c r="BX27" s="30">
-        <f>((AZ27^2)/(AZ27^2+BI27))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>3.4372239036265163E-2</v>
       </c>
       <c r="BY27" s="30">
-        <f>0.5*LN((1+BX27)/(1-BX27))</f>
+        <f t="shared" si="3"/>
         <v>3.4385785009859983E-2</v>
       </c>
       <c r="BZ27" s="30">
-        <f>((1-(BY27^2)^2)/(BI27-1))</f>
+        <f t="shared" si="4"/>
         <v>4.1118363567940286E-4</v>
       </c>
       <c r="CA27" s="30">
-        <f>1/(BI27-3)</f>
+        <f t="shared" si="5"/>
         <v>4.1152263374485596E-4</v>
       </c>
       <c r="CE27" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>3.4372239036265163E-2</v>
       </c>
       <c r="CF27" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>3.4385785009859983E-2</v>
       </c>
       <c r="CG27" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>4.1118363567940286E-4</v>
       </c>
+      <c r="CH27" s="30">
+        <f t="shared" si="9"/>
+        <v>4.1152263374485596E-4</v>
+      </c>
     </row>
-    <row r="28" spans="1:85">
+    <row r="28" spans="1:86">
       <c r="A28" s="94" t="s">
         <v>68</v>
       </c>
@@ -53567,7 +53707,7 @@
         <v>2</v>
       </c>
       <c r="AZ28" s="94">
-        <f>AU28/AW28</f>
+        <f t="shared" si="12"/>
         <v>1.6066610455311974</v>
       </c>
       <c r="BA28" s="114">
@@ -53639,38 +53779,42 @@
         <v>1</v>
       </c>
       <c r="BX28" s="30">
-        <f>((AZ28^2)/(AZ28^2+BI28))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>9.0874644742587773E-2</v>
       </c>
       <c r="BY28" s="30">
-        <f>0.5*LN((1+BX28)/(1-BX28))</f>
+        <f t="shared" si="3"/>
         <v>9.112604528874467E-2</v>
       </c>
       <c r="BZ28" s="30">
-        <f>((1-(BY28^2)^2)/(BI28-1))</f>
+        <f t="shared" si="4"/>
         <v>3.2360227971281281E-3</v>
       </c>
       <c r="CA28" s="30">
-        <f>1/(BI28-3)</f>
+        <f t="shared" si="5"/>
         <v>3.2573289902280132E-3</v>
       </c>
       <c r="CB28" s="94"/>
       <c r="CC28" s="94"/>
       <c r="CD28" s="94"/>
       <c r="CE28" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>9.0874644742587773E-2</v>
       </c>
       <c r="CF28" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>9.112604528874467E-2</v>
       </c>
       <c r="CG28" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>3.2360227971281281E-3</v>
       </c>
+      <c r="CH28" s="30">
+        <f t="shared" si="9"/>
+        <v>3.2573289902280132E-3</v>
+      </c>
     </row>
-    <row r="29" spans="1:85">
+    <row r="29" spans="1:86">
       <c r="A29" s="94" t="s">
         <v>68</v>
       </c>
@@ -53823,7 +53967,7 @@
         <v>2</v>
       </c>
       <c r="AZ29" s="94">
-        <f>AU29/AW29</f>
+        <f t="shared" si="12"/>
         <v>0.67517730496453898</v>
       </c>
       <c r="BA29" s="114">
@@ -53895,38 +54039,42 @@
         <v>1</v>
       </c>
       <c r="BX29" s="30">
-        <f>((AZ29^2)/(AZ29^2+BI29))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>3.8319329539764628E-2</v>
       </c>
       <c r="BY29" s="30">
-        <f>0.5*LN((1+BX29)/(1-BX29))</f>
+        <f t="shared" si="3"/>
         <v>3.8338101745567565E-2</v>
       </c>
       <c r="BZ29" s="30">
-        <f>((1-(BY29^2)^2)/(BI29-1))</f>
+        <f t="shared" si="4"/>
         <v>3.2362389632958908E-3</v>
       </c>
       <c r="CA29" s="30">
-        <f>1/(BI29-3)</f>
+        <f t="shared" si="5"/>
         <v>3.2573289902280132E-3</v>
       </c>
       <c r="CB29" s="94"/>
       <c r="CC29" s="94"/>
       <c r="CD29" s="94"/>
       <c r="CE29" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>3.8319329539764628E-2</v>
       </c>
       <c r="CF29" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>3.8338101745567565E-2</v>
       </c>
       <c r="CG29" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>3.2362389632958908E-3</v>
       </c>
+      <c r="CH29" s="30">
+        <f t="shared" si="9"/>
+        <v>3.2573289902280132E-3</v>
+      </c>
     </row>
-    <row r="30" spans="1:85">
+    <row r="30" spans="1:86">
       <c r="A30" s="94" t="s">
         <v>68</v>
       </c>
@@ -54079,7 +54227,7 @@
         <v>1</v>
       </c>
       <c r="AZ30" s="94">
-        <f>AU30/AW30</f>
+        <f t="shared" si="12"/>
         <v>1.9500875656742556</v>
       </c>
       <c r="BA30" s="114">
@@ -54151,38 +54299,42 @@
         <v>1</v>
       </c>
       <c r="BX30" s="30">
-        <f>((AZ30^2)/(AZ30^2+BI30))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>0.11008437401907406</v>
       </c>
       <c r="BY30" s="30">
-        <f>0.5*LN((1+BX30)/(1-BX30))</f>
+        <f t="shared" si="3"/>
         <v>0.11053232404190938</v>
       </c>
       <c r="BZ30" s="30">
-        <f>((1-(BY30^2)^2)/(BI30-1))</f>
+        <f t="shared" si="4"/>
         <v>3.235762897306693E-3</v>
       </c>
       <c r="CA30" s="30">
-        <f>1/(BI30-3)</f>
+        <f t="shared" si="5"/>
         <v>3.2573289902280132E-3</v>
       </c>
       <c r="CB30" s="94"/>
       <c r="CC30" s="94"/>
       <c r="CD30" s="94"/>
       <c r="CE30" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>0.11008437401907406</v>
       </c>
       <c r="CF30" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0.11053232404190938</v>
       </c>
       <c r="CG30" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>3.235762897306693E-3</v>
       </c>
+      <c r="CH30" s="30">
+        <f t="shared" si="9"/>
+        <v>3.2573289902280132E-3</v>
+      </c>
     </row>
-    <row r="31" spans="1:85">
+    <row r="31" spans="1:86">
       <c r="A31" s="94" t="s">
         <v>68</v>
       </c>
@@ -54406,38 +54558,42 @@
         <v>1</v>
       </c>
       <c r="BX31" s="30">
-        <f>((AZ31^2)/(AZ31^2+BI31))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>2.9731353950735877E-2</v>
       </c>
       <c r="BY31" s="30">
-        <f>0.5*LN((1+BX31)/(1-BX31))</f>
+        <f t="shared" si="3"/>
         <v>2.9740118977144511E-2</v>
       </c>
       <c r="BZ31" s="30">
-        <f>((1-(BY31^2)^2)/(BI31-1))</f>
+        <f t="shared" si="4"/>
         <v>8.6805487647964076E-4</v>
       </c>
       <c r="CA31" s="30">
-        <f>1/(BI31-3)</f>
+        <f t="shared" si="5"/>
         <v>8.6956521739130438E-4</v>
       </c>
       <c r="CB31" s="94"/>
       <c r="CC31" s="94"/>
       <c r="CD31" s="94"/>
       <c r="CE31" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>8.5593158559973195E-3</v>
       </c>
       <c r="CF31" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>8.5595248890655371E-3</v>
       </c>
       <c r="CG31" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>7.1828759850033863E-5</v>
       </c>
+      <c r="CH31" s="30">
+        <f t="shared" si="9"/>
+        <v>7.1839080459770114E-5</v>
+      </c>
     </row>
-    <row r="32" spans="1:85">
+    <row r="32" spans="1:86">
       <c r="A32" t="s">
         <v>68</v>
       </c>
@@ -54660,35 +54816,39 @@
         <v>1</v>
       </c>
       <c r="BX32" s="30">
-        <f>((AZ32^2)/(AZ32^2+BI32))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>1.6644567843645545E-2</v>
       </c>
       <c r="BY32" s="30">
-        <f>0.5*LN((1+BX32)/(1-BX32))</f>
+        <f t="shared" si="3"/>
         <v>1.6646105178647452E-2</v>
       </c>
       <c r="BZ32" s="30">
-        <f>((1-(BY32^2)^2)/(BI32-1))</f>
+        <f t="shared" si="4"/>
         <v>1.0448457475501714E-6</v>
       </c>
       <c r="CA32" s="30">
-        <f>1/(BI32-3)</f>
+        <f t="shared" si="5"/>
         <v>1.0448480111840532E-6</v>
       </c>
       <c r="CE32" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>1.6644567843645545E-2</v>
       </c>
       <c r="CF32" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>1.6646105178647452E-2</v>
       </c>
       <c r="CG32" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.0448457475501714E-6</v>
       </c>
+      <c r="CH32" s="30">
+        <f t="shared" si="9"/>
+        <v>1.0448480111840532E-6</v>
+      </c>
     </row>
-    <row r="33" spans="1:85">
+    <row r="33" spans="1:86">
       <c r="A33" t="s">
         <v>68</v>
       </c>
@@ -54911,35 +55071,39 @@
         <v>1</v>
       </c>
       <c r="BX33" s="30">
-        <f>((AZ33^2)/(AZ33^2+BI33))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>1.6216400678486488E-2</v>
       </c>
       <c r="BY33" s="30">
-        <f>0.5*LN((1+BX33)/(1-BX33))</f>
+        <f t="shared" si="3"/>
         <v>1.6217822387367728E-2</v>
       </c>
       <c r="BZ33" s="30">
-        <f>((1-(BY33^2)^2)/(BI33-1))</f>
+        <f t="shared" si="4"/>
         <v>1.0448457554931792E-6</v>
       </c>
       <c r="CA33" s="30">
-        <f>1/(BI33-3)</f>
+        <f t="shared" si="5"/>
         <v>1.0448480111840532E-6</v>
       </c>
       <c r="CE33" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>1.6216400678486488E-2</v>
       </c>
       <c r="CF33" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>1.6217822387367728E-2</v>
       </c>
       <c r="CG33" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.0448457554931792E-6</v>
       </c>
+      <c r="CH33" s="30">
+        <f t="shared" si="9"/>
+        <v>1.0448480111840532E-6</v>
+      </c>
     </row>
-    <row r="34" spans="1:85">
+    <row r="34" spans="1:86">
       <c r="A34" t="s">
         <v>68</v>
       </c>
@@ -55162,35 +55326,39 @@
         <v>1</v>
       </c>
       <c r="BX34" s="30">
-        <f>((AZ34^2)/(AZ34^2+BI34))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>1.1925383671592018E-3</v>
       </c>
       <c r="BY34" s="30">
-        <f>0.5*LN((1+BX34)/(1-BX34))</f>
+        <f t="shared" si="3"/>
         <v>1.1925389324815921E-3</v>
       </c>
       <c r="BZ34" s="30">
-        <f>((1-(BY34^2)^2)/(BI34-1))</f>
+        <f t="shared" si="4"/>
         <v>1.0448458277717697E-6</v>
       </c>
       <c r="CA34" s="30">
-        <f>1/(BI34-3)</f>
+        <f t="shared" si="5"/>
         <v>1.0448480111840532E-6</v>
       </c>
       <c r="CE34" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>1.1925383671592018E-3</v>
       </c>
       <c r="CF34" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>1.1925389324815921E-3</v>
       </c>
       <c r="CG34" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.0448458277717697E-6</v>
       </c>
+      <c r="CH34" s="30">
+        <f t="shared" si="9"/>
+        <v>1.0448480111840532E-6</v>
+      </c>
     </row>
-    <row r="35" spans="1:85">
+    <row r="35" spans="1:86">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -55413,35 +55581,39 @@
         <v>1</v>
       </c>
       <c r="BX35" s="30">
-        <f>((AZ35^2)/(AZ35^2+BI35))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>9.4354709087100688E-4</v>
       </c>
       <c r="BY35" s="30">
-        <f>0.5*LN((1+BX35)/(1-BX35))</f>
+        <f t="shared" si="3"/>
         <v>9.4354737087855463E-4</v>
       </c>
       <c r="BZ35" s="30">
-        <f>((1-(BY35^2)^2)/(BI35-1))</f>
+        <f t="shared" si="4"/>
         <v>1.0448458277730546E-6</v>
       </c>
       <c r="CA35" s="30">
-        <f>1/(BI35-3)</f>
+        <f t="shared" si="5"/>
         <v>1.0448480111840532E-6</v>
       </c>
       <c r="CE35" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>9.4354709087100688E-4</v>
       </c>
       <c r="CF35" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>9.4354737087855463E-4</v>
       </c>
       <c r="CG35" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.0448458277730546E-6</v>
       </c>
+      <c r="CH35" s="30">
+        <f t="shared" si="9"/>
+        <v>1.0448480111840532E-6</v>
+      </c>
     </row>
-    <row r="36" spans="1:85" ht="18" customHeight="1">
+    <row r="36" spans="1:86" ht="18" customHeight="1">
       <c r="A36" s="11" t="s">
         <v>301</v>
       </c>
@@ -55663,19 +55835,19 @@
         <v>1</v>
       </c>
       <c r="BX36" s="30">
-        <f>((AZ36^2)/(AZ36^2+BI36))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>9.7825640875171802E-2</v>
       </c>
       <c r="BY36" s="30">
-        <f>0.5*LN((1+BX36)/(1-BX36))</f>
+        <f t="shared" si="3"/>
         <v>9.8139504130778904E-2</v>
       </c>
       <c r="BZ36" s="30">
-        <f>((1-(BY36^2)^2)/(BI36-1))</f>
+        <f t="shared" si="4"/>
         <v>2.5060331750897343E-3</v>
       </c>
       <c r="CA36" s="30">
-        <f>1/(BI36-3)</f>
+        <f t="shared" si="5"/>
         <v>2.5188916876574307E-3</v>
       </c>
       <c r="CC36" s="105">
@@ -55683,19 +55855,23 @@
         <v>398</v>
       </c>
       <c r="CE36" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>9.7825640875171802E-2</v>
       </c>
       <c r="CF36" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>9.8139504130778904E-2</v>
       </c>
       <c r="CG36" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.5060331750897343E-3</v>
       </c>
+      <c r="CH36" s="30">
+        <f t="shared" si="9"/>
+        <v>2.5188916876574307E-3</v>
+      </c>
     </row>
-    <row r="37" spans="1:85" ht="18" customHeight="1">
+    <row r="37" spans="1:86" ht="18" customHeight="1">
       <c r="A37" s="11" t="s">
         <v>301</v>
       </c>
@@ -55917,19 +56093,19 @@
         <v>1</v>
       </c>
       <c r="BX37" s="30">
-        <f>((AZ37^2)/(AZ37^2+BI37))^(1/2)</f>
+        <f t="shared" si="2"/>
         <v>0.1283416849069389</v>
       </c>
       <c r="BY37" s="30">
-        <f>0.5*LN((1+BX37)/(1-BX37))</f>
+        <f t="shared" si="3"/>
         <v>0.12905339585554831</v>
       </c>
       <c r="BZ37" s="30">
-        <f>((1-(BY37^2)^2)/(BI37-1))</f>
+        <f t="shared" si="4"/>
         <v>2.5055704720227212E-3</v>
       </c>
       <c r="CA37" s="30">
-        <f>1/(BI37-3)</f>
+        <f t="shared" si="5"/>
         <v>2.5188916876574307E-3</v>
       </c>
       <c r="CC37" s="105">
@@ -55937,50 +56113,54 @@
         <v>398</v>
       </c>
       <c r="CE37" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>0.1283416849069389</v>
       </c>
       <c r="CF37" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>0.12905339585554831</v>
       </c>
       <c r="CG37" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.5055704720227212E-3</v>
       </c>
+      <c r="CH37" s="30">
+        <f t="shared" si="9"/>
+        <v>2.5188916876574307E-3</v>
+      </c>
     </row>
-    <row r="38" spans="1:85">
+    <row r="38" spans="1:86">
       <c r="M38" s="18"/>
     </row>
-    <row r="39" spans="1:85">
+    <row r="39" spans="1:86">
       <c r="M39" s="18"/>
     </row>
-    <row r="40" spans="1:85">
+    <row r="40" spans="1:86">
       <c r="M40" s="18"/>
     </row>
-    <row r="41" spans="1:85">
+    <row r="41" spans="1:86">
       <c r="M41" s="18"/>
     </row>
-    <row r="42" spans="1:85">
+    <row r="42" spans="1:86">
       <c r="M42" s="18"/>
     </row>
-    <row r="43" spans="1:85">
+    <row r="43" spans="1:86">
       <c r="M43" s="18"/>
     </row>
-    <row r="44" spans="1:85">
+    <row r="44" spans="1:86">
       <c r="M44" s="18"/>
     </row>
-    <row r="45" spans="1:85">
+    <row r="45" spans="1:86">
       <c r="M45" s="18"/>
     </row>
-    <row r="46" spans="1:85">
+    <row r="46" spans="1:86">
       <c r="M46" s="18"/>
     </row>
-    <row r="47" spans="1:85" ht="15.75" customHeight="1">
+    <row r="47" spans="1:86" ht="15.75" customHeight="1">
       <c r="M47" s="18"/>
       <c r="BX47" s="30"/>
     </row>
-    <row r="48" spans="1:85">
+    <row r="48" spans="1:86">
       <c r="M48" s="18"/>
       <c r="BA48" s="117"/>
       <c r="BB48" s="117"/>
@@ -55999,8 +56179,8 @@
       <c r="BB51" s="118"/>
     </row>
   </sheetData>
-  <autoFilter ref="AR1:AR46" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:CD51">
+  <autoFilter ref="AR1:AR46"/>
+  <sortState ref="A2:CD51">
     <sortCondition ref="C2:C51"/>
   </sortState>
   <dataConsolidate/>
@@ -56011,17 +56191,17 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations xWindow="603" yWindow="1085" count="5">
-    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="I1 I5:I1048576" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="I1 I5:I1048576">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="AQ5:AQ6 AD1:AG1048576" xr:uid="{00000000-0002-0000-0100-000002000000}"/>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="Y38:AC1048576 Y18:Y37 Z14:AC37 Y1:AC13" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="AQ5:AQ6 AD1:AG1048576"/>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="Y38:AC1048576 Y18:Y37 Z14:AC37 Y1:AC13">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN38:BN1048576 BN1:BN35" xr:uid="{00000000-0002-0000-0100-000004000000}"/>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH1:AP1048576 U1:U1048576 S1:S1048576" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN38:BN1048576 BN1:BN35"/>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH1:AP1048576 U1:U1048576 S1:S1048576">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -56032,127 +56212,127 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="603" yWindow="1085" count="21">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000007000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B$2:$B$4</xm:f>
           </x14:formula1>
           <xm:sqref>U1:U6 U10:U1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000008000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$A$2:$A$4</xm:f>
           </x14:formula1>
           <xm:sqref>BU18:BW20 BU36:BW1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000009000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$C$2:$C$4</xm:f>
           </x14:formula1>
           <xm:sqref>BS21:BT35 BP21:BQ35 BO38:BO1048576 BO1:BO35</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000A000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$I$2:$I$3</xm:f>
           </x14:formula1>
           <xm:sqref>AV27:AV1048576 AV1:AV20</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000010000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$O:$O</xm:f>
           </x14:formula1>
           <xm:sqref>BT38:BT1048576 BT1:BT20</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000B000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$L$2:$L$9</xm:f>
           </x14:formula1>
           <xm:sqref>U1:U1048576 S1:S1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000C000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$K$2:$K$3</xm:f>
           </x14:formula1>
           <xm:sqref>U1:W1048576 S1:S1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000D000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$N$2:$N$7</xm:f>
           </x14:formula1>
           <xm:sqref>U1:W1048576 S1:S1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000F000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$J$2:$J$12</xm:f>
           </x14:formula1>
           <xm:sqref>K1:K1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000011000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$S:$S</xm:f>
           </x14:formula1>
           <xm:sqref>G1:G1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000012000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$G:$G</xm:f>
           </x14:formula1>
           <xm:sqref>AR1:AR1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000013000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$F:$F</xm:f>
           </x14:formula1>
           <xm:sqref>M52:M1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000014000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$P:$P</xm:f>
           </x14:formula1>
           <xm:sqref>AT1:AT1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000015000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D:$D</xm:f>
           </x14:formula1>
           <xm:sqref>S1:S1048576 U1:W1048576 N1:N1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000016000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$N:$N</xm:f>
           </x14:formula1>
           <xm:sqref>O1:O1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000017000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B:$B</xm:f>
           </x14:formula1>
           <xm:sqref>T1:T1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000018000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$R:$R</xm:f>
           </x14:formula1>
           <xm:sqref>E1:E1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000019000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$H:$H</xm:f>
           </x14:formula1>
           <xm:sqref>S1:S1048576 U1:U1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00001A000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$M:$M</xm:f>
           </x14:formula1>
           <xm:sqref>U1:U1048576 P1:P1048576 S1:S1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00001B000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$L$2:$L$10</xm:f>
           </x14:formula1>
           <xm:sqref>R1:R1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00001C000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$H$1:$H$7</xm:f>
           </x14:formula1>
@@ -56165,9 +56345,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4103C6B8-D66D-FF4D-BFD0-320CD520D889}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BJ18"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="28.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41" bestFit="1" customWidth="1"/>
@@ -59070,9 +59250,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S99"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="3" max="3" width="15.5" customWidth="1"/>
     <col min="5" max="5" width="19.625" customWidth="1"/>
@@ -59083,7 +59263,7 @@
     <col min="10" max="10" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17.100000000000001">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>384</v>
       </c>
@@ -59139,7 +59319,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="33.950000000000003">
+    <row r="2" spans="1:19" ht="31.5">
       <c r="A2">
         <v>0</v>
       </c>
@@ -59195,7 +59375,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="33.950000000000003">
+    <row r="3" spans="1:19" ht="31.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -59251,7 +59431,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="51">
+    <row r="4" spans="1:19" ht="47.25">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -59301,7 +59481,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="51">
+    <row r="5" spans="1:19" ht="47.25">
       <c r="D5" t="s">
         <v>293</v>
       </c>
@@ -60302,7 +60482,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="R2:S91">
+  <sortState ref="R2:S91">
     <sortCondition ref="R2:R91"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/appliances_usage.xlsx
+++ b/appliances_usage.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-4485" yWindow="-21105" windowWidth="38400" windowHeight="19395" firstSheet="1" activeTab="1"/>
+    <workbookView xWindow="-4488" yWindow="-21108" windowWidth="38400" windowHeight="19392" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Usage" sheetId="5" state="hidden" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="22" r:id="rId5"/>
+    <pivotCache cacheId="5" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3169" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3169" uniqueCount="619">
   <si>
     <t>Coder</t>
   </si>
@@ -2260,6 +2260,9 @@
   </si>
   <si>
     <t>Informing Versus Nudging in Environmental Policy</t>
+  </si>
+  <si>
+    <t>dishwasher</t>
   </si>
 </sst>
 </file>
@@ -34727,7 +34730,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="22" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:BJ18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="92">
     <pivotField showAll="0"/>
@@ -35581,55 +35584,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BP53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="4" max="4" width="20.625" customWidth="1"/>
-    <col min="5" max="5" width="14.125" customWidth="1"/>
-    <col min="7" max="7" width="16.125" customWidth="1"/>
-    <col min="8" max="8" width="16.625" customWidth="1"/>
-    <col min="10" max="10" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.59765625" customWidth="1"/>
+    <col min="5" max="5" width="14.09765625" customWidth="1"/>
+    <col min="7" max="7" width="16.09765625" customWidth="1"/>
+    <col min="8" max="8" width="16.59765625" customWidth="1"/>
+    <col min="10" max="10" width="18.09765625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" hidden="1" customWidth="1"/>
     <col min="12" max="17" width="0" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="16" hidden="1" customWidth="1"/>
     <col min="19" max="22" width="0" hidden="1" customWidth="1"/>
-    <col min="23" max="24" width="12.125" hidden="1" customWidth="1"/>
+    <col min="23" max="24" width="12.09765625" hidden="1" customWidth="1"/>
     <col min="25" max="25" width="0" hidden="1" customWidth="1"/>
     <col min="26" max="26" width="0" style="12" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="18.625" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="14.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.625" style="7" customWidth="1"/>
-    <col min="30" max="30" width="13.625" customWidth="1"/>
-    <col min="31" max="31" width="14.625" customWidth="1"/>
-    <col min="32" max="32" width="13.625" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="19.125" hidden="1" customWidth="1"/>
-    <col min="34" max="34" width="10.625" hidden="1" customWidth="1"/>
-    <col min="35" max="35" width="13.125" hidden="1" customWidth="1"/>
-    <col min="36" max="36" width="22.125" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="10.625" hidden="1" customWidth="1"/>
-    <col min="38" max="38" width="18.125" customWidth="1"/>
-    <col min="39" max="39" width="14.125" customWidth="1"/>
-    <col min="40" max="40" width="9.625" customWidth="1"/>
-    <col min="41" max="41" width="19.125" customWidth="1"/>
-    <col min="42" max="42" width="12.125" customWidth="1"/>
+    <col min="27" max="27" width="18.59765625" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.59765625" style="7" customWidth="1"/>
+    <col min="30" max="30" width="13.59765625" customWidth="1"/>
+    <col min="31" max="31" width="14.59765625" customWidth="1"/>
+    <col min="32" max="32" width="13.59765625" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="19.09765625" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="10.59765625" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="13.09765625" hidden="1" customWidth="1"/>
+    <col min="36" max="36" width="22.09765625" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="10.59765625" hidden="1" customWidth="1"/>
+    <col min="38" max="38" width="18.09765625" customWidth="1"/>
+    <col min="39" max="39" width="14.09765625" customWidth="1"/>
+    <col min="40" max="40" width="9.59765625" customWidth="1"/>
+    <col min="41" max="41" width="19.09765625" customWidth="1"/>
+    <col min="42" max="42" width="12.09765625" customWidth="1"/>
     <col min="44" max="45" width="0" hidden="1" customWidth="1"/>
-    <col min="46" max="47" width="13.125" hidden="1" customWidth="1"/>
+    <col min="46" max="47" width="13.09765625" hidden="1" customWidth="1"/>
     <col min="48" max="51" width="0" hidden="1" customWidth="1"/>
-    <col min="52" max="52" width="13.625" style="17" hidden="1" customWidth="1"/>
+    <col min="52" max="52" width="13.59765625" style="17" hidden="1" customWidth="1"/>
     <col min="53" max="53" width="26.5" hidden="1" customWidth="1"/>
-    <col min="54" max="54" width="20.625" hidden="1" customWidth="1"/>
+    <col min="54" max="54" width="20.59765625" hidden="1" customWidth="1"/>
     <col min="55" max="55" width="0" hidden="1" customWidth="1"/>
-    <col min="56" max="56" width="17.625" hidden="1" customWidth="1"/>
-    <col min="57" max="57" width="16.125" hidden="1" customWidth="1"/>
-    <col min="58" max="58" width="15.125" hidden="1" customWidth="1"/>
-    <col min="59" max="59" width="20.625" hidden="1" customWidth="1"/>
-    <col min="60" max="60" width="24.625" hidden="1" customWidth="1"/>
-    <col min="61" max="61" width="19.625" style="30" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="24.125" style="30" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="17.59765625" hidden="1" customWidth="1"/>
+    <col min="57" max="57" width="16.09765625" hidden="1" customWidth="1"/>
+    <col min="58" max="58" width="15.09765625" hidden="1" customWidth="1"/>
+    <col min="59" max="59" width="20.59765625" hidden="1" customWidth="1"/>
+    <col min="60" max="60" width="24.59765625" hidden="1" customWidth="1"/>
+    <col min="61" max="61" width="19.59765625" style="30" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="24.09765625" style="30" bestFit="1" customWidth="1"/>
     <col min="63" max="65" width="11" style="30"/>
-    <col min="67" max="67" width="25.125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="25.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="45">
+    <row r="1" spans="1:68" ht="43.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -43427,7 +43430,7 @@
         <v>6.7567567567567571E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:66" s="41" customFormat="1" ht="16.5">
+    <row r="39" spans="1:66" s="41" customFormat="1" ht="16.8">
       <c r="A39" s="45" t="s">
         <v>68</v>
       </c>
@@ -43632,7 +43635,7 @@
       </c>
       <c r="BN39" s="43"/>
     </row>
-    <row r="40" spans="1:66" s="41" customFormat="1" ht="16.5">
+    <row r="40" spans="1:66" s="41" customFormat="1" ht="16.8">
       <c r="A40" s="45" t="s">
         <v>68</v>
       </c>
@@ -43837,7 +43840,7 @@
       </c>
       <c r="BN40" s="43"/>
     </row>
-    <row r="41" spans="1:66" s="41" customFormat="1" ht="16.5">
+    <row r="41" spans="1:66" s="41" customFormat="1" ht="16.8">
       <c r="A41" s="45" t="s">
         <v>68</v>
       </c>
@@ -44046,7 +44049,7 @@
         <v>2.0421052631578922</v>
       </c>
     </row>
-    <row r="42" spans="1:66" s="41" customFormat="1" ht="16.5">
+    <row r="42" spans="1:66" s="41" customFormat="1" ht="16.8">
       <c r="A42" s="45" t="s">
         <v>68</v>
       </c>
@@ -46532,59 +46535,59 @@
   <dimension ref="A1:CH51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="5" max="5" width="24.625" customWidth="1"/>
-    <col min="6" max="6" width="17.625" customWidth="1"/>
-    <col min="7" max="7" width="14.125" customWidth="1"/>
+    <col min="5" max="5" width="24.59765625" customWidth="1"/>
+    <col min="6" max="6" width="17.59765625" customWidth="1"/>
+    <col min="7" max="7" width="14.09765625" customWidth="1"/>
     <col min="8" max="8" width="16.5" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="16.125" customWidth="1"/>
-    <col min="11" max="11" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.125" customWidth="1"/>
+    <col min="10" max="10" width="16.09765625" customWidth="1"/>
+    <col min="11" max="11" width="15.09765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.59765625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.09765625" customWidth="1"/>
     <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="14.625" customWidth="1"/>
-    <col min="17" max="17" width="13.125" customWidth="1"/>
+    <col min="16" max="16" width="14.59765625" customWidth="1"/>
+    <col min="17" max="17" width="13.09765625" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
-    <col min="19" max="19" width="14.125" customWidth="1"/>
+    <col min="19" max="19" width="14.09765625" customWidth="1"/>
     <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="21" width="21.125" customWidth="1"/>
+    <col min="21" max="21" width="21.09765625" customWidth="1"/>
     <col min="22" max="22" width="16" customWidth="1"/>
-    <col min="23" max="23" width="14.625" customWidth="1"/>
+    <col min="23" max="23" width="14.59765625" customWidth="1"/>
     <col min="24" max="24" width="12.5" customWidth="1"/>
     <col min="25" max="33" width="11" customWidth="1"/>
     <col min="34" max="35" width="16" customWidth="1"/>
     <col min="36" max="39" width="11" customWidth="1"/>
-    <col min="40" max="41" width="12.125" customWidth="1"/>
+    <col min="40" max="41" width="12.09765625" customWidth="1"/>
     <col min="42" max="42" width="11" customWidth="1"/>
-    <col min="43" max="43" width="27.625" customWidth="1"/>
-    <col min="44" max="44" width="41.125" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="54.625" customWidth="1"/>
+    <col min="43" max="43" width="27.59765625" customWidth="1"/>
+    <col min="44" max="44" width="41.09765625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="54.59765625" customWidth="1"/>
     <col min="46" max="46" width="21" customWidth="1"/>
-    <col min="47" max="47" width="26.625" style="7" customWidth="1"/>
-    <col min="48" max="48" width="14.125" style="7" customWidth="1"/>
-    <col min="49" max="49" width="13.125" customWidth="1"/>
-    <col min="50" max="50" width="9.625" customWidth="1"/>
+    <col min="47" max="47" width="26.59765625" style="7" customWidth="1"/>
+    <col min="48" max="48" width="14.09765625" style="7" customWidth="1"/>
+    <col min="49" max="49" width="13.09765625" customWidth="1"/>
+    <col min="50" max="50" width="9.59765625" customWidth="1"/>
     <col min="51" max="51" width="17" customWidth="1"/>
     <col min="52" max="52" width="9"/>
-    <col min="53" max="54" width="14.125" customWidth="1"/>
-    <col min="55" max="55" width="13.625" customWidth="1"/>
-    <col min="56" max="56" width="12.625" customWidth="1"/>
-    <col min="57" max="57" width="10.625" customWidth="1"/>
+    <col min="53" max="54" width="14.09765625" customWidth="1"/>
+    <col min="55" max="55" width="13.59765625" customWidth="1"/>
+    <col min="56" max="56" width="12.59765625" customWidth="1"/>
+    <col min="57" max="57" width="10.59765625" customWidth="1"/>
     <col min="58" max="58" width="13" customWidth="1"/>
-    <col min="59" max="60" width="10.625" customWidth="1"/>
-    <col min="61" max="62" width="11.125" customWidth="1"/>
+    <col min="59" max="60" width="10.59765625" customWidth="1"/>
+    <col min="61" max="62" width="11.09765625" customWidth="1"/>
     <col min="63" max="64" width="11" customWidth="1"/>
-    <col min="65" max="65" width="12.625" customWidth="1"/>
-    <col min="66" max="66" width="18.125" customWidth="1"/>
-    <col min="67" max="67" width="22.125" customWidth="1"/>
-    <col min="68" max="68" width="15.125" customWidth="1"/>
+    <col min="65" max="65" width="12.59765625" customWidth="1"/>
+    <col min="66" max="66" width="18.09765625" customWidth="1"/>
+    <col min="67" max="67" width="22.09765625" customWidth="1"/>
+    <col min="68" max="68" width="15.09765625" customWidth="1"/>
     <col min="69" max="69" width="18" customWidth="1"/>
-    <col min="70" max="70" width="17.125" customWidth="1"/>
-    <col min="71" max="71" width="21.125" customWidth="1"/>
-    <col min="72" max="72" width="10.125" customWidth="1"/>
+    <col min="70" max="70" width="17.09765625" customWidth="1"/>
+    <col min="71" max="71" width="21.09765625" customWidth="1"/>
+    <col min="72" max="72" width="10.09765625" customWidth="1"/>
     <col min="73" max="73" width="13" customWidth="1"/>
     <col min="74" max="74" width="14" customWidth="1"/>
-    <col min="75" max="75" width="13.125" customWidth="1"/>
+    <col min="75" max="75" width="13.09765625" customWidth="1"/>
     <col min="82" max="82" width="24" customWidth="1"/>
   </cols>
   <sheetData>
@@ -46695,7 +46698,7 @@
         <v>195</v>
       </c>
       <c r="AJ1" s="75" t="s">
-        <v>18</v>
+        <v>618</v>
       </c>
       <c r="AK1" s="75" t="s">
         <v>19</v>
@@ -46848,7 +46851,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="2" spans="1:86">
+    <row r="2" spans="1:86" ht="15.6">
       <c r="A2" s="11" t="s">
         <v>68</v>
       </c>
@@ -47105,7 +47108,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="3" spans="1:86">
+    <row r="3" spans="1:86" ht="15.6">
       <c r="A3" s="11" t="s">
         <v>68</v>
       </c>
@@ -47362,7 +47365,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="4" spans="1:86">
+    <row r="4" spans="1:86" ht="15.6">
       <c r="A4" s="11" t="s">
         <v>68</v>
       </c>
@@ -47619,7 +47622,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="5" spans="1:86">
+    <row r="5" spans="1:86" ht="15.6">
       <c r="A5" s="11" t="s">
         <v>68</v>
       </c>
@@ -47876,7 +47879,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:86">
+    <row r="6" spans="1:86" ht="15.6">
       <c r="A6" s="11" t="s">
         <v>68</v>
       </c>
@@ -48133,7 +48136,7 @@
         <v>4.0133242364650637E-5</v>
       </c>
     </row>
-    <row r="7" spans="1:86">
+    <row r="7" spans="1:86" ht="15.6">
       <c r="A7" s="11" t="s">
         <v>68</v>
       </c>
@@ -48390,7 +48393,7 @@
         <v>4.4202802457675817E-5</v>
       </c>
     </row>
-    <row r="8" spans="1:86" s="105" customFormat="1">
+    <row r="8" spans="1:86" s="105" customFormat="1" ht="15.6">
       <c r="A8" s="11" t="s">
         <v>68</v>
       </c>
@@ -48650,7 +48653,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="9" spans="1:86" s="105" customFormat="1">
+    <row r="9" spans="1:86" s="105" customFormat="1" ht="15.6">
       <c r="A9" s="11" t="s">
         <v>68</v>
       </c>
@@ -48910,7 +48913,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="10" spans="1:86" s="105" customFormat="1">
+    <row r="10" spans="1:86" s="105" customFormat="1" ht="15.6">
       <c r="A10" s="11" t="s">
         <v>68</v>
       </c>
@@ -49170,7 +49173,7 @@
         <v>4.0133242364650637E-5</v>
       </c>
     </row>
-    <row r="11" spans="1:86" s="105" customFormat="1">
+    <row r="11" spans="1:86" s="105" customFormat="1" ht="15.6">
       <c r="A11" s="11" t="s">
         <v>68</v>
       </c>
@@ -49430,7 +49433,7 @@
         <v>4.8550759819391176E-5</v>
       </c>
     </row>
-    <row r="12" spans="1:86">
+    <row r="12" spans="1:86" ht="15.6">
       <c r="A12" s="11" t="s">
         <v>68</v>
       </c>
@@ -49687,7 +49690,7 @@
         <v>4.8550759819391176E-5</v>
       </c>
     </row>
-    <row r="13" spans="1:86" s="107" customFormat="1">
+    <row r="13" spans="1:86" s="107" customFormat="1" ht="15.6">
       <c r="A13" s="11" t="s">
         <v>68</v>
       </c>
@@ -49947,7 +49950,7 @@
         <v>4.8550759819391176E-5</v>
       </c>
     </row>
-    <row r="14" spans="1:86">
+    <row r="14" spans="1:86" ht="15.6">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -50202,7 +50205,7 @@
         <v>5.6882821387940839E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:86">
+    <row r="15" spans="1:86" ht="15.6">
       <c r="A15" t="s">
         <v>68</v>
       </c>
@@ -50457,7 +50460,7 @@
         <v>5.6882821387940839E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:86">
+    <row r="16" spans="1:86" ht="15.6">
       <c r="A16" t="s">
         <v>68</v>
       </c>
@@ -50712,7 +50715,7 @@
         <v>1.1061946902654867E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:86">
+    <row r="17" spans="1:86" ht="15.6">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -50967,7 +50970,7 @@
         <v>1.1061946902654867E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:86" s="107" customFormat="1">
+    <row r="18" spans="1:86" s="107" customFormat="1" ht="15.6">
       <c r="A18" s="11" t="s">
         <v>68</v>
       </c>
@@ -51489,7 +51492,7 @@
         <v>2.6660978991148553E-5</v>
       </c>
     </row>
-    <row r="20" spans="1:86" s="107" customFormat="1">
+    <row r="20" spans="1:86" s="107" customFormat="1" ht="15.6">
       <c r="A20" s="11" t="s">
         <v>68</v>
       </c>
@@ -51750,7 +51753,7 @@
         <v>1.4545242978283952E-5</v>
       </c>
     </row>
-    <row r="21" spans="1:86">
+    <row r="21" spans="1:86" ht="15.6">
       <c r="A21" s="11" t="s">
         <v>68</v>
       </c>
@@ -52008,7 +52011,7 @@
         <v>3.0061626333984669E-5</v>
       </c>
     </row>
-    <row r="22" spans="1:86">
+    <row r="22" spans="1:86" ht="15.6">
       <c r="A22" s="11" t="s">
         <v>68</v>
       </c>
@@ -52267,7 +52270,7 @@
         <v>1.953125E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:86">
+    <row r="23" spans="1:86" ht="15.6">
       <c r="A23" s="11" t="s">
         <v>68</v>
       </c>
@@ -52526,7 +52529,7 @@
         <v>1.953125E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:86">
+    <row r="24" spans="1:86" ht="15.6">
       <c r="A24" s="11" t="s">
         <v>68</v>
       </c>
@@ -53040,7 +53043,7 @@
         <v>4.1152263374485596E-4</v>
       </c>
     </row>
-    <row r="26" spans="1:86">
+    <row r="26" spans="1:86" ht="15.6">
       <c r="A26" s="11" t="s">
         <v>68</v>
       </c>
@@ -53297,7 +53300,7 @@
         <v>4.0950040950040953E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:86">
+    <row r="27" spans="1:86" ht="15.6">
       <c r="A27" s="11" t="s">
         <v>68</v>
       </c>
@@ -53554,7 +53557,7 @@
         <v>4.1152263374485596E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:86">
+    <row r="28" spans="1:86" ht="15.6">
       <c r="A28" s="94" t="s">
         <v>68</v>
       </c>
@@ -53814,7 +53817,7 @@
         <v>3.2573289902280132E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:86">
+    <row r="29" spans="1:86" ht="15.6">
       <c r="A29" s="94" t="s">
         <v>68</v>
       </c>
@@ -54074,7 +54077,7 @@
         <v>3.2573289902280132E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:86">
+    <row r="30" spans="1:86" ht="15.6">
       <c r="A30" s="94" t="s">
         <v>68</v>
       </c>
@@ -54334,7 +54337,7 @@
         <v>3.2573289902280132E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:86">
+    <row r="31" spans="1:86" ht="15.6">
       <c r="A31" s="94" t="s">
         <v>68</v>
       </c>
@@ -54593,7 +54596,7 @@
         <v>7.1839080459770114E-5</v>
       </c>
     </row>
-    <row r="32" spans="1:86">
+    <row r="32" spans="1:86" ht="15.6">
       <c r="A32" t="s">
         <v>68</v>
       </c>
@@ -54848,7 +54851,7 @@
         <v>1.0448480111840532E-6</v>
       </c>
     </row>
-    <row r="33" spans="1:86">
+    <row r="33" spans="1:86" ht="15.6">
       <c r="A33" t="s">
         <v>68</v>
       </c>
@@ -55103,7 +55106,7 @@
         <v>1.0448480111840532E-6</v>
       </c>
     </row>
-    <row r="34" spans="1:86">
+    <row r="34" spans="1:86" ht="15.6">
       <c r="A34" t="s">
         <v>68</v>
       </c>
@@ -55358,7 +55361,7 @@
         <v>1.0448480111840532E-6</v>
       </c>
     </row>
-    <row r="35" spans="1:86">
+    <row r="35" spans="1:86" ht="15.6">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -56129,43 +56132,43 @@
         <v>2.5188916876574307E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:86">
+    <row r="38" spans="1:86" ht="15.6">
       <c r="M38" s="18"/>
     </row>
-    <row r="39" spans="1:86">
+    <row r="39" spans="1:86" ht="15.6">
       <c r="M39" s="18"/>
     </row>
-    <row r="40" spans="1:86">
+    <row r="40" spans="1:86" ht="15.6">
       <c r="M40" s="18"/>
     </row>
-    <row r="41" spans="1:86">
+    <row r="41" spans="1:86" ht="15.6">
       <c r="M41" s="18"/>
     </row>
-    <row r="42" spans="1:86">
+    <row r="42" spans="1:86" ht="15.6">
       <c r="M42" s="18"/>
     </row>
-    <row r="43" spans="1:86">
+    <row r="43" spans="1:86" ht="15.6">
       <c r="M43" s="18"/>
     </row>
-    <row r="44" spans="1:86">
+    <row r="44" spans="1:86" ht="15.6">
       <c r="M44" s="18"/>
     </row>
-    <row r="45" spans="1:86">
+    <row r="45" spans="1:86" ht="15.6">
       <c r="M45" s="18"/>
     </row>
-    <row r="46" spans="1:86">
+    <row r="46" spans="1:86" ht="15.6">
       <c r="M46" s="18"/>
     </row>
     <row r="47" spans="1:86" ht="15.75" customHeight="1">
       <c r="M47" s="18"/>
       <c r="BX47" s="30"/>
     </row>
-    <row r="48" spans="1:86">
+    <row r="48" spans="1:86" ht="15.6">
       <c r="M48" s="18"/>
       <c r="BA48" s="117"/>
       <c r="BB48" s="117"/>
     </row>
-    <row r="49" spans="13:54">
+    <row r="49" spans="13:54" ht="15.6">
       <c r="M49" s="18"/>
       <c r="BA49" s="117"/>
       <c r="BB49" s="117"/>
@@ -56173,7 +56176,7 @@
     <row r="50" spans="13:54" ht="15.75" customHeight="1">
       <c r="M50" s="18"/>
     </row>
-    <row r="51" spans="13:54">
+    <row r="51" spans="13:54" ht="15.6">
       <c r="M51" s="18"/>
       <c r="BA51" s="118"/>
       <c r="BB51" s="118"/>
@@ -56201,7 +56204,7 @@
       <formula2>1</formula2>
     </dataValidation>
     <dataValidation errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN38:BN1048576 BN1:BN35"/>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH1:AP1048576 U1:U1048576 S1:S1048576">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1:S1048576 U1:U1048576 AH1:AI1048576 AK1:AP1048576 AJ2:AJ1048576">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -56347,70 +56350,70 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BJ18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="28.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.8984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.09765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.8984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.8984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.59765625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="30" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="28.125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.59765625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.09765625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="28.09765625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.09765625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.59765625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="15" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.3984375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.8984375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.8984375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.59765625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="11" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="22.625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="23.8984375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18.8984375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="22.59765625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.8984375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.09765625" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="17" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="18.8984375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="36.3984375" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="29" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="21.875" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="17.8984375" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="21.8984375" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="20.09765625" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="15" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="21.8984375" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="29.625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="23.8984375" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="17.09765625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="29.59765625" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="33" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="35.5" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.875" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="24.375" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="25.875" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.8984375" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="24.3984375" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="17.8984375" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="25.8984375" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="35" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="26.375" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="26.3984375" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.3984375" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="15.59765625" bestFit="1" customWidth="1"/>
     <col min="63" max="64" width="18.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -59252,15 +59255,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S99"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
     <col min="3" max="3" width="15.5" customWidth="1"/>
-    <col min="5" max="5" width="19.625" customWidth="1"/>
+    <col min="5" max="5" width="19.59765625" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="18.125" style="26" customWidth="1"/>
+    <col min="7" max="7" width="18.09765625" style="26" customWidth="1"/>
     <col min="8" max="8" width="20.5" customWidth="1"/>
-    <col min="9" max="9" width="14.125" customWidth="1"/>
-    <col min="10" max="10" width="15.125" customWidth="1"/>
+    <col min="9" max="9" width="14.09765625" customWidth="1"/>
+    <col min="10" max="10" width="15.09765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
@@ -59319,7 +59322,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="31.5">
+    <row r="2" spans="1:19" ht="31.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -59375,7 +59378,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="31.5">
+    <row r="3" spans="1:19" ht="31.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -59431,7 +59434,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="47.25">
+    <row r="4" spans="1:19" ht="46.8">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -59481,7 +59484,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="47.25">
+    <row r="5" spans="1:19" ht="46.8">
       <c r="D5" t="s">
         <v>293</v>
       </c>

--- a/appliances_usage.xlsx
+++ b/appliances_usage.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-4488" yWindow="-21108" windowWidth="38400" windowHeight="19392" firstSheet="1" activeTab="1"/>
+    <workbookView xWindow="-4485" yWindow="-21105" windowWidth="38400" windowHeight="19395" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Usage" sheetId="5" state="hidden" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2735,7 +2735,7 @@
     <xf numFmtId="9" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2887,6 +2887,7 @@
     </xf>
     <xf numFmtId="0" fontId="33" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Link" xfId="2" builtinId="8"/>
@@ -34730,7 +34731,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:BJ18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="92">
     <pivotField showAll="0"/>
@@ -35584,55 +35585,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BP53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="4" max="4" width="20.59765625" customWidth="1"/>
-    <col min="5" max="5" width="14.09765625" customWidth="1"/>
-    <col min="7" max="7" width="16.09765625" customWidth="1"/>
-    <col min="8" max="8" width="16.59765625" customWidth="1"/>
-    <col min="10" max="10" width="18.09765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.625" customWidth="1"/>
+    <col min="5" max="5" width="14.125" customWidth="1"/>
+    <col min="7" max="7" width="16.125" customWidth="1"/>
+    <col min="8" max="8" width="16.625" customWidth="1"/>
+    <col min="10" max="10" width="18.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" hidden="1" customWidth="1"/>
     <col min="12" max="17" width="0" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="16" hidden="1" customWidth="1"/>
     <col min="19" max="22" width="0" hidden="1" customWidth="1"/>
-    <col min="23" max="24" width="12.09765625" hidden="1" customWidth="1"/>
+    <col min="23" max="24" width="12.125" hidden="1" customWidth="1"/>
     <col min="25" max="25" width="0" hidden="1" customWidth="1"/>
     <col min="26" max="26" width="0" style="12" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="18.59765625" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.59765625" style="7" customWidth="1"/>
-    <col min="30" max="30" width="13.59765625" customWidth="1"/>
-    <col min="31" max="31" width="14.59765625" customWidth="1"/>
-    <col min="32" max="32" width="13.59765625" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="19.09765625" hidden="1" customWidth="1"/>
-    <col min="34" max="34" width="10.59765625" hidden="1" customWidth="1"/>
-    <col min="35" max="35" width="13.09765625" hidden="1" customWidth="1"/>
-    <col min="36" max="36" width="22.09765625" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="10.59765625" hidden="1" customWidth="1"/>
-    <col min="38" max="38" width="18.09765625" customWidth="1"/>
-    <col min="39" max="39" width="14.09765625" customWidth="1"/>
-    <col min="40" max="40" width="9.59765625" customWidth="1"/>
-    <col min="41" max="41" width="19.09765625" customWidth="1"/>
-    <col min="42" max="42" width="12.09765625" customWidth="1"/>
+    <col min="27" max="27" width="18.625" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="14.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.625" style="7" customWidth="1"/>
+    <col min="30" max="30" width="13.625" customWidth="1"/>
+    <col min="31" max="31" width="14.625" customWidth="1"/>
+    <col min="32" max="32" width="13.625" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="19.125" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="10.625" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="13.125" hidden="1" customWidth="1"/>
+    <col min="36" max="36" width="22.125" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="10.625" hidden="1" customWidth="1"/>
+    <col min="38" max="38" width="18.125" customWidth="1"/>
+    <col min="39" max="39" width="14.125" customWidth="1"/>
+    <col min="40" max="40" width="9.625" customWidth="1"/>
+    <col min="41" max="41" width="19.125" customWidth="1"/>
+    <col min="42" max="42" width="12.125" customWidth="1"/>
     <col min="44" max="45" width="0" hidden="1" customWidth="1"/>
-    <col min="46" max="47" width="13.09765625" hidden="1" customWidth="1"/>
+    <col min="46" max="47" width="13.125" hidden="1" customWidth="1"/>
     <col min="48" max="51" width="0" hidden="1" customWidth="1"/>
-    <col min="52" max="52" width="13.59765625" style="17" hidden="1" customWidth="1"/>
+    <col min="52" max="52" width="13.625" style="17" hidden="1" customWidth="1"/>
     <col min="53" max="53" width="26.5" hidden="1" customWidth="1"/>
-    <col min="54" max="54" width="20.59765625" hidden="1" customWidth="1"/>
+    <col min="54" max="54" width="20.625" hidden="1" customWidth="1"/>
     <col min="55" max="55" width="0" hidden="1" customWidth="1"/>
-    <col min="56" max="56" width="17.59765625" hidden="1" customWidth="1"/>
-    <col min="57" max="57" width="16.09765625" hidden="1" customWidth="1"/>
-    <col min="58" max="58" width="15.09765625" hidden="1" customWidth="1"/>
-    <col min="59" max="59" width="20.59765625" hidden="1" customWidth="1"/>
-    <col min="60" max="60" width="24.59765625" hidden="1" customWidth="1"/>
-    <col min="61" max="61" width="19.59765625" style="30" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="24.09765625" style="30" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="17.625" hidden="1" customWidth="1"/>
+    <col min="57" max="57" width="16.125" hidden="1" customWidth="1"/>
+    <col min="58" max="58" width="15.125" hidden="1" customWidth="1"/>
+    <col min="59" max="59" width="20.625" hidden="1" customWidth="1"/>
+    <col min="60" max="60" width="24.625" hidden="1" customWidth="1"/>
+    <col min="61" max="61" width="19.625" style="30" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="24.125" style="30" bestFit="1" customWidth="1"/>
     <col min="63" max="65" width="11" style="30"/>
-    <col min="67" max="67" width="25.09765625" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="25.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="43.2">
+    <row r="1" spans="1:68" ht="45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -43430,7 +43431,7 @@
         <v>6.7567567567567571E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:66" s="41" customFormat="1" ht="16.8">
+    <row r="39" spans="1:66" s="41" customFormat="1" ht="16.5">
       <c r="A39" s="45" t="s">
         <v>68</v>
       </c>
@@ -43635,7 +43636,7 @@
       </c>
       <c r="BN39" s="43"/>
     </row>
-    <row r="40" spans="1:66" s="41" customFormat="1" ht="16.8">
+    <row r="40" spans="1:66" s="41" customFormat="1" ht="16.5">
       <c r="A40" s="45" t="s">
         <v>68</v>
       </c>
@@ -43840,7 +43841,7 @@
       </c>
       <c r="BN40" s="43"/>
     </row>
-    <row r="41" spans="1:66" s="41" customFormat="1" ht="16.8">
+    <row r="41" spans="1:66" s="41" customFormat="1" ht="16.5">
       <c r="A41" s="45" t="s">
         <v>68</v>
       </c>
@@ -44049,7 +44050,7 @@
         <v>2.0421052631578922</v>
       </c>
     </row>
-    <row r="42" spans="1:66" s="41" customFormat="1" ht="16.8">
+    <row r="42" spans="1:66" s="41" customFormat="1" ht="16.5">
       <c r="A42" s="45" t="s">
         <v>68</v>
       </c>
@@ -46535,59 +46536,59 @@
   <dimension ref="A1:CH51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="5" max="5" width="24.59765625" customWidth="1"/>
-    <col min="6" max="6" width="17.59765625" customWidth="1"/>
-    <col min="7" max="7" width="14.09765625" customWidth="1"/>
+    <col min="5" max="5" width="24.625" customWidth="1"/>
+    <col min="6" max="6" width="17.625" customWidth="1"/>
+    <col min="7" max="7" width="14.125" customWidth="1"/>
     <col min="8" max="8" width="16.5" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="16.09765625" customWidth="1"/>
-    <col min="11" max="11" width="15.09765625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.59765625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.09765625" customWidth="1"/>
+    <col min="10" max="10" width="16.125" customWidth="1"/>
+    <col min="11" max="11" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.125" customWidth="1"/>
     <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="14.59765625" customWidth="1"/>
-    <col min="17" max="17" width="13.09765625" customWidth="1"/>
+    <col min="16" max="16" width="14.625" customWidth="1"/>
+    <col min="17" max="17" width="13.125" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
-    <col min="19" max="19" width="14.09765625" customWidth="1"/>
+    <col min="19" max="19" width="14.125" customWidth="1"/>
     <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="21" width="21.09765625" customWidth="1"/>
+    <col min="21" max="21" width="21.125" customWidth="1"/>
     <col min="22" max="22" width="16" customWidth="1"/>
-    <col min="23" max="23" width="14.59765625" customWidth="1"/>
+    <col min="23" max="23" width="14.625" customWidth="1"/>
     <col min="24" max="24" width="12.5" customWidth="1"/>
     <col min="25" max="33" width="11" customWidth="1"/>
     <col min="34" max="35" width="16" customWidth="1"/>
     <col min="36" max="39" width="11" customWidth="1"/>
-    <col min="40" max="41" width="12.09765625" customWidth="1"/>
+    <col min="40" max="41" width="12.125" customWidth="1"/>
     <col min="42" max="42" width="11" customWidth="1"/>
-    <col min="43" max="43" width="27.59765625" customWidth="1"/>
-    <col min="44" max="44" width="41.09765625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="54.59765625" customWidth="1"/>
+    <col min="43" max="43" width="27.625" customWidth="1"/>
+    <col min="44" max="44" width="41.125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="54.625" customWidth="1"/>
     <col min="46" max="46" width="21" customWidth="1"/>
-    <col min="47" max="47" width="26.59765625" style="7" customWidth="1"/>
-    <col min="48" max="48" width="14.09765625" style="7" customWidth="1"/>
-    <col min="49" max="49" width="13.09765625" customWidth="1"/>
-    <col min="50" max="50" width="9.59765625" customWidth="1"/>
+    <col min="47" max="47" width="26.625" style="7" customWidth="1"/>
+    <col min="48" max="48" width="14.125" style="7" customWidth="1"/>
+    <col min="49" max="49" width="13.125" customWidth="1"/>
+    <col min="50" max="50" width="9.625" customWidth="1"/>
     <col min="51" max="51" width="17" customWidth="1"/>
     <col min="52" max="52" width="9"/>
-    <col min="53" max="54" width="14.09765625" customWidth="1"/>
-    <col min="55" max="55" width="13.59765625" customWidth="1"/>
-    <col min="56" max="56" width="12.59765625" customWidth="1"/>
-    <col min="57" max="57" width="10.59765625" customWidth="1"/>
+    <col min="53" max="54" width="14.125" customWidth="1"/>
+    <col min="55" max="55" width="13.625" customWidth="1"/>
+    <col min="56" max="56" width="12.625" customWidth="1"/>
+    <col min="57" max="57" width="10.625" customWidth="1"/>
     <col min="58" max="58" width="13" customWidth="1"/>
-    <col min="59" max="60" width="10.59765625" customWidth="1"/>
-    <col min="61" max="62" width="11.09765625" customWidth="1"/>
+    <col min="59" max="60" width="10.625" customWidth="1"/>
+    <col min="61" max="62" width="11.125" customWidth="1"/>
     <col min="63" max="64" width="11" customWidth="1"/>
-    <col min="65" max="65" width="12.59765625" customWidth="1"/>
-    <col min="66" max="66" width="18.09765625" customWidth="1"/>
-    <col min="67" max="67" width="22.09765625" customWidth="1"/>
-    <col min="68" max="68" width="15.09765625" customWidth="1"/>
+    <col min="65" max="65" width="12.625" customWidth="1"/>
+    <col min="66" max="66" width="18.125" customWidth="1"/>
+    <col min="67" max="67" width="22.125" customWidth="1"/>
+    <col min="68" max="68" width="15.125" customWidth="1"/>
     <col min="69" max="69" width="18" customWidth="1"/>
-    <col min="70" max="70" width="17.09765625" customWidth="1"/>
-    <col min="71" max="71" width="21.09765625" customWidth="1"/>
-    <col min="72" max="72" width="10.09765625" customWidth="1"/>
+    <col min="70" max="70" width="17.125" customWidth="1"/>
+    <col min="71" max="71" width="21.125" customWidth="1"/>
+    <col min="72" max="72" width="10.125" customWidth="1"/>
     <col min="73" max="73" width="13" customWidth="1"/>
     <col min="74" max="74" width="14" customWidth="1"/>
-    <col min="75" max="75" width="13.09765625" customWidth="1"/>
+    <col min="75" max="75" width="13.125" customWidth="1"/>
     <col min="82" max="82" width="24" customWidth="1"/>
   </cols>
   <sheetData>
@@ -46851,7 +46852,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="2" spans="1:86" ht="15.6">
+    <row r="2" spans="1:86">
       <c r="A2" s="11" t="s">
         <v>68</v>
       </c>
@@ -47108,7 +47109,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="3" spans="1:86" ht="15.6">
+    <row r="3" spans="1:86">
       <c r="A3" s="11" t="s">
         <v>68</v>
       </c>
@@ -47365,7 +47366,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="4" spans="1:86" ht="15.6">
+    <row r="4" spans="1:86">
       <c r="A4" s="11" t="s">
         <v>68</v>
       </c>
@@ -47622,7 +47623,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="5" spans="1:86" ht="15.6">
+    <row r="5" spans="1:86">
       <c r="A5" s="11" t="s">
         <v>68</v>
       </c>
@@ -47879,7 +47880,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:86" ht="15.6">
+    <row r="6" spans="1:86">
       <c r="A6" s="11" t="s">
         <v>68</v>
       </c>
@@ -48136,7 +48137,7 @@
         <v>4.0133242364650637E-5</v>
       </c>
     </row>
-    <row r="7" spans="1:86" ht="15.6">
+    <row r="7" spans="1:86">
       <c r="A7" s="11" t="s">
         <v>68</v>
       </c>
@@ -48393,7 +48394,7 @@
         <v>4.4202802457675817E-5</v>
       </c>
     </row>
-    <row r="8" spans="1:86" s="105" customFormat="1" ht="15.6">
+    <row r="8" spans="1:86" s="105" customFormat="1">
       <c r="A8" s="11" t="s">
         <v>68</v>
       </c>
@@ -48653,7 +48654,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="9" spans="1:86" s="105" customFormat="1" ht="15.6">
+    <row r="9" spans="1:86" s="105" customFormat="1">
       <c r="A9" s="11" t="s">
         <v>68</v>
       </c>
@@ -48913,7 +48914,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="10" spans="1:86" s="105" customFormat="1" ht="15.6">
+    <row r="10" spans="1:86" s="105" customFormat="1">
       <c r="A10" s="11" t="s">
         <v>68</v>
       </c>
@@ -49173,7 +49174,7 @@
         <v>4.0133242364650637E-5</v>
       </c>
     </row>
-    <row r="11" spans="1:86" s="105" customFormat="1" ht="15.6">
+    <row r="11" spans="1:86" s="105" customFormat="1">
       <c r="A11" s="11" t="s">
         <v>68</v>
       </c>
@@ -49433,7 +49434,7 @@
         <v>4.8550759819391176E-5</v>
       </c>
     </row>
-    <row r="12" spans="1:86" ht="15.6">
+    <row r="12" spans="1:86">
       <c r="A12" s="11" t="s">
         <v>68</v>
       </c>
@@ -49690,7 +49691,7 @@
         <v>4.8550759819391176E-5</v>
       </c>
     </row>
-    <row r="13" spans="1:86" s="107" customFormat="1" ht="15.6">
+    <row r="13" spans="1:86" s="107" customFormat="1">
       <c r="A13" s="11" t="s">
         <v>68</v>
       </c>
@@ -49950,7 +49951,7 @@
         <v>4.8550759819391176E-5</v>
       </c>
     </row>
-    <row r="14" spans="1:86" ht="15.6">
+    <row r="14" spans="1:86">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -50205,7 +50206,7 @@
         <v>5.6882821387940839E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:86" ht="15.6">
+    <row r="15" spans="1:86">
       <c r="A15" t="s">
         <v>68</v>
       </c>
@@ -50460,7 +50461,7 @@
         <v>5.6882821387940839E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:86" ht="15.6">
+    <row r="16" spans="1:86">
       <c r="A16" t="s">
         <v>68</v>
       </c>
@@ -50715,7 +50716,7 @@
         <v>1.1061946902654867E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:86" ht="15.6">
+    <row r="17" spans="1:86">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -50970,7 +50971,7 @@
         <v>1.1061946902654867E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:86" s="107" customFormat="1" ht="15.6">
+    <row r="18" spans="1:86" s="107" customFormat="1">
       <c r="A18" s="11" t="s">
         <v>68</v>
       </c>
@@ -51492,7 +51493,7 @@
         <v>2.6660978991148553E-5</v>
       </c>
     </row>
-    <row r="20" spans="1:86" s="107" customFormat="1" ht="15.6">
+    <row r="20" spans="1:86" s="107" customFormat="1">
       <c r="A20" s="11" t="s">
         <v>68</v>
       </c>
@@ -51753,7 +51754,7 @@
         <v>1.4545242978283952E-5</v>
       </c>
     </row>
-    <row r="21" spans="1:86" ht="15.6">
+    <row r="21" spans="1:86">
       <c r="A21" s="11" t="s">
         <v>68</v>
       </c>
@@ -52011,7 +52012,7 @@
         <v>3.0061626333984669E-5</v>
       </c>
     </row>
-    <row r="22" spans="1:86" ht="15.6">
+    <row r="22" spans="1:86">
       <c r="A22" s="11" t="s">
         <v>68</v>
       </c>
@@ -52104,7 +52105,7 @@
         <v>0</v>
       </c>
       <c r="AF22" s="101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG22" s="101" t="s">
         <v>267</v>
@@ -52270,7 +52271,7 @@
         <v>1.953125E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:86" ht="15.6">
+    <row r="23" spans="1:86">
       <c r="A23" s="11" t="s">
         <v>68</v>
       </c>
@@ -52363,7 +52364,7 @@
         <v>0</v>
       </c>
       <c r="AF23" s="101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG23" s="101" t="s">
         <v>267</v>
@@ -52529,7 +52530,7 @@
         <v>1.953125E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:86" ht="15.6">
+    <row r="24" spans="1:86">
       <c r="A24" s="11" t="s">
         <v>68</v>
       </c>
@@ -52549,7 +52550,7 @@
       <c r="G24" t="s">
         <v>271</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" s="123" t="s">
         <v>272</v>
       </c>
       <c r="I24" s="101">
@@ -52616,13 +52617,13 @@
         <v>0</v>
       </c>
       <c r="AD24" s="101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE24" s="101">
         <v>0</v>
       </c>
       <c r="AF24" s="101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG24" s="101" t="s">
         <v>274</v>
@@ -52873,13 +52874,13 @@
         <v>0</v>
       </c>
       <c r="AD25" s="101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE25" s="101">
         <v>0</v>
       </c>
       <c r="AF25" s="101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG25" s="101" t="s">
         <v>277</v>
@@ -53043,7 +53044,7 @@
         <v>4.1152263374485596E-4</v>
       </c>
     </row>
-    <row r="26" spans="1:86" ht="15.6">
+    <row r="26" spans="1:86">
       <c r="A26" s="11" t="s">
         <v>68</v>
       </c>
@@ -53130,13 +53131,13 @@
         <v>0</v>
       </c>
       <c r="AD26" s="101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE26" s="101">
         <v>0</v>
       </c>
       <c r="AF26" s="101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG26" s="101" t="s">
         <v>277</v>
@@ -53300,7 +53301,7 @@
         <v>4.0950040950040953E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:86" ht="15.6">
+    <row r="27" spans="1:86">
       <c r="A27" s="11" t="s">
         <v>68</v>
       </c>
@@ -53387,13 +53388,13 @@
         <v>0</v>
       </c>
       <c r="AD27" s="101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE27" s="101">
         <v>0</v>
       </c>
       <c r="AF27" s="101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG27" s="101" t="s">
         <v>277</v>
@@ -53557,7 +53558,7 @@
         <v>4.1152263374485596E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:86" ht="15.6">
+    <row r="28" spans="1:86">
       <c r="A28" s="94" t="s">
         <v>68</v>
       </c>
@@ -53817,7 +53818,7 @@
         <v>3.2573289902280132E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:86" ht="15.6">
+    <row r="29" spans="1:86">
       <c r="A29" s="94" t="s">
         <v>68</v>
       </c>
@@ -54077,7 +54078,7 @@
         <v>3.2573289902280132E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:86" ht="15.6">
+    <row r="30" spans="1:86">
       <c r="A30" s="94" t="s">
         <v>68</v>
       </c>
@@ -54337,7 +54338,7 @@
         <v>3.2573289902280132E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:86" ht="15.6">
+    <row r="31" spans="1:86">
       <c r="A31" s="94" t="s">
         <v>68</v>
       </c>
@@ -54596,7 +54597,7 @@
         <v>7.1839080459770114E-5</v>
       </c>
     </row>
-    <row r="32" spans="1:86" ht="15.6">
+    <row r="32" spans="1:86">
       <c r="A32" t="s">
         <v>68</v>
       </c>
@@ -54851,7 +54852,7 @@
         <v>1.0448480111840532E-6</v>
       </c>
     </row>
-    <row r="33" spans="1:86" ht="15.6">
+    <row r="33" spans="1:86">
       <c r="A33" t="s">
         <v>68</v>
       </c>
@@ -55106,7 +55107,7 @@
         <v>1.0448480111840532E-6</v>
       </c>
     </row>
-    <row r="34" spans="1:86" ht="15.6">
+    <row r="34" spans="1:86">
       <c r="A34" t="s">
         <v>68</v>
       </c>
@@ -55361,7 +55362,7 @@
         <v>1.0448480111840532E-6</v>
       </c>
     </row>
-    <row r="35" spans="1:86" ht="15.6">
+    <row r="35" spans="1:86">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -56132,43 +56133,43 @@
         <v>2.5188916876574307E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:86" ht="15.6">
+    <row r="38" spans="1:86">
       <c r="M38" s="18"/>
     </row>
-    <row r="39" spans="1:86" ht="15.6">
+    <row r="39" spans="1:86">
       <c r="M39" s="18"/>
     </row>
-    <row r="40" spans="1:86" ht="15.6">
+    <row r="40" spans="1:86">
       <c r="M40" s="18"/>
     </row>
-    <row r="41" spans="1:86" ht="15.6">
+    <row r="41" spans="1:86">
       <c r="M41" s="18"/>
     </row>
-    <row r="42" spans="1:86" ht="15.6">
+    <row r="42" spans="1:86">
       <c r="M42" s="18"/>
     </row>
-    <row r="43" spans="1:86" ht="15.6">
+    <row r="43" spans="1:86">
       <c r="M43" s="18"/>
     </row>
-    <row r="44" spans="1:86" ht="15.6">
+    <row r="44" spans="1:86">
       <c r="M44" s="18"/>
     </row>
-    <row r="45" spans="1:86" ht="15.6">
+    <row r="45" spans="1:86">
       <c r="M45" s="18"/>
     </row>
-    <row r="46" spans="1:86" ht="15.6">
+    <row r="46" spans="1:86">
       <c r="M46" s="18"/>
     </row>
     <row r="47" spans="1:86" ht="15.75" customHeight="1">
       <c r="M47" s="18"/>
       <c r="BX47" s="30"/>
     </row>
-    <row r="48" spans="1:86" ht="15.6">
+    <row r="48" spans="1:86">
       <c r="M48" s="18"/>
       <c r="BA48" s="117"/>
       <c r="BB48" s="117"/>
     </row>
-    <row r="49" spans="13:54" ht="15.6">
+    <row r="49" spans="13:54">
       <c r="M49" s="18"/>
       <c r="BA49" s="117"/>
       <c r="BB49" s="117"/>
@@ -56176,7 +56177,7 @@
     <row r="50" spans="13:54" ht="15.75" customHeight="1">
       <c r="M50" s="18"/>
     </row>
-    <row r="51" spans="13:54" ht="15.6">
+    <row r="51" spans="13:54">
       <c r="M51" s="18"/>
       <c r="BA51" s="118"/>
       <c r="BB51" s="118"/>
@@ -56350,70 +56351,70 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BJ18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="28.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.09765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.59765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.8984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.8984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="30" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.59765625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.3984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.09765625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="28.09765625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.09765625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.59765625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="28.125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="15" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.3984375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.8984375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.8984375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="11" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="23.8984375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.8984375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="22.59765625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.8984375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.09765625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="22.625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.125" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="17" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="18.8984375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.09765625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="36.3984375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="36.375" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="29" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="17.8984375" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="21.8984375" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="20.09765625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="20.125" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="15" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="13.3984375" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="21.8984375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="21.875" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="23.8984375" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="17.09765625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="29.59765625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="29.625" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="33" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="35.5" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.8984375" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="24.3984375" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="17.8984375" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="25.8984375" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="24.375" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="25.875" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="35" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="26.3984375" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="26.375" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.375" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="15.625" bestFit="1" customWidth="1"/>
     <col min="63" max="64" width="18.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -59255,15 +59256,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S99"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="3" max="3" width="15.5" customWidth="1"/>
-    <col min="5" max="5" width="19.59765625" customWidth="1"/>
+    <col min="5" max="5" width="19.625" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="18.09765625" style="26" customWidth="1"/>
+    <col min="7" max="7" width="18.125" style="26" customWidth="1"/>
     <col min="8" max="8" width="20.5" customWidth="1"/>
-    <col min="9" max="9" width="14.09765625" customWidth="1"/>
-    <col min="10" max="10" width="15.09765625" customWidth="1"/>
+    <col min="9" max="9" width="14.125" customWidth="1"/>
+    <col min="10" max="10" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
@@ -59322,7 +59323,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="31.2">
+    <row r="2" spans="1:19" ht="31.5">
       <c r="A2">
         <v>0</v>
       </c>
@@ -59378,7 +59379,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="31.2">
+    <row r="3" spans="1:19" ht="31.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -59434,7 +59435,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="46.8">
+    <row r="4" spans="1:19" ht="47.25">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -59484,7 +59485,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="46.8">
+    <row r="5" spans="1:19" ht="47.25">
       <c r="D5" t="s">
         <v>293</v>
       </c>

--- a/appliances_usage.xlsx
+++ b/appliances_usage.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dand\Documents\GitHub\appliances_interventions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dianadanilenko/Desktop/appliances_interventions/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480E55D7-B38C-534C-BF74-F350DFDAE5D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4485" yWindow="-21105" windowWidth="38400" windowHeight="19395" firstSheet="1" activeTab="1"/>
+    <workbookView xWindow="-5280" yWindow="-21100" windowWidth="38400" windowHeight="19400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Usage" sheetId="5" state="hidden" r:id="rId1"/>
@@ -21,9 +22,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Appliances!$AR$1:$AR$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Usage!$A$1:$BN$53</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -45,62 +46,35 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={73C2226C-6106-4DC2-88CF-9C0A06F48311}</author>
     <author>tc={CEE78422-255C-40DC-AFED-5AA185CC03E1}</author>
     <author>tc={C7CEED71-5EFE-4791-84D8-7010C40A69F0}</author>
   </authors>
   <commentList>
-    <comment ref="AQ1" authorId="0" shapeId="0">
+    <comment ref="AQ1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     is this supposed to capture mean difference between control and treatment or ?</t>
-        </r>
       </text>
     </comment>
-    <comment ref="AZ1" authorId="1" shapeId="0">
+    <comment ref="AZ1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     daily kWh</t>
-        </r>
       </text>
     </comment>
-    <comment ref="AQ22" authorId="2" shapeId="0">
+    <comment ref="AQ22" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     in kWh</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -108,26 +82,17 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={1DD52412-77C6-1E43-B8CC-07AD562D2C6E}</author>
   </authors>
   <commentList>
-    <comment ref="AA1" authorId="0" shapeId="0">
+    <comment ref="AA1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     check label studies from srmt for label type</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -135,28 +100,19 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={CF36070F-7893-4948-8AB8-1CADF6EBBFD9}</author>
   </authors>
   <commentList>
-    <comment ref="D6" authorId="0" shapeId="0">
+    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     a bit confused as of where it’s correlation and where - quasi-experimental
 Reply:
     the way i reassessed this was - market statistics - correlation, whereas hypothetical choice - quasi-experimental</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -2268,7 +2224,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
     <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
@@ -2735,7 +2691,7 @@
     <xf numFmtId="9" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2887,12 +2843,11 @@
     </xf>
     <xf numFmtId="0" fontId="33" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Link" xfId="2" builtinId="8"/>
-    <cellStyle name="Prozent" xfId="1" builtinId="5"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -2926,7 +2881,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="45057.552441087966" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="334">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="45057.552441087966" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="334" xr:uid="{00000000-000A-0000-FFFF-FFFF01000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:CD1048576" sheet="Appliances"/>
   </cacheSource>
@@ -34731,7 +34686,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:BJ18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="92">
     <pivotField showAll="0"/>
@@ -35583,57 +35538,57 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BP53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="4" max="4" width="20.625" customWidth="1"/>
-    <col min="5" max="5" width="14.125" customWidth="1"/>
-    <col min="7" max="7" width="16.125" customWidth="1"/>
-    <col min="8" max="8" width="16.625" customWidth="1"/>
-    <col min="10" max="10" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.1640625" customWidth="1"/>
+    <col min="7" max="7" width="16.1640625" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="10" max="10" width="18.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" hidden="1" customWidth="1"/>
     <col min="12" max="17" width="0" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="16" hidden="1" customWidth="1"/>
     <col min="19" max="22" width="0" hidden="1" customWidth="1"/>
-    <col min="23" max="24" width="12.125" hidden="1" customWidth="1"/>
+    <col min="23" max="24" width="12.1640625" hidden="1" customWidth="1"/>
     <col min="25" max="25" width="0" hidden="1" customWidth="1"/>
     <col min="26" max="26" width="0" style="12" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="18.625" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="14.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.625" style="7" customWidth="1"/>
-    <col min="30" max="30" width="13.625" customWidth="1"/>
-    <col min="31" max="31" width="14.625" customWidth="1"/>
-    <col min="32" max="32" width="13.625" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="19.125" hidden="1" customWidth="1"/>
-    <col min="34" max="34" width="10.625" hidden="1" customWidth="1"/>
-    <col min="35" max="35" width="13.125" hidden="1" customWidth="1"/>
-    <col min="36" max="36" width="22.125" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="10.625" hidden="1" customWidth="1"/>
-    <col min="38" max="38" width="18.125" customWidth="1"/>
-    <col min="39" max="39" width="14.125" customWidth="1"/>
-    <col min="40" max="40" width="9.625" customWidth="1"/>
-    <col min="41" max="41" width="19.125" customWidth="1"/>
-    <col min="42" max="42" width="12.125" customWidth="1"/>
+    <col min="27" max="27" width="18.6640625" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="14.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.6640625" style="7" customWidth="1"/>
+    <col min="30" max="30" width="13.6640625" customWidth="1"/>
+    <col min="31" max="31" width="14.6640625" customWidth="1"/>
+    <col min="32" max="32" width="13.6640625" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="19.1640625" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="10.6640625" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="13.1640625" hidden="1" customWidth="1"/>
+    <col min="36" max="36" width="22.1640625" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="10.6640625" hidden="1" customWidth="1"/>
+    <col min="38" max="38" width="18.1640625" customWidth="1"/>
+    <col min="39" max="39" width="14.1640625" customWidth="1"/>
+    <col min="40" max="40" width="9.6640625" customWidth="1"/>
+    <col min="41" max="41" width="19.1640625" customWidth="1"/>
+    <col min="42" max="42" width="12.1640625" customWidth="1"/>
     <col min="44" max="45" width="0" hidden="1" customWidth="1"/>
-    <col min="46" max="47" width="13.125" hidden="1" customWidth="1"/>
+    <col min="46" max="47" width="13.1640625" hidden="1" customWidth="1"/>
     <col min="48" max="51" width="0" hidden="1" customWidth="1"/>
-    <col min="52" max="52" width="13.625" style="17" hidden="1" customWidth="1"/>
+    <col min="52" max="52" width="13.6640625" style="17" hidden="1" customWidth="1"/>
     <col min="53" max="53" width="26.5" hidden="1" customWidth="1"/>
-    <col min="54" max="54" width="20.625" hidden="1" customWidth="1"/>
+    <col min="54" max="54" width="20.6640625" hidden="1" customWidth="1"/>
     <col min="55" max="55" width="0" hidden="1" customWidth="1"/>
-    <col min="56" max="56" width="17.625" hidden="1" customWidth="1"/>
-    <col min="57" max="57" width="16.125" hidden="1" customWidth="1"/>
-    <col min="58" max="58" width="15.125" hidden="1" customWidth="1"/>
-    <col min="59" max="59" width="20.625" hidden="1" customWidth="1"/>
-    <col min="60" max="60" width="24.625" hidden="1" customWidth="1"/>
-    <col min="61" max="61" width="19.625" style="30" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="24.125" style="30" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="17.6640625" hidden="1" customWidth="1"/>
+    <col min="57" max="57" width="16.1640625" hidden="1" customWidth="1"/>
+    <col min="58" max="58" width="15.1640625" hidden="1" customWidth="1"/>
+    <col min="59" max="59" width="20.6640625" hidden="1" customWidth="1"/>
+    <col min="60" max="60" width="24.6640625" hidden="1" customWidth="1"/>
+    <col min="61" max="61" width="19.6640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="24.1640625" style="30" bestFit="1" customWidth="1"/>
     <col min="63" max="65" width="11" style="30"/>
-    <col min="67" max="67" width="25.125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="25.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="45">
+    <row r="1" spans="1:68" ht="48">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -41177,11 +41132,11 @@
       </c>
       <c r="BI27" s="30">
         <f t="shared" si="14"/>
-        <v>6.4285714285714259E-3</v>
+        <v>6.4285714285714276E-3</v>
       </c>
       <c r="BJ27" s="30">
         <f t="shared" si="15"/>
-        <v>6.4285714285714259E-3</v>
+        <v>6.4285714285714276E-3</v>
       </c>
       <c r="BK27" s="30">
         <f t="shared" si="9"/>
@@ -43431,7 +43386,7 @@
         <v>6.7567567567567571E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:66" s="41" customFormat="1" ht="16.5">
+    <row r="39" spans="1:66" s="41" customFormat="1" ht="17">
       <c r="A39" s="45" t="s">
         <v>68</v>
       </c>
@@ -43636,7 +43591,7 @@
       </c>
       <c r="BN39" s="43"/>
     </row>
-    <row r="40" spans="1:66" s="41" customFormat="1" ht="16.5">
+    <row r="40" spans="1:66" s="41" customFormat="1" ht="17">
       <c r="A40" s="45" t="s">
         <v>68</v>
       </c>
@@ -43841,7 +43796,7 @@
       </c>
       <c r="BN40" s="43"/>
     </row>
-    <row r="41" spans="1:66" s="41" customFormat="1" ht="16.5">
+    <row r="41" spans="1:66" s="41" customFormat="1" ht="17">
       <c r="A41" s="45" t="s">
         <v>68</v>
       </c>
@@ -44050,7 +44005,7 @@
         <v>2.0421052631578922</v>
       </c>
     </row>
-    <row r="42" spans="1:66" s="41" customFormat="1" ht="16.5">
+    <row r="42" spans="1:66" s="41" customFormat="1" ht="17">
       <c r="A42" s="45" t="s">
         <v>68</v>
       </c>
@@ -46447,34 +46402,34 @@
   </sheetData>
   <dataConsolidate/>
   <dataValidations count="10">
-    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="M11:M12 N29:N32 M14:M16 L1:L1048576">
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="M11:M12 N29:N32 M14:M16 L1:L1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="R1:W1 R2:Y9 X10:X12 BB43:BB52 BC29:BC32 S23:Y28 BB39:BC42 BC43:BC51 BC17:BC22 BB54:BB1048576 BB13:BC16 R33:Y1048576 BB17:BB38 BB1:BB12">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="R1:W1 R2:Y9 X10:X12 BB43:BB52 BC29:BC32 S23:Y28 BB39:BC42 BC43:BC51 BC17:BC22 BB54:BB1048576 BB13:BC16 R33:Y1048576 BB17:BB38 BB1:BB12" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="M1:Q9 M10 Y10:Y12 N10:W12 O29:Y32 P23:R28 N17:O28 P17:Y22 M13 N13:Y16 M17:M32 M33:Q1048576">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="M1:Q9 M10 Y10:Y12 N10:W12 O29:Y32 P23:R28 N17:O28 P17:Y22 M13 N13:Y16 M17:M32 M33:Q1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AO54:AO1048576 AO43:AO52 AO1:AO38">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AO54:AO1048576 AO43:AO52 AO1:AO38" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>0</formula1>
       <formula2>3</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="X1"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA53 AR53"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J23:J37 J1:J12">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="X1" xr:uid="{00000000-0002-0000-0000-000004000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA53 AR53" xr:uid="{00000000-0002-0000-0000-000005000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J23:J37 J1:J12" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>$F$2:$F$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K23:K37 K1:K12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K23:K37 K1:K12" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>$D$2:$D$6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K43:K51">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K43:K51" xr:uid="{00000000-0002-0000-0000-000008000000}">
       <formula1>$D$2:$D$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J43:J51">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J43:J51" xr:uid="{00000000-0002-0000-0000-000009000000}">
       <formula1>$F$2:$F$10</formula1>
     </dataValidation>
   </dataValidations>
@@ -46483,43 +46438,43 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Option to Opt/in - 1_x000a_No Option to Opt/in - 0_x000a_NA_x000a__x000a_">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Option to Opt/in - 1_x000a_No Option to Opt/in - 0_x000a_NA_x000a__x000a_" xr:uid="{00000000-0002-0000-0000-00000A000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B$2:$B$4</xm:f>
           </x14:formula1>
           <xm:sqref>BC23:BC28 BC54:BC1048576 BC33:BC38 BC1:BC12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000B000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$F$2:$F$9</xm:f>
           </x14:formula1>
           <xm:sqref>J54:J1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000C000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$A$2:$A$4</xm:f>
           </x14:formula1>
           <xm:sqref>AS43:AX51 AS54:AX1048576 AS23:AX38 AS2:AX12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000D000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$F$2:$F$10</xm:f>
           </x14:formula1>
           <xm:sqref>J38</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000E000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$E$2:$E$4</xm:f>
           </x14:formula1>
           <xm:sqref>AO43:AO51</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000F000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D$2:$D$6</xm:f>
           </x14:formula1>
           <xm:sqref>K54:K1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000010000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D$2:$D$7</xm:f>
           </x14:formula1>
@@ -46532,67 +46487,67 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CH51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="5" max="5" width="24.625" customWidth="1"/>
-    <col min="6" max="6" width="17.625" customWidth="1"/>
-    <col min="7" max="7" width="14.125" customWidth="1"/>
+    <col min="5" max="5" width="24.6640625" customWidth="1"/>
+    <col min="6" max="6" width="17.6640625" customWidth="1"/>
+    <col min="7" max="7" width="14.1640625" customWidth="1"/>
     <col min="8" max="8" width="16.5" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="16.125" customWidth="1"/>
-    <col min="11" max="11" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.125" customWidth="1"/>
+    <col min="10" max="10" width="16.1640625" customWidth="1"/>
+    <col min="11" max="11" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.1640625" customWidth="1"/>
     <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="14.625" customWidth="1"/>
-    <col min="17" max="17" width="13.125" customWidth="1"/>
+    <col min="16" max="16" width="14.6640625" customWidth="1"/>
+    <col min="17" max="17" width="13.1640625" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
-    <col min="19" max="19" width="14.125" customWidth="1"/>
+    <col min="19" max="19" width="14.1640625" customWidth="1"/>
     <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="21" width="21.125" customWidth="1"/>
+    <col min="21" max="21" width="21.1640625" customWidth="1"/>
     <col min="22" max="22" width="16" customWidth="1"/>
-    <col min="23" max="23" width="14.625" customWidth="1"/>
+    <col min="23" max="23" width="14.6640625" customWidth="1"/>
     <col min="24" max="24" width="12.5" customWidth="1"/>
     <col min="25" max="33" width="11" customWidth="1"/>
     <col min="34" max="35" width="16" customWidth="1"/>
     <col min="36" max="39" width="11" customWidth="1"/>
-    <col min="40" max="41" width="12.125" customWidth="1"/>
+    <col min="40" max="41" width="12.1640625" customWidth="1"/>
     <col min="42" max="42" width="11" customWidth="1"/>
-    <col min="43" max="43" width="27.625" customWidth="1"/>
-    <col min="44" max="44" width="41.125" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="54.625" customWidth="1"/>
+    <col min="43" max="43" width="27.6640625" customWidth="1"/>
+    <col min="44" max="44" width="41.1640625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="54.6640625" customWidth="1"/>
     <col min="46" max="46" width="21" customWidth="1"/>
-    <col min="47" max="47" width="26.625" style="7" customWidth="1"/>
-    <col min="48" max="48" width="14.125" style="7" customWidth="1"/>
-    <col min="49" max="49" width="13.125" customWidth="1"/>
-    <col min="50" max="50" width="9.625" customWidth="1"/>
+    <col min="47" max="47" width="26.6640625" style="7" customWidth="1"/>
+    <col min="48" max="48" width="14.1640625" style="7" customWidth="1"/>
+    <col min="49" max="49" width="13.1640625" customWidth="1"/>
+    <col min="50" max="50" width="9.6640625" customWidth="1"/>
     <col min="51" max="51" width="17" customWidth="1"/>
     <col min="52" max="52" width="9"/>
-    <col min="53" max="54" width="14.125" customWidth="1"/>
-    <col min="55" max="55" width="13.625" customWidth="1"/>
-    <col min="56" max="56" width="12.625" customWidth="1"/>
-    <col min="57" max="57" width="10.625" customWidth="1"/>
+    <col min="53" max="54" width="14.1640625" customWidth="1"/>
+    <col min="55" max="55" width="13.6640625" customWidth="1"/>
+    <col min="56" max="56" width="12.6640625" customWidth="1"/>
+    <col min="57" max="57" width="10.6640625" customWidth="1"/>
     <col min="58" max="58" width="13" customWidth="1"/>
-    <col min="59" max="60" width="10.625" customWidth="1"/>
-    <col min="61" max="62" width="11.125" customWidth="1"/>
+    <col min="59" max="60" width="10.6640625" customWidth="1"/>
+    <col min="61" max="62" width="11.1640625" customWidth="1"/>
     <col min="63" max="64" width="11" customWidth="1"/>
-    <col min="65" max="65" width="12.625" customWidth="1"/>
-    <col min="66" max="66" width="18.125" customWidth="1"/>
-    <col min="67" max="67" width="22.125" customWidth="1"/>
-    <col min="68" max="68" width="15.125" customWidth="1"/>
+    <col min="65" max="65" width="12.6640625" customWidth="1"/>
+    <col min="66" max="66" width="18.1640625" customWidth="1"/>
+    <col min="67" max="67" width="22.1640625" customWidth="1"/>
+    <col min="68" max="68" width="15.1640625" customWidth="1"/>
     <col min="69" max="69" width="18" customWidth="1"/>
-    <col min="70" max="70" width="17.125" customWidth="1"/>
-    <col min="71" max="71" width="21.125" customWidth="1"/>
-    <col min="72" max="72" width="10.125" customWidth="1"/>
+    <col min="70" max="70" width="17.1640625" customWidth="1"/>
+    <col min="71" max="71" width="21.1640625" customWidth="1"/>
+    <col min="72" max="72" width="10.1640625" customWidth="1"/>
     <col min="73" max="73" width="13" customWidth="1"/>
     <col min="74" max="74" width="14" customWidth="1"/>
-    <col min="75" max="75" width="13.125" customWidth="1"/>
+    <col min="75" max="75" width="13.1640625" customWidth="1"/>
     <col min="82" max="82" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:86" ht="17.100000000000001" customHeight="1">
+    <row r="1" spans="1:86" ht="17" customHeight="1">
       <c r="A1" s="59" t="s">
         <v>181</v>
       </c>
@@ -46852,7 +46807,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="2" spans="1:86">
+    <row r="2" spans="1:86" ht="16">
       <c r="A2" s="11" t="s">
         <v>68</v>
       </c>
@@ -47109,7 +47064,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="3" spans="1:86">
+    <row r="3" spans="1:86" ht="16">
       <c r="A3" s="11" t="s">
         <v>68</v>
       </c>
@@ -47366,7 +47321,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="4" spans="1:86">
+    <row r="4" spans="1:86" ht="16">
       <c r="A4" s="11" t="s">
         <v>68</v>
       </c>
@@ -47623,7 +47578,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="5" spans="1:86">
+    <row r="5" spans="1:86" ht="16">
       <c r="A5" s="11" t="s">
         <v>68</v>
       </c>
@@ -47880,7 +47835,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:86">
+    <row r="6" spans="1:86" ht="16">
       <c r="A6" s="11" t="s">
         <v>68</v>
       </c>
@@ -48137,7 +48092,7 @@
         <v>4.0133242364650637E-5</v>
       </c>
     </row>
-    <row r="7" spans="1:86">
+    <row r="7" spans="1:86" ht="16">
       <c r="A7" s="11" t="s">
         <v>68</v>
       </c>
@@ -48394,7 +48349,7 @@
         <v>4.4202802457675817E-5</v>
       </c>
     </row>
-    <row r="8" spans="1:86" s="105" customFormat="1">
+    <row r="8" spans="1:86" s="105" customFormat="1" ht="16">
       <c r="A8" s="11" t="s">
         <v>68</v>
       </c>
@@ -48654,7 +48609,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="9" spans="1:86" s="105" customFormat="1">
+    <row r="9" spans="1:86" s="105" customFormat="1" ht="16">
       <c r="A9" s="11" t="s">
         <v>68</v>
       </c>
@@ -48914,7 +48869,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="10" spans="1:86" s="105" customFormat="1">
+    <row r="10" spans="1:86" s="105" customFormat="1" ht="16">
       <c r="A10" s="11" t="s">
         <v>68</v>
       </c>
@@ -49174,7 +49129,7 @@
         <v>4.0133242364650637E-5</v>
       </c>
     </row>
-    <row r="11" spans="1:86" s="105" customFormat="1">
+    <row r="11" spans="1:86" s="105" customFormat="1" ht="16">
       <c r="A11" s="11" t="s">
         <v>68</v>
       </c>
@@ -49434,7 +49389,7 @@
         <v>4.8550759819391176E-5</v>
       </c>
     </row>
-    <row r="12" spans="1:86">
+    <row r="12" spans="1:86" ht="16">
       <c r="A12" s="11" t="s">
         <v>68</v>
       </c>
@@ -49691,7 +49646,7 @@
         <v>4.8550759819391176E-5</v>
       </c>
     </row>
-    <row r="13" spans="1:86" s="107" customFormat="1">
+    <row r="13" spans="1:86" s="107" customFormat="1" ht="16">
       <c r="A13" s="11" t="s">
         <v>68</v>
       </c>
@@ -49951,7 +49906,7 @@
         <v>4.8550759819391176E-5</v>
       </c>
     </row>
-    <row r="14" spans="1:86">
+    <row r="14" spans="1:86" ht="16">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -50206,7 +50161,7 @@
         <v>5.6882821387940839E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:86">
+    <row r="15" spans="1:86" ht="16">
       <c r="A15" t="s">
         <v>68</v>
       </c>
@@ -50461,7 +50416,7 @@
         <v>5.6882821387940839E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:86">
+    <row r="16" spans="1:86" ht="16">
       <c r="A16" t="s">
         <v>68</v>
       </c>
@@ -50716,7 +50671,7 @@
         <v>1.1061946902654867E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:86">
+    <row r="17" spans="1:86" ht="16">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -50971,7 +50926,7 @@
         <v>1.1061946902654867E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:86" s="107" customFormat="1">
+    <row r="18" spans="1:86" s="107" customFormat="1" ht="16">
       <c r="A18" s="11" t="s">
         <v>68</v>
       </c>
@@ -51232,7 +51187,7 @@
         <v>9.2264540891644526E-6</v>
       </c>
     </row>
-    <row r="19" spans="1:86" s="107" customFormat="1" ht="17.100000000000001" customHeight="1">
+    <row r="19" spans="1:86" s="107" customFormat="1" ht="17" customHeight="1">
       <c r="A19" s="11" t="s">
         <v>68</v>
       </c>
@@ -51493,7 +51448,7 @@
         <v>2.6660978991148553E-5</v>
       </c>
     </row>
-    <row r="20" spans="1:86" s="107" customFormat="1">
+    <row r="20" spans="1:86" s="107" customFormat="1" ht="16">
       <c r="A20" s="11" t="s">
         <v>68</v>
       </c>
@@ -51754,7 +51709,7 @@
         <v>1.4545242978283952E-5</v>
       </c>
     </row>
-    <row r="21" spans="1:86">
+    <row r="21" spans="1:86" ht="16">
       <c r="A21" s="11" t="s">
         <v>68</v>
       </c>
@@ -52012,7 +51967,7 @@
         <v>3.0061626333984669E-5</v>
       </c>
     </row>
-    <row r="22" spans="1:86">
+    <row r="22" spans="1:86" ht="16">
       <c r="A22" s="11" t="s">
         <v>68</v>
       </c>
@@ -52271,7 +52226,7 @@
         <v>1.953125E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:86">
+    <row r="23" spans="1:86" ht="16">
       <c r="A23" s="11" t="s">
         <v>68</v>
       </c>
@@ -52530,7 +52485,7 @@
         <v>1.953125E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:86">
+    <row r="24" spans="1:86" ht="16">
       <c r="A24" s="11" t="s">
         <v>68</v>
       </c>
@@ -52550,7 +52505,7 @@
       <c r="G24" t="s">
         <v>271</v>
       </c>
-      <c r="H24" s="123" t="s">
+      <c r="H24" t="s">
         <v>272</v>
       </c>
       <c r="I24" s="101">
@@ -53044,7 +52999,7 @@
         <v>4.1152263374485596E-4</v>
       </c>
     </row>
-    <row r="26" spans="1:86">
+    <row r="26" spans="1:86" ht="16">
       <c r="A26" s="11" t="s">
         <v>68</v>
       </c>
@@ -53301,7 +53256,7 @@
         <v>4.0950040950040953E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:86">
+    <row r="27" spans="1:86" ht="16">
       <c r="A27" s="11" t="s">
         <v>68</v>
       </c>
@@ -53558,7 +53513,7 @@
         <v>4.1152263374485596E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:86">
+    <row r="28" spans="1:86" ht="16">
       <c r="A28" s="94" t="s">
         <v>68</v>
       </c>
@@ -53818,7 +53773,7 @@
         <v>3.2573289902280132E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:86">
+    <row r="29" spans="1:86" ht="16">
       <c r="A29" s="94" t="s">
         <v>68</v>
       </c>
@@ -54078,7 +54033,7 @@
         <v>3.2573289902280132E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:86">
+    <row r="30" spans="1:86" ht="16">
       <c r="A30" s="94" t="s">
         <v>68</v>
       </c>
@@ -54338,7 +54293,7 @@
         <v>3.2573289902280132E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:86">
+    <row r="31" spans="1:86" ht="16">
       <c r="A31" s="94" t="s">
         <v>68</v>
       </c>
@@ -54597,7 +54552,7 @@
         <v>7.1839080459770114E-5</v>
       </c>
     </row>
-    <row r="32" spans="1:86">
+    <row r="32" spans="1:86" ht="16">
       <c r="A32" t="s">
         <v>68</v>
       </c>
@@ -54852,7 +54807,7 @@
         <v>1.0448480111840532E-6</v>
       </c>
     </row>
-    <row r="33" spans="1:86">
+    <row r="33" spans="1:86" ht="16">
       <c r="A33" t="s">
         <v>68</v>
       </c>
@@ -55107,7 +55062,7 @@
         <v>1.0448480111840532E-6</v>
       </c>
     </row>
-    <row r="34" spans="1:86">
+    <row r="34" spans="1:86" ht="16">
       <c r="A34" t="s">
         <v>68</v>
       </c>
@@ -55362,7 +55317,7 @@
         <v>1.0448480111840532E-6</v>
       </c>
     </row>
-    <row r="35" spans="1:86">
+    <row r="35" spans="1:86" ht="16">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -55751,7 +55706,7 @@
         <v>308</v>
       </c>
       <c r="AT36" t="s">
-        <v>73</v>
+        <v>236</v>
       </c>
       <c r="AU36">
         <v>0.154</v>
@@ -56009,7 +55964,7 @@
         <v>308</v>
       </c>
       <c r="AT37" t="s">
-        <v>73</v>
+        <v>236</v>
       </c>
       <c r="AU37">
         <v>0.28299999999999997</v>
@@ -56133,43 +56088,43 @@
         <v>2.5188916876574307E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:86">
+    <row r="38" spans="1:86" ht="16">
       <c r="M38" s="18"/>
     </row>
-    <row r="39" spans="1:86">
+    <row r="39" spans="1:86" ht="16">
       <c r="M39" s="18"/>
     </row>
-    <row r="40" spans="1:86">
+    <row r="40" spans="1:86" ht="16">
       <c r="M40" s="18"/>
     </row>
-    <row r="41" spans="1:86">
+    <row r="41" spans="1:86" ht="16">
       <c r="M41" s="18"/>
     </row>
-    <row r="42" spans="1:86">
+    <row r="42" spans="1:86" ht="16">
       <c r="M42" s="18"/>
     </row>
-    <row r="43" spans="1:86">
+    <row r="43" spans="1:86" ht="16">
       <c r="M43" s="18"/>
     </row>
-    <row r="44" spans="1:86">
+    <row r="44" spans="1:86" ht="16">
       <c r="M44" s="18"/>
     </row>
-    <row r="45" spans="1:86">
+    <row r="45" spans="1:86" ht="16">
       <c r="M45" s="18"/>
     </row>
-    <row r="46" spans="1:86">
+    <row r="46" spans="1:86" ht="16">
       <c r="M46" s="18"/>
     </row>
     <row r="47" spans="1:86" ht="15.75" customHeight="1">
       <c r="M47" s="18"/>
       <c r="BX47" s="30"/>
     </row>
-    <row r="48" spans="1:86">
+    <row r="48" spans="1:86" ht="16">
       <c r="M48" s="18"/>
       <c r="BA48" s="117"/>
       <c r="BB48" s="117"/>
     </row>
-    <row r="49" spans="13:54">
+    <row r="49" spans="13:54" ht="16">
       <c r="M49" s="18"/>
       <c r="BA49" s="117"/>
       <c r="BB49" s="117"/>
@@ -56177,14 +56132,14 @@
     <row r="50" spans="13:54" ht="15.75" customHeight="1">
       <c r="M50" s="18"/>
     </row>
-    <row r="51" spans="13:54">
+    <row r="51" spans="13:54" ht="16">
       <c r="M51" s="18"/>
       <c r="BA51" s="118"/>
       <c r="BB51" s="118"/>
     </row>
   </sheetData>
-  <autoFilter ref="AR1:AR46"/>
-  <sortState ref="A2:CD51">
+  <autoFilter ref="AR1:AR46" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:CD51">
     <sortCondition ref="C2:C51"/>
   </sortState>
   <dataConsolidate/>
@@ -56195,17 +56150,17 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations xWindow="603" yWindow="1085" count="5">
-    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="I1 I5:I1048576">
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="I1 I5:I1048576" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="AQ5:AQ6 AD1:AG1048576"/>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="Y38:AC1048576 Y18:Y37 Z14:AC37 Y1:AC13">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="AQ5:AQ6 AD1:AG1048576" xr:uid="{00000000-0002-0000-0100-000001000000}"/>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="Y38:AC1048576 Y18:Y37 Z14:AC37 Y1:AC13" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN38:BN1048576 BN1:BN35"/>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1:S1048576 U1:U1048576 AH1:AI1048576 AK1:AP1048576 AJ2:AJ1048576">
+    <dataValidation errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN38:BN1048576 BN1:BN35" xr:uid="{00000000-0002-0000-0100-000003000000}"/>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1:S1048576 U1:U1048576 AH1:AI1048576 AK1:AP1048576 AJ2:AJ1048576" xr:uid="{00000000-0002-0000-0100-000004000000}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -56216,127 +56171,127 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="603" yWindow="1085" count="21">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000005000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B$2:$B$4</xm:f>
           </x14:formula1>
           <xm:sqref>U1:U6 U10:U1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000006000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$A$2:$A$4</xm:f>
           </x14:formula1>
           <xm:sqref>BU18:BW20 BU36:BW1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000007000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$C$2:$C$4</xm:f>
           </x14:formula1>
           <xm:sqref>BS21:BT35 BP21:BQ35 BO38:BO1048576 BO1:BO35</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000008000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$I$2:$I$3</xm:f>
           </x14:formula1>
           <xm:sqref>AV27:AV1048576 AV1:AV20</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000009000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$O:$O</xm:f>
           </x14:formula1>
           <xm:sqref>BT38:BT1048576 BT1:BT20</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000A000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$L$2:$L$9</xm:f>
           </x14:formula1>
           <xm:sqref>U1:U1048576 S1:S1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000B000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$K$2:$K$3</xm:f>
           </x14:formula1>
           <xm:sqref>U1:W1048576 S1:S1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000C000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$N$2:$N$7</xm:f>
           </x14:formula1>
           <xm:sqref>U1:W1048576 S1:S1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000D000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$J$2:$J$12</xm:f>
           </x14:formula1>
           <xm:sqref>K1:K1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000E000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$S:$S</xm:f>
           </x14:formula1>
           <xm:sqref>G1:G1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000F000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$G:$G</xm:f>
           </x14:formula1>
           <xm:sqref>AR1:AR1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000010000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$F:$F</xm:f>
           </x14:formula1>
           <xm:sqref>M52:M1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000011000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$P:$P</xm:f>
           </x14:formula1>
           <xm:sqref>AT1:AT1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000012000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D:$D</xm:f>
           </x14:formula1>
           <xm:sqref>S1:S1048576 U1:W1048576 N1:N1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000013000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$N:$N</xm:f>
           </x14:formula1>
           <xm:sqref>O1:O1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000014000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B:$B</xm:f>
           </x14:formula1>
           <xm:sqref>T1:T1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000015000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$R:$R</xm:f>
           </x14:formula1>
           <xm:sqref>E1:E1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000016000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$H:$H</xm:f>
           </x14:formula1>
           <xm:sqref>S1:S1048576 U1:U1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000017000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$M:$M</xm:f>
           </x14:formula1>
           <xm:sqref>U1:U1048576 P1:P1048576 S1:S1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000018000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$L$2:$L$10</xm:f>
           </x14:formula1>
           <xm:sqref>R1:R1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000019000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$H$1:$H$7</xm:f>
           </x14:formula1>
@@ -56349,72 +56304,72 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:BJ18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="28.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.83203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="30" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="28.125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="15" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="11" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="22.625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.1640625" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="17" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="36.33203125" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="29" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="21.875" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="20.1640625" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="15" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="21.83203125" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="29.625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="29.6640625" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="33" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="35.5" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.875" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="24.375" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="25.875" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="25.83203125" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="35" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="26.375" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="63" max="64" width="18.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -59254,20 +59209,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:S99"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="15.5" customWidth="1"/>
-    <col min="5" max="5" width="19.625" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="18.125" style="26" customWidth="1"/>
+    <col min="7" max="7" width="18.1640625" style="26" customWidth="1"/>
     <col min="8" max="8" width="20.5" customWidth="1"/>
-    <col min="9" max="9" width="14.125" customWidth="1"/>
-    <col min="10" max="10" width="15.125" customWidth="1"/>
+    <col min="9" max="9" width="14.1640625" customWidth="1"/>
+    <col min="10" max="10" width="15.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" ht="17">
       <c r="A1" t="s">
         <v>384</v>
       </c>
@@ -59323,7 +59278,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="31.5">
+    <row r="2" spans="1:19" ht="34">
       <c r="A2">
         <v>0</v>
       </c>
@@ -59379,7 +59334,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="31.5">
+    <row r="3" spans="1:19" ht="34">
       <c r="A3">
         <v>1</v>
       </c>
@@ -59435,7 +59390,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="47.25">
+    <row r="4" spans="1:19" ht="51">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -59485,7 +59440,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="47.25">
+    <row r="5" spans="1:19" ht="51">
       <c r="D5" t="s">
         <v>293</v>
       </c>
@@ -60486,7 +60441,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="R2:S91">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="R2:S91">
     <sortCondition ref="R2:R91"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/appliances_usage.xlsx
+++ b/appliances_usage.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-4485" yWindow="-21105" windowWidth="38400" windowHeight="19395" firstSheet="1" activeTab="1"/>
+    <workbookView xWindow="-4488" yWindow="-21108" windowWidth="38400" windowHeight="19392" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Usage" sheetId="5" state="hidden" r:id="rId1"/>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3169" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3159" uniqueCount="620">
   <si>
     <t>Coder</t>
   </si>
@@ -1118,9 +1118,6 @@
     <t xml:space="preserve">for owners of ES AC </t>
   </si>
   <si>
-    <t>Alberini, Towe</t>
-  </si>
-  <si>
     <t>Information v. energy efficiency incentives: Evidence from residential electricity consumption in Maryland</t>
   </si>
   <si>
@@ -1587,9 +1584,6 @@
     <t>dummy (0/1)</t>
   </si>
   <si>
-    <t>Alberini, Bigano</t>
-  </si>
-  <si>
     <t>How effective are energy-efficiency incentive programs? Evidence from Italian homeowners</t>
   </si>
   <si>
@@ -1609,9 +1603,6 @@
   </si>
   <si>
     <t>alphabetical</t>
-  </si>
-  <si>
-    <t>Alberini, Bigano, Boeri</t>
   </si>
   <si>
     <t>Looking for free riding: energy efficiency incentives and Italian homeowners</t>
@@ -2263,6 +2254,18 @@
   </si>
   <si>
     <t>dishwasher</t>
+  </si>
+  <si>
+    <t>Albertini, Towe</t>
+  </si>
+  <si>
+    <t>Albertini, Bigano</t>
+  </si>
+  <si>
+    <t>Albertini, Bigano, Boeri</t>
+  </si>
+  <si>
+    <t>Albertini, Gans, Towe</t>
   </si>
 </sst>
 </file>
@@ -2280,9 +2283,16 @@
     <numFmt numFmtId="171" formatCode="0.0%"/>
     <numFmt numFmtId="172" formatCode="0.0000;[Red]0.0000"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="36">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -2732,45 +2742,45 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2780,114 +2790,119 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="19" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="168" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="170" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="20" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="19" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="21" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="20" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="20" fillId="15" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="20" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="21" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="21" fillId="15" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="21" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="15" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="171" fontId="21" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Link" xfId="2" builtinId="8"/>
@@ -35585,55 +35600,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BP53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="4" max="4" width="20.625" customWidth="1"/>
-    <col min="5" max="5" width="14.125" customWidth="1"/>
-    <col min="7" max="7" width="16.125" customWidth="1"/>
-    <col min="8" max="8" width="16.625" customWidth="1"/>
-    <col min="10" max="10" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.59765625" customWidth="1"/>
+    <col min="5" max="5" width="14.09765625" customWidth="1"/>
+    <col min="7" max="7" width="16.09765625" customWidth="1"/>
+    <col min="8" max="8" width="16.59765625" customWidth="1"/>
+    <col min="10" max="10" width="18.09765625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" hidden="1" customWidth="1"/>
     <col min="12" max="17" width="0" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="16" hidden="1" customWidth="1"/>
     <col min="19" max="22" width="0" hidden="1" customWidth="1"/>
-    <col min="23" max="24" width="12.125" hidden="1" customWidth="1"/>
+    <col min="23" max="24" width="12.09765625" hidden="1" customWidth="1"/>
     <col min="25" max="25" width="0" hidden="1" customWidth="1"/>
     <col min="26" max="26" width="0" style="12" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="18.625" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="14.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.625" style="7" customWidth="1"/>
-    <col min="30" max="30" width="13.625" customWidth="1"/>
-    <col min="31" max="31" width="14.625" customWidth="1"/>
-    <col min="32" max="32" width="13.625" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="19.125" hidden="1" customWidth="1"/>
-    <col min="34" max="34" width="10.625" hidden="1" customWidth="1"/>
-    <col min="35" max="35" width="13.125" hidden="1" customWidth="1"/>
-    <col min="36" max="36" width="22.125" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="10.625" hidden="1" customWidth="1"/>
-    <col min="38" max="38" width="18.125" customWidth="1"/>
-    <col min="39" max="39" width="14.125" customWidth="1"/>
-    <col min="40" max="40" width="9.625" customWidth="1"/>
-    <col min="41" max="41" width="19.125" customWidth="1"/>
-    <col min="42" max="42" width="12.125" customWidth="1"/>
+    <col min="27" max="27" width="18.59765625" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.59765625" style="7" customWidth="1"/>
+    <col min="30" max="30" width="13.59765625" customWidth="1"/>
+    <col min="31" max="31" width="14.59765625" customWidth="1"/>
+    <col min="32" max="32" width="13.59765625" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="19.09765625" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="10.59765625" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="13.09765625" hidden="1" customWidth="1"/>
+    <col min="36" max="36" width="22.09765625" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="10.59765625" hidden="1" customWidth="1"/>
+    <col min="38" max="38" width="18.09765625" customWidth="1"/>
+    <col min="39" max="39" width="14.09765625" customWidth="1"/>
+    <col min="40" max="40" width="9.59765625" customWidth="1"/>
+    <col min="41" max="41" width="19.09765625" customWidth="1"/>
+    <col min="42" max="42" width="12.09765625" customWidth="1"/>
     <col min="44" max="45" width="0" hidden="1" customWidth="1"/>
-    <col min="46" max="47" width="13.125" hidden="1" customWidth="1"/>
+    <col min="46" max="47" width="13.09765625" hidden="1" customWidth="1"/>
     <col min="48" max="51" width="0" hidden="1" customWidth="1"/>
-    <col min="52" max="52" width="13.625" style="17" hidden="1" customWidth="1"/>
+    <col min="52" max="52" width="13.59765625" style="17" hidden="1" customWidth="1"/>
     <col min="53" max="53" width="26.5" hidden="1" customWidth="1"/>
-    <col min="54" max="54" width="20.625" hidden="1" customWidth="1"/>
+    <col min="54" max="54" width="20.59765625" hidden="1" customWidth="1"/>
     <col min="55" max="55" width="0" hidden="1" customWidth="1"/>
-    <col min="56" max="56" width="17.625" hidden="1" customWidth="1"/>
-    <col min="57" max="57" width="16.125" hidden="1" customWidth="1"/>
-    <col min="58" max="58" width="15.125" hidden="1" customWidth="1"/>
-    <col min="59" max="59" width="20.625" hidden="1" customWidth="1"/>
-    <col min="60" max="60" width="24.625" hidden="1" customWidth="1"/>
-    <col min="61" max="61" width="19.625" style="30" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="24.125" style="30" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="17.59765625" hidden="1" customWidth="1"/>
+    <col min="57" max="57" width="16.09765625" hidden="1" customWidth="1"/>
+    <col min="58" max="58" width="15.09765625" hidden="1" customWidth="1"/>
+    <col min="59" max="59" width="20.59765625" hidden="1" customWidth="1"/>
+    <col min="60" max="60" width="24.59765625" hidden="1" customWidth="1"/>
+    <col min="61" max="61" width="19.59765625" style="30" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="24.09765625" style="30" bestFit="1" customWidth="1"/>
     <col min="63" max="65" width="11" style="30"/>
-    <col min="67" max="67" width="25.125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="25.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="45">
+    <row r="1" spans="1:68" ht="43.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -43431,7 +43446,7 @@
         <v>6.7567567567567571E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:66" s="41" customFormat="1" ht="16.5">
+    <row r="39" spans="1:66" s="41" customFormat="1" ht="16.8">
       <c r="A39" s="45" t="s">
         <v>68</v>
       </c>
@@ -43636,7 +43651,7 @@
       </c>
       <c r="BN39" s="43"/>
     </row>
-    <row r="40" spans="1:66" s="41" customFormat="1" ht="16.5">
+    <row r="40" spans="1:66" s="41" customFormat="1" ht="16.8">
       <c r="A40" s="45" t="s">
         <v>68</v>
       </c>
@@ -43841,7 +43856,7 @@
       </c>
       <c r="BN40" s="43"/>
     </row>
-    <row r="41" spans="1:66" s="41" customFormat="1" ht="16.5">
+    <row r="41" spans="1:66" s="41" customFormat="1" ht="16.8">
       <c r="A41" s="45" t="s">
         <v>68</v>
       </c>
@@ -44050,7 +44065,7 @@
         <v>2.0421052631578922</v>
       </c>
     </row>
-    <row r="42" spans="1:66" s="41" customFormat="1" ht="16.5">
+    <row r="42" spans="1:66" s="41" customFormat="1" ht="16.8">
       <c r="A42" s="45" t="s">
         <v>68</v>
       </c>
@@ -46536,59 +46551,59 @@
   <dimension ref="A1:CH51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="5" max="5" width="24.625" customWidth="1"/>
-    <col min="6" max="6" width="17.625" customWidth="1"/>
-    <col min="7" max="7" width="14.125" customWidth="1"/>
+    <col min="5" max="5" width="24.59765625" customWidth="1"/>
+    <col min="6" max="6" width="17.59765625" customWidth="1"/>
+    <col min="7" max="7" width="14.09765625" customWidth="1"/>
     <col min="8" max="8" width="16.5" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="16.125" customWidth="1"/>
-    <col min="11" max="11" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.125" customWidth="1"/>
+    <col min="10" max="10" width="16.09765625" customWidth="1"/>
+    <col min="11" max="11" width="15.09765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.59765625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.09765625" customWidth="1"/>
     <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="14.625" customWidth="1"/>
-    <col min="17" max="17" width="13.125" customWidth="1"/>
+    <col min="16" max="16" width="14.59765625" customWidth="1"/>
+    <col min="17" max="17" width="13.09765625" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
-    <col min="19" max="19" width="14.125" customWidth="1"/>
+    <col min="19" max="19" width="14.09765625" customWidth="1"/>
     <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="21" width="21.125" customWidth="1"/>
+    <col min="21" max="21" width="21.09765625" customWidth="1"/>
     <col min="22" max="22" width="16" customWidth="1"/>
-    <col min="23" max="23" width="14.625" customWidth="1"/>
+    <col min="23" max="23" width="14.59765625" customWidth="1"/>
     <col min="24" max="24" width="12.5" customWidth="1"/>
     <col min="25" max="33" width="11" customWidth="1"/>
     <col min="34" max="35" width="16" customWidth="1"/>
     <col min="36" max="39" width="11" customWidth="1"/>
-    <col min="40" max="41" width="12.125" customWidth="1"/>
+    <col min="40" max="41" width="12.09765625" customWidth="1"/>
     <col min="42" max="42" width="11" customWidth="1"/>
-    <col min="43" max="43" width="27.625" customWidth="1"/>
-    <col min="44" max="44" width="41.125" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="54.625" customWidth="1"/>
+    <col min="43" max="43" width="27.59765625" customWidth="1"/>
+    <col min="44" max="44" width="41.09765625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="54.59765625" customWidth="1"/>
     <col min="46" max="46" width="21" customWidth="1"/>
-    <col min="47" max="47" width="26.625" style="7" customWidth="1"/>
-    <col min="48" max="48" width="14.125" style="7" customWidth="1"/>
-    <col min="49" max="49" width="13.125" customWidth="1"/>
-    <col min="50" max="50" width="9.625" customWidth="1"/>
+    <col min="47" max="47" width="26.59765625" style="7" customWidth="1"/>
+    <col min="48" max="48" width="14.09765625" style="7" customWidth="1"/>
+    <col min="49" max="49" width="13.09765625" customWidth="1"/>
+    <col min="50" max="50" width="9.59765625" customWidth="1"/>
     <col min="51" max="51" width="17" customWidth="1"/>
     <col min="52" max="52" width="9"/>
-    <col min="53" max="54" width="14.125" customWidth="1"/>
-    <col min="55" max="55" width="13.625" customWidth="1"/>
-    <col min="56" max="56" width="12.625" customWidth="1"/>
-    <col min="57" max="57" width="10.625" customWidth="1"/>
+    <col min="53" max="54" width="14.09765625" customWidth="1"/>
+    <col min="55" max="55" width="13.59765625" customWidth="1"/>
+    <col min="56" max="56" width="12.59765625" customWidth="1"/>
+    <col min="57" max="57" width="10.59765625" customWidth="1"/>
     <col min="58" max="58" width="13" customWidth="1"/>
-    <col min="59" max="60" width="10.625" customWidth="1"/>
-    <col min="61" max="62" width="11.125" customWidth="1"/>
+    <col min="59" max="60" width="10.59765625" customWidth="1"/>
+    <col min="61" max="62" width="11.09765625" customWidth="1"/>
     <col min="63" max="64" width="11" customWidth="1"/>
-    <col min="65" max="65" width="12.625" customWidth="1"/>
-    <col min="66" max="66" width="18.125" customWidth="1"/>
-    <col min="67" max="67" width="22.125" customWidth="1"/>
-    <col min="68" max="68" width="15.125" customWidth="1"/>
+    <col min="65" max="65" width="12.59765625" customWidth="1"/>
+    <col min="66" max="66" width="18.09765625" customWidth="1"/>
+    <col min="67" max="67" width="22.09765625" customWidth="1"/>
+    <col min="68" max="68" width="15.09765625" customWidth="1"/>
     <col min="69" max="69" width="18" customWidth="1"/>
-    <col min="70" max="70" width="17.125" customWidth="1"/>
-    <col min="71" max="71" width="21.125" customWidth="1"/>
-    <col min="72" max="72" width="10.125" customWidth="1"/>
+    <col min="70" max="70" width="17.09765625" customWidth="1"/>
+    <col min="71" max="71" width="21.09765625" customWidth="1"/>
+    <col min="72" max="72" width="10.09765625" customWidth="1"/>
     <col min="73" max="73" width="13" customWidth="1"/>
     <col min="74" max="74" width="14" customWidth="1"/>
-    <col min="75" max="75" width="13.125" customWidth="1"/>
+    <col min="75" max="75" width="13.09765625" customWidth="1"/>
     <col min="82" max="82" width="24" customWidth="1"/>
   </cols>
   <sheetData>
@@ -46699,7 +46714,7 @@
         <v>195</v>
       </c>
       <c r="AJ1" s="75" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="AK1" s="75" t="s">
         <v>19</v>
@@ -46852,7 +46867,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="2" spans="1:86">
+    <row r="2" spans="1:86" ht="15.6">
       <c r="A2" s="11" t="s">
         <v>68</v>
       </c>
@@ -47109,7 +47124,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="3" spans="1:86">
+    <row r="3" spans="1:86" ht="15.6">
       <c r="A3" s="11" t="s">
         <v>68</v>
       </c>
@@ -47366,7 +47381,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="4" spans="1:86">
+    <row r="4" spans="1:86" ht="15.6">
       <c r="A4" s="11" t="s">
         <v>68</v>
       </c>
@@ -47623,7 +47638,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="5" spans="1:86">
+    <row r="5" spans="1:86" ht="15.6">
       <c r="A5" s="11" t="s">
         <v>68</v>
       </c>
@@ -47880,7 +47895,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:86">
+    <row r="6" spans="1:86" ht="15.6">
       <c r="A6" s="11" t="s">
         <v>68</v>
       </c>
@@ -48137,7 +48152,7 @@
         <v>4.0133242364650637E-5</v>
       </c>
     </row>
-    <row r="7" spans="1:86">
+    <row r="7" spans="1:86" ht="15.6">
       <c r="A7" s="11" t="s">
         <v>68</v>
       </c>
@@ -48394,7 +48409,7 @@
         <v>4.4202802457675817E-5</v>
       </c>
     </row>
-    <row r="8" spans="1:86" s="105" customFormat="1">
+    <row r="8" spans="1:86" s="105" customFormat="1" ht="15.6">
       <c r="A8" s="11" t="s">
         <v>68</v>
       </c>
@@ -48654,7 +48669,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="9" spans="1:86" s="105" customFormat="1">
+    <row r="9" spans="1:86" s="105" customFormat="1" ht="15.6">
       <c r="A9" s="11" t="s">
         <v>68</v>
       </c>
@@ -48914,7 +48929,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="10" spans="1:86" s="105" customFormat="1">
+    <row r="10" spans="1:86" s="105" customFormat="1" ht="15.6">
       <c r="A10" s="11" t="s">
         <v>68</v>
       </c>
@@ -49174,7 +49189,7 @@
         <v>4.0133242364650637E-5</v>
       </c>
     </row>
-    <row r="11" spans="1:86" s="105" customFormat="1">
+    <row r="11" spans="1:86" s="105" customFormat="1" ht="15.6">
       <c r="A11" s="11" t="s">
         <v>68</v>
       </c>
@@ -49434,7 +49449,7 @@
         <v>4.8550759819391176E-5</v>
       </c>
     </row>
-    <row r="12" spans="1:86">
+    <row r="12" spans="1:86" ht="15.6">
       <c r="A12" s="11" t="s">
         <v>68</v>
       </c>
@@ -49691,7 +49706,7 @@
         <v>4.8550759819391176E-5</v>
       </c>
     </row>
-    <row r="13" spans="1:86" s="107" customFormat="1">
+    <row r="13" spans="1:86" s="107" customFormat="1" ht="15.6">
       <c r="A13" s="11" t="s">
         <v>68</v>
       </c>
@@ -49951,7 +49966,7 @@
         <v>4.8550759819391176E-5</v>
       </c>
     </row>
-    <row r="14" spans="1:86">
+    <row r="14" spans="1:86" ht="15.6">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -50106,8 +50121,9 @@
         <f t="shared" si="0"/>
         <v>1.8213567929369965</v>
       </c>
-      <c r="BA14" s="41" t="s">
-        <v>73</v>
+      <c r="BA14" s="125">
+        <f>AU14/8260.69</f>
+        <v>4.9147831476547353E-2</v>
       </c>
       <c r="BB14" s="41"/>
       <c r="BC14" t="s">
@@ -50206,7 +50222,7 @@
         <v>5.6882821387940839E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:86">
+    <row r="15" spans="1:86" ht="15.6">
       <c r="A15" t="s">
         <v>68</v>
       </c>
@@ -50361,8 +50377,9 @@
         <f t="shared" si="0"/>
         <v>1.7220426989123607</v>
       </c>
-      <c r="BA15" s="41" t="s">
-        <v>73</v>
+      <c r="BA15" s="125">
+        <f t="shared" ref="BA15:BA17" si="10">AU15/8260.69</f>
+        <v>0.43415949515113139</v>
       </c>
       <c r="BB15" s="41"/>
       <c r="BC15" t="s">
@@ -50461,7 +50478,7 @@
         <v>5.6882821387940839E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:86">
+    <row r="16" spans="1:86" ht="15.6">
       <c r="A16" t="s">
         <v>68</v>
       </c>
@@ -50616,8 +50633,9 @@
         <f t="shared" si="0"/>
         <v>2.2952440645363477</v>
       </c>
-      <c r="BA16" s="41" t="s">
-        <v>73</v>
+      <c r="BA16" s="125">
+        <f t="shared" si="10"/>
+        <v>2.5711532571734322E-2</v>
       </c>
       <c r="BB16" s="41"/>
       <c r="BC16" t="s">
@@ -50716,7 +50734,7 @@
         <v>1.1061946902654867E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:86">
+    <row r="17" spans="1:86" ht="15.6">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -50871,8 +50889,9 @@
         <f t="shared" si="0"/>
         <v>0.4628137059347513</v>
       </c>
-      <c r="BA17" s="41" t="s">
-        <v>73</v>
+      <c r="BA17" s="125">
+        <f t="shared" si="10"/>
+        <v>3.6542589057330564E-2</v>
       </c>
       <c r="BB17" s="41"/>
       <c r="BC17" t="s">
@@ -50971,7 +50990,7 @@
         <v>1.1061946902654867E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:86" s="107" customFormat="1">
+    <row r="18" spans="1:86" s="107" customFormat="1" ht="15.6">
       <c r="A18" s="11" t="s">
         <v>68</v>
       </c>
@@ -50983,34 +51002,34 @@
         <v>137</v>
       </c>
       <c r="E18" t="s">
-        <v>250</v>
+        <v>616</v>
       </c>
       <c r="F18" s="100">
         <v>2015</v>
       </c>
       <c r="G18" t="s">
+        <v>250</v>
+      </c>
+      <c r="H18" t="s">
         <v>251</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" s="101">
+        <v>1</v>
+      </c>
+      <c r="J18" t="s">
         <v>252</v>
       </c>
-      <c r="I18" s="101">
-        <v>1</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="K18" s="100" t="s">
+        <v>73</v>
+      </c>
+      <c r="L18" t="s">
         <v>253</v>
       </c>
-      <c r="K18" s="100" t="s">
-        <v>73</v>
-      </c>
-      <c r="L18" t="s">
+      <c r="M18" s="18" t="s">
         <v>254</v>
       </c>
-      <c r="M18" s="18" t="s">
+      <c r="N18" t="s">
         <v>255</v>
-      </c>
-      <c r="N18" t="s">
-        <v>256</v>
       </c>
       <c r="O18" t="s">
         <v>81</v>
@@ -51067,7 +51086,7 @@
         <v>0</v>
       </c>
       <c r="AG18" s="101" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AH18" s="101">
         <v>0</v>
@@ -51103,7 +51122,7 @@
         <v>234</v>
       </c>
       <c r="AS18" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AT18" t="s">
         <v>236</v>
@@ -51115,7 +51134,7 @@
         <v>86</v>
       </c>
       <c r="AW18">
-        <f t="shared" ref="AW18:AW23" si="10">AU18/AZ18</f>
+        <f t="shared" ref="AW18:AW23" si="11">AU18/AZ18</f>
         <v>1.3627450980392156E-2</v>
       </c>
       <c r="AX18">
@@ -51128,7 +51147,7 @@
         <v>2.04</v>
       </c>
       <c r="BA18" s="102">
-        <f t="shared" ref="BA18:BA27" si="11">EXP(AU18) - 1</f>
+        <f t="shared" ref="BA18:BA27" si="12">EXP(AU18) - 1</f>
         <v>2.8190025851083211E-2</v>
       </c>
       <c r="BB18" s="102"/>
@@ -51164,13 +51183,13 @@
         <v>73</v>
       </c>
       <c r="BM18" s="101" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BN18" s="101">
         <v>0.1</v>
       </c>
       <c r="BO18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BP18" s="103" t="s">
         <v>73</v>
@@ -51244,34 +51263,34 @@
         <v>137</v>
       </c>
       <c r="E19" t="s">
-        <v>250</v>
+        <v>616</v>
       </c>
       <c r="F19" s="100">
         <v>2015</v>
       </c>
       <c r="G19" t="s">
+        <v>250</v>
+      </c>
+      <c r="H19" t="s">
         <v>251</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" s="101">
+        <v>1</v>
+      </c>
+      <c r="J19" t="s">
         <v>252</v>
       </c>
-      <c r="I19" s="101">
-        <v>1</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="K19" s="100" t="s">
+        <v>73</v>
+      </c>
+      <c r="L19" t="s">
         <v>253</v>
       </c>
-      <c r="K19" s="100" t="s">
-        <v>73</v>
-      </c>
-      <c r="L19" t="s">
+      <c r="M19" s="18" t="s">
         <v>254</v>
       </c>
-      <c r="M19" s="18" t="s">
+      <c r="N19" t="s">
         <v>255</v>
-      </c>
-      <c r="N19" t="s">
-        <v>256</v>
       </c>
       <c r="O19" t="s">
         <v>81</v>
@@ -51328,7 +51347,7 @@
         <v>0</v>
       </c>
       <c r="AG19" s="101" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AH19" s="101">
         <v>0</v>
@@ -51358,13 +51377,13 @@
         <v>0</v>
       </c>
       <c r="AQ19" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AR19" t="s">
         <v>234</v>
       </c>
       <c r="AS19" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AT19" t="s">
         <v>236</v>
@@ -51376,7 +51395,7 @@
         <v>86</v>
       </c>
       <c r="AW19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.4986225895316804E-2</v>
       </c>
       <c r="AX19">
@@ -51389,7 +51408,7 @@
         <v>3.63</v>
       </c>
       <c r="BA19" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5.590688044596992E-2</v>
       </c>
       <c r="BB19" s="102"/>
@@ -51425,13 +51444,13 @@
         <v>73</v>
       </c>
       <c r="BM19" s="101" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BN19" s="101">
         <v>0.1</v>
       </c>
       <c r="BO19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BP19" s="103" t="s">
         <v>73</v>
@@ -51493,7 +51512,7 @@
         <v>2.6660978991148553E-5</v>
       </c>
     </row>
-    <row r="20" spans="1:86" s="107" customFormat="1">
+    <row r="20" spans="1:86" s="107" customFormat="1" ht="15.6">
       <c r="A20" s="11" t="s">
         <v>68</v>
       </c>
@@ -51505,34 +51524,34 @@
         <v>137</v>
       </c>
       <c r="E20" t="s">
-        <v>250</v>
+        <v>616</v>
       </c>
       <c r="F20" s="100">
         <v>2015</v>
       </c>
       <c r="G20" t="s">
+        <v>250</v>
+      </c>
+      <c r="H20" t="s">
         <v>251</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" s="101">
+        <v>1</v>
+      </c>
+      <c r="J20" t="s">
         <v>252</v>
       </c>
-      <c r="I20" s="101">
-        <v>1</v>
-      </c>
-      <c r="J20" t="s">
-        <v>253</v>
-      </c>
       <c r="K20" s="100" t="s">
         <v>73</v>
       </c>
       <c r="L20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="M20" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="N20" t="s">
         <v>255</v>
-      </c>
-      <c r="N20" t="s">
-        <v>256</v>
       </c>
       <c r="O20" t="s">
         <v>81</v>
@@ -51589,7 +51608,7 @@
         <v>0</v>
       </c>
       <c r="AG20" s="101" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AH20" s="101">
         <v>0</v>
@@ -51625,7 +51644,7 @@
         <v>234</v>
       </c>
       <c r="AS20" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AT20" t="s">
         <v>236</v>
@@ -51637,7 +51656,7 @@
         <v>86</v>
       </c>
       <c r="AW20">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.7333333333333336E-2</v>
       </c>
       <c r="AX20">
@@ -51650,7 +51669,7 @@
         <v>3.15</v>
       </c>
       <c r="BA20" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5.6118082941604586E-2</v>
       </c>
       <c r="BB20" s="102"/>
@@ -51686,13 +51705,13 @@
         <v>73</v>
       </c>
       <c r="BM20" s="101" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BN20" s="101">
         <v>0.1</v>
       </c>
       <c r="BO20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BP20" s="103" t="s">
         <v>73</v>
@@ -51754,7 +51773,7 @@
         <v>1.4545242978283952E-5</v>
       </c>
     </row>
-    <row r="21" spans="1:86">
+    <row r="21" spans="1:86" ht="15.6">
       <c r="A21" s="11" t="s">
         <v>68</v>
       </c>
@@ -51766,34 +51785,34 @@
         <v>137</v>
       </c>
       <c r="E21" t="s">
-        <v>250</v>
+        <v>616</v>
       </c>
       <c r="F21" s="100">
         <v>2015</v>
       </c>
       <c r="G21" t="s">
+        <v>250</v>
+      </c>
+      <c r="H21" t="s">
         <v>251</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" s="101">
+        <v>1</v>
+      </c>
+      <c r="J21" t="s">
         <v>252</v>
       </c>
-      <c r="I21" s="101">
-        <v>1</v>
-      </c>
-      <c r="J21" t="s">
-        <v>253</v>
-      </c>
       <c r="K21" s="100" t="s">
         <v>73</v>
       </c>
       <c r="L21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="M21" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="N21" t="s">
         <v>255</v>
-      </c>
-      <c r="N21" t="s">
-        <v>256</v>
       </c>
       <c r="O21" t="s">
         <v>81</v>
@@ -51850,7 +51869,7 @@
         <v>0</v>
       </c>
       <c r="AG21" s="101" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AH21" s="101">
         <v>0</v>
@@ -51880,13 +51899,13 @@
         <v>0</v>
       </c>
       <c r="AQ21" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AR21" t="s">
         <v>234</v>
       </c>
       <c r="AS21" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AT21" t="s">
         <v>236</v>
@@ -51898,7 +51917,7 @@
         <v>86</v>
       </c>
       <c r="AW21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.682730923694779E-2</v>
       </c>
       <c r="AX21">
@@ -51911,7 +51930,7 @@
         <v>2.4900000000000002</v>
       </c>
       <c r="BA21" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4.2790194517186686E-2</v>
       </c>
       <c r="BB21" s="102"/>
@@ -51947,13 +51966,13 @@
         <v>73</v>
       </c>
       <c r="BM21" s="101" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BN21" s="101">
         <v>0.1</v>
       </c>
       <c r="BO21" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BP21" s="103" t="s">
         <v>73</v>
@@ -52012,7 +52031,7 @@
         <v>3.0061626333984669E-5</v>
       </c>
     </row>
-    <row r="22" spans="1:86">
+    <row r="22" spans="1:86" ht="15.6">
       <c r="A22" s="11" t="s">
         <v>68</v>
       </c>
@@ -52024,16 +52043,16 @@
         <v>138</v>
       </c>
       <c r="E22" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F22" s="100">
         <v>1988</v>
       </c>
       <c r="G22" t="s">
+        <v>263</v>
+      </c>
+      <c r="H22" t="s">
         <v>264</v>
-      </c>
-      <c r="H22" t="s">
-        <v>265</v>
       </c>
       <c r="I22" s="101">
         <v>1</v>
@@ -52051,7 +52070,7 @@
         <v>93</v>
       </c>
       <c r="N22" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O22" t="s">
         <v>81</v>
@@ -52063,7 +52082,7 @@
         <v>229</v>
       </c>
       <c r="R22" s="32" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -52108,7 +52127,7 @@
         <v>0</v>
       </c>
       <c r="AG22" s="101" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AH22" s="101">
         <v>0</v>
@@ -52144,7 +52163,7 @@
         <v>234</v>
       </c>
       <c r="AS22" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AT22" t="s">
         <v>236</v>
@@ -52156,7 +52175,7 @@
         <v>86</v>
       </c>
       <c r="AW22">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.3478260869565216E-2</v>
       </c>
       <c r="AX22">
@@ -52169,7 +52188,7 @@
         <v>0.23</v>
       </c>
       <c r="BA22" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.0050167084167949E-2</v>
       </c>
       <c r="BB22" s="102"/>
@@ -52212,7 +52231,7 @@
         <v>1</v>
       </c>
       <c r="BO22" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BP22" s="103" t="s">
         <v>73</v>
@@ -52271,7 +52290,7 @@
         <v>1.953125E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:86">
+    <row r="23" spans="1:86" ht="15.6">
       <c r="A23" s="11" t="s">
         <v>68</v>
       </c>
@@ -52283,16 +52302,16 @@
         <v>138</v>
       </c>
       <c r="E23" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F23" s="100">
         <v>1988</v>
       </c>
       <c r="G23" t="s">
+        <v>263</v>
+      </c>
+      <c r="H23" t="s">
         <v>264</v>
-      </c>
-      <c r="H23" t="s">
-        <v>265</v>
       </c>
       <c r="I23" s="101">
         <v>1</v>
@@ -52310,7 +52329,7 @@
         <v>93</v>
       </c>
       <c r="N23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O23" t="s">
         <v>81</v>
@@ -52322,7 +52341,7 @@
         <v>229</v>
       </c>
       <c r="R23" s="32" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -52367,7 +52386,7 @@
         <v>0</v>
       </c>
       <c r="AG23" s="101" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AH23" s="101">
         <v>0</v>
@@ -52397,13 +52416,13 @@
         <v>0</v>
       </c>
       <c r="AQ23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AR23" t="s">
         <v>234</v>
       </c>
       <c r="AS23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AT23" t="s">
         <v>236</v>
@@ -52415,7 +52434,7 @@
         <v>86</v>
       </c>
       <c r="AW23">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.4844720496894408E-2</v>
       </c>
       <c r="AX23">
@@ -52428,7 +52447,7 @@
         <v>4.83</v>
       </c>
       <c r="BA23" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.12749685157937574</v>
       </c>
       <c r="BB23" s="102"/>
@@ -52471,7 +52490,7 @@
         <v>1</v>
       </c>
       <c r="BO23" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BP23" s="103" t="s">
         <v>73</v>
@@ -52530,7 +52549,7 @@
         <v>1.953125E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:86">
+    <row r="24" spans="1:86" ht="15.6">
       <c r="A24" s="11" t="s">
         <v>68</v>
       </c>
@@ -52542,16 +52561,16 @@
         <v>139</v>
       </c>
       <c r="E24" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F24" s="100">
         <v>2013</v>
       </c>
       <c r="G24" t="s">
+        <v>270</v>
+      </c>
+      <c r="H24" s="123" t="s">
         <v>271</v>
-      </c>
-      <c r="H24" s="123" t="s">
-        <v>272</v>
       </c>
       <c r="I24" s="101">
         <v>1</v>
@@ -52572,7 +52591,7 @@
         <v>227</v>
       </c>
       <c r="O24" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P24" t="s">
         <v>228</v>
@@ -52626,7 +52645,7 @@
         <v>0</v>
       </c>
       <c r="AG24" s="101" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AH24" s="101">
         <v>0</v>
@@ -52662,7 +52681,7 @@
         <v>234</v>
       </c>
       <c r="AS24" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AT24" t="s">
         <v>236</v>
@@ -52683,11 +52702,11 @@
         <v>1</v>
       </c>
       <c r="AZ24">
-        <f t="shared" ref="AZ24:AZ30" si="12">AU24/AW24</f>
+        <f t="shared" ref="AZ24:AZ30" si="13">AU24/AW24</f>
         <v>20.342105263157897</v>
       </c>
       <c r="BA24" s="109">
-        <f t="shared" si="11"/>
+        <f>EXP(AU24) - 1</f>
         <v>1.1662552812206535</v>
       </c>
       <c r="BB24" s="109"/>
@@ -52799,16 +52818,16 @@
         <v>139</v>
       </c>
       <c r="E25" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F25" s="100">
         <v>2013</v>
       </c>
       <c r="G25" t="s">
+        <v>270</v>
+      </c>
+      <c r="H25" t="s">
         <v>271</v>
-      </c>
-      <c r="H25" t="s">
-        <v>272</v>
       </c>
       <c r="I25" s="101">
         <v>1</v>
@@ -52823,13 +52842,13 @@
         <v>283</v>
       </c>
       <c r="M25" s="18" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="N25" t="s">
         <v>227</v>
       </c>
       <c r="O25" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P25" t="s">
         <v>228</v>
@@ -52883,7 +52902,7 @@
         <v>0</v>
       </c>
       <c r="AG25" s="101" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AH25" s="101">
         <v>0</v>
@@ -52919,7 +52938,7 @@
         <v>234</v>
       </c>
       <c r="AS25" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AT25" t="s">
         <v>236</v>
@@ -52940,11 +52959,11 @@
         <v>1</v>
       </c>
       <c r="AZ25">
+        <f t="shared" si="13"/>
+        <v>13.770491803278688</v>
+      </c>
+      <c r="BA25" s="109">
         <f t="shared" si="12"/>
-        <v>13.770491803278688</v>
-      </c>
-      <c r="BA25" s="109">
-        <f t="shared" si="11"/>
         <v>1.3163669767810915</v>
       </c>
       <c r="BB25" s="109"/>
@@ -53044,7 +53063,7 @@
         <v>4.1152263374485596E-4</v>
       </c>
     </row>
-    <row r="26" spans="1:86">
+    <row r="26" spans="1:86" ht="15.6">
       <c r="A26" s="11" t="s">
         <v>68</v>
       </c>
@@ -53056,16 +53075,16 @@
         <v>139</v>
       </c>
       <c r="E26" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F26" s="100">
         <v>2013</v>
       </c>
       <c r="G26" t="s">
+        <v>270</v>
+      </c>
+      <c r="H26" t="s">
         <v>271</v>
-      </c>
-      <c r="H26" t="s">
-        <v>272</v>
       </c>
       <c r="I26" s="101">
         <v>1</v>
@@ -53086,7 +53105,7 @@
         <v>227</v>
       </c>
       <c r="O26" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P26" t="s">
         <v>228</v>
@@ -53140,7 +53159,7 @@
         <v>0</v>
       </c>
       <c r="AG26" s="101" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AH26" s="101">
         <v>0</v>
@@ -53176,7 +53195,7 @@
         <v>234</v>
       </c>
       <c r="AS26" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AT26" t="s">
         <v>236</v>
@@ -53197,11 +53216,11 @@
         <v>2</v>
       </c>
       <c r="AZ26">
+        <f t="shared" si="13"/>
+        <v>0.36666666666666664</v>
+      </c>
+      <c r="BA26" s="102">
         <f t="shared" si="12"/>
-        <v>0.36666666666666664</v>
-      </c>
-      <c r="BA26" s="102">
-        <f t="shared" si="11"/>
         <v>1.1060722444719451E-2</v>
       </c>
       <c r="BB26" s="102"/>
@@ -53301,7 +53320,7 @@
         <v>4.0950040950040953E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:86">
+    <row r="27" spans="1:86" ht="15.6">
       <c r="A27" s="11" t="s">
         <v>68</v>
       </c>
@@ -53313,16 +53332,16 @@
         <v>139</v>
       </c>
       <c r="E27" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F27" s="100">
         <v>2013</v>
       </c>
       <c r="G27" t="s">
+        <v>270</v>
+      </c>
+      <c r="H27" t="s">
         <v>271</v>
-      </c>
-      <c r="H27" t="s">
-        <v>272</v>
       </c>
       <c r="I27" s="101">
         <v>1</v>
@@ -53337,13 +53356,13 @@
         <v>283</v>
       </c>
       <c r="M27" s="18" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="N27" t="s">
         <v>227</v>
       </c>
       <c r="O27" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P27" t="s">
         <v>228</v>
@@ -53397,7 +53416,7 @@
         <v>0</v>
       </c>
       <c r="AG27" s="101" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AH27" s="101">
         <v>0</v>
@@ -53433,7 +53452,7 @@
         <v>234</v>
       </c>
       <c r="AS27" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AT27" t="s">
         <v>236</v>
@@ -53454,11 +53473,11 @@
         <v>1</v>
       </c>
       <c r="AZ27">
+        <f t="shared" si="13"/>
+        <v>1.6964285714285714</v>
+      </c>
+      <c r="BA27" s="102">
         <f t="shared" si="12"/>
-        <v>1.6964285714285714</v>
-      </c>
-      <c r="BA27" s="102">
-        <f t="shared" si="11"/>
         <v>9.9658855126102841E-2</v>
       </c>
       <c r="BB27" s="102"/>
@@ -53558,7 +53577,7 @@
         <v>4.1152263374485596E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:86">
+    <row r="28" spans="1:86" ht="15.6">
       <c r="A28" s="94" t="s">
         <v>68</v>
       </c>
@@ -53570,16 +53589,16 @@
         <v>140</v>
       </c>
       <c r="E28" s="94" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F28" s="94">
         <v>2016</v>
       </c>
       <c r="G28" s="58" t="s">
+        <v>279</v>
+      </c>
+      <c r="H28" s="94" t="s">
         <v>280</v>
-      </c>
-      <c r="H28" s="94" t="s">
-        <v>281</v>
       </c>
       <c r="I28" s="94">
         <v>1</v>
@@ -53606,10 +53625,10 @@
         <v>242</v>
       </c>
       <c r="Q28" s="94" t="s">
+        <v>281</v>
+      </c>
+      <c r="R28" s="94" t="s">
         <v>282</v>
-      </c>
-      <c r="R28" s="94" t="s">
-        <v>283</v>
       </c>
       <c r="S28" s="94">
         <v>0</v>
@@ -53621,76 +53640,76 @@
         <v>0</v>
       </c>
       <c r="V28" s="94" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="W28" s="94" t="s">
         <v>232</v>
       </c>
       <c r="X28" s="94" t="s">
+        <v>284</v>
+      </c>
+      <c r="Y28" s="94">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="94">
+        <v>1</v>
+      </c>
+      <c r="AG28" s="94" t="s">
         <v>285</v>
       </c>
-      <c r="Y28" s="94">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AC28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AD28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AE28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AF28" s="94">
-        <v>1</v>
-      </c>
-      <c r="AG28" s="94" t="s">
+      <c r="AH28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="94">
+        <v>1</v>
+      </c>
+      <c r="AP28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="94" t="s">
         <v>286</v>
-      </c>
-      <c r="AH28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AI28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AJ28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AK28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AL28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AM28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AN28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AO28" s="94">
-        <v>1</v>
-      </c>
-      <c r="AP28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AQ28" s="94" t="s">
-        <v>287</v>
       </c>
       <c r="AR28" s="94" t="s">
         <v>234</v>
       </c>
       <c r="AS28" s="94" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AT28" s="41" t="s">
         <v>236</v>
@@ -53711,12 +53730,12 @@
         <v>2</v>
       </c>
       <c r="AZ28" s="94">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.6066610455311974</v>
       </c>
       <c r="BA28" s="114">
-        <f>(EXP(AU28)-1)</f>
-        <v>44.19561188793142</v>
+        <f>AU28*AW28*SQRT(BI28)*0.25/100</f>
+        <v>0.39790050382451009</v>
       </c>
       <c r="BB28" s="114"/>
       <c r="BC28" s="94" t="s">
@@ -53818,7 +53837,7 @@
         <v>3.2573289902280132E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:86">
+    <row r="29" spans="1:86" ht="15.6">
       <c r="A29" s="94" t="s">
         <v>68</v>
       </c>
@@ -53830,16 +53849,16 @@
         <v>140</v>
       </c>
       <c r="E29" s="94" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F29" s="94">
         <v>2016</v>
       </c>
       <c r="G29" s="58" t="s">
+        <v>279</v>
+      </c>
+      <c r="H29" s="94" t="s">
         <v>280</v>
-      </c>
-      <c r="H29" s="94" t="s">
-        <v>281</v>
       </c>
       <c r="I29" s="94">
         <v>1</v>
@@ -53866,10 +53885,10 @@
         <v>242</v>
       </c>
       <c r="Q29" s="94" t="s">
+        <v>281</v>
+      </c>
+      <c r="R29" s="94" t="s">
         <v>282</v>
-      </c>
-      <c r="R29" s="94" t="s">
-        <v>283</v>
       </c>
       <c r="S29" s="94">
         <v>0</v>
@@ -53881,41 +53900,41 @@
         <v>0</v>
       </c>
       <c r="V29" s="94" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="W29" s="94" t="s">
         <v>232</v>
       </c>
       <c r="X29" s="94" t="s">
+        <v>284</v>
+      </c>
+      <c r="Y29" s="94">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="94">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="94">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="94">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="94">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="94">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="94">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="94">
+        <v>1</v>
+      </c>
+      <c r="AG29" s="94" t="s">
         <v>285</v>
       </c>
-      <c r="Y29" s="94">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="94">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="94">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="94">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="94">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="94">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="94">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="94">
-        <v>1</v>
-      </c>
-      <c r="AG29" s="94" t="s">
-        <v>286</v>
-      </c>
       <c r="AH29" s="94">
         <v>0</v>
       </c>
@@ -53944,13 +53963,13 @@
         <v>0</v>
       </c>
       <c r="AQ29" s="94" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AR29" s="94" t="s">
         <v>234</v>
       </c>
       <c r="AS29" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AT29" s="41" t="s">
         <v>236</v>
@@ -53971,12 +53990,12 @@
         <v>2</v>
       </c>
       <c r="AZ29" s="94">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.67517730496453898</v>
       </c>
       <c r="BA29" s="114">
-        <f>(EXP(AU29)-1)</f>
-        <v>5.7126915785915049</v>
+        <f t="shared" ref="BA29:BA30" si="14">AU29*AW29*SQRT(BI29)*0.25/100</f>
+        <v>0.23633982409742121</v>
       </c>
       <c r="BB29" s="114"/>
       <c r="BC29" s="94" t="s">
@@ -54078,7 +54097,7 @@
         <v>3.2573289902280132E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:86">
+    <row r="30" spans="1:86" ht="15.6">
       <c r="A30" s="94" t="s">
         <v>68</v>
       </c>
@@ -54090,16 +54109,16 @@
         <v>140</v>
       </c>
       <c r="E30" s="94" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F30" s="94">
         <v>2016</v>
       </c>
       <c r="G30" s="58" t="s">
+        <v>279</v>
+      </c>
+      <c r="H30" s="94" t="s">
         <v>280</v>
-      </c>
-      <c r="H30" s="94" t="s">
-        <v>281</v>
       </c>
       <c r="I30" s="94">
         <v>1</v>
@@ -54126,10 +54145,10 @@
         <v>242</v>
       </c>
       <c r="Q30" s="94" t="s">
+        <v>281</v>
+      </c>
+      <c r="R30" s="94" t="s">
         <v>282</v>
-      </c>
-      <c r="R30" s="94" t="s">
-        <v>283</v>
       </c>
       <c r="S30" s="94">
         <v>0</v>
@@ -54141,41 +54160,41 @@
         <v>0</v>
       </c>
       <c r="V30" s="94" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="W30" s="94" t="s">
         <v>232</v>
       </c>
       <c r="X30" s="94" t="s">
+        <v>284</v>
+      </c>
+      <c r="Y30" s="94">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="94">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="94">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="94">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="94">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="94">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="94">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="94">
+        <v>1</v>
+      </c>
+      <c r="AG30" s="94" t="s">
         <v>285</v>
       </c>
-      <c r="Y30" s="94">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="94">
-        <v>0</v>
-      </c>
-      <c r="AA30" s="94">
-        <v>0</v>
-      </c>
-      <c r="AB30" s="94">
-        <v>0</v>
-      </c>
-      <c r="AC30" s="94">
-        <v>0</v>
-      </c>
-      <c r="AD30" s="94">
-        <v>0</v>
-      </c>
-      <c r="AE30" s="94">
-        <v>0</v>
-      </c>
-      <c r="AF30" s="94">
-        <v>1</v>
-      </c>
-      <c r="AG30" s="94" t="s">
-        <v>286</v>
-      </c>
       <c r="AH30" s="94">
         <v>0</v>
       </c>
@@ -54204,13 +54223,13 @@
         <v>0</v>
       </c>
       <c r="AQ30" s="94" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AR30" s="94" t="s">
         <v>234</v>
       </c>
       <c r="AS30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AT30" s="41" t="s">
         <v>236</v>
@@ -54231,12 +54250,12 @@
         <v>1</v>
       </c>
       <c r="AZ30" s="94">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.9500875656742556</v>
       </c>
       <c r="BA30" s="114">
-        <f>(EXP(AU30)-1)</f>
-        <v>796.11582942023051</v>
+        <f t="shared" si="14"/>
+        <v>1.0075107436727511</v>
       </c>
       <c r="BB30" s="114"/>
       <c r="BC30" s="94" t="s">
@@ -54338,7 +54357,7 @@
         <v>3.2573289902280132E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:86">
+    <row r="31" spans="1:86" ht="15.6">
       <c r="A31" s="94" t="s">
         <v>68</v>
       </c>
@@ -54350,13 +54369,13 @@
         <v>148</v>
       </c>
       <c r="E31" s="96" t="s">
-        <v>291</v>
+        <v>619</v>
       </c>
       <c r="F31" s="94">
         <v>2016</v>
       </c>
       <c r="G31" s="97" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H31" s="94" t="s">
         <v>177</v>
@@ -54377,7 +54396,7 @@
         <v>93</v>
       </c>
       <c r="N31" s="94" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O31" s="94" t="s">
         <v>81</v>
@@ -54401,7 +54420,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="94" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="W31" s="94" t="s">
         <v>232</v>
@@ -54464,13 +54483,13 @@
         <v>0</v>
       </c>
       <c r="AQ31" s="94" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AR31" s="94" t="s">
         <v>234</v>
       </c>
       <c r="AS31" s="94" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AT31" s="94" t="s">
         <v>236</v>
@@ -54529,13 +54548,13 @@
         <v>73</v>
       </c>
       <c r="BM31" s="94" t="s">
+        <v>295</v>
+      </c>
+      <c r="BN31" t="s">
+        <v>73</v>
+      </c>
+      <c r="BO31" t="s">
         <v>296</v>
-      </c>
-      <c r="BN31" t="s">
-        <v>73</v>
-      </c>
-      <c r="BO31" t="s">
-        <v>297</v>
       </c>
       <c r="BP31" s="94" t="s">
         <v>73</v>
@@ -54597,7 +54616,7 @@
         <v>7.1839080459770114E-5</v>
       </c>
     </row>
-    <row r="32" spans="1:86">
+    <row r="32" spans="1:86" ht="15.6">
       <c r="A32" t="s">
         <v>68</v>
       </c>
@@ -54608,7 +54627,7 @@
         <v>150</v>
       </c>
       <c r="E32" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F32">
         <v>2014</v>
@@ -54635,7 +54654,7 @@
         <v>120</v>
       </c>
       <c r="N32" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O32" t="s">
         <v>131</v>
@@ -54647,7 +54666,7 @@
         <v>229</v>
       </c>
       <c r="R32" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -54722,7 +54741,7 @@
         <v>0</v>
       </c>
       <c r="AQ32" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AR32" t="s">
         <v>234</v>
@@ -54752,8 +54771,8 @@
         <f>AU32/AW32</f>
         <v>16.285714285714288</v>
       </c>
-      <c r="BA32" s="111" t="s">
-        <v>73</v>
+      <c r="BA32" s="124">
+        <v>0.08</v>
       </c>
       <c r="BB32" s="111"/>
       <c r="BC32" s="94" t="s">
@@ -54787,13 +54806,13 @@
         <v>73</v>
       </c>
       <c r="BM32" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="BN32" t="s">
         <v>73</v>
       </c>
       <c r="BO32" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BP32" t="s">
         <v>73</v>
@@ -54852,7 +54871,7 @@
         <v>1.0448480111840532E-6</v>
       </c>
     </row>
-    <row r="33" spans="1:86">
+    <row r="33" spans="1:86" ht="15.6">
       <c r="A33" t="s">
         <v>68</v>
       </c>
@@ -54863,7 +54882,7 @@
         <v>150</v>
       </c>
       <c r="E33" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F33">
         <v>2014</v>
@@ -54890,7 +54909,7 @@
         <v>120</v>
       </c>
       <c r="N33" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O33" t="s">
         <v>131</v>
@@ -54902,7 +54921,7 @@
         <v>229</v>
       </c>
       <c r="R33" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -54977,7 +54996,7 @@
         <v>0</v>
       </c>
       <c r="AQ33" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AR33" t="s">
         <v>234</v>
@@ -55007,8 +55026,8 @@
         <f>AU33/AW33</f>
         <v>15.866666666666667</v>
       </c>
-      <c r="BA33" s="111" t="s">
-        <v>73</v>
+      <c r="BA33" s="124">
+        <v>0.08</v>
       </c>
       <c r="BB33" s="111"/>
       <c r="BC33" s="94" t="s">
@@ -55042,13 +55061,13 @@
         <v>73</v>
       </c>
       <c r="BM33" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="BN33" t="s">
         <v>73</v>
       </c>
       <c r="BO33" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BP33" t="s">
         <v>73</v>
@@ -55107,7 +55126,7 @@
         <v>1.0448480111840532E-6</v>
       </c>
     </row>
-    <row r="34" spans="1:86">
+    <row r="34" spans="1:86" ht="15.6">
       <c r="A34" t="s">
         <v>68</v>
       </c>
@@ -55118,7 +55137,7 @@
         <v>150</v>
       </c>
       <c r="E34" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F34">
         <v>2014</v>
@@ -55145,7 +55164,7 @@
         <v>120</v>
       </c>
       <c r="N34" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O34" t="s">
         <v>131</v>
@@ -55157,7 +55176,7 @@
         <v>229</v>
       </c>
       <c r="R34" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -55232,7 +55251,7 @@
         <v>0</v>
       </c>
       <c r="AQ34" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AR34" t="s">
         <v>234</v>
@@ -55262,8 +55281,8 @@
         <f>AU34/AW34</f>
         <v>1.1666666666666667</v>
       </c>
-      <c r="BA34" s="111" t="s">
-        <v>73</v>
+      <c r="BA34" s="124">
+        <v>0.02</v>
       </c>
       <c r="BB34" s="111"/>
       <c r="BC34" s="94" t="s">
@@ -55297,13 +55316,13 @@
         <v>73</v>
       </c>
       <c r="BM34" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="BN34" t="s">
         <v>73</v>
       </c>
       <c r="BO34" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BP34" t="s">
         <v>73</v>
@@ -55362,7 +55381,7 @@
         <v>1.0448480111840532E-6</v>
       </c>
     </row>
-    <row r="35" spans="1:86">
+    <row r="35" spans="1:86" ht="15.6">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -55373,7 +55392,7 @@
         <v>150</v>
       </c>
       <c r="E35" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F35">
         <v>2014</v>
@@ -55400,7 +55419,7 @@
         <v>120</v>
       </c>
       <c r="N35" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O35" t="s">
         <v>131</v>
@@ -55412,7 +55431,7 @@
         <v>229</v>
       </c>
       <c r="R35" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -55487,7 +55506,7 @@
         <v>0</v>
       </c>
       <c r="AQ35" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AR35" t="s">
         <v>234</v>
@@ -55517,8 +55536,8 @@
         <f>AU35/AW35</f>
         <v>0.92307692307692302</v>
       </c>
-      <c r="BA35" s="111" t="s">
-        <v>73</v>
+      <c r="BA35" s="124">
+        <v>0.02</v>
       </c>
       <c r="BB35" s="111"/>
       <c r="BC35" s="94" t="s">
@@ -55552,13 +55571,13 @@
         <v>73</v>
       </c>
       <c r="BM35" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="BN35" t="s">
         <v>73</v>
       </c>
       <c r="BO35" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BP35" t="s">
         <v>73</v>
@@ -55619,7 +55638,7 @@
     </row>
     <row r="36" spans="1:86" ht="18" customHeight="1">
       <c r="A36" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C36" s="106">
         <v>3049</v>
@@ -55628,16 +55647,16 @@
         <v>313</v>
       </c>
       <c r="E36" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F36">
         <v>2014</v>
       </c>
       <c r="G36" t="s">
+        <v>302</v>
+      </c>
+      <c r="H36" t="s">
         <v>303</v>
-      </c>
-      <c r="H36" t="s">
-        <v>304</v>
       </c>
       <c r="I36">
         <v>1</v>
@@ -55646,7 +55665,7 @@
         <v>2013</v>
       </c>
       <c r="K36" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L36">
         <v>514</v>
@@ -55658,7 +55677,7 @@
         <v>227</v>
       </c>
       <c r="O36" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P36" s="18" t="s">
         <v>242</v>
@@ -55667,7 +55686,7 @@
         <v>229</v>
       </c>
       <c r="R36" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="S36">
         <v>1</v>
@@ -55682,10 +55701,10 @@
         <v>232</v>
       </c>
       <c r="W36" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="X36" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Y36">
         <v>0</v>
@@ -55748,7 +55767,7 @@
         <v>234</v>
       </c>
       <c r="AS36" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AT36" t="s">
         <v>73</v>
@@ -55772,8 +55791,9 @@
         <f>TINV(AX36,CC36)</f>
         <v>1.965942323976257</v>
       </c>
-      <c r="BA36" t="s">
-        <v>73</v>
+      <c r="BA36" s="102">
+        <f t="shared" ref="BA36:BA37" si="15">EXP(AU36) - 1</f>
+        <v>0.1664908867784396</v>
       </c>
       <c r="BC36" t="s">
         <v>73</v>
@@ -55782,7 +55802,7 @@
         <v>73</v>
       </c>
       <c r="BE36" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="BF36" t="s">
         <v>73</v>
@@ -55806,7 +55826,7 @@
         <v>73</v>
       </c>
       <c r="BM36" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="BN36" t="s">
         <v>73</v>
@@ -55877,7 +55897,7 @@
     </row>
     <row r="37" spans="1:86" ht="18" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C37" s="106">
         <v>3050</v>
@@ -55886,16 +55906,16 @@
         <v>313</v>
       </c>
       <c r="E37" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F37">
         <v>2014</v>
       </c>
       <c r="G37" t="s">
+        <v>302</v>
+      </c>
+      <c r="H37" t="s">
         <v>303</v>
-      </c>
-      <c r="H37" t="s">
-        <v>304</v>
       </c>
       <c r="I37">
         <v>1</v>
@@ -55904,7 +55924,7 @@
         <v>2013</v>
       </c>
       <c r="K37" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L37">
         <v>514</v>
@@ -55916,7 +55936,7 @@
         <v>227</v>
       </c>
       <c r="O37" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P37" s="18" t="s">
         <v>242</v>
@@ -55925,7 +55945,7 @@
         <v>229</v>
       </c>
       <c r="R37" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="S37">
         <v>1</v>
@@ -55940,10 +55960,10 @@
         <v>232</v>
       </c>
       <c r="W37" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="X37" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Y37">
         <v>0</v>
@@ -56006,7 +56026,7 @@
         <v>234</v>
       </c>
       <c r="AS37" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AT37" t="s">
         <v>73</v>
@@ -56030,8 +56050,9 @@
         <f>TINV(AX37,CC37)</f>
         <v>2.5882384049343825</v>
       </c>
-      <c r="BA37" t="s">
-        <v>73</v>
+      <c r="BA37" s="102">
+        <f t="shared" si="15"/>
+        <v>0.32710516181715721</v>
       </c>
       <c r="BC37" t="s">
         <v>73</v>
@@ -56040,7 +56061,7 @@
         <v>73</v>
       </c>
       <c r="BE37" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="BF37" t="s">
         <v>73</v>
@@ -56064,7 +56085,7 @@
         <v>73</v>
       </c>
       <c r="BM37" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="BN37" t="s">
         <v>73</v>
@@ -56133,43 +56154,43 @@
         <v>2.5188916876574307E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:86">
+    <row r="38" spans="1:86" ht="15.6">
       <c r="M38" s="18"/>
     </row>
-    <row r="39" spans="1:86">
+    <row r="39" spans="1:86" ht="15.6">
       <c r="M39" s="18"/>
     </row>
-    <row r="40" spans="1:86">
+    <row r="40" spans="1:86" ht="15.6">
       <c r="M40" s="18"/>
     </row>
-    <row r="41" spans="1:86">
+    <row r="41" spans="1:86" ht="15.6">
       <c r="M41" s="18"/>
     </row>
-    <row r="42" spans="1:86">
+    <row r="42" spans="1:86" ht="15.6">
       <c r="M42" s="18"/>
     </row>
-    <row r="43" spans="1:86">
+    <row r="43" spans="1:86" ht="15.6">
       <c r="M43" s="18"/>
     </row>
-    <row r="44" spans="1:86">
+    <row r="44" spans="1:86" ht="15.6">
       <c r="M44" s="18"/>
     </row>
-    <row r="45" spans="1:86">
+    <row r="45" spans="1:86" ht="15.6">
       <c r="M45" s="18"/>
     </row>
-    <row r="46" spans="1:86">
+    <row r="46" spans="1:86" ht="15.6">
       <c r="M46" s="18"/>
     </row>
     <row r="47" spans="1:86" ht="15.75" customHeight="1">
       <c r="M47" s="18"/>
       <c r="BX47" s="30"/>
     </row>
-    <row r="48" spans="1:86">
+    <row r="48" spans="1:86" ht="15.6">
       <c r="M48" s="18"/>
       <c r="BA48" s="117"/>
       <c r="BB48" s="117"/>
     </row>
-    <row r="49" spans="13:54">
+    <row r="49" spans="13:54" ht="15.6">
       <c r="M49" s="18"/>
       <c r="BA49" s="117"/>
       <c r="BB49" s="117"/>
@@ -56177,7 +56198,7 @@
     <row r="50" spans="13:54" ht="15.75" customHeight="1">
       <c r="M50" s="18"/>
     </row>
-    <row r="51" spans="13:54">
+    <row r="51" spans="13:54" ht="15.6">
       <c r="M51" s="18"/>
       <c r="BA51" s="118"/>
       <c r="BB51" s="118"/>
@@ -56188,7 +56209,7 @@
     <sortCondition ref="C2:C51"/>
   </sortState>
   <dataConsolidate/>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <conditionalFormatting sqref="AU1:AU1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>1</formula>
@@ -56351,70 +56372,70 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BJ18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="28.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.8984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.09765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.8984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.8984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.59765625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="30" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="28.125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.59765625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.09765625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="28.09765625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.09765625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.59765625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="15" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.3984375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.8984375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.8984375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.59765625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="11" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="22.625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="23.8984375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18.8984375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="22.59765625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.8984375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.09765625" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="17" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="18.8984375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="36.3984375" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="29" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="21.875" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="17.8984375" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="21.8984375" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="20.09765625" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="15" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="21.8984375" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="29.625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="23.8984375" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="17.09765625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="29.59765625" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="33" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="35.5" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.875" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="24.375" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="25.875" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.8984375" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="24.3984375" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="17.8984375" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="25.8984375" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="35" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="26.375" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="26.3984375" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.3984375" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="15.59765625" bestFit="1" customWidth="1"/>
     <col min="63" max="64" width="18.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -56431,200 +56452,200 @@
         <v>198</v>
       </c>
       <c r="B2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:62">
       <c r="A4" s="119" t="s">
+        <v>311</v>
+      </c>
+      <c r="B4" t="s">
         <v>312</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>313</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>314</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>315</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>316</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>317</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>318</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>319</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>320</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>321</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>322</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>323</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>324</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>325</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>326</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>327</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>328</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>329</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>330</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>331</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>332</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>333</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>334</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>335</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>336</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>337</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>338</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>339</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>340</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>341</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>342</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AG4" t="s">
         <v>343</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AH4" t="s">
         <v>344</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AI4" t="s">
         <v>345</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AJ4" t="s">
         <v>346</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AK4" t="s">
         <v>347</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AL4" t="s">
         <v>348</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AM4" t="s">
         <v>349</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AN4" t="s">
         <v>350</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AO4" t="s">
         <v>351</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AP4" t="s">
         <v>352</v>
       </c>
-      <c r="AP4" t="s">
+      <c r="AQ4" t="s">
         <v>353</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="AR4" t="s">
         <v>354</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="AS4" t="s">
         <v>355</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AT4" t="s">
         <v>356</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AU4" t="s">
         <v>357</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AV4" t="s">
         <v>358</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AW4" t="s">
         <v>359</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AX4" t="s">
         <v>360</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="AY4" t="s">
         <v>361</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="AZ4" t="s">
         <v>362</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="BA4" t="s">
         <v>363</v>
       </c>
-      <c r="BA4" t="s">
+      <c r="BB4" t="s">
         <v>364</v>
       </c>
-      <c r="BB4" t="s">
+      <c r="BC4" t="s">
         <v>365</v>
       </c>
-      <c r="BC4" t="s">
+      <c r="BD4" t="s">
         <v>366</v>
       </c>
-      <c r="BD4" t="s">
+      <c r="BE4" t="s">
         <v>367</v>
       </c>
-      <c r="BE4" t="s">
+      <c r="BF4" t="s">
         <v>368</v>
       </c>
-      <c r="BF4" t="s">
+      <c r="BG4" t="s">
         <v>369</v>
       </c>
-      <c r="BG4" t="s">
+      <c r="BH4" t="s">
         <v>370</v>
       </c>
-      <c r="BH4" t="s">
+      <c r="BI4" t="s">
         <v>371</v>
       </c>
-      <c r="BI4" t="s">
+      <c r="BJ4" t="s">
         <v>372</v>
-      </c>
-      <c r="BJ4" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="5" spans="1:62">
       <c r="A5" s="120" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -56994,7 +57015,7 @@
     </row>
     <row r="7" spans="1:62">
       <c r="A7" s="120" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -57558,7 +57579,7 @@
     </row>
     <row r="10" spans="1:62">
       <c r="A10" s="120" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B10">
         <v>23</v>
@@ -57746,7 +57767,7 @@
     </row>
     <row r="11" spans="1:62">
       <c r="A11" s="120" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -57934,7 +57955,7 @@
     </row>
     <row r="12" spans="1:62">
       <c r="A12" s="120" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -58122,7 +58143,7 @@
     </row>
     <row r="13" spans="1:62">
       <c r="A13" s="120" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B13">
         <v>6</v>
@@ -58310,7 +58331,7 @@
     </row>
     <row r="14" spans="1:62">
       <c r="A14" s="120" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B14">
         <v>6</v>
@@ -58498,7 +58519,7 @@
     </row>
     <row r="15" spans="1:62">
       <c r="A15" s="120" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -58686,7 +58707,7 @@
     </row>
     <row r="16" spans="1:62">
       <c r="A16" s="120" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B16">
         <v>22</v>
@@ -59062,7 +59083,7 @@
     </row>
     <row r="18" spans="1:62">
       <c r="A18" s="120" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B18">
         <v>144</v>
@@ -59256,26 +59277,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S99"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
     <col min="3" max="3" width="15.5" customWidth="1"/>
-    <col min="5" max="5" width="19.625" customWidth="1"/>
+    <col min="5" max="5" width="19.59765625" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="18.125" style="26" customWidth="1"/>
+    <col min="7" max="7" width="18.09765625" style="26" customWidth="1"/>
     <col min="8" max="8" width="20.5" customWidth="1"/>
-    <col min="9" max="9" width="14.125" customWidth="1"/>
-    <col min="10" max="10" width="15.125" customWidth="1"/>
+    <col min="9" max="9" width="14.09765625" customWidth="1"/>
+    <col min="10" max="10" width="15.09765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B1" t="s">
         <v>189</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D1" t="s">
         <v>10</v>
@@ -59287,7 +59308,7 @@
         <v>9</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1" s="38" t="s">
         <v>186</v>
@@ -59299,7 +59320,7 @@
         <v>7</v>
       </c>
       <c r="K1" s="39" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L1" s="39" t="s">
         <v>187</v>
@@ -59323,7 +59344,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="31.5">
+    <row r="2" spans="1:19" ht="31.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -59331,7 +59352,7 @@
         <v>189</v>
       </c>
       <c r="C2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D2" t="s">
         <v>112</v>
@@ -59343,22 +59364,22 @@
         <v>93</v>
       </c>
       <c r="G2" s="26" t="s">
+        <v>387</v>
+      </c>
+      <c r="H2" t="s">
         <v>388</v>
-      </c>
-      <c r="H2" t="s">
-        <v>389</v>
       </c>
       <c r="I2" t="s">
         <v>80</v>
       </c>
       <c r="J2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="K2" t="s">
         <v>232</v>
       </c>
       <c r="L2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="M2" t="s">
         <v>242</v>
@@ -59367,75 +59388,75 @@
         <v>81</v>
       </c>
       <c r="O2" t="s">
+        <v>391</v>
+      </c>
+      <c r="P2" s="41" t="s">
         <v>392</v>
       </c>
-      <c r="P2" s="41" t="s">
+      <c r="R2" s="47" t="s">
+        <v>617</v>
+      </c>
+      <c r="S2" s="47" t="s">
         <v>393</v>
       </c>
-      <c r="R2" s="47" t="s">
+    </row>
+    <row r="3" spans="1:19" ht="31.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>394</v>
       </c>
-      <c r="S2" s="47" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="31.5">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>396</v>
-      </c>
       <c r="C3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I3" t="s">
         <v>86</v>
       </c>
       <c r="J3" t="s">
+        <v>396</v>
+      </c>
+      <c r="K3" t="s">
+        <v>283</v>
+      </c>
+      <c r="L3" t="s">
+        <v>397</v>
+      </c>
+      <c r="M3" t="s">
         <v>398</v>
-      </c>
-      <c r="K3" t="s">
-        <v>284</v>
-      </c>
-      <c r="L3" t="s">
-        <v>399</v>
-      </c>
-      <c r="M3" t="s">
-        <v>400</v>
       </c>
       <c r="N3" t="s">
         <v>148</v>
       </c>
       <c r="O3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="P3" s="41" t="s">
         <v>236</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>402</v>
+        <v>618</v>
       </c>
       <c r="S3" s="46" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="47.25">
+    <row r="4" spans="1:19" ht="46.8">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -59452,16 +59473,16 @@
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="J4" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="L4" t="s">
         <v>230</v>
@@ -59470,24 +59491,24 @@
         <v>228</v>
       </c>
       <c r="N4" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="O4" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="P4" s="41" t="s">
-        <v>409</v>
-      </c>
-      <c r="R4" s="44" t="s">
+        <v>406</v>
+      </c>
+      <c r="R4" s="126" t="s">
+        <v>616</v>
+      </c>
+      <c r="S4" s="44" t="s">
         <v>250</v>
       </c>
-      <c r="S4" s="44" t="s">
-        <v>251</v>
-      </c>
     </row>
-    <row r="5" spans="1:19" ht="47.25">
+    <row r="5" spans="1:19" ht="46.8">
       <c r="D5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F5" t="s">
         <v>120</v>
@@ -59496,13 +59517,13 @@
         <v>234</v>
       </c>
       <c r="H5" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="J5" s="41" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="L5" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="M5" t="s">
         <v>73</v>
@@ -59511,71 +59532,71 @@
         <v>124</v>
       </c>
       <c r="O5" s="41" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="P5" t="s">
         <v>73</v>
       </c>
       <c r="R5" s="46" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="S5" s="46" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="D6" s="41" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F6" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H6" t="s">
         <v>229</v>
       </c>
       <c r="J6" t="s">
+        <v>415</v>
+      </c>
+      <c r="L6" t="s">
+        <v>416</v>
+      </c>
+      <c r="N6" t="s">
+        <v>305</v>
+      </c>
+      <c r="O6" t="s">
+        <v>73</v>
+      </c>
+      <c r="R6" s="46" t="s">
+        <v>417</v>
+      </c>
+      <c r="S6" s="46" t="s">
         <v>418</v>
-      </c>
-      <c r="L6" t="s">
-        <v>419</v>
-      </c>
-      <c r="N6" t="s">
-        <v>306</v>
-      </c>
-      <c r="O6" t="s">
-        <v>73</v>
-      </c>
-      <c r="R6" s="46" t="s">
-        <v>420</v>
-      </c>
-      <c r="S6" s="46" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="F7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H7" t="s">
         <v>243</v>
       </c>
       <c r="J7" s="41" t="s">
+        <v>419</v>
+      </c>
+      <c r="L7" t="s">
+        <v>282</v>
+      </c>
+      <c r="N7" t="s">
+        <v>420</v>
+      </c>
+      <c r="O7" t="s">
+        <v>421</v>
+      </c>
+      <c r="R7" s="46" t="s">
         <v>422</v>
       </c>
-      <c r="L7" t="s">
-        <v>283</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="S7" s="46" t="s">
         <v>423</v>
-      </c>
-      <c r="O7" t="s">
-        <v>424</v>
-      </c>
-      <c r="R7" s="46" t="s">
-        <v>425</v>
-      </c>
-      <c r="S7" s="46" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -59583,39 +59604,39 @@
         <v>107</v>
       </c>
       <c r="J8" s="41" t="s">
+        <v>424</v>
+      </c>
+      <c r="L8" t="s">
+        <v>421</v>
+      </c>
+      <c r="N8" t="s">
+        <v>425</v>
+      </c>
+      <c r="R8" s="46" t="s">
+        <v>426</v>
+      </c>
+      <c r="S8" s="46" t="s">
         <v>427</v>
-      </c>
-      <c r="L8" t="s">
-        <v>424</v>
-      </c>
-      <c r="N8" t="s">
-        <v>428</v>
-      </c>
-      <c r="R8" s="46" t="s">
-        <v>429</v>
-      </c>
-      <c r="S8" s="46" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="F9" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J9" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="L9" t="s">
+        <v>428</v>
+      </c>
+      <c r="N9" t="s">
+        <v>429</v>
+      </c>
+      <c r="R9" s="44" t="s">
+        <v>430</v>
+      </c>
+      <c r="S9" s="44" t="s">
         <v>431</v>
-      </c>
-      <c r="N9" t="s">
-        <v>432</v>
-      </c>
-      <c r="R9" s="44" t="s">
-        <v>433</v>
-      </c>
-      <c r="S9" s="44" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -59623,19 +59644,19 @@
         <v>155</v>
       </c>
       <c r="J10" t="s">
+        <v>432</v>
+      </c>
+      <c r="L10" t="s">
+        <v>265</v>
+      </c>
+      <c r="N10" t="s">
+        <v>433</v>
+      </c>
+      <c r="R10" s="44" t="s">
+        <v>434</v>
+      </c>
+      <c r="S10" s="44" t="s">
         <v>435</v>
-      </c>
-      <c r="L10" t="s">
-        <v>266</v>
-      </c>
-      <c r="N10" t="s">
-        <v>436</v>
-      </c>
-      <c r="R10" s="44" t="s">
-        <v>437</v>
-      </c>
-      <c r="S10" s="44" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -59643,61 +59664,61 @@
         <v>247</v>
       </c>
       <c r="J11" t="s">
+        <v>436</v>
+      </c>
+      <c r="N11" t="s">
+        <v>437</v>
+      </c>
+      <c r="R11" s="44" t="s">
+        <v>438</v>
+      </c>
+      <c r="S11" s="44" t="s">
         <v>439</v>
-      </c>
-      <c r="N11" t="s">
-        <v>440</v>
-      </c>
-      <c r="R11" s="44" t="s">
-        <v>441</v>
-      </c>
-      <c r="S11" s="44" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="F12" t="s">
+        <v>440</v>
+      </c>
+      <c r="J12" t="s">
+        <v>73</v>
+      </c>
+      <c r="N12" t="s">
+        <v>441</v>
+      </c>
+      <c r="R12" s="44" t="s">
+        <v>442</v>
+      </c>
+      <c r="S12" s="44" t="s">
         <v>443</v>
-      </c>
-      <c r="J12" t="s">
-        <v>73</v>
-      </c>
-      <c r="N12" t="s">
-        <v>444</v>
-      </c>
-      <c r="R12" s="44" t="s">
-        <v>445</v>
-      </c>
-      <c r="S12" s="44" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="13" spans="1:19">
       <c r="F13" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="N13" t="s">
         <v>96</v>
       </c>
       <c r="R13" s="46" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="S13" s="46" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="14" spans="1:19">
       <c r="F14" s="41" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="N14" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="R14" s="44" t="s">
+        <v>269</v>
+      </c>
+      <c r="S14" s="44" t="s">
         <v>270</v>
-      </c>
-      <c r="S14" s="44" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -59705,52 +59726,52 @@
         <v>155</v>
       </c>
       <c r="N15" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="R15" s="46" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="S15" s="46" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="F16" s="41" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="N16" t="s">
         <v>156</v>
       </c>
       <c r="R16" s="46" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="S16" s="46" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="17" spans="6:19">
       <c r="F17" s="41" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N17" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="R17" s="44" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="S17" s="44" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="18" spans="6:19">
       <c r="F18" s="41" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="N18" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="R18" s="46" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="S18" s="46" t="s">
         <v>127</v>
@@ -59761,13 +59782,13 @@
         <v>238</v>
       </c>
       <c r="N19" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="R19" s="44" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="S19" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="20" spans="6:19">
@@ -59775,13 +59796,13 @@
         <v>226</v>
       </c>
       <c r="N20" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="R20" s="46" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="S20" s="46" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="21" spans="6:19">
@@ -59789,111 +59810,111 @@
         <v>237</v>
       </c>
       <c r="N21" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="R21" s="44" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="S21" s="44" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="22" spans="6:19">
       <c r="F22" s="41" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N22" t="s">
         <v>138</v>
       </c>
       <c r="R22" s="46" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="S22" s="46" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="23" spans="6:19">
       <c r="F23" s="41" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="N23" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="R23" s="44" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="S23" s="44" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="24" spans="6:19">
       <c r="F24" s="41" t="s">
+        <v>470</v>
+      </c>
+      <c r="N24" t="s">
+        <v>471</v>
+      </c>
+      <c r="R24" s="44" t="s">
+        <v>472</v>
+      </c>
+      <c r="S24" s="44" t="s">
         <v>473</v>
-      </c>
-      <c r="N24" t="s">
-        <v>474</v>
-      </c>
-      <c r="R24" s="44" t="s">
-        <v>475</v>
-      </c>
-      <c r="S24" s="44" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="25" spans="6:19">
       <c r="F25" s="41" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="N25" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="R25" s="44" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="S25" s="44" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="26" spans="6:19">
       <c r="F26" s="41" t="s">
+        <v>476</v>
+      </c>
+      <c r="N26" t="s">
+        <v>477</v>
+      </c>
+      <c r="R26" s="44" t="s">
+        <v>478</v>
+      </c>
+      <c r="S26" s="44" t="s">
         <v>479</v>
-      </c>
-      <c r="N26" t="s">
-        <v>480</v>
-      </c>
-      <c r="R26" s="44" t="s">
-        <v>481</v>
-      </c>
-      <c r="S26" s="44" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="27" spans="6:19">
       <c r="F27" s="41" t="s">
+        <v>480</v>
+      </c>
+      <c r="N27" t="s">
+        <v>481</v>
+      </c>
+      <c r="R27" s="44" t="s">
+        <v>482</v>
+      </c>
+      <c r="S27" s="44" t="s">
         <v>483</v>
-      </c>
-      <c r="N27" t="s">
-        <v>484</v>
-      </c>
-      <c r="R27" s="44" t="s">
-        <v>485</v>
-      </c>
-      <c r="S27" s="44" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="28" spans="6:19">
       <c r="F28" s="41" t="s">
+        <v>484</v>
+      </c>
+      <c r="N28" t="s">
+        <v>485</v>
+      </c>
+      <c r="R28" s="44" t="s">
+        <v>486</v>
+      </c>
+      <c r="S28" s="44" t="s">
         <v>487</v>
-      </c>
-      <c r="N28" t="s">
-        <v>488</v>
-      </c>
-      <c r="R28" s="44" t="s">
-        <v>489</v>
-      </c>
-      <c r="S28" s="44" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="29" spans="6:19">
@@ -59901,27 +59922,27 @@
         <v>172</v>
       </c>
       <c r="N29" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="R29" s="44" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="S29" s="44" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="30" spans="6:19">
       <c r="F30" s="41" t="s">
+        <v>491</v>
+      </c>
+      <c r="N30" t="s">
+        <v>492</v>
+      </c>
+      <c r="R30" s="44" t="s">
+        <v>493</v>
+      </c>
+      <c r="S30" s="44" t="s">
         <v>494</v>
-      </c>
-      <c r="N30" t="s">
-        <v>495</v>
-      </c>
-      <c r="R30" s="44" t="s">
-        <v>496</v>
-      </c>
-      <c r="S30" s="44" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="31" spans="6:19">
@@ -59929,21 +59950,21 @@
         <v>174</v>
       </c>
       <c r="R31" s="44" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="S31" s="44" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="32" spans="6:19">
       <c r="N32" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="R32" s="44" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="S32" s="44" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="33" spans="14:19">
@@ -59951,95 +59972,95 @@
         <v>131</v>
       </c>
       <c r="R33" s="44" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="S33" s="44" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="34" spans="14:19">
       <c r="R34" s="44" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="S34" s="44" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="35" spans="14:19">
       <c r="R35" s="44" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="S35" s="44" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="36" spans="14:19">
       <c r="R36" s="44" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="S36" s="44" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="37" spans="14:19">
       <c r="R37" s="46" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="S37" s="46" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="38" spans="14:19">
       <c r="R38" s="46" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="S38" s="46" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="39" spans="14:19">
       <c r="R39" s="46" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="S39" s="46" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="40" spans="14:19">
       <c r="R40" s="44" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="S40" s="44" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="41" spans="14:19">
       <c r="R41" s="44" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="S41" s="44" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="42" spans="14:19">
       <c r="R42" s="46" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="S42" s="46" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="43" spans="14:19">
       <c r="R43" s="46" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="S43" s="46" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="44" spans="14:19">
       <c r="R44" s="44" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S44" s="17" t="s">
         <v>117</v>
@@ -60047,50 +60068,50 @@
     </row>
     <row r="45" spans="14:19">
       <c r="R45" s="46" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="S45" s="46" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="46" spans="14:19">
       <c r="R46" s="44" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="S46" s="44" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="47" spans="14:19">
       <c r="R47" s="46" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="S47" s="46" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="48" spans="14:19">
       <c r="R48" s="44" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="S48" s="44" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="49" spans="18:19">
       <c r="R49" s="44" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="S49" s="44" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="50" spans="18:19">
       <c r="R50" s="44" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="S50" s="44" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="51" spans="18:19">
@@ -60103,242 +60124,242 @@
     </row>
     <row r="52" spans="18:19">
       <c r="R52" s="44" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="S52" s="44" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="53" spans="18:19">
       <c r="R53" s="44" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="S53" s="17" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="54" spans="18:19">
       <c r="R54" s="44" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="S54" s="44" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="55" spans="18:19">
       <c r="R55" s="44" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="S55" s="44" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="56" spans="18:19">
       <c r="R56" s="44" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="S56" s="44" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="57" spans="18:19">
       <c r="R57" s="44" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="S57" s="44" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="58" spans="18:19">
       <c r="R58" s="44" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="S58" s="44" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="59" spans="18:19">
       <c r="R59" s="44" t="s">
+        <v>278</v>
+      </c>
+      <c r="S59" s="44" t="s">
         <v>279</v>
-      </c>
-      <c r="S59" s="44" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="60" spans="18:19">
       <c r="R60" s="44" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="S60" s="44" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="61" spans="18:19">
       <c r="R61" s="44" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="S61" s="44" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="62" spans="18:19">
       <c r="R62" s="44" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="S62" s="44" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="63" spans="18:19">
       <c r="R63" s="44" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="S63" s="44" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="64" spans="18:19">
       <c r="R64" s="44" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="S64" s="44" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="65" spans="18:19">
       <c r="R65" s="44" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="S65" s="44" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="66" spans="18:19">
       <c r="R66" s="44" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="S66" s="44" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="67" spans="18:19">
       <c r="R67" s="44" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="S67" s="44" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="68" spans="18:19">
       <c r="R68" s="44" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="S68" s="44" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="69" spans="18:19">
       <c r="R69" s="44" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="S69" s="44" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="70" spans="18:19">
       <c r="R70" s="44" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="S70" s="44" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="71" spans="18:19">
       <c r="R71" s="44" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="S71" s="44" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="72" spans="18:19">
       <c r="R72" s="44" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="S72" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="73" spans="18:19">
       <c r="R73" s="46" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="S73" s="46" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="74" spans="18:19">
       <c r="R74" s="44" t="s">
+        <v>262</v>
+      </c>
+      <c r="S74" s="44" t="s">
         <v>263</v>
-      </c>
-      <c r="S74" s="44" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="75" spans="18:19">
       <c r="R75" s="46" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="S75" s="46" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="76" spans="18:19">
       <c r="R76" s="44" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="S76" s="44" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="77" spans="18:19">
       <c r="R77" s="44" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="S77" s="44" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="78" spans="18:19">
       <c r="R78" s="46" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="S78" s="46" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="79" spans="18:19">
       <c r="R79" s="46" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="S79" s="46" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="80" spans="18:19">
       <c r="R80" s="44" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="S80" s="44" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="81" spans="18:19">
       <c r="R81" s="44" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="S81" s="44" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="82" spans="18:19">
@@ -60351,127 +60372,127 @@
     </row>
     <row r="83" spans="18:19">
       <c r="R83" s="46" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="S83" s="46" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="84" spans="18:19">
       <c r="R84" s="46" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="S84" s="46" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="85" spans="18:19">
       <c r="R85" s="44" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="S85" s="44" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
     </row>
     <row r="86" spans="18:19">
       <c r="R86" s="44" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="S86" s="44" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="87" spans="18:19">
       <c r="R87" s="44" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="S87" s="44" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="88" spans="18:19">
       <c r="R88" s="44" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="S88" s="44" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="89" spans="18:19">
       <c r="R89" s="44" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="S89" s="44" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="90" spans="18:19">
       <c r="R90" s="44" t="s">
+        <v>301</v>
+      </c>
+      <c r="S90" s="44" t="s">
         <v>302</v>
-      </c>
-      <c r="S90" s="44" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="91" spans="18:19">
       <c r="R91" s="44" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="S91" s="44" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="92" spans="18:19">
       <c r="R92" s="44" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="S92" s="44" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="93" spans="18:19">
       <c r="R93" s="44" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="S93" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="94" spans="18:19">
       <c r="R94" s="44" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="S94" s="44" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="95" spans="18:19">
       <c r="R95" s="44" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="S95" s="44" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="96" spans="18:19">
       <c r="R96" s="44" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="S96" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="97" spans="18:19">
       <c r="R97" s="44" t="s">
+        <v>290</v>
+      </c>
+      <c r="S97" s="57" t="s">
         <v>291</v>
-      </c>
-      <c r="S97" s="57" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="98" spans="18:19">
       <c r="R98" s="57" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="S98" s="32" t="s">
         <v>133</v>
@@ -60479,10 +60500,10 @@
     </row>
     <row r="99" spans="18:19">
       <c r="R99" s="44" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="S99" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
   </sheetData>

--- a/appliances_usage.xlsx
+++ b/appliances_usage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dianadanilenko/Desktop/appliances_interventions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5A60D8-DEB5-6643-A830-ABFB46617300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC961BEF-9C2B-4C49-A863-30D0D60AEC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-5280" yWindow="-21100" windowWidth="38400" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId5"/>
+    <pivotCache cacheId="3" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34691,7 +34691,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:BJ18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="92">
     <pivotField showAll="0"/>

--- a/appliances_usage.xlsx
+++ b/appliances_usage.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dianadanilenko/Desktop/appliances_interventions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dand\Documents\GitHub\appliances_interventions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC961BEF-9C2B-4C49-A863-30D0D60AEC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5280" yWindow="-21100" windowWidth="38400" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="-4485" yWindow="-21105" windowWidth="38400" windowHeight="19395" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Usage" sheetId="5" state="hidden" r:id="rId1"/>
@@ -22,59 +21,76 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Appliances!$AR$1:$AR$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Usage!$A$1:$BN$53</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={73C2226C-6106-4DC2-88CF-9C0A06F48311}</author>
     <author>tc={CEE78422-255C-40DC-AFED-5AA185CC03E1}</author>
     <author>tc={C7CEED71-5EFE-4791-84D8-7010C40A69F0}</author>
   </authors>
   <commentList>
-    <comment ref="AQ1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="AQ1" authorId="0" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     is this supposed to capture mean difference between control and treatment or ?</t>
+        </r>
       </text>
     </comment>
-    <comment ref="AZ1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="AZ1" authorId="1" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     daily kWh</t>
+        </r>
       </text>
     </comment>
-    <comment ref="AQ22" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="AQ22" authorId="2" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     in kWh</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -82,17 +98,26 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={1DD52412-77C6-1E43-B8CC-07AD562D2C6E}</author>
   </authors>
   <commentList>
-    <comment ref="AA1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="AA1" authorId="0" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     check label studies from srmt for label type</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -100,19 +125,28 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={CF36070F-7893-4948-8AB8-1CADF6EBBFD9}</author>
   </authors>
   <commentList>
-    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+    <comment ref="D6" authorId="0" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     a bit confused as of where it’s correlation and where - quasi-experimental
 Reply:
     the way i reassessed this was - market statistics - correlation, whereas hypothetical choice - quasi-experimental</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -120,7 +154,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3181" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3165" uniqueCount="619">
   <si>
     <t>Coder</t>
   </si>
@@ -918,6 +952,9 @@
     <t>percent_change</t>
   </si>
   <si>
+    <t>percent_change(binary predictor)</t>
+  </si>
+  <si>
     <t>monetary_incentive_size</t>
   </si>
   <si>
@@ -1069,6 +1106,9 @@
   </si>
   <si>
     <t xml:space="preserve">for owners of ES AC </t>
+  </si>
+  <si>
+    <t>Alberini, Towe</t>
   </si>
   <si>
     <t>Information v. energy efficiency incentives: Evidence from residential electricity consumption in Maryland</t>
@@ -1226,6 +1266,9 @@
     <t>after additional purchase</t>
   </si>
   <si>
+    <t>Alberini, Gans, Towe</t>
+  </si>
+  <si>
     <t>Free Riding, Upsizing, and Energy Efﬁciency Incentives in Maryland Homes</t>
   </si>
   <si>
@@ -1534,6 +1577,9 @@
     <t>dummy (0/1)</t>
   </si>
   <si>
+    <t>Alberini, Bigano</t>
+  </si>
+  <si>
     <t>How effective are energy-efficiency incentive programs? Evidence from Italian homeowners</t>
   </si>
   <si>
@@ -1553,6 +1599,9 @@
   </si>
   <si>
     <t>alphabetical</t>
+  </si>
+  <si>
+    <t>Alberini, Bigano, Boeri</t>
   </si>
   <si>
     <t>Looking for free riding: energy efficiency incentives and Italian homeowners</t>
@@ -2204,27 +2253,12 @@
   </si>
   <si>
     <t>dishwasher</t>
-  </si>
-  <si>
-    <t>percent_change_ci</t>
-  </si>
-  <si>
-    <t>Albertini, Bigano</t>
-  </si>
-  <si>
-    <t>Albertini, Bigano, Boeri</t>
-  </si>
-  <si>
-    <t>Albertini, Towe</t>
-  </si>
-  <si>
-    <t>Albertini, Gans, Towe</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="9">
     <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
@@ -2447,13 +2481,11 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="21">
@@ -2693,7 +2725,7 @@
     <xf numFmtId="9" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2845,14 +2877,13 @@
     </xf>
     <xf numFmtId="0" fontId="33" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="0" fillId="15" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="20" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="171" fontId="20" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
+    <cellStyle name="Link" xfId="2" builtinId="8"/>
+    <cellStyle name="Prozent" xfId="1" builtinId="5"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -2886,7 +2917,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="45057.552441087966" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="334" xr:uid="{00000000-000A-0000-FFFF-FFFF01000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="45057.552441087966" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="334">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:CD1048576" sheet="Appliances"/>
   </cacheSource>
@@ -3290,7 +3321,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="334">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="334">
   <r>
     <x v="0"/>
     <n v="1"/>
@@ -34691,7 +34722,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:BJ18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="92">
     <pivotField showAll="0"/>
@@ -35207,9 +35238,6 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
     </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
   </extLst>
 </pivotTableDefinition>
 </file>
@@ -35543,57 +35571,57 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BP53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.1640625" customWidth="1"/>
-    <col min="7" max="7" width="16.1640625" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" customWidth="1"/>
-    <col min="10" max="10" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.625" customWidth="1"/>
+    <col min="5" max="5" width="14.125" customWidth="1"/>
+    <col min="7" max="7" width="16.125" customWidth="1"/>
+    <col min="8" max="8" width="16.625" customWidth="1"/>
+    <col min="10" max="10" width="18.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" hidden="1" customWidth="1"/>
     <col min="12" max="17" width="0" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="16" hidden="1" customWidth="1"/>
     <col min="19" max="22" width="0" hidden="1" customWidth="1"/>
-    <col min="23" max="24" width="12.1640625" hidden="1" customWidth="1"/>
+    <col min="23" max="24" width="12.125" hidden="1" customWidth="1"/>
     <col min="25" max="25" width="0" hidden="1" customWidth="1"/>
     <col min="26" max="26" width="0" style="12" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="18.6640625" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="14.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.6640625" style="7" customWidth="1"/>
-    <col min="30" max="30" width="13.6640625" customWidth="1"/>
-    <col min="31" max="31" width="14.6640625" customWidth="1"/>
-    <col min="32" max="32" width="13.6640625" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="19.1640625" hidden="1" customWidth="1"/>
-    <col min="34" max="34" width="10.6640625" hidden="1" customWidth="1"/>
-    <col min="35" max="35" width="13.1640625" hidden="1" customWidth="1"/>
-    <col min="36" max="36" width="22.1640625" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="10.6640625" hidden="1" customWidth="1"/>
-    <col min="38" max="38" width="18.1640625" customWidth="1"/>
-    <col min="39" max="39" width="14.1640625" customWidth="1"/>
-    <col min="40" max="40" width="9.6640625" customWidth="1"/>
-    <col min="41" max="41" width="19.1640625" customWidth="1"/>
-    <col min="42" max="42" width="12.1640625" customWidth="1"/>
+    <col min="27" max="27" width="18.625" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="14.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.625" style="7" customWidth="1"/>
+    <col min="30" max="30" width="13.625" customWidth="1"/>
+    <col min="31" max="31" width="14.625" customWidth="1"/>
+    <col min="32" max="32" width="13.625" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="19.125" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="10.625" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="13.125" hidden="1" customWidth="1"/>
+    <col min="36" max="36" width="22.125" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="10.625" hidden="1" customWidth="1"/>
+    <col min="38" max="38" width="18.125" customWidth="1"/>
+    <col min="39" max="39" width="14.125" customWidth="1"/>
+    <col min="40" max="40" width="9.625" customWidth="1"/>
+    <col min="41" max="41" width="19.125" customWidth="1"/>
+    <col min="42" max="42" width="12.125" customWidth="1"/>
     <col min="44" max="45" width="0" hidden="1" customWidth="1"/>
-    <col min="46" max="47" width="13.1640625" hidden="1" customWidth="1"/>
+    <col min="46" max="47" width="13.125" hidden="1" customWidth="1"/>
     <col min="48" max="51" width="0" hidden="1" customWidth="1"/>
-    <col min="52" max="52" width="13.6640625" style="17" hidden="1" customWidth="1"/>
+    <col min="52" max="52" width="13.625" style="17" hidden="1" customWidth="1"/>
     <col min="53" max="53" width="26.5" hidden="1" customWidth="1"/>
-    <col min="54" max="54" width="20.6640625" hidden="1" customWidth="1"/>
+    <col min="54" max="54" width="20.625" hidden="1" customWidth="1"/>
     <col min="55" max="55" width="0" hidden="1" customWidth="1"/>
-    <col min="56" max="56" width="17.6640625" hidden="1" customWidth="1"/>
-    <col min="57" max="57" width="16.1640625" hidden="1" customWidth="1"/>
-    <col min="58" max="58" width="15.1640625" hidden="1" customWidth="1"/>
-    <col min="59" max="59" width="20.6640625" hidden="1" customWidth="1"/>
-    <col min="60" max="60" width="24.6640625" hidden="1" customWidth="1"/>
-    <col min="61" max="61" width="19.6640625" style="30" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="24.1640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="17.625" hidden="1" customWidth="1"/>
+    <col min="57" max="57" width="16.125" hidden="1" customWidth="1"/>
+    <col min="58" max="58" width="15.125" hidden="1" customWidth="1"/>
+    <col min="59" max="59" width="20.625" hidden="1" customWidth="1"/>
+    <col min="60" max="60" width="24.625" hidden="1" customWidth="1"/>
+    <col min="61" max="61" width="19.625" style="30" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="24.125" style="30" bestFit="1" customWidth="1"/>
     <col min="63" max="65" width="11" style="30"/>
-    <col min="67" max="67" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="25.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="48">
+    <row r="1" spans="1:68" ht="45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -41137,11 +41165,11 @@
       </c>
       <c r="BI27" s="30">
         <f t="shared" si="14"/>
-        <v>6.4285714285714276E-3</v>
+        <v>6.4285714285714259E-3</v>
       </c>
       <c r="BJ27" s="30">
         <f t="shared" si="15"/>
-        <v>6.4285714285714276E-3</v>
+        <v>6.4285714285714259E-3</v>
       </c>
       <c r="BK27" s="30">
         <f t="shared" si="9"/>
@@ -43391,7 +43419,7 @@
         <v>6.7567567567567571E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:66" s="41" customFormat="1" ht="17">
+    <row r="39" spans="1:66" s="41" customFormat="1" ht="16.5">
       <c r="A39" s="45" t="s">
         <v>68</v>
       </c>
@@ -43596,7 +43624,7 @@
       </c>
       <c r="BN39" s="43"/>
     </row>
-    <row r="40" spans="1:66" s="41" customFormat="1" ht="17">
+    <row r="40" spans="1:66" s="41" customFormat="1" ht="16.5">
       <c r="A40" s="45" t="s">
         <v>68</v>
       </c>
@@ -43801,7 +43829,7 @@
       </c>
       <c r="BN40" s="43"/>
     </row>
-    <row r="41" spans="1:66" s="41" customFormat="1" ht="17">
+    <row r="41" spans="1:66" s="41" customFormat="1" ht="16.5">
       <c r="A41" s="45" t="s">
         <v>68</v>
       </c>
@@ -44010,7 +44038,7 @@
         <v>2.0421052631578922</v>
       </c>
     </row>
-    <row r="42" spans="1:66" s="41" customFormat="1" ht="17">
+    <row r="42" spans="1:66" s="41" customFormat="1" ht="16.5">
       <c r="A42" s="45" t="s">
         <v>68</v>
       </c>
@@ -46407,34 +46435,34 @@
   </sheetData>
   <dataConsolidate/>
   <dataValidations count="10">
-    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="M11:M12 N29:N32 M14:M16 L1:L1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="M11:M12 N29:N32 M14:M16 L1:L1048576">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="R1:W1 R2:Y9 X10:X12 BB43:BB52 BC29:BC32 S23:Y28 BB39:BC42 BC43:BC51 BC17:BC22 BB54:BB1048576 BB13:BC16 R33:Y1048576 BB17:BB38 BB1:BB12" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="R1:W1 R2:Y9 X10:X12 BB43:BB52 BC29:BC32 S23:Y28 BB39:BC42 BC43:BC51 BC17:BC22 BB54:BB1048576 BB13:BC16 R33:Y1048576 BB17:BB38 BB1:BB12">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="M1:Q9 M10 Y10:Y12 N10:W12 O29:Y32 P23:R28 N17:O28 P17:Y22 M13 N13:Y16 M17:M32 M33:Q1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="M1:Q9 M10 Y10:Y12 N10:W12 O29:Y32 P23:R28 N17:O28 P17:Y22 M13 N13:Y16 M17:M32 M33:Q1048576">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AO54:AO1048576 AO43:AO52 AO1:AO38" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AO54:AO1048576 AO43:AO52 AO1:AO38">
       <formula1>0</formula1>
       <formula2>3</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="X1" xr:uid="{00000000-0002-0000-0000-000004000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA53 AR53" xr:uid="{00000000-0002-0000-0000-000005000000}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J23:J37 J1:J12" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="X1"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA53 AR53"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J23:J37 J1:J12">
       <formula1>$F$2:$F$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K23:K37 K1:K12" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K23:K37 K1:K12">
       <formula1>$D$2:$D$6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K43:K51" xr:uid="{00000000-0002-0000-0000-000008000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K43:K51">
       <formula1>$D$2:$D$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J43:J51" xr:uid="{00000000-0002-0000-0000-000009000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J43:J51">
       <formula1>$F$2:$F$10</formula1>
     </dataValidation>
   </dataValidations>
@@ -46443,43 +46471,43 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Option to Opt/in - 1_x000a_No Option to Opt/in - 0_x000a_NA_x000a__x000a_" xr:uid="{00000000-0002-0000-0000-00000A000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Option to Opt/in - 1_x000a_No Option to Opt/in - 0_x000a_NA_x000a__x000a_">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B$2:$B$4</xm:f>
           </x14:formula1>
           <xm:sqref>BC23:BC28 BC54:BC1048576 BC33:BC38 BC1:BC12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000B000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$F$2:$F$9</xm:f>
           </x14:formula1>
           <xm:sqref>J54:J1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000C000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$A$2:$A$4</xm:f>
           </x14:formula1>
           <xm:sqref>AS43:AX51 AS54:AX1048576 AS23:AX38 AS2:AX12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000D000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$F$2:$F$10</xm:f>
           </x14:formula1>
           <xm:sqref>J38</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000E000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$E$2:$E$4</xm:f>
           </x14:formula1>
           <xm:sqref>AO43:AO51</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000F000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D$2:$D$6</xm:f>
           </x14:formula1>
           <xm:sqref>K54:K1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000010000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D$2:$D$7</xm:f>
           </x14:formula1>
@@ -46492,67 +46520,67 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:CH51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="5" max="5" width="24.6640625" customWidth="1"/>
-    <col min="6" max="6" width="17.6640625" customWidth="1"/>
-    <col min="7" max="7" width="14.1640625" customWidth="1"/>
+    <col min="5" max="5" width="24.625" customWidth="1"/>
+    <col min="6" max="6" width="17.625" customWidth="1"/>
+    <col min="7" max="7" width="14.125" customWidth="1"/>
     <col min="8" max="8" width="16.5" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="16.1640625" customWidth="1"/>
-    <col min="11" max="11" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.1640625" customWidth="1"/>
+    <col min="10" max="10" width="16.125" customWidth="1"/>
+    <col min="11" max="11" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.125" customWidth="1"/>
     <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="14.6640625" customWidth="1"/>
-    <col min="17" max="17" width="13.1640625" customWidth="1"/>
+    <col min="16" max="16" width="14.625" customWidth="1"/>
+    <col min="17" max="17" width="13.125" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
-    <col min="19" max="19" width="14.1640625" customWidth="1"/>
+    <col min="19" max="19" width="14.125" customWidth="1"/>
     <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="21" width="21.1640625" customWidth="1"/>
+    <col min="21" max="21" width="21.125" customWidth="1"/>
     <col min="22" max="22" width="16" customWidth="1"/>
-    <col min="23" max="23" width="14.6640625" customWidth="1"/>
+    <col min="23" max="23" width="14.625" customWidth="1"/>
     <col min="24" max="24" width="12.5" customWidth="1"/>
     <col min="25" max="33" width="11" customWidth="1"/>
     <col min="34" max="35" width="16" customWidth="1"/>
     <col min="36" max="39" width="11" customWidth="1"/>
-    <col min="40" max="41" width="12.1640625" customWidth="1"/>
+    <col min="40" max="41" width="12.125" customWidth="1"/>
     <col min="42" max="42" width="11" customWidth="1"/>
-    <col min="43" max="43" width="27.6640625" customWidth="1"/>
-    <col min="44" max="44" width="41.1640625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="54.6640625" customWidth="1"/>
+    <col min="43" max="43" width="27.625" customWidth="1"/>
+    <col min="44" max="44" width="41.125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="54.625" customWidth="1"/>
     <col min="46" max="46" width="21" customWidth="1"/>
-    <col min="47" max="47" width="26.6640625" style="7" customWidth="1"/>
-    <col min="48" max="48" width="14.1640625" style="7" customWidth="1"/>
-    <col min="49" max="49" width="13.1640625" customWidth="1"/>
-    <col min="50" max="50" width="9.6640625" customWidth="1"/>
+    <col min="47" max="47" width="26.625" style="7" customWidth="1"/>
+    <col min="48" max="48" width="14.125" style="7" customWidth="1"/>
+    <col min="49" max="49" width="13.125" customWidth="1"/>
+    <col min="50" max="50" width="9.625" customWidth="1"/>
     <col min="51" max="51" width="17" customWidth="1"/>
     <col min="52" max="52" width="9"/>
-    <col min="53" max="54" width="14.1640625" customWidth="1"/>
-    <col min="55" max="55" width="13.6640625" customWidth="1"/>
-    <col min="56" max="56" width="12.6640625" customWidth="1"/>
-    <col min="57" max="57" width="10.6640625" customWidth="1"/>
+    <col min="53" max="54" width="14.125" customWidth="1"/>
+    <col min="55" max="55" width="13.625" customWidth="1"/>
+    <col min="56" max="56" width="12.625" customWidth="1"/>
+    <col min="57" max="57" width="10.625" customWidth="1"/>
     <col min="58" max="58" width="13" customWidth="1"/>
-    <col min="59" max="60" width="10.6640625" customWidth="1"/>
-    <col min="61" max="62" width="11.1640625" customWidth="1"/>
+    <col min="59" max="60" width="10.625" customWidth="1"/>
+    <col min="61" max="62" width="11.125" customWidth="1"/>
     <col min="63" max="64" width="11" customWidth="1"/>
-    <col min="65" max="65" width="12.6640625" customWidth="1"/>
-    <col min="66" max="66" width="18.1640625" customWidth="1"/>
-    <col min="67" max="67" width="22.1640625" customWidth="1"/>
-    <col min="68" max="68" width="15.1640625" customWidth="1"/>
+    <col min="65" max="65" width="12.625" customWidth="1"/>
+    <col min="66" max="66" width="18.125" customWidth="1"/>
+    <col min="67" max="67" width="22.125" customWidth="1"/>
+    <col min="68" max="68" width="15.125" customWidth="1"/>
     <col min="69" max="69" width="18" customWidth="1"/>
-    <col min="70" max="70" width="17.1640625" customWidth="1"/>
-    <col min="71" max="71" width="21.1640625" customWidth="1"/>
-    <col min="72" max="72" width="10.1640625" customWidth="1"/>
+    <col min="70" max="70" width="17.125" customWidth="1"/>
+    <col min="71" max="71" width="21.125" customWidth="1"/>
+    <col min="72" max="72" width="10.125" customWidth="1"/>
     <col min="73" max="73" width="13" customWidth="1"/>
     <col min="74" max="74" width="14" customWidth="1"/>
-    <col min="75" max="75" width="13.1640625" customWidth="1"/>
+    <col min="75" max="75" width="13.125" customWidth="1"/>
     <col min="82" max="82" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:86" ht="17" customHeight="1">
+    <row r="1" spans="1:86" ht="17.100000000000001" customHeight="1">
       <c r="A1" s="59" t="s">
         <v>181</v>
       </c>
@@ -46659,7 +46687,7 @@
         <v>195</v>
       </c>
       <c r="AJ1" s="75" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="AK1" s="75" t="s">
         <v>19</v>
@@ -46713,7 +46741,7 @@
         <v>202</v>
       </c>
       <c r="BB1" s="80" t="s">
-        <v>614</v>
+        <v>203</v>
       </c>
       <c r="BC1" s="81" t="s">
         <v>31</v>
@@ -46746,40 +46774,40 @@
         <v>43</v>
       </c>
       <c r="BM1" s="84" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="BN1" s="85" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="BO1" s="86" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="BP1" s="87" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="BQ1" s="88" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="BR1" s="88" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="BS1" s="88" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="BT1" s="86" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="BU1" s="89" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="BV1" s="90" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="BW1" s="91" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="BX1" s="28" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="BY1" s="92" t="s">
         <v>62</v>
@@ -46794,25 +46822,25 @@
         <v>65</v>
       </c>
       <c r="CC1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="CD1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="CE1" s="28" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="CF1" s="92" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="CG1" s="93" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="CH1" s="93" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
-    <row r="2" spans="1:86" ht="16">
+    <row r="2" spans="1:86">
       <c r="A2" s="11" t="s">
         <v>68</v>
       </c>
@@ -46824,22 +46852,22 @@
         <v>107</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F2" s="11">
         <v>2020</v>
       </c>
       <c r="G2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H2" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I2" s="18">
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>73</v>
@@ -46848,37 +46876,37 @@
         <v>5</v>
       </c>
       <c r="M2" s="18" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O2" t="s">
         <v>96</v>
       </c>
       <c r="P2" s="18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S2">
         <v>1</v>
       </c>
       <c r="T2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U2">
         <v>0</v>
       </c>
       <c r="V2" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W2" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X2" s="18" t="s">
         <v>73</v>
@@ -46908,7 +46936,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -46941,13 +46969,13 @@
         <v>73</v>
       </c>
       <c r="AR2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AT2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU2" s="21">
         <v>5.8000000000000003E-2</v>
@@ -46968,8 +46996,9 @@
         <f t="shared" ref="AZ2:AZ17" si="0">AU2/AW2</f>
         <v>2.7619047619047619</v>
       </c>
-      <c r="BA2" s="102" t="s">
-        <v>73</v>
+      <c r="BA2" s="102">
+        <f t="shared" ref="BA2:BA13" si="1">EXP(AU2) - 1</f>
+        <v>5.9714995710287599E-2</v>
       </c>
       <c r="BB2" s="102"/>
       <c r="BC2" t="s">
@@ -47036,19 +47065,19 @@
         <v>1</v>
       </c>
       <c r="BX2" s="30">
-        <f t="shared" ref="BX2:BX37" si="1">((AZ2^2)/(AZ2^2+BI2))^(1/2)</f>
+        <f t="shared" ref="BX2:BX37" si="2">((AZ2^2)/(AZ2^2+BI2))^(1/2)</f>
         <v>0.11481772350402021</v>
       </c>
       <c r="BY2" s="30">
-        <f t="shared" ref="BY2:BY37" si="2">0.5*LN((1+BX2)/(1-BX2))</f>
+        <f t="shared" ref="BY2:BY37" si="3">0.5*LN((1+BX2)/(1-BX2))</f>
         <v>0.11532630395472614</v>
       </c>
       <c r="BZ2" s="30">
-        <f t="shared" ref="BZ2:BZ37" si="3">((1-(BY2^2)^2)/(BI2-1))</f>
+        <f t="shared" ref="BZ2:BZ37" si="4">((1-(BY2^2)^2)/(BI2-1))</f>
         <v>1.754075624280991E-3</v>
       </c>
       <c r="CA2" s="30">
-        <f t="shared" ref="CA2:CA37" si="4">1/(BI2-3)</f>
+        <f t="shared" ref="CA2:CA37" si="5">1/(BI2-3)</f>
         <v>1.7605633802816902E-3</v>
       </c>
       <c r="CE2" s="30">
@@ -47068,7 +47097,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="3" spans="1:86" ht="16">
+    <row r="3" spans="1:86">
       <c r="A3" s="11" t="s">
         <v>68</v>
       </c>
@@ -47080,22 +47109,22 @@
         <v>107</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F3" s="11">
         <v>2020</v>
       </c>
       <c r="G3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I3" s="18">
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K3" s="10" t="s">
         <v>73</v>
@@ -47104,37 +47133,37 @@
         <v>5</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O3" t="s">
         <v>96</v>
       </c>
       <c r="P3" s="18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S3">
         <v>1</v>
       </c>
       <c r="T3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U3">
         <v>0</v>
       </c>
       <c r="V3" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W3" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X3" s="18" t="s">
         <v>73</v>
@@ -47164,7 +47193,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -47197,13 +47226,13 @@
         <v>73</v>
       </c>
       <c r="AR3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AT3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU3" s="21">
         <v>5.3999999999999999E-2</v>
@@ -47224,8 +47253,9 @@
         <f t="shared" si="0"/>
         <v>2.5714285714285712</v>
       </c>
-      <c r="BA3" s="102" t="s">
-        <v>73</v>
+      <c r="BA3" s="102">
+        <f t="shared" si="1"/>
+        <v>5.5484602155080109E-2</v>
       </c>
       <c r="BB3" s="102"/>
       <c r="BC3" t="s">
@@ -47292,31 +47322,31 @@
         <v>1</v>
       </c>
       <c r="BX3" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.10699322282140411</v>
       </c>
       <c r="BY3" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.10740432025194586</v>
       </c>
       <c r="BZ3" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.7541525050915158E-3</v>
       </c>
       <c r="CA3" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.7605633802816902E-3</v>
       </c>
       <c r="CE3" s="30">
-        <f t="shared" ref="CE3:CE37" si="5">((AZ3^2)/(AZ3^2+BJ3))^(1/2)</f>
+        <f t="shared" ref="CE3:CE37" si="6">((AZ3^2)/(AZ3^2+BJ3))^(1/2)</f>
         <v>1.604274888962573E-2</v>
       </c>
       <c r="CF3" s="30">
-        <f t="shared" ref="CF3:CF37" si="6">0.5*LN((1+CE3)/(1-CE3))</f>
+        <f t="shared" ref="CF3:CF37" si="7">0.5*LN((1+CE3)/(1-CE3))</f>
         <v>1.6044125408511214E-2</v>
       </c>
       <c r="CG3" s="30">
-        <f t="shared" ref="CG3:CG37" si="7">((1-(CF3^2)^2)/(BJ3-1))</f>
+        <f t="shared" ref="CG3:CG37" si="8">((1-(CF3^2)^2)/(BJ3-1))</f>
         <v>3.8934742786873272E-5</v>
       </c>
       <c r="CH3" s="30">
@@ -47324,7 +47354,7 @@
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="4" spans="1:86" ht="16">
+    <row r="4" spans="1:86">
       <c r="A4" s="11" t="s">
         <v>68</v>
       </c>
@@ -47336,22 +47366,22 @@
         <v>107</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F4" s="11">
         <v>2020</v>
       </c>
       <c r="G4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I4" s="18">
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K4" s="10" t="s">
         <v>73</v>
@@ -47360,37 +47390,37 @@
         <v>5</v>
       </c>
       <c r="M4" s="18" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O4" t="s">
         <v>96</v>
       </c>
       <c r="P4" s="18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S4">
         <v>1</v>
       </c>
       <c r="T4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U4">
         <v>0</v>
       </c>
       <c r="V4" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W4" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X4" s="18" t="s">
         <v>73</v>
@@ -47420,7 +47450,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -47453,13 +47483,13 @@
         <v>73</v>
       </c>
       <c r="AR4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AT4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU4" s="21">
         <v>5.3999999999999999E-2</v>
@@ -47480,8 +47510,9 @@
         <f t="shared" si="0"/>
         <v>2.5714285714285712</v>
       </c>
-      <c r="BA4" s="102" t="s">
-        <v>73</v>
+      <c r="BA4" s="102">
+        <f t="shared" si="1"/>
+        <v>5.5484602155080109E-2</v>
       </c>
       <c r="BB4" s="102"/>
       <c r="BC4" t="s">
@@ -47548,39 +47579,39 @@
         <v>1</v>
       </c>
       <c r="BX4" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.10699322282140411</v>
       </c>
       <c r="BY4" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.10740432025194586</v>
       </c>
       <c r="BZ4" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.7541525050915158E-3</v>
       </c>
       <c r="CA4" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.7605633802816902E-3</v>
       </c>
       <c r="CE4" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.604274888962573E-2</v>
       </c>
       <c r="CF4" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.6044125408511214E-2</v>
       </c>
       <c r="CG4" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.8934742786873272E-5</v>
       </c>
       <c r="CH4" s="30">
-        <f t="shared" ref="CH4:CH37" si="8">1/(BJ4-3)</f>
+        <f t="shared" ref="CH4:CH37" si="9">1/(BJ4-3)</f>
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="5" spans="1:86" ht="16">
+    <row r="5" spans="1:86">
       <c r="A5" s="11" t="s">
         <v>68</v>
       </c>
@@ -47592,22 +47623,22 @@
         <v>107</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F5" s="11">
         <v>2020</v>
       </c>
       <c r="G5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I5" s="18">
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K5" s="10" t="s">
         <v>73</v>
@@ -47616,37 +47647,37 @@
         <v>5</v>
       </c>
       <c r="M5" s="18" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O5" t="s">
         <v>96</v>
       </c>
       <c r="P5" s="18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S5">
         <v>1</v>
       </c>
       <c r="T5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U5">
         <v>0</v>
       </c>
       <c r="V5" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W5" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X5" s="18" t="s">
         <v>73</v>
@@ -47676,7 +47707,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -47709,13 +47740,13 @@
         <v>73</v>
       </c>
       <c r="AR5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AT5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU5" s="21">
         <v>5.1999999999999998E-2</v>
@@ -47736,8 +47767,9 @@
         <f t="shared" si="0"/>
         <v>2.4761904761904758</v>
       </c>
-      <c r="BA5" s="102" t="s">
-        <v>73</v>
+      <c r="BA5" s="102">
+        <f t="shared" si="1"/>
+        <v>5.3375742513364743E-2</v>
       </c>
       <c r="BB5" s="102"/>
       <c r="BC5" t="s">
@@ -47804,39 +47836,39 @@
         <v>1</v>
       </c>
       <c r="BX5" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.10307341191556092</v>
       </c>
       <c r="BY5" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.10344077825830729</v>
       </c>
       <c r="BZ5" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.7541851054656437E-3</v>
       </c>
       <c r="CA5" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.7605633802816902E-3</v>
       </c>
       <c r="CE5" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.5448717538944366E-2</v>
       </c>
       <c r="CF5" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.5449946726739888E-2</v>
       </c>
       <c r="CG5" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.8934743148337576E-5</v>
       </c>
       <c r="CH5" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:86" ht="16">
+    <row r="6" spans="1:86">
       <c r="A6" s="11" t="s">
         <v>68</v>
       </c>
@@ -47848,22 +47880,22 @@
         <v>107</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F6" s="11">
         <v>2020</v>
       </c>
       <c r="G6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I6" s="18">
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K6" s="10" t="s">
         <v>73</v>
@@ -47872,37 +47904,37 @@
         <v>5</v>
       </c>
       <c r="M6" s="18" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O6" t="s">
         <v>96</v>
       </c>
       <c r="P6" s="18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S6">
         <v>1</v>
       </c>
       <c r="T6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U6">
         <v>0</v>
       </c>
       <c r="V6" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W6" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X6" s="18" t="s">
         <v>73</v>
@@ -47932,7 +47964,7 @@
         <v>0</v>
       </c>
       <c r="AG6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -47965,13 +47997,13 @@
         <v>73</v>
       </c>
       <c r="AR6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AT6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU6" s="21">
         <v>5.6000000000000001E-2</v>
@@ -47992,8 +48024,9 @@
         <f t="shared" si="0"/>
         <v>2.6666666666666665</v>
       </c>
-      <c r="BA6" s="102" t="s">
-        <v>73</v>
+      <c r="BA6" s="102">
+        <f t="shared" si="1"/>
+        <v>5.7597683736611227E-2</v>
       </c>
       <c r="BB6" s="102"/>
       <c r="BC6" t="s">
@@ -48060,39 +48093,39 @@
         <v>1</v>
       </c>
       <c r="BX6" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.1109080511509852</v>
       </c>
       <c r="BY6" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.11136618214120936</v>
       </c>
       <c r="BZ6" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.7541161049408759E-3</v>
       </c>
       <c r="CA6" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.7605633802816902E-3</v>
       </c>
       <c r="CE6" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.6890120870043275E-2</v>
       </c>
       <c r="CF6" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.6891727261415537E-2</v>
       </c>
       <c r="CG6" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.0130018001787165E-5</v>
       </c>
       <c r="CH6" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.0133242364650637E-5</v>
       </c>
     </row>
-    <row r="7" spans="1:86" ht="16">
+    <row r="7" spans="1:86">
       <c r="A7" s="11" t="s">
         <v>68</v>
       </c>
@@ -48104,22 +48137,22 @@
         <v>107</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F7" s="11">
         <v>2020</v>
       </c>
       <c r="G7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I7" s="18">
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K7" s="10" t="s">
         <v>73</v>
@@ -48128,37 +48161,37 @@
         <v>5</v>
       </c>
       <c r="M7" s="18" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O7" t="s">
         <v>96</v>
       </c>
       <c r="P7" s="18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S7">
         <v>1</v>
       </c>
       <c r="T7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U7">
         <v>0</v>
       </c>
       <c r="V7" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W7" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X7" s="18" t="s">
         <v>73</v>
@@ -48188,7 +48221,7 @@
         <v>0</v>
       </c>
       <c r="AG7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -48221,13 +48254,13 @@
         <v>73</v>
       </c>
       <c r="AR7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AT7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU7" s="21">
         <v>4.4999999999999998E-2</v>
@@ -48248,8 +48281,9 @@
         <f t="shared" si="0"/>
         <v>2.0454545454545454</v>
       </c>
-      <c r="BA7" s="102" t="s">
-        <v>73</v>
+      <c r="BA7" s="102">
+        <f t="shared" si="1"/>
+        <v>4.6027859908716939E-2</v>
       </c>
       <c r="BB7" s="102"/>
       <c r="BC7" t="s">
@@ -48316,39 +48350,39 @@
         <v>1</v>
       </c>
       <c r="BX7" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.5287714841797826E-2</v>
       </c>
       <c r="BY7" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8.5495416206607486E-2</v>
       </c>
       <c r="BZ7" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.7542922310596193E-3</v>
       </c>
       <c r="CA7" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.7605633802816902E-3</v>
       </c>
       <c r="CE7" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.3597084343537518E-2</v>
       </c>
       <c r="CF7" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.3597922382671032E-2</v>
       </c>
       <c r="CG7" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.419889351649495E-5</v>
       </c>
       <c r="CH7" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.4202802457675817E-5</v>
       </c>
     </row>
-    <row r="8" spans="1:86" s="105" customFormat="1" ht="16">
+    <row r="8" spans="1:86" s="105" customFormat="1">
       <c r="A8" s="11" t="s">
         <v>68</v>
       </c>
@@ -48360,22 +48394,22 @@
         <v>107</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F8" s="11">
         <v>2020</v>
       </c>
       <c r="G8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I8" s="18">
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K8" s="10" t="s">
         <v>73</v>
@@ -48384,37 +48418,37 @@
         <v>6</v>
       </c>
       <c r="M8" s="18" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O8" t="s">
         <v>96</v>
       </c>
       <c r="P8" s="18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S8">
         <v>1</v>
       </c>
       <c r="T8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U8">
         <v>0</v>
       </c>
       <c r="V8" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W8" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X8" s="18" t="s">
         <v>73</v>
@@ -48444,7 +48478,7 @@
         <v>0</v>
       </c>
       <c r="AG8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AH8">
         <v>0</v>
@@ -48477,13 +48511,13 @@
         <v>73</v>
       </c>
       <c r="AR8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AT8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU8" s="21">
         <v>5.7000000000000002E-2</v>
@@ -48504,8 +48538,9 @@
         <f t="shared" si="0"/>
         <v>1.9655172413793103</v>
       </c>
-      <c r="BA8" s="102" t="s">
-        <v>73</v>
+      <c r="BA8" s="102">
+        <f t="shared" si="1"/>
+        <v>5.8655810395500163E-2</v>
       </c>
       <c r="BB8" s="102"/>
       <c r="BC8" t="s">
@@ -48572,42 +48607,42 @@
         <v>1</v>
       </c>
       <c r="BX8" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.1977483380554009E-2</v>
       </c>
       <c r="BY8" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8.2161865388990771E-2</v>
       </c>
       <c r="BZ8" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.7543060171508703E-3</v>
       </c>
       <c r="CA8" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.7605633802816902E-3</v>
       </c>
       <c r="CB8"/>
       <c r="CC8"/>
       <c r="CD8"/>
       <c r="CE8" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.2263217028804526E-2</v>
       </c>
       <c r="CF8" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.2263831825009192E-2</v>
       </c>
       <c r="CG8" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.8934744486036733E-5</v>
       </c>
       <c r="CH8" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="9" spans="1:86" s="105" customFormat="1" ht="16">
+    <row r="9" spans="1:86" s="105" customFormat="1">
       <c r="A9" s="11" t="s">
         <v>68</v>
       </c>
@@ -48619,22 +48654,22 @@
         <v>107</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F9" s="11">
         <v>2020</v>
       </c>
       <c r="G9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I9" s="18">
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K9" s="10" t="s">
         <v>73</v>
@@ -48643,37 +48678,37 @@
         <v>6</v>
       </c>
       <c r="M9" s="18" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O9" t="s">
         <v>96</v>
       </c>
       <c r="P9" s="18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S9">
         <v>1</v>
       </c>
       <c r="T9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U9">
         <v>0</v>
       </c>
       <c r="V9" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W9" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X9" s="18" t="s">
         <v>73</v>
@@ -48703,7 +48738,7 @@
         <v>0</v>
       </c>
       <c r="AG9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AH9">
         <v>0</v>
@@ -48736,13 +48771,13 @@
         <v>73</v>
       </c>
       <c r="AR9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AT9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU9" s="21">
         <v>6.4000000000000001E-2</v>
@@ -48763,8 +48798,9 @@
         <f t="shared" si="0"/>
         <v>3.0476190476190474</v>
       </c>
-      <c r="BA9" s="102" t="s">
-        <v>73</v>
+      <c r="BA9" s="102">
+        <f t="shared" si="1"/>
+        <v>6.6092398761505189E-2</v>
       </c>
       <c r="BB9" s="102"/>
       <c r="BC9" t="s">
@@ -48831,42 +48867,42 @@
         <v>1</v>
       </c>
       <c r="BX9" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.12651408859229724</v>
       </c>
       <c r="BY9" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.12719563288286462</v>
       </c>
       <c r="BZ9" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.7539267521528995E-3</v>
       </c>
       <c r="CA9" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.7605633802816902E-3</v>
       </c>
       <c r="CB9"/>
       <c r="CC9"/>
       <c r="CD9"/>
       <c r="CE9" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.901263827271819E-2</v>
       </c>
       <c r="CF9" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.9014929668500848E-2</v>
       </c>
       <c r="CG9" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.8934740276783467E-5</v>
       </c>
       <c r="CH9" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.8937777431664201E-5</v>
       </c>
     </row>
-    <row r="10" spans="1:86" s="105" customFormat="1" ht="16">
+    <row r="10" spans="1:86" s="105" customFormat="1">
       <c r="A10" s="11" t="s">
         <v>68</v>
       </c>
@@ -48878,22 +48914,22 @@
         <v>107</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F10" s="11">
         <v>2020</v>
       </c>
       <c r="G10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I10" s="18">
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K10" s="10" t="s">
         <v>73</v>
@@ -48902,37 +48938,37 @@
         <v>6</v>
       </c>
       <c r="M10" s="18" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O10" t="s">
         <v>96</v>
       </c>
       <c r="P10" s="18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S10">
         <v>1</v>
       </c>
       <c r="T10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U10">
         <v>0</v>
       </c>
       <c r="V10" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W10" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X10" s="18" t="s">
         <v>73</v>
@@ -48962,7 +48998,7 @@
         <v>0</v>
       </c>
       <c r="AG10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AH10">
         <v>0</v>
@@ -48995,13 +49031,13 @@
         <v>73</v>
       </c>
       <c r="AR10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AT10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU10" s="21">
         <v>6.5000000000000002E-2</v>
@@ -49022,8 +49058,9 @@
         <f t="shared" si="0"/>
         <v>3.0952380952380953</v>
       </c>
-      <c r="BA10" s="102" t="s">
-        <v>73</v>
+      <c r="BA10" s="102">
+        <f t="shared" si="1"/>
+        <v>6.7159024384192634E-2</v>
       </c>
       <c r="BB10" s="102"/>
       <c r="BC10" t="s">
@@ -49090,42 +49127,42 @@
         <v>1</v>
       </c>
       <c r="BX10" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.12845849802371542</v>
       </c>
       <c r="BY10" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.12917216710458213</v>
       </c>
       <c r="BZ10" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.7538975364909846E-3</v>
       </c>
       <c r="CA10" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.7605633802816902E-3</v>
       </c>
       <c r="CB10"/>
       <c r="CC10"/>
       <c r="CD10"/>
       <c r="CE10" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.9603633594857048E-2</v>
       </c>
       <c r="CF10" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.960614541553575E-2</v>
       </c>
       <c r="CG10" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.0130015339135551E-5</v>
       </c>
       <c r="CH10" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.0133242364650637E-5</v>
       </c>
     </row>
-    <row r="11" spans="1:86" s="105" customFormat="1" ht="16">
+    <row r="11" spans="1:86" s="105" customFormat="1">
       <c r="A11" s="11" t="s">
         <v>68</v>
       </c>
@@ -49137,22 +49174,22 @@
         <v>107</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F11" s="11">
         <v>2020</v>
       </c>
       <c r="G11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I11" s="18">
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K11" s="10" t="s">
         <v>73</v>
@@ -49161,37 +49198,37 @@
         <v>6</v>
       </c>
       <c r="M11" s="18" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O11" t="s">
         <v>96</v>
       </c>
       <c r="P11" s="18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S11">
         <v>1</v>
       </c>
       <c r="T11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U11">
         <v>0</v>
       </c>
       <c r="V11" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W11" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X11" s="18" t="s">
         <v>73</v>
@@ -49221,7 +49258,7 @@
         <v>0</v>
       </c>
       <c r="AG11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AH11">
         <v>0</v>
@@ -49254,13 +49291,13 @@
         <v>73</v>
       </c>
       <c r="AR11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AT11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU11" s="21">
         <v>7.8E-2</v>
@@ -49281,8 +49318,9 @@
         <f t="shared" si="0"/>
         <v>3.5454545454545459</v>
       </c>
-      <c r="BA11" s="102" t="s">
-        <v>73</v>
+      <c r="BA11" s="102">
+        <f t="shared" si="1"/>
+        <v>8.1122658670083059E-2</v>
       </c>
       <c r="BB11" s="102"/>
       <c r="BC11" t="s">
@@ -49349,42 +49387,42 @@
         <v>1</v>
       </c>
       <c r="BX11" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.14676596375341069</v>
       </c>
       <c r="BY11" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.14783358799274471</v>
       </c>
       <c r="BZ11" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.753548015859059E-3</v>
       </c>
       <c r="CA11" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.7605633802816902E-3</v>
       </c>
       <c r="CB11"/>
       <c r="CC11"/>
       <c r="CD11"/>
       <c r="CE11" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.4694819007967089E-2</v>
       </c>
       <c r="CF11" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.4699840759681221E-2</v>
       </c>
       <c r="CG11" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.8546027855710976E-5</v>
       </c>
       <c r="CH11" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.8550759819391176E-5</v>
       </c>
     </row>
-    <row r="12" spans="1:86" ht="16">
+    <row r="12" spans="1:86">
       <c r="A12" s="11" t="s">
         <v>68</v>
       </c>
@@ -49396,22 +49434,22 @@
         <v>107</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F12" s="11">
         <v>2020</v>
       </c>
       <c r="G12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I12" s="18">
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>73</v>
@@ -49420,37 +49458,37 @@
         <v>7</v>
       </c>
       <c r="M12" s="18" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O12" t="s">
         <v>96</v>
       </c>
       <c r="P12" s="18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S12">
         <v>1</v>
       </c>
       <c r="T12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U12">
         <v>0</v>
       </c>
       <c r="V12" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W12" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X12" s="18" t="s">
         <v>73</v>
@@ -49480,7 +49518,7 @@
         <v>0</v>
       </c>
       <c r="AG12" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AH12">
         <v>0</v>
@@ -49513,13 +49551,13 @@
         <v>73</v>
       </c>
       <c r="AR12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AT12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU12" s="21">
         <v>7.8E-2</v>
@@ -49540,8 +49578,9 @@
         <f t="shared" si="0"/>
         <v>3.5454545454545459</v>
       </c>
-      <c r="BA12" s="102" t="s">
-        <v>73</v>
+      <c r="BA12" s="102">
+        <f t="shared" si="1"/>
+        <v>8.1122658670083059E-2</v>
       </c>
       <c r="BB12" s="102"/>
       <c r="BC12" t="s">
@@ -49608,39 +49647,39 @@
         <v>1</v>
       </c>
       <c r="BX12" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.14676596375341069</v>
       </c>
       <c r="BY12" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.14783358799274471</v>
       </c>
       <c r="BZ12" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.753548015859059E-3</v>
       </c>
       <c r="CA12" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.7605633802816902E-3</v>
       </c>
       <c r="CE12" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.4694819007967089E-2</v>
       </c>
       <c r="CF12" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.4699840759681221E-2</v>
       </c>
       <c r="CG12" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.8546027855710976E-5</v>
       </c>
       <c r="CH12" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.8550759819391176E-5</v>
       </c>
     </row>
-    <row r="13" spans="1:86" s="107" customFormat="1" ht="16">
+    <row r="13" spans="1:86" s="107" customFormat="1">
       <c r="A13" s="11" t="s">
         <v>68</v>
       </c>
@@ -49652,22 +49691,22 @@
         <v>107</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F13" s="11">
         <v>2020</v>
       </c>
       <c r="G13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I13" s="18">
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K13" s="10" t="s">
         <v>73</v>
@@ -49676,37 +49715,37 @@
         <v>7</v>
       </c>
       <c r="M13" s="18" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O13" t="s">
         <v>96</v>
       </c>
       <c r="P13" s="18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S13">
         <v>1</v>
       </c>
       <c r="T13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U13">
         <v>0</v>
       </c>
       <c r="V13" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W13" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X13" s="18" t="s">
         <v>73</v>
@@ -49736,7 +49775,7 @@
         <v>0</v>
       </c>
       <c r="AG13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AH13">
         <v>0</v>
@@ -49769,13 +49808,13 @@
         <v>73</v>
       </c>
       <c r="AR13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AT13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU13" s="21">
         <v>6.9000000000000006E-2</v>
@@ -49796,8 +49835,9 @@
         <f t="shared" si="0"/>
         <v>2.6538461538461542</v>
       </c>
-      <c r="BA13" s="102" t="s">
-        <v>73</v>
+      <c r="BA13" s="102">
+        <f t="shared" si="1"/>
+        <v>7.1436209148346252E-2</v>
       </c>
       <c r="BB13" s="102"/>
       <c r="BC13" t="s">
@@ -49864,42 +49904,42 @@
         <v>1</v>
       </c>
       <c r="BX13" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.11038135154213211</v>
       </c>
       <c r="BY13" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.11083295461476669</v>
       </c>
       <c r="BZ13" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.7541212363579208E-3</v>
       </c>
       <c r="CA13" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.7605633802816902E-3</v>
       </c>
       <c r="CB13"/>
       <c r="CC13"/>
       <c r="CD13"/>
       <c r="CE13" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.8487062317075937E-2</v>
       </c>
       <c r="CF13" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.8489168865908314E-2</v>
       </c>
       <c r="CG13" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.8546040251420529E-5</v>
       </c>
       <c r="CH13" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.8550759819391176E-5</v>
       </c>
     </row>
-    <row r="14" spans="1:86" ht="16">
+    <row r="14" spans="1:86">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -49910,16 +49950,16 @@
         <v>130</v>
       </c>
       <c r="E14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F14">
         <v>2018</v>
       </c>
       <c r="G14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I14">
         <v>1</v>
@@ -49937,34 +49977,34 @@
         <v>120</v>
       </c>
       <c r="N14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O14" t="s">
         <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="R14" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
       <c r="T14" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U14">
         <v>0</v>
       </c>
       <c r="V14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X14" t="s">
         <v>73</v>
@@ -49994,7 +50034,7 @@
         <v>1</v>
       </c>
       <c r="AG14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AH14">
         <v>0</v>
@@ -50024,13 +50064,13 @@
         <v>0</v>
       </c>
       <c r="AQ14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AR14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AT14" t="s">
         <v>73</v>
@@ -50054,9 +50094,8 @@
         <f t="shared" si="0"/>
         <v>1.8213567929369965</v>
       </c>
-      <c r="BA14" s="123">
-        <f>AU14/8260.69</f>
-        <v>4.9147831476547353E-2</v>
+      <c r="BA14" s="41" t="s">
+        <v>73</v>
       </c>
       <c r="BB14" s="41"/>
       <c r="BC14" t="s">
@@ -50123,39 +50162,39 @@
         <v>1</v>
       </c>
       <c r="BX14" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.336173775143707E-2</v>
       </c>
       <c r="BY14" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.3388945280999909E-2</v>
       </c>
       <c r="BZ14" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.6817980444038869E-4</v>
       </c>
       <c r="CA14" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.6882821387940839E-4</v>
       </c>
       <c r="CE14" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.336173775143707E-2</v>
       </c>
       <c r="CF14" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.3388945280999909E-2</v>
       </c>
       <c r="CG14" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.6817980444038869E-4</v>
       </c>
       <c r="CH14" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5.6882821387940839E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:86" ht="16">
+    <row r="15" spans="1:86">
       <c r="A15" t="s">
         <v>68</v>
       </c>
@@ -50166,16 +50205,16 @@
         <v>130</v>
       </c>
       <c r="E15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F15">
         <v>2018</v>
       </c>
       <c r="G15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I15">
         <v>1</v>
@@ -50190,37 +50229,37 @@
         <v>347</v>
       </c>
       <c r="M15" s="18" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N15" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O15" t="s">
         <v>81</v>
       </c>
       <c r="P15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q15" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="R15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
       <c r="T15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U15">
         <v>0</v>
       </c>
       <c r="V15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X15" t="s">
         <v>73</v>
@@ -50250,7 +50289,7 @@
         <v>1</v>
       </c>
       <c r="AG15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AH15">
         <v>0</v>
@@ -50280,13 +50319,13 @@
         <v>0</v>
       </c>
       <c r="AQ15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AR15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AT15" t="s">
         <v>73</v>
@@ -50310,9 +50349,8 @@
         <f t="shared" si="0"/>
         <v>1.7220426989123607</v>
       </c>
-      <c r="BA15" s="123">
-        <f t="shared" ref="BA15:BA17" si="9">AU15/8260.69</f>
-        <v>0.43415949515113139</v>
+      <c r="BA15" s="41" t="s">
+        <v>73</v>
       </c>
       <c r="BB15" s="41"/>
       <c r="BC15" t="s">
@@ -50379,39 +50417,39 @@
         <v>1</v>
       </c>
       <c r="BX15" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.1001418393220745E-2</v>
       </c>
       <c r="BY15" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.1024417647402674E-2</v>
       </c>
       <c r="BZ15" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.6818020880763031E-4</v>
       </c>
       <c r="CA15" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.6882821387940839E-4</v>
       </c>
       <c r="CE15" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.1001418393220745E-2</v>
       </c>
       <c r="CF15" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.1024417647402674E-2</v>
       </c>
       <c r="CG15" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.6818020880763031E-4</v>
       </c>
       <c r="CH15" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5.6882821387940839E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:86" ht="16">
+    <row r="16" spans="1:86">
       <c r="A16" t="s">
         <v>68</v>
       </c>
@@ -50422,16 +50460,16 @@
         <v>130</v>
       </c>
       <c r="E16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F16">
         <v>2018</v>
       </c>
       <c r="G16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I16">
         <v>1</v>
@@ -50449,34 +50487,34 @@
         <v>120</v>
       </c>
       <c r="N16" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O16" t="s">
         <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="R16" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
       <c r="T16" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U16">
         <v>0</v>
       </c>
       <c r="V16" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W16" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X16" t="s">
         <v>73</v>
@@ -50506,7 +50544,7 @@
         <v>1</v>
       </c>
       <c r="AG16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AH16">
         <v>0</v>
@@ -50536,13 +50574,13 @@
         <v>0</v>
       </c>
       <c r="AQ16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AR16" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AT16" t="s">
         <v>73</v>
@@ -50566,9 +50604,8 @@
         <f t="shared" si="0"/>
         <v>2.2952440645363477</v>
       </c>
-      <c r="BA16" s="123">
-        <f t="shared" si="9"/>
-        <v>2.5711532571734322E-2</v>
+      <c r="BA16" s="41" t="s">
+        <v>73</v>
       </c>
       <c r="BB16" s="41"/>
       <c r="BC16" t="s">
@@ -50635,39 +50672,39 @@
         <v>1</v>
       </c>
       <c r="BX16" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.5991955053229768E-2</v>
       </c>
       <c r="BY16" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.6138742860659789E-2</v>
       </c>
       <c r="BZ16" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.1037156661555521E-3</v>
       </c>
       <c r="CA16" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.1061946902654867E-3</v>
       </c>
       <c r="CE16" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7.5991955053229768E-2</v>
       </c>
       <c r="CF16" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.6138742860659789E-2</v>
       </c>
       <c r="CG16" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.1037156661555521E-3</v>
       </c>
       <c r="CH16" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.1061946902654867E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:86" ht="16">
+    <row r="17" spans="1:86">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -50678,16 +50715,16 @@
         <v>130</v>
       </c>
       <c r="E17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F17">
         <v>2018</v>
       </c>
       <c r="G17" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H17" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I17">
         <v>1</v>
@@ -50702,37 +50739,37 @@
         <v>348</v>
       </c>
       <c r="M17" s="18" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O17" t="s">
         <v>81</v>
       </c>
       <c r="P17" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q17" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="R17" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U17">
         <v>0</v>
       </c>
       <c r="V17" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W17" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X17" t="s">
         <v>73</v>
@@ -50762,7 +50799,7 @@
         <v>1</v>
       </c>
       <c r="AG17" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AH17">
         <v>0</v>
@@ -50792,13 +50829,13 @@
         <v>0</v>
       </c>
       <c r="AQ17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AR17" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AT17" t="s">
         <v>73</v>
@@ -50822,9 +50859,8 @@
         <f t="shared" si="0"/>
         <v>0.4628137059347513</v>
       </c>
-      <c r="BA17" s="123">
-        <f t="shared" si="9"/>
-        <v>3.6542589057330564E-2</v>
+      <c r="BA17" s="41" t="s">
+        <v>73</v>
       </c>
       <c r="BB17" s="41"/>
       <c r="BC17" t="s">
@@ -50891,39 +50927,39 @@
         <v>1</v>
       </c>
       <c r="BX17" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.5365662610743538E-2</v>
       </c>
       <c r="BY17" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.5366872078105973E-2</v>
       </c>
       <c r="BZ17" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.1037526978339323E-3</v>
       </c>
       <c r="CA17" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.1061946902654867E-3</v>
       </c>
       <c r="CE17" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.5365662610743538E-2</v>
       </c>
       <c r="CF17" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.5366872078105973E-2</v>
       </c>
       <c r="CG17" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.1037526978339323E-3</v>
       </c>
       <c r="CH17" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.1061946902654867E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:86" s="107" customFormat="1" ht="16">
+    <row r="18" spans="1:86" s="107" customFormat="1">
       <c r="A18" s="11" t="s">
         <v>68</v>
       </c>
@@ -50935,46 +50971,46 @@
         <v>137</v>
       </c>
       <c r="E18" t="s">
-        <v>617</v>
+        <v>250</v>
       </c>
       <c r="F18" s="100">
         <v>2015</v>
       </c>
       <c r="G18" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H18" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I18" s="101">
         <v>1</v>
       </c>
       <c r="J18" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K18" s="100" t="s">
         <v>73</v>
       </c>
       <c r="L18" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M18" s="18" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N18" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O18" t="s">
         <v>81</v>
       </c>
       <c r="P18" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q18" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R18" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -50986,10 +51022,10 @@
         <v>0</v>
       </c>
       <c r="V18" s="100" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W18" s="100" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X18" s="100" t="s">
         <v>73</v>
@@ -51019,7 +51055,7 @@
         <v>0</v>
       </c>
       <c r="AG18" s="101" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AH18" s="101">
         <v>0</v>
@@ -51052,13 +51088,13 @@
         <v>73</v>
       </c>
       <c r="AR18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS18" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AT18" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU18" s="21">
         <v>2.7799999999999998E-2</v>
@@ -51079,8 +51115,9 @@
       <c r="AZ18">
         <v>2.04</v>
       </c>
-      <c r="BA18" s="102" t="s">
-        <v>73</v>
+      <c r="BA18" s="102">
+        <f t="shared" ref="BA18:BA27" si="11">EXP(AU18) - 1</f>
+        <v>2.8190025851083211E-2</v>
       </c>
       <c r="BB18" s="102"/>
       <c r="BC18" s="103" t="s">
@@ -51115,13 +51152,13 @@
         <v>73</v>
       </c>
       <c r="BM18" s="101" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="BN18" s="101">
         <v>0.1</v>
       </c>
       <c r="BO18" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="BP18" s="103" t="s">
         <v>73</v>
@@ -51148,42 +51185,42 @@
         <v>1</v>
       </c>
       <c r="BX18" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.9399418017388252E-2</v>
       </c>
       <c r="BY18" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.9401852142681517E-2</v>
       </c>
       <c r="BZ18" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9.0473161883565525E-5</v>
       </c>
       <c r="CA18" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.0489548457153195E-5</v>
       </c>
       <c r="CB18"/>
       <c r="CC18"/>
       <c r="CD18"/>
       <c r="CE18" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6.1963113535979377E-3</v>
       </c>
       <c r="CF18" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6.1963906563842173E-3</v>
       </c>
       <c r="CG18" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9.2262838237946257E-6</v>
       </c>
       <c r="CH18" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.2264540891644526E-6</v>
       </c>
     </row>
-    <row r="19" spans="1:86" s="107" customFormat="1" ht="17" customHeight="1">
+    <row r="19" spans="1:86" s="107" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A19" s="11" t="s">
         <v>68</v>
       </c>
@@ -51195,46 +51232,46 @@
         <v>137</v>
       </c>
       <c r="E19" t="s">
-        <v>617</v>
+        <v>250</v>
       </c>
       <c r="F19" s="100">
         <v>2015</v>
       </c>
       <c r="G19" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H19" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I19" s="101">
         <v>1</v>
       </c>
       <c r="J19" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K19" s="100" t="s">
         <v>73</v>
       </c>
       <c r="L19" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M19" s="18" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N19" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O19" t="s">
         <v>81</v>
       </c>
       <c r="P19" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q19" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R19" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -51246,10 +51283,10 @@
         <v>0</v>
       </c>
       <c r="V19" s="100" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W19" s="100" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X19" s="100" t="s">
         <v>73</v>
@@ -51279,7 +51316,7 @@
         <v>0</v>
       </c>
       <c r="AG19" s="101" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AH19" s="101">
         <v>0</v>
@@ -51309,16 +51346,16 @@
         <v>0</v>
       </c>
       <c r="AQ19" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AR19" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AT19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU19">
         <v>5.4399999999999997E-2</v>
@@ -51339,8 +51376,9 @@
       <c r="AZ19">
         <v>3.63</v>
       </c>
-      <c r="BA19" s="102" t="s">
-        <v>73</v>
+      <c r="BA19" s="102">
+        <f t="shared" si="11"/>
+        <v>5.590688044596992E-2</v>
       </c>
       <c r="BB19" s="102"/>
       <c r="BC19" s="103" t="s">
@@ -51375,13 +51413,13 @@
         <v>73</v>
       </c>
       <c r="BM19" s="101" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="BN19" s="101">
         <v>0.1</v>
       </c>
       <c r="BO19" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="BP19" s="103" t="s">
         <v>73</v>
@@ -51408,42 +51446,42 @@
         <v>1</v>
       </c>
       <c r="BX19" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.4505490005142594E-2</v>
       </c>
       <c r="BY19" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.4519194206964816E-2</v>
       </c>
       <c r="BZ19" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9.0473046245324396E-5</v>
       </c>
       <c r="CA19" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.0489548457153195E-5</v>
       </c>
       <c r="CB19"/>
       <c r="CC19"/>
       <c r="CD19"/>
       <c r="CE19" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.8739199625567457E-2</v>
       </c>
       <c r="CF19" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.8741393558640896E-2</v>
       </c>
       <c r="CG19" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.6659554162372169E-5</v>
       </c>
       <c r="CH19" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.6660978991148553E-5</v>
       </c>
     </row>
-    <row r="20" spans="1:86" s="107" customFormat="1" ht="16">
+    <row r="20" spans="1:86" s="107" customFormat="1">
       <c r="A20" s="11" t="s">
         <v>68</v>
       </c>
@@ -51455,46 +51493,46 @@
         <v>137</v>
       </c>
       <c r="E20" t="s">
-        <v>617</v>
+        <v>250</v>
       </c>
       <c r="F20" s="100">
         <v>2015</v>
       </c>
       <c r="G20" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H20" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I20" s="101">
         <v>1</v>
       </c>
       <c r="J20" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K20" s="100" t="s">
         <v>73</v>
       </c>
       <c r="L20" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M20" s="18" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N20" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O20" t="s">
         <v>81</v>
       </c>
       <c r="P20" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q20" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R20" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -51506,10 +51544,10 @@
         <v>0</v>
       </c>
       <c r="V20" s="100" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W20" s="100" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X20" s="100" t="s">
         <v>73</v>
@@ -51539,7 +51577,7 @@
         <v>0</v>
       </c>
       <c r="AG20" s="101" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AH20" s="101">
         <v>0</v>
@@ -51572,13 +51610,13 @@
         <v>73</v>
       </c>
       <c r="AR20" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS20" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AT20" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU20" s="21">
         <v>5.4600000000000003E-2</v>
@@ -51599,8 +51637,9 @@
       <c r="AZ20">
         <v>3.15</v>
       </c>
-      <c r="BA20" s="102" t="s">
-        <v>73</v>
+      <c r="BA20" s="102">
+        <f t="shared" si="11"/>
+        <v>5.6118082941604586E-2</v>
       </c>
       <c r="BB20" s="102"/>
       <c r="BC20" s="103" t="s">
@@ -51635,13 +51674,13 @@
         <v>73</v>
       </c>
       <c r="BM20" s="101" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="BN20" s="101">
         <v>0.1</v>
       </c>
       <c r="BO20" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="BP20" s="103" t="s">
         <v>73</v>
@@ -51668,42 +51707,42 @@
         <v>1</v>
       </c>
       <c r="BX20" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.9877055832671907E-2</v>
       </c>
       <c r="BY20" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.9885950400025899E-2</v>
       </c>
       <c r="BZ20" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9.0049455402728065E-5</v>
       </c>
       <c r="CA20" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.0065747996037111E-5</v>
       </c>
       <c r="CB20"/>
       <c r="CC20"/>
       <c r="CD20"/>
       <c r="CE20" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.2012412374711942E-2</v>
       </c>
       <c r="CF20" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.2012990213972756E-2</v>
       </c>
       <c r="CG20" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.4544819559496541E-5</v>
       </c>
       <c r="CH20" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.4545242978283952E-5</v>
       </c>
     </row>
-    <row r="21" spans="1:86" ht="16">
+    <row r="21" spans="1:86">
       <c r="A21" s="11" t="s">
         <v>68</v>
       </c>
@@ -51715,46 +51754,46 @@
         <v>137</v>
       </c>
       <c r="E21" t="s">
-        <v>617</v>
+        <v>250</v>
       </c>
       <c r="F21" s="100">
         <v>2015</v>
       </c>
       <c r="G21" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H21" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I21" s="101">
         <v>1</v>
       </c>
       <c r="J21" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K21" s="100" t="s">
         <v>73</v>
       </c>
       <c r="L21" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M21" s="18" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N21" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O21" t="s">
         <v>81</v>
       </c>
       <c r="P21" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q21" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R21" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -51766,10 +51805,10 @@
         <v>0</v>
       </c>
       <c r="V21" s="100" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W21" s="100" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X21" s="100" t="s">
         <v>73</v>
@@ -51799,7 +51838,7 @@
         <v>0</v>
       </c>
       <c r="AG21" s="101" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AH21" s="101">
         <v>0</v>
@@ -51829,16 +51868,16 @@
         <v>0</v>
       </c>
       <c r="AQ21" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AR21" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS21" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AT21" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU21" s="21">
         <v>4.19E-2</v>
@@ -51859,8 +51898,9 @@
       <c r="AZ21">
         <v>2.4900000000000002</v>
       </c>
-      <c r="BA21" s="102" t="s">
-        <v>73</v>
+      <c r="BA21" s="102">
+        <f t="shared" si="11"/>
+        <v>4.2790194517186686E-2</v>
       </c>
       <c r="BB21" s="102"/>
       <c r="BC21" s="103" t="s">
@@ -51895,13 +51935,13 @@
         <v>73</v>
       </c>
       <c r="BM21" s="101" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="BN21" s="101">
         <v>0.1</v>
       </c>
       <c r="BO21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="BP21" s="103" t="s">
         <v>73</v>
@@ -51928,39 +51968,39 @@
         <v>1</v>
       </c>
       <c r="BX21" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.3621056611749961E-2</v>
       </c>
       <c r="BY21" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.3625451239868967E-2</v>
       </c>
       <c r="BZ21" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9.0049499185523786E-5</v>
       </c>
       <c r="CA21" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.0065747996037111E-5</v>
       </c>
       <c r="CE21" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.3650404945197309E-2</v>
       </c>
       <c r="CF21" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.3651252882826532E-2</v>
       </c>
       <c r="CG21" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.0059817995947289E-5</v>
       </c>
       <c r="CH21" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.0061626333984669E-5</v>
       </c>
     </row>
-    <row r="22" spans="1:86" ht="16">
+    <row r="22" spans="1:86">
       <c r="A22" s="11" t="s">
         <v>68</v>
       </c>
@@ -51972,16 +52012,16 @@
         <v>138</v>
       </c>
       <c r="E22" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F22" s="100">
         <v>1988</v>
       </c>
       <c r="G22" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H22" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I22" s="101">
         <v>1</v>
@@ -51999,19 +52039,19 @@
         <v>93</v>
       </c>
       <c r="N22" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O22" t="s">
         <v>81</v>
       </c>
       <c r="P22" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R22" s="32" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -52023,10 +52063,10 @@
         <v>0</v>
       </c>
       <c r="V22" s="100" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W22" s="100" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X22" s="100" t="s">
         <v>73</v>
@@ -52056,7 +52096,7 @@
         <v>0</v>
       </c>
       <c r="AG22" s="101" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AH22" s="101">
         <v>0</v>
@@ -52089,13 +52129,13 @@
         <v>73</v>
       </c>
       <c r="AR22" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS22" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AT22" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU22" s="7">
         <v>0.01</v>
@@ -52116,8 +52156,9 @@
       <c r="AZ22">
         <v>0.23</v>
       </c>
-      <c r="BA22" s="102" t="s">
-        <v>73</v>
+      <c r="BA22" s="102">
+        <f t="shared" si="11"/>
+        <v>1.0050167084167949E-2</v>
       </c>
       <c r="BB22" s="102"/>
       <c r="BC22" s="103" t="s">
@@ -52159,7 +52200,7 @@
         <v>1</v>
       </c>
       <c r="BO22" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="BP22" s="103" t="s">
         <v>73</v>
@@ -52186,39 +52227,39 @@
         <v>1</v>
       </c>
       <c r="BX22" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.0134490446309997E-2</v>
       </c>
       <c r="BY22" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.0134837431758794E-2</v>
       </c>
       <c r="BZ22" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.9455252713028077E-3</v>
       </c>
       <c r="CA22" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.953125E-3</v>
       </c>
       <c r="CE22" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.0134490446309997E-2</v>
       </c>
       <c r="CF22" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.0134837431758794E-2</v>
       </c>
       <c r="CG22" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.9455252713028077E-3</v>
       </c>
       <c r="CH22" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.953125E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:86" ht="16">
+    <row r="23" spans="1:86">
       <c r="A23" s="11" t="s">
         <v>68</v>
       </c>
@@ -52230,16 +52271,16 @@
         <v>138</v>
       </c>
       <c r="E23" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F23" s="100">
         <v>1988</v>
       </c>
       <c r="G23" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H23" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I23" s="101">
         <v>1</v>
@@ -52257,19 +52298,19 @@
         <v>93</v>
       </c>
       <c r="N23" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O23" t="s">
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q23" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R23" s="32" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -52281,10 +52322,10 @@
         <v>0</v>
       </c>
       <c r="V23" s="100" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W23" s="100" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X23" s="100" t="s">
         <v>73</v>
@@ -52314,7 +52355,7 @@
         <v>0</v>
       </c>
       <c r="AG23" s="101" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AH23" s="101">
         <v>0</v>
@@ -52344,16 +52385,16 @@
         <v>0</v>
       </c>
       <c r="AQ23" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AR23" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS23" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AT23" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU23" s="7">
         <v>0.12</v>
@@ -52374,8 +52415,9 @@
       <c r="AZ23">
         <v>4.83</v>
       </c>
-      <c r="BA23" s="102" t="s">
-        <v>73</v>
+      <c r="BA23" s="102">
+        <f t="shared" si="11"/>
+        <v>0.12749685157937574</v>
       </c>
       <c r="BB23" s="102"/>
       <c r="BC23" s="103" t="s">
@@ -52417,7 +52459,7 @@
         <v>1</v>
       </c>
       <c r="BO23" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="BP23" s="103" t="s">
         <v>73</v>
@@ -52444,39 +52486,39 @@
         <v>1</v>
       </c>
       <c r="BX23" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.20817246417215696</v>
       </c>
       <c r="BY23" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.21126026317506777</v>
       </c>
       <c r="BZ23" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.9416499666781906E-3</v>
       </c>
       <c r="CA23" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.953125E-3</v>
       </c>
       <c r="CE23" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.20817246417215696</v>
       </c>
       <c r="CF23" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.21126026317506777</v>
       </c>
       <c r="CG23" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.9416499666781906E-3</v>
       </c>
       <c r="CH23" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.953125E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:86" ht="16">
+    <row r="24" spans="1:86">
       <c r="A24" s="11" t="s">
         <v>68</v>
       </c>
@@ -52488,16 +52530,16 @@
         <v>139</v>
       </c>
       <c r="E24" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F24" s="100">
         <v>2013</v>
       </c>
       <c r="G24" t="s">
-        <v>269</v>
-      </c>
-      <c r="H24" t="s">
-        <v>270</v>
+        <v>271</v>
+      </c>
+      <c r="H24" s="123" t="s">
+        <v>272</v>
       </c>
       <c r="I24" s="101">
         <v>1</v>
@@ -52515,34 +52557,34 @@
         <v>120</v>
       </c>
       <c r="N24" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O24" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P24" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q24" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R24" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S24">
         <v>0</v>
       </c>
       <c r="T24" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U24">
         <v>0</v>
       </c>
       <c r="V24" s="100" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W24" s="100" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X24" s="100" t="s">
         <v>73</v>
@@ -52572,7 +52614,7 @@
         <v>0</v>
       </c>
       <c r="AG24" s="101" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AH24" s="101">
         <v>0</v>
@@ -52605,13 +52647,13 @@
         <v>73</v>
       </c>
       <c r="AR24" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS24" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AT24" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU24" s="108">
         <v>0.77300000000000002</v>
@@ -52629,11 +52671,12 @@
         <v>1</v>
       </c>
       <c r="AZ24">
-        <f t="shared" ref="AZ24:AZ30" si="11">AU24/AW24</f>
+        <f t="shared" ref="AZ24:AZ30" si="12">AU24/AW24</f>
         <v>20.342105263157897</v>
       </c>
-      <c r="BA24" s="102" t="s">
-        <v>73</v>
+      <c r="BA24" s="109">
+        <f>EXP(AU24) - 1</f>
+        <v>1.1662552812206535</v>
       </c>
       <c r="BB24" s="109"/>
       <c r="BC24" s="103" t="s">
@@ -52700,35 +52743,35 @@
         <v>0</v>
       </c>
       <c r="BX24" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.38045554301813767</v>
       </c>
       <c r="BY24" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.40059218306919919</v>
       </c>
       <c r="BZ24" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.9862850415234801E-4</v>
       </c>
       <c r="CA24" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.0950040950040953E-4</v>
       </c>
       <c r="CE24" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.38045554301813767</v>
       </c>
       <c r="CF24" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.40059218306919919</v>
       </c>
       <c r="CG24" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.9862850415234801E-4</v>
       </c>
       <c r="CH24" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.0950040950040953E-4</v>
       </c>
     </row>
@@ -52744,16 +52787,16 @@
         <v>139</v>
       </c>
       <c r="E25" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F25" s="100">
         <v>2013</v>
       </c>
       <c r="G25" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H25" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="I25" s="101">
         <v>1</v>
@@ -52768,37 +52811,37 @@
         <v>283</v>
       </c>
       <c r="M25" s="18" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N25" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O25" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P25" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q25" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R25" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S25">
         <v>0</v>
       </c>
       <c r="T25" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U25">
         <v>0</v>
       </c>
       <c r="V25" s="100" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W25" s="100" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X25" s="100" t="s">
         <v>73</v>
@@ -52828,46 +52871,46 @@
         <v>0</v>
       </c>
       <c r="AG25" s="101" t="s">
+        <v>277</v>
+      </c>
+      <c r="AH25" s="101">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="101">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="101">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="101">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="101">
+        <v>0</v>
+      </c>
+      <c r="AM25" s="101">
+        <v>1</v>
+      </c>
+      <c r="AN25" s="101">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="101">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="101">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR25" t="s">
+        <v>234</v>
+      </c>
+      <c r="AS25" t="s">
         <v>275</v>
       </c>
-      <c r="AH25" s="101">
-        <v>0</v>
-      </c>
-      <c r="AI25" s="101">
-        <v>0</v>
-      </c>
-      <c r="AJ25" s="101">
-        <v>0</v>
-      </c>
-      <c r="AK25" s="101">
-        <v>0</v>
-      </c>
-      <c r="AL25" s="101">
-        <v>0</v>
-      </c>
-      <c r="AM25" s="101">
-        <v>1</v>
-      </c>
-      <c r="AN25" s="101">
-        <v>0</v>
-      </c>
-      <c r="AO25" s="101">
-        <v>0</v>
-      </c>
-      <c r="AP25" s="101">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR25" t="s">
-        <v>233</v>
-      </c>
-      <c r="AS25" t="s">
-        <v>273</v>
-      </c>
       <c r="AT25" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU25" s="108">
         <v>0.84</v>
@@ -52885,11 +52928,12 @@
         <v>1</v>
       </c>
       <c r="AZ25">
+        <f t="shared" si="12"/>
+        <v>13.770491803278688</v>
+      </c>
+      <c r="BA25" s="109">
         <f t="shared" si="11"/>
-        <v>13.770491803278688</v>
-      </c>
-      <c r="BA25" s="102" t="s">
-        <v>73</v>
+        <v>1.3163669767810915</v>
       </c>
       <c r="BB25" s="109"/>
       <c r="BC25" s="103" t="s">
@@ -52956,39 +53000,39 @@
         <v>1</v>
       </c>
       <c r="BX25" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.26889407517381664</v>
       </c>
       <c r="BY25" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.27567131993753202</v>
       </c>
       <c r="BZ25" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.0880954322490722E-4</v>
       </c>
       <c r="CA25" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.1152263374485596E-4</v>
       </c>
       <c r="CE25" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.26889407517381664</v>
       </c>
       <c r="CF25" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.27567131993753202</v>
       </c>
       <c r="CG25" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.0880954322490722E-4</v>
       </c>
       <c r="CH25" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.1152263374485596E-4</v>
       </c>
     </row>
-    <row r="26" spans="1:86" ht="16">
+    <row r="26" spans="1:86">
       <c r="A26" s="11" t="s">
         <v>68</v>
       </c>
@@ -53000,16 +53044,16 @@
         <v>139</v>
       </c>
       <c r="E26" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F26" s="100">
         <v>2013</v>
       </c>
       <c r="G26" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H26" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="I26" s="101">
         <v>1</v>
@@ -53027,34 +53071,34 @@
         <v>120</v>
       </c>
       <c r="N26" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O26" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P26" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q26" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R26" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S26">
         <v>0</v>
       </c>
       <c r="T26" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U26">
         <v>0</v>
       </c>
       <c r="V26" s="100" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W26" s="100" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X26" s="100" t="s">
         <v>73</v>
@@ -53084,7 +53128,7 @@
         <v>0</v>
       </c>
       <c r="AG26" s="101" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AH26" s="101">
         <v>0</v>
@@ -53117,13 +53161,13 @@
         <v>73</v>
       </c>
       <c r="AR26" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS26" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AT26" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU26" s="108">
         <v>1.0999999999999999E-2</v>
@@ -53141,11 +53185,12 @@
         <v>2</v>
       </c>
       <c r="AZ26">
+        <f t="shared" si="12"/>
+        <v>0.36666666666666664</v>
+      </c>
+      <c r="BA26" s="102">
         <f t="shared" si="11"/>
-        <v>0.36666666666666664</v>
-      </c>
-      <c r="BA26" s="102" t="s">
-        <v>73</v>
+        <v>1.1060722444719451E-2</v>
       </c>
       <c r="BB26" s="102"/>
       <c r="BC26" s="103" t="s">
@@ -53212,39 +53257,39 @@
         <v>0</v>
       </c>
       <c r="BX26" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.4151520133472265E-3</v>
       </c>
       <c r="BY26" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.4152879239220478E-3</v>
       </c>
       <c r="BZ26" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.0916530154520679E-4</v>
       </c>
       <c r="CA26" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.0950040950040953E-4</v>
       </c>
       <c r="CE26" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7.4151520133472265E-3</v>
       </c>
       <c r="CF26" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.4152879239220478E-3</v>
       </c>
       <c r="CG26" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.0916530154520679E-4</v>
       </c>
       <c r="CH26" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.0950040950040953E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:86" ht="16">
+    <row r="27" spans="1:86">
       <c r="A27" s="11" t="s">
         <v>68</v>
       </c>
@@ -53256,16 +53301,16 @@
         <v>139</v>
       </c>
       <c r="E27" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F27" s="100">
         <v>2013</v>
       </c>
       <c r="G27" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H27" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="I27" s="101">
         <v>1</v>
@@ -53280,37 +53325,37 @@
         <v>283</v>
       </c>
       <c r="M27" s="18" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N27" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O27" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P27" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q27" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R27" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S27">
         <v>0</v>
       </c>
       <c r="T27" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U27">
         <v>0</v>
       </c>
       <c r="V27" s="100" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W27" s="100" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X27" s="100" t="s">
         <v>73</v>
@@ -53340,7 +53385,7 @@
         <v>0</v>
       </c>
       <c r="AG27" s="101" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AH27" s="101">
         <v>0</v>
@@ -53373,13 +53418,13 @@
         <v>73</v>
       </c>
       <c r="AR27" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS27" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AT27" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU27" s="108">
         <v>9.5000000000000001E-2</v>
@@ -53397,11 +53442,12 @@
         <v>1</v>
       </c>
       <c r="AZ27">
+        <f t="shared" si="12"/>
+        <v>1.6964285714285714</v>
+      </c>
+      <c r="BA27" s="102">
         <f t="shared" si="11"/>
-        <v>1.6964285714285714</v>
-      </c>
-      <c r="BA27" s="102" t="s">
-        <v>73</v>
+        <v>9.9658855126102841E-2</v>
       </c>
       <c r="BB27" s="102"/>
       <c r="BC27" s="103" t="s">
@@ -53468,39 +53514,39 @@
         <v>1</v>
       </c>
       <c r="BX27" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.4372239036265163E-2</v>
       </c>
       <c r="BY27" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.4385785009859983E-2</v>
       </c>
       <c r="BZ27" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.1118363567940286E-4</v>
       </c>
       <c r="CA27" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.1152263374485596E-4</v>
       </c>
       <c r="CE27" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.4372239036265163E-2</v>
       </c>
       <c r="CF27" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.4385785009859983E-2</v>
       </c>
       <c r="CG27" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.1118363567940286E-4</v>
       </c>
       <c r="CH27" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.1152263374485596E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:86" ht="16">
+    <row r="28" spans="1:86">
       <c r="A28" s="94" t="s">
         <v>68</v>
       </c>
@@ -53512,16 +53558,16 @@
         <v>140</v>
       </c>
       <c r="E28" s="94" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F28" s="94">
         <v>2016</v>
       </c>
       <c r="G28" s="58" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H28" s="94" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I28" s="94">
         <v>1</v>
@@ -53539,37 +53585,37 @@
         <v>120</v>
       </c>
       <c r="N28" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O28" s="94" t="s">
         <v>124</v>
       </c>
       <c r="P28" s="94" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q28" s="94" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="R28" s="94" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="S28" s="94">
         <v>0</v>
       </c>
       <c r="T28" s="94" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U28" s="94">
         <v>0</v>
       </c>
       <c r="V28" s="94" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="W28" s="94" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X28" s="94" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Y28" s="94">
         <v>0</v>
@@ -53596,7 +53642,7 @@
         <v>1</v>
       </c>
       <c r="AG28" s="94" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AH28" s="94">
         <v>0</v>
@@ -53626,16 +53672,16 @@
         <v>0</v>
       </c>
       <c r="AQ28" s="94" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AR28" s="94" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS28" s="94" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AT28" s="41" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU28" s="113">
         <v>3.8109999999999999</v>
@@ -53653,12 +53699,12 @@
         <v>2</v>
       </c>
       <c r="AZ28" s="94">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.6066610455311974</v>
       </c>
       <c r="BA28" s="114">
-        <f>AU28/437.369</f>
-        <v>8.7134662035946754E-3</v>
+        <f>AU28*AW28*SQRT(BI28)*0.25/100</f>
+        <v>0.39790050382451009</v>
       </c>
       <c r="BB28" s="114"/>
       <c r="BC28" s="94" t="s">
@@ -53725,42 +53771,42 @@
         <v>1</v>
       </c>
       <c r="BX28" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9.0874644742587773E-2</v>
       </c>
       <c r="BY28" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9.112604528874467E-2</v>
       </c>
       <c r="BZ28" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.2360227971281281E-3</v>
       </c>
       <c r="CA28" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.2573289902280132E-3</v>
       </c>
       <c r="CB28" s="94"/>
       <c r="CC28" s="94"/>
       <c r="CD28" s="94"/>
       <c r="CE28" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.0874644742587773E-2</v>
       </c>
       <c r="CF28" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.112604528874467E-2</v>
       </c>
       <c r="CG28" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.2360227971281281E-3</v>
       </c>
       <c r="CH28" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.2573289902280132E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:86" ht="16">
+    <row r="29" spans="1:86">
       <c r="A29" s="94" t="s">
         <v>68</v>
       </c>
@@ -53772,16 +53818,16 @@
         <v>140</v>
       </c>
       <c r="E29" s="94" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F29" s="94">
         <v>2016</v>
       </c>
       <c r="G29" s="58" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H29" s="94" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I29" s="94">
         <v>1</v>
@@ -53799,37 +53845,37 @@
         <v>120</v>
       </c>
       <c r="N29" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O29" s="94" t="s">
         <v>124</v>
       </c>
       <c r="P29" s="94" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q29" s="94" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="R29" s="94" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="S29" s="94">
         <v>0</v>
       </c>
       <c r="T29" s="94" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U29" s="94">
         <v>0</v>
       </c>
       <c r="V29" s="94" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="W29" s="94" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X29" s="94" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Y29" s="94">
         <v>0</v>
@@ -53856,7 +53902,7 @@
         <v>1</v>
       </c>
       <c r="AG29" s="94" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AH29" s="94">
         <v>0</v>
@@ -53886,16 +53932,16 @@
         <v>0</v>
       </c>
       <c r="AQ29" s="94" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AR29" s="94" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS29" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AT29" s="41" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU29" s="113">
         <v>1.9039999999999999</v>
@@ -53913,12 +53959,12 @@
         <v>2</v>
       </c>
       <c r="AZ29" s="94">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.67517730496453898</v>
       </c>
       <c r="BA29" s="114">
-        <f t="shared" ref="BA29:BA30" si="12">AU29/437.369</f>
-        <v>4.3533035034490327E-3</v>
+        <f>AU29*AW29*SQRT(BI29)*0.25/100</f>
+        <v>0.23633982409742121</v>
       </c>
       <c r="BB29" s="114"/>
       <c r="BC29" s="94" t="s">
@@ -53985,42 +54031,42 @@
         <v>1</v>
       </c>
       <c r="BX29" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.8319329539764628E-2</v>
       </c>
       <c r="BY29" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.8338101745567565E-2</v>
       </c>
       <c r="BZ29" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.2362389632958908E-3</v>
       </c>
       <c r="CA29" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.2573289902280132E-3</v>
       </c>
       <c r="CB29" s="94"/>
       <c r="CC29" s="94"/>
       <c r="CD29" s="94"/>
       <c r="CE29" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.8319329539764628E-2</v>
       </c>
       <c r="CF29" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.8338101745567565E-2</v>
       </c>
       <c r="CG29" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.2362389632958908E-3</v>
       </c>
       <c r="CH29" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.2573289902280132E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:86" ht="16">
+    <row r="30" spans="1:86">
       <c r="A30" s="94" t="s">
         <v>68</v>
       </c>
@@ -54032,16 +54078,16 @@
         <v>140</v>
       </c>
       <c r="E30" s="94" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F30" s="94">
         <v>2016</v>
       </c>
       <c r="G30" s="58" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H30" s="94" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I30" s="94">
         <v>1</v>
@@ -54059,37 +54105,37 @@
         <v>120</v>
       </c>
       <c r="N30" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O30" s="94" t="s">
         <v>124</v>
       </c>
       <c r="P30" s="94" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q30" s="94" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="R30" s="94" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="S30" s="94">
         <v>0</v>
       </c>
       <c r="T30" s="94" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U30" s="94">
         <v>0</v>
       </c>
       <c r="V30" s="94" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="W30" s="94" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X30" s="94" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Y30" s="94">
         <v>0</v>
@@ -54116,7 +54162,7 @@
         <v>1</v>
       </c>
       <c r="AG30" s="94" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AH30" s="94">
         <v>0</v>
@@ -54146,16 +54192,16 @@
         <v>0</v>
       </c>
       <c r="AQ30" s="94" t="s">
+        <v>290</v>
+      </c>
+      <c r="AR30" s="94" t="s">
+        <v>234</v>
+      </c>
+      <c r="AS30" t="s">
         <v>288</v>
       </c>
-      <c r="AR30" s="94" t="s">
-        <v>233</v>
-      </c>
-      <c r="AS30" t="s">
-        <v>286</v>
-      </c>
       <c r="AT30" s="41" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU30" s="113">
         <v>6.681</v>
@@ -54173,12 +54219,12 @@
         <v>1</v>
       </c>
       <c r="AZ30" s="94">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.9500875656742556</v>
       </c>
       <c r="BA30" s="114">
-        <f t="shared" si="12"/>
-        <v>1.5275431043352409E-2</v>
+        <f>AU30*AW30*SQRT(BI30)*0.25/100</f>
+        <v>1.0075107436727511</v>
       </c>
       <c r="BB30" s="114"/>
       <c r="BC30" s="94" t="s">
@@ -54245,42 +54291,42 @@
         <v>1</v>
       </c>
       <c r="BX30" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.11008437401907406</v>
       </c>
       <c r="BY30" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.11053232404190938</v>
       </c>
       <c r="BZ30" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.235762897306693E-3</v>
       </c>
       <c r="CA30" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.2573289902280132E-3</v>
       </c>
       <c r="CB30" s="94"/>
       <c r="CC30" s="94"/>
       <c r="CD30" s="94"/>
       <c r="CE30" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.11008437401907406</v>
       </c>
       <c r="CF30" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.11053232404190938</v>
       </c>
       <c r="CG30" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.235762897306693E-3</v>
       </c>
       <c r="CH30" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.2573289902280132E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:86" ht="16">
+    <row r="31" spans="1:86">
       <c r="A31" s="94" t="s">
         <v>68</v>
       </c>
@@ -54292,13 +54338,13 @@
         <v>148</v>
       </c>
       <c r="E31" s="96" t="s">
-        <v>618</v>
+        <v>291</v>
       </c>
       <c r="F31" s="94">
         <v>2016</v>
       </c>
       <c r="G31" s="97" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="H31" s="94" t="s">
         <v>177</v>
@@ -54319,19 +54365,19 @@
         <v>93</v>
       </c>
       <c r="N31" s="94" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="O31" s="94" t="s">
         <v>81</v>
       </c>
       <c r="P31" s="94" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q31" s="94" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R31" s="94" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S31" s="94">
         <v>0</v>
@@ -54343,10 +54389,10 @@
         <v>0</v>
       </c>
       <c r="V31" s="94" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="W31" s="94" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X31" s="94" t="s">
         <v>180</v>
@@ -54406,16 +54452,16 @@
         <v>0</v>
       </c>
       <c r="AQ31" s="94" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AR31" s="94" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS31" s="94" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AT31" s="94" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AU31" s="98">
         <v>3.5900000000000001E-2</v>
@@ -54436,7 +54482,7 @@
       <c r="AZ31" s="94">
         <v>1.01</v>
       </c>
-      <c r="BA31" s="124">
+      <c r="BA31" s="99">
         <v>0.08</v>
       </c>
       <c r="BB31" s="99"/>
@@ -54471,13 +54517,13 @@
         <v>73</v>
       </c>
       <c r="BM31" s="94" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="BN31" t="s">
         <v>73</v>
       </c>
       <c r="BO31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="BP31" s="94" t="s">
         <v>73</v>
@@ -54504,42 +54550,42 @@
         <v>1</v>
       </c>
       <c r="BX31" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.9731353950735877E-2</v>
       </c>
       <c r="BY31" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.9740118977144511E-2</v>
       </c>
       <c r="BZ31" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.6805487647964076E-4</v>
       </c>
       <c r="CA31" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8.6956521739130438E-4</v>
       </c>
       <c r="CB31" s="94"/>
       <c r="CC31" s="94"/>
       <c r="CD31" s="94"/>
       <c r="CE31" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.5593158559973195E-3</v>
       </c>
       <c r="CF31" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8.5595248890655371E-3</v>
       </c>
       <c r="CG31" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7.1828759850033863E-5</v>
       </c>
       <c r="CH31" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>7.1839080459770114E-5</v>
       </c>
     </row>
-    <row r="32" spans="1:86" ht="16">
+    <row r="32" spans="1:86">
       <c r="A32" t="s">
         <v>68</v>
       </c>
@@ -54550,7 +54596,7 @@
         <v>150</v>
       </c>
       <c r="E32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F32">
         <v>2014</v>
@@ -54577,19 +54623,19 @@
         <v>120</v>
       </c>
       <c r="N32" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="O32" t="s">
         <v>131</v>
       </c>
       <c r="P32" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q32" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R32" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -54601,10 +54647,10 @@
         <v>0</v>
       </c>
       <c r="V32" s="94" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W32" s="94" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X32" s="94" t="s">
         <v>73</v>
@@ -54664,10 +54710,10 @@
         <v>0</v>
       </c>
       <c r="AQ32" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AR32" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS32" s="94" t="s">
         <v>130</v>
@@ -54676,14 +54722,13 @@
         <v>73</v>
       </c>
       <c r="AU32" s="110">
-        <v>0.08</v>
+        <v>11.4</v>
       </c>
       <c r="AV32" s="95" t="s">
         <v>86</v>
       </c>
       <c r="AW32" s="94">
-        <f>AU32/AZ32</f>
-        <v>4.9122807017543853E-3</v>
+        <v>0.7</v>
       </c>
       <c r="AX32" s="94">
         <v>0.05</v>
@@ -54692,9 +54737,10 @@
         <v>1</v>
       </c>
       <c r="AZ32" s="94">
+        <f>AU32/AW32</f>
         <v>16.285714285714288</v>
       </c>
-      <c r="BA32" s="125">
+      <c r="BA32" s="124">
         <v>0.08</v>
       </c>
       <c r="BB32" s="111"/>
@@ -54729,13 +54775,13 @@
         <v>73</v>
       </c>
       <c r="BM32" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="BN32" t="s">
         <v>73</v>
       </c>
       <c r="BO32" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="BP32" t="s">
         <v>73</v>
@@ -54762,39 +54808,39 @@
         <v>1</v>
       </c>
       <c r="BX32" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.6644567843645545E-2</v>
       </c>
       <c r="BY32" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.6646105178647452E-2</v>
       </c>
       <c r="BZ32" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.0448457475501714E-6</v>
       </c>
       <c r="CA32" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.0448480111840532E-6</v>
       </c>
       <c r="CE32" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.6644567843645545E-2</v>
       </c>
       <c r="CF32" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.6646105178647452E-2</v>
       </c>
       <c r="CG32" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.0448457475501714E-6</v>
       </c>
       <c r="CH32" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.0448480111840532E-6</v>
       </c>
     </row>
-    <row r="33" spans="1:86" ht="16">
+    <row r="33" spans="1:86">
       <c r="A33" t="s">
         <v>68</v>
       </c>
@@ -54805,7 +54851,7 @@
         <v>150</v>
       </c>
       <c r="E33" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F33">
         <v>2014</v>
@@ -54832,19 +54878,19 @@
         <v>120</v>
       </c>
       <c r="N33" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="O33" t="s">
         <v>131</v>
       </c>
       <c r="P33" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q33" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R33" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -54856,10 +54902,10 @@
         <v>0</v>
       </c>
       <c r="V33" s="94" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W33" s="94" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X33" s="94" t="s">
         <v>73</v>
@@ -54919,10 +54965,10 @@
         <v>0</v>
       </c>
       <c r="AQ33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AR33" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS33" s="94" t="s">
         <v>130</v>
@@ -54931,14 +54977,13 @@
         <v>73</v>
       </c>
       <c r="AU33" s="110">
-        <v>0.08</v>
+        <v>11.9</v>
       </c>
       <c r="AV33" s="95" t="s">
         <v>86</v>
       </c>
       <c r="AW33" s="94">
-        <f t="shared" ref="AW33:AW35" si="13">AU33/AZ33</f>
-        <v>5.0420168067226894E-3</v>
+        <v>0.75</v>
       </c>
       <c r="AX33" s="94">
         <v>0.05</v>
@@ -54947,9 +54992,10 @@
         <v>1</v>
       </c>
       <c r="AZ33" s="94">
+        <f>AU33/AW33</f>
         <v>15.866666666666667</v>
       </c>
-      <c r="BA33" s="125">
+      <c r="BA33" s="124">
         <v>0.08</v>
       </c>
       <c r="BB33" s="111"/>
@@ -54984,13 +55030,13 @@
         <v>73</v>
       </c>
       <c r="BM33" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="BN33" t="s">
         <v>73</v>
       </c>
       <c r="BO33" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="BP33" t="s">
         <v>73</v>
@@ -55017,39 +55063,39 @@
         <v>1</v>
       </c>
       <c r="BX33" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.6216400678486488E-2</v>
       </c>
       <c r="BY33" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.6217822387367728E-2</v>
       </c>
       <c r="BZ33" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.0448457554931792E-6</v>
       </c>
       <c r="CA33" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.0448480111840532E-6</v>
       </c>
       <c r="CE33" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.6216400678486488E-2</v>
       </c>
       <c r="CF33" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.6217822387367728E-2</v>
       </c>
       <c r="CG33" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.0448457554931792E-6</v>
       </c>
       <c r="CH33" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.0448480111840532E-6</v>
       </c>
     </row>
-    <row r="34" spans="1:86" ht="16">
+    <row r="34" spans="1:86">
       <c r="A34" t="s">
         <v>68</v>
       </c>
@@ -55060,7 +55106,7 @@
         <v>150</v>
       </c>
       <c r="E34" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F34">
         <v>2014</v>
@@ -55087,19 +55133,19 @@
         <v>120</v>
       </c>
       <c r="N34" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="O34" t="s">
         <v>131</v>
       </c>
       <c r="P34" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q34" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R34" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -55111,10 +55157,10 @@
         <v>0</v>
       </c>
       <c r="V34" s="94" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W34" s="94" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X34" s="94" t="s">
         <v>73</v>
@@ -55174,10 +55220,10 @@
         <v>0</v>
       </c>
       <c r="AQ34" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AR34" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS34" s="94" t="s">
         <v>130</v>
@@ -55186,14 +55232,13 @@
         <v>73</v>
       </c>
       <c r="AU34" s="110">
-        <v>0.02</v>
+        <v>1.4</v>
       </c>
       <c r="AV34" s="95" t="s">
         <v>80</v>
       </c>
       <c r="AW34" s="94">
-        <f t="shared" si="13"/>
-        <v>1.7142857142857144E-2</v>
+        <v>1.2</v>
       </c>
       <c r="AX34" s="94">
         <v>0.1</v>
@@ -55202,9 +55247,10 @@
         <v>2</v>
       </c>
       <c r="AZ34" s="94">
+        <f>AU34/AW34</f>
         <v>1.1666666666666667</v>
       </c>
-      <c r="BA34" s="125">
+      <c r="BA34" s="124">
         <v>0.02</v>
       </c>
       <c r="BB34" s="111"/>
@@ -55239,13 +55285,13 @@
         <v>73</v>
       </c>
       <c r="BM34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="BN34" t="s">
         <v>73</v>
       </c>
       <c r="BO34" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="BP34" t="s">
         <v>73</v>
@@ -55272,39 +55318,39 @@
         <v>1</v>
       </c>
       <c r="BX34" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.1925383671592018E-3</v>
       </c>
       <c r="BY34" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.1925389324815921E-3</v>
       </c>
       <c r="BZ34" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.0448458277717697E-6</v>
       </c>
       <c r="CA34" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.0448480111840532E-6</v>
       </c>
       <c r="CE34" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.1925383671592018E-3</v>
       </c>
       <c r="CF34" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.1925389324815921E-3</v>
       </c>
       <c r="CG34" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.0448458277717697E-6</v>
       </c>
       <c r="CH34" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.0448480111840532E-6</v>
       </c>
     </row>
-    <row r="35" spans="1:86" ht="16">
+    <row r="35" spans="1:86">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -55315,7 +55361,7 @@
         <v>150</v>
       </c>
       <c r="E35" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F35">
         <v>2014</v>
@@ -55342,19 +55388,19 @@
         <v>120</v>
       </c>
       <c r="N35" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="O35" t="s">
         <v>131</v>
       </c>
       <c r="P35" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R35" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -55366,10 +55412,10 @@
         <v>0</v>
       </c>
       <c r="V35" s="94" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W35" s="94" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X35" s="94" t="s">
         <v>73</v>
@@ -55429,10 +55475,10 @@
         <v>0</v>
       </c>
       <c r="AQ35" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AR35" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS35" s="94" t="s">
         <v>130</v>
@@ -55441,14 +55487,13 @@
         <v>73</v>
       </c>
       <c r="AU35" s="110">
-        <v>0.02</v>
+        <v>1.2</v>
       </c>
       <c r="AV35" s="95" t="s">
         <v>80</v>
       </c>
       <c r="AW35" s="94">
-        <f t="shared" si="13"/>
-        <v>2.1666666666666667E-2</v>
+        <v>1.3</v>
       </c>
       <c r="AX35" s="94">
         <v>0.1</v>
@@ -55457,9 +55502,10 @@
         <v>2</v>
       </c>
       <c r="AZ35" s="94">
+        <f>AU35/AW35</f>
         <v>0.92307692307692302</v>
       </c>
-      <c r="BA35" s="125">
+      <c r="BA35" s="124">
         <v>0.02</v>
       </c>
       <c r="BB35" s="111"/>
@@ -55494,13 +55540,13 @@
         <v>73</v>
       </c>
       <c r="BM35" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="BN35" t="s">
         <v>73</v>
       </c>
       <c r="BO35" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="BP35" t="s">
         <v>73</v>
@@ -55527,41 +55573,41 @@
         <v>1</v>
       </c>
       <c r="BX35" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9.4354709087100688E-4</v>
       </c>
       <c r="BY35" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9.4354737087855463E-4</v>
       </c>
       <c r="BZ35" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.0448458277730546E-6</v>
       </c>
       <c r="CA35" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.0448480111840532E-6</v>
       </c>
       <c r="CE35" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.4354709087100688E-4</v>
       </c>
       <c r="CF35" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.4354737087855463E-4</v>
       </c>
       <c r="CG35" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.0448458277730546E-6</v>
       </c>
       <c r="CH35" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.0448480111840532E-6</v>
       </c>
     </row>
     <row r="36" spans="1:86" ht="18" customHeight="1">
       <c r="A36" s="11" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C36" s="106">
         <v>3049</v>
@@ -55570,16 +55616,16 @@
         <v>313</v>
       </c>
       <c r="E36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F36">
         <v>2014</v>
       </c>
       <c r="G36" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="H36" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="I36">
         <v>1</v>
@@ -55588,7 +55634,7 @@
         <v>2013</v>
       </c>
       <c r="K36" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L36">
         <v>514</v>
@@ -55597,37 +55643,37 @@
         <v>120</v>
       </c>
       <c r="N36" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O36" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="P36" s="18" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q36" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R36" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="S36">
         <v>1</v>
       </c>
       <c r="T36" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U36">
         <v>0</v>
       </c>
       <c r="V36" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W36" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="X36" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Y36">
         <v>0</v>
@@ -55687,13 +55733,13 @@
         <v>73</v>
       </c>
       <c r="AR36" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS36" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AT36" t="s">
-        <v>235</v>
+        <v>73</v>
       </c>
       <c r="AU36">
         <v>0.154</v>
@@ -55701,9 +55747,8 @@
       <c r="AV36" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="AW36" s="7">
-        <f>AU36/AZ36</f>
-        <v>7.8333935905364777E-2</v>
+      <c r="AW36" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="AX36">
         <v>0.05</v>
@@ -55725,7 +55770,7 @@
         <v>73</v>
       </c>
       <c r="BE36" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="BF36" t="s">
         <v>73</v>
@@ -55749,7 +55794,7 @@
         <v>73</v>
       </c>
       <c r="BM36" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="BN36" t="s">
         <v>73</v>
@@ -55782,19 +55827,19 @@
         <v>1</v>
       </c>
       <c r="BX36" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9.7825640875171802E-2</v>
       </c>
       <c r="BY36" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9.8139504130778904E-2</v>
       </c>
       <c r="BZ36" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.5060331750897343E-3</v>
       </c>
       <c r="CA36" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.5188916876574307E-3</v>
       </c>
       <c r="CC36" s="105">
@@ -55802,25 +55847,25 @@
         <v>398</v>
       </c>
       <c r="CE36" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.7825640875171802E-2</v>
       </c>
       <c r="CF36" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.8139504130778904E-2</v>
       </c>
       <c r="CG36" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.5060331750897343E-3</v>
       </c>
       <c r="CH36" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.5188916876574307E-3</v>
       </c>
     </row>
     <row r="37" spans="1:86" ht="18" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C37" s="106">
         <v>3050</v>
@@ -55829,16 +55874,16 @@
         <v>313</v>
       </c>
       <c r="E37" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F37">
         <v>2014</v>
       </c>
       <c r="G37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="H37" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="I37">
         <v>1</v>
@@ -55847,7 +55892,7 @@
         <v>2013</v>
       </c>
       <c r="K37" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L37">
         <v>514</v>
@@ -55856,37 +55901,37 @@
         <v>120</v>
       </c>
       <c r="N37" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O37" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="P37" s="18" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q37" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R37" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="S37">
         <v>1</v>
       </c>
       <c r="T37" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U37">
         <v>0</v>
       </c>
       <c r="V37" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W37" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="X37" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Y37">
         <v>0</v>
@@ -55946,13 +55991,13 @@
         <v>73</v>
       </c>
       <c r="AR37" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AS37" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AT37" t="s">
-        <v>235</v>
+        <v>73</v>
       </c>
       <c r="AU37">
         <v>0.28299999999999997</v>
@@ -55960,9 +56005,8 @@
       <c r="AV37" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="AW37" s="7">
-        <f>AU37/AZ37</f>
-        <v>0.10934077767352141</v>
+      <c r="AW37" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="AX37">
         <v>0.01</v>
@@ -55984,7 +56028,7 @@
         <v>73</v>
       </c>
       <c r="BE37" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="BF37" t="s">
         <v>73</v>
@@ -56008,7 +56052,7 @@
         <v>73</v>
       </c>
       <c r="BM37" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="BN37" t="s">
         <v>73</v>
@@ -56041,19 +56085,19 @@
         <v>1</v>
       </c>
       <c r="BX37" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.1283416849069389</v>
       </c>
       <c r="BY37" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.12905339585554831</v>
       </c>
       <c r="BZ37" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.5055704720227212E-3</v>
       </c>
       <c r="CA37" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.5188916876574307E-3</v>
       </c>
       <c r="CC37" s="105">
@@ -56061,59 +56105,59 @@
         <v>398</v>
       </c>
       <c r="CE37" s="30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.1283416849069389</v>
       </c>
       <c r="CF37" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.12905339585554831</v>
       </c>
       <c r="CG37" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.5055704720227212E-3</v>
       </c>
       <c r="CH37" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.5188916876574307E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:86" ht="16">
+    <row r="38" spans="1:86">
       <c r="M38" s="18"/>
     </row>
-    <row r="39" spans="1:86" ht="16">
+    <row r="39" spans="1:86">
       <c r="M39" s="18"/>
     </row>
-    <row r="40" spans="1:86" ht="16">
+    <row r="40" spans="1:86">
       <c r="M40" s="18"/>
     </row>
-    <row r="41" spans="1:86" ht="16">
+    <row r="41" spans="1:86">
       <c r="M41" s="18"/>
     </row>
-    <row r="42" spans="1:86" ht="16">
+    <row r="42" spans="1:86">
       <c r="M42" s="18"/>
     </row>
-    <row r="43" spans="1:86" ht="16">
+    <row r="43" spans="1:86">
       <c r="M43" s="18"/>
     </row>
-    <row r="44" spans="1:86" ht="16">
+    <row r="44" spans="1:86">
       <c r="M44" s="18"/>
     </row>
-    <row r="45" spans="1:86" ht="16">
+    <row r="45" spans="1:86">
       <c r="M45" s="18"/>
     </row>
-    <row r="46" spans="1:86" ht="16">
+    <row r="46" spans="1:86">
       <c r="M46" s="18"/>
     </row>
     <row r="47" spans="1:86" ht="15.75" customHeight="1">
       <c r="M47" s="18"/>
       <c r="BX47" s="30"/>
     </row>
-    <row r="48" spans="1:86" ht="16">
+    <row r="48" spans="1:86">
       <c r="M48" s="18"/>
       <c r="BA48" s="117"/>
       <c r="BB48" s="117"/>
     </row>
-    <row r="49" spans="13:54" ht="16">
+    <row r="49" spans="13:54">
       <c r="M49" s="18"/>
       <c r="BA49" s="117"/>
       <c r="BB49" s="117"/>
@@ -56121,14 +56165,14 @@
     <row r="50" spans="13:54" ht="15.75" customHeight="1">
       <c r="M50" s="18"/>
     </row>
-    <row r="51" spans="13:54" ht="16">
+    <row r="51" spans="13:54">
       <c r="M51" s="18"/>
       <c r="BA51" s="118"/>
       <c r="BB51" s="118"/>
     </row>
   </sheetData>
-  <autoFilter ref="AR1:AR46" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:CD51">
+  <autoFilter ref="AR1:AR46"/>
+  <sortState ref="A2:CD51">
     <sortCondition ref="C2:C51"/>
   </sortState>
   <dataConsolidate/>
@@ -56139,17 +56183,17 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations xWindow="603" yWindow="1085" count="5">
-    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="I1 I5:I1048576" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="I1 I5:I1048576">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="AQ5:AQ6 AD1:AG1048576" xr:uid="{00000000-0002-0000-0100-000001000000}"/>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="Y38:AC1048576 Y18:Y37 Z14:AC37 Y1:AC13" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="AQ5:AQ6 AD1:AG1048576"/>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="Y38:AC1048576 Y18:Y37 Z14:AC37 Y1:AC13">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN38:BN1048576 BN1:BN35" xr:uid="{00000000-0002-0000-0100-000003000000}"/>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1:S1048576 U1:U1048576 AH1:AI1048576 AK1:AP1048576 AJ2:AJ1048576" xr:uid="{00000000-0002-0000-0100-000004000000}">
+    <dataValidation errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN38:BN1048576 BN1:BN35"/>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1:S1048576 U1:U1048576 AH1:AI1048576 AK1:AP1048576 AJ2:AJ1048576">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -56160,127 +56204,127 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="603" yWindow="1085" count="21">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000005000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B$2:$B$4</xm:f>
           </x14:formula1>
           <xm:sqref>U1:U6 U10:U1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000006000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$A$2:$A$4</xm:f>
           </x14:formula1>
           <xm:sqref>BU18:BW20 BU36:BW1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000007000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$C$2:$C$4</xm:f>
           </x14:formula1>
           <xm:sqref>BS21:BT35 BP21:BQ35 BO38:BO1048576 BO1:BO35</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000008000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$I$2:$I$3</xm:f>
           </x14:formula1>
           <xm:sqref>AV27:AV1048576 AV1:AV20</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000009000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$O:$O</xm:f>
           </x14:formula1>
           <xm:sqref>BT38:BT1048576 BT1:BT20</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000A000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$L$2:$L$9</xm:f>
           </x14:formula1>
           <xm:sqref>U1:U1048576 S1:S1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000B000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$K$2:$K$3</xm:f>
           </x14:formula1>
           <xm:sqref>U1:W1048576 S1:S1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000C000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$N$2:$N$7</xm:f>
           </x14:formula1>
           <xm:sqref>U1:W1048576 S1:S1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000D000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$J$2:$J$12</xm:f>
           </x14:formula1>
           <xm:sqref>K1:K1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000E000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$S:$S</xm:f>
           </x14:formula1>
           <xm:sqref>G1:G1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000F000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$G:$G</xm:f>
           </x14:formula1>
           <xm:sqref>AR1:AR1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000010000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$F:$F</xm:f>
           </x14:formula1>
           <xm:sqref>M52:M1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000011000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$P:$P</xm:f>
           </x14:formula1>
           <xm:sqref>AT1:AT1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000012000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D:$D</xm:f>
           </x14:formula1>
           <xm:sqref>S1:S1048576 U1:W1048576 N1:N1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000013000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$N:$N</xm:f>
           </x14:formula1>
           <xm:sqref>O1:O1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000014000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B:$B</xm:f>
           </x14:formula1>
           <xm:sqref>T1:T1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000015000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$R:$R</xm:f>
           </x14:formula1>
           <xm:sqref>E1:E1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000016000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$H:$H</xm:f>
           </x14:formula1>
           <xm:sqref>S1:S1048576 U1:U1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000017000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$M:$M</xm:f>
           </x14:formula1>
           <xm:sqref>U1:U1048576 P1:P1048576 S1:S1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000018000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$L$2:$L$10</xm:f>
           </x14:formula1>
           <xm:sqref>R1:R1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000019000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$H$1:$H$7</xm:f>
           </x14:formula1>
@@ -56293,72 +56337,72 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BJ18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="28.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="30" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.1640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="28.1640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="28.125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="15" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="11" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="22.625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.125" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="17" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="36.375" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="29" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="20.125" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="15" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="21.875" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="29.625" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="33" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="35.5" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="24.375" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="25.875" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="35" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="26.375" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.375" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="15.625" bestFit="1" customWidth="1"/>
     <col min="63" max="64" width="18.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -56375,200 +56419,200 @@
         <v>198</v>
       </c>
       <c r="B2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:62">
       <c r="A4" s="119" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B4" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C4" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D4" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E4" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F4" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="G4" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="H4" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I4" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J4" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="K4" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="L4" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="M4" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="N4" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="O4" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="P4" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q4" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="R4" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="S4" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="T4" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="U4" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="V4" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="W4" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="X4" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Y4" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Z4" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AA4" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AB4" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="AC4" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AD4" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AE4" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AF4" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AG4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AH4" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AI4" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AJ4" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AK4" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AL4" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AM4" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AN4" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AO4" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AP4" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AQ4" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AR4" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AS4" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AT4" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AU4" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AV4" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AW4" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="AX4" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AY4" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AZ4" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="BA4" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="BB4" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="BC4" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BD4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BE4" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="BF4" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="BG4" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="BH4" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="BI4" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="BJ4" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" spans="1:62">
       <c r="A5" s="120" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -56938,7 +56982,7 @@
     </row>
     <row r="7" spans="1:62">
       <c r="A7" s="120" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -57502,7 +57546,7 @@
     </row>
     <row r="10" spans="1:62">
       <c r="A10" s="120" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B10">
         <v>23</v>
@@ -57690,7 +57734,7 @@
     </row>
     <row r="11" spans="1:62">
       <c r="A11" s="120" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -57878,7 +57922,7 @@
     </row>
     <row r="12" spans="1:62">
       <c r="A12" s="120" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -58066,7 +58110,7 @@
     </row>
     <row r="13" spans="1:62">
       <c r="A13" s="120" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B13">
         <v>6</v>
@@ -58254,7 +58298,7 @@
     </row>
     <row r="14" spans="1:62">
       <c r="A14" s="120" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B14">
         <v>6</v>
@@ -58442,7 +58486,7 @@
     </row>
     <row r="15" spans="1:62">
       <c r="A15" s="120" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -58630,7 +58674,7 @@
     </row>
     <row r="16" spans="1:62">
       <c r="A16" s="120" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B16">
         <v>22</v>
@@ -59006,7 +59050,7 @@
     </row>
     <row r="18" spans="1:62">
       <c r="A18" s="120" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B18">
         <v>144</v>
@@ -59198,28 +59242,28 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S99"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="3" max="3" width="15.5" customWidth="1"/>
-    <col min="5" max="5" width="19.6640625" customWidth="1"/>
+    <col min="5" max="5" width="19.625" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="18.1640625" style="26" customWidth="1"/>
+    <col min="7" max="7" width="18.125" style="26" customWidth="1"/>
     <col min="8" max="8" width="20.5" customWidth="1"/>
-    <col min="9" max="9" width="14.1640625" customWidth="1"/>
-    <col min="10" max="10" width="15.1640625" customWidth="1"/>
+    <col min="9" max="9" width="14.125" customWidth="1"/>
+    <col min="10" max="10" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B1" t="s">
         <v>189</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D1" t="s">
         <v>10</v>
@@ -59231,7 +59275,7 @@
         <v>9</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="H1" s="38" t="s">
         <v>186</v>
@@ -59243,7 +59287,7 @@
         <v>7</v>
       </c>
       <c r="K1" s="39" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="L1" s="39" t="s">
         <v>187</v>
@@ -59255,7 +59299,7 @@
         <v>50</v>
       </c>
       <c r="O1" s="39" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P1" s="42" t="s">
         <v>200</v>
@@ -59267,7 +59311,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="34">
+    <row r="2" spans="1:19" ht="31.5">
       <c r="A2">
         <v>0</v>
       </c>
@@ -59275,7 +59319,7 @@
         <v>189</v>
       </c>
       <c r="C2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D2" t="s">
         <v>112</v>
@@ -59287,166 +59331,166 @@
         <v>93</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="H2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="I2" t="s">
         <v>80</v>
       </c>
       <c r="J2" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="K2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="M2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N2" t="s">
         <v>81</v>
       </c>
       <c r="O2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="P2" s="41" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="R2" s="47" t="s">
-        <v>615</v>
+        <v>394</v>
       </c>
       <c r="S2" s="47" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="34">
+    <row r="3" spans="1:19" ht="31.5">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="H3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I3" t="s">
         <v>86</v>
       </c>
       <c r="J3" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="K3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L3" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="M3" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="N3" t="s">
         <v>148</v>
       </c>
       <c r="O3" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="P3" s="41" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>616</v>
+        <v>402</v>
       </c>
       <c r="S3" s="46" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="51">
+    <row r="4" spans="1:19" ht="47.25">
       <c r="A4" t="s">
         <v>73</v>
       </c>
       <c r="B4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C4" t="s">
         <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H4" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="J4" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="L4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N4" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="O4" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="P4" s="41" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="R4" s="44" t="s">
-        <v>617</v>
+        <v>250</v>
       </c>
       <c r="S4" s="44" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="51">
+    <row r="5" spans="1:19" ht="47.25">
       <c r="D5" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F5" t="s">
         <v>120</v>
       </c>
       <c r="G5" s="40" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H5" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="J5" s="41" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="L5" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="M5" t="s">
         <v>73</v>
@@ -59455,71 +59499,71 @@
         <v>124</v>
       </c>
       <c r="O5" s="41" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="P5" t="s">
         <v>73</v>
       </c>
       <c r="R5" s="46" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="S5" s="46" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="D6" s="41" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="F6" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="H6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J6" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="L6" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="N6" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="O6" t="s">
         <v>73</v>
       </c>
       <c r="R6" s="46" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="S6" s="46" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="F7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J7" s="41" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="L7" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N7" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="O7" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="R7" s="46" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="S7" s="46" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -59527,39 +59571,39 @@
         <v>107</v>
       </c>
       <c r="J8" s="41" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="L8" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="N8" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="R8" s="46" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="S8" s="46" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="F9" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J9" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="L9" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="N9" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="R9" s="44" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="S9" s="44" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -59567,81 +59611,81 @@
         <v>155</v>
       </c>
       <c r="J10" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="L10" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N10" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="R10" s="44" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="S10" s="44" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="11" spans="1:19">
       <c r="F11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J11" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="N11" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="R11" s="44" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="S11" s="44" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="F12" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="J12" t="s">
         <v>73</v>
       </c>
       <c r="N12" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="R12" s="44" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="S12" s="44" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="13" spans="1:19">
       <c r="F13" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="N13" t="s">
         <v>96</v>
       </c>
       <c r="R13" s="46" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="S13" s="46" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="14" spans="1:19">
       <c r="F14" s="41" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="N14" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="R14" s="44" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="S14" s="44" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -59649,52 +59693,52 @@
         <v>155</v>
       </c>
       <c r="N15" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="R15" s="46" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="S15" s="46" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="F16" s="41" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="N16" t="s">
         <v>156</v>
       </c>
       <c r="R16" s="46" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="S16" s="46" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="17" spans="6:19">
       <c r="F17" s="41" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="N17" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="R17" s="44" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="S17" s="44" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="18" spans="6:19">
       <c r="F18" s="41" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="N18" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="R18" s="46" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="S18" s="46" t="s">
         <v>127</v>
@@ -59702,142 +59746,142 @@
     </row>
     <row r="19" spans="6:19">
       <c r="F19" s="41" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N19" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="R19" s="44" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="S19" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="20" spans="6:19">
       <c r="F20" s="41" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N20" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="R20" s="46" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="S20" s="46" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="21" spans="6:19">
       <c r="F21" s="41" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N21" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="R21" s="44" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="S21" s="44" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="22" spans="6:19">
       <c r="F22" s="41" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="N22" t="s">
         <v>138</v>
       </c>
       <c r="R22" s="46" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="S22" s="46" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="23" spans="6:19">
       <c r="F23" s="41" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="N23" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="R23" s="44" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="S23" s="44" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="24" spans="6:19">
       <c r="F24" s="41" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="N24" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="R24" s="44" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="S24" s="44" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="25" spans="6:19">
       <c r="F25" s="41" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N25" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R25" s="44" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="S25" s="44" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="26" spans="6:19">
       <c r="F26" s="41" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="N26" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="R26" s="44" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="S26" s="44" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="27" spans="6:19">
       <c r="F27" s="41" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="N27" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="R27" s="44" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="S27" s="44" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="28" spans="6:19">
       <c r="F28" s="41" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="N28" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="R28" s="44" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="S28" s="44" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="29" spans="6:19">
@@ -59845,27 +59889,27 @@
         <v>172</v>
       </c>
       <c r="N29" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="R29" s="44" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="S29" s="44" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="30" spans="6:19">
       <c r="F30" s="41" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="N30" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="R30" s="44" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="S30" s="44" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="31" spans="6:19">
@@ -59873,21 +59917,21 @@
         <v>174</v>
       </c>
       <c r="R31" s="44" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="S31" s="44" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="32" spans="6:19">
       <c r="N32" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="R32" s="44" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="S32" s="44" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="33" spans="14:19">
@@ -59895,95 +59939,95 @@
         <v>131</v>
       </c>
       <c r="R33" s="44" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="S33" s="44" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="34" spans="14:19">
       <c r="R34" s="44" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="S34" s="44" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="35" spans="14:19">
       <c r="R35" s="44" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="S35" s="44" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="36" spans="14:19">
       <c r="R36" s="44" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="S36" s="44" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="37" spans="14:19">
       <c r="R37" s="46" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="S37" s="46" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="38" spans="14:19">
       <c r="R38" s="46" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="S38" s="46" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="39" spans="14:19">
       <c r="R39" s="46" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="S39" s="46" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="40" spans="14:19">
       <c r="R40" s="44" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="S40" s="44" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="41" spans="14:19">
       <c r="R41" s="44" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="S41" s="44" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="42" spans="14:19">
       <c r="R42" s="46" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="S42" s="46" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="43" spans="14:19">
       <c r="R43" s="46" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="S43" s="46" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="44" spans="14:19">
       <c r="R44" s="44" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="S44" s="17" t="s">
         <v>117</v>
@@ -59991,431 +60035,431 @@
     </row>
     <row r="45" spans="14:19">
       <c r="R45" s="46" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="S45" s="46" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
     </row>
     <row r="46" spans="14:19">
       <c r="R46" s="44" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="S46" s="44" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="47" spans="14:19">
       <c r="R47" s="46" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="S47" s="46" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
     </row>
     <row r="48" spans="14:19">
       <c r="R48" s="44" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="S48" s="44" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
     </row>
     <row r="49" spans="18:19">
       <c r="R49" s="44" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="S49" s="44" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="50" spans="18:19">
       <c r="R50" s="44" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="S50" s="44" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
     </row>
     <row r="51" spans="18:19">
       <c r="R51" s="44" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="S51" s="44" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="52" spans="18:19">
       <c r="R52" s="44" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="S52" s="44" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
     </row>
     <row r="53" spans="18:19">
       <c r="R53" s="44" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="S53" s="17" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
     </row>
     <row r="54" spans="18:19">
       <c r="R54" s="44" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="S54" s="44" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
     </row>
     <row r="55" spans="18:19">
       <c r="R55" s="44" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="S55" s="44" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
     </row>
     <row r="56" spans="18:19">
       <c r="R56" s="44" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="S56" s="44" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
     </row>
     <row r="57" spans="18:19">
       <c r="R57" s="44" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="S57" s="44" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
     </row>
     <row r="58" spans="18:19">
       <c r="R58" s="44" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="S58" s="44" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
     </row>
     <row r="59" spans="18:19">
       <c r="R59" s="44" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="S59" s="44" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="60" spans="18:19">
       <c r="R60" s="44" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="S60" s="44" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
     </row>
     <row r="61" spans="18:19">
       <c r="R61" s="44" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="S61" s="44" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="62" spans="18:19">
       <c r="R62" s="44" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="S62" s="44" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
     </row>
     <row r="63" spans="18:19">
       <c r="R63" s="44" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="S63" s="44" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
     </row>
     <row r="64" spans="18:19">
       <c r="R64" s="44" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="S64" s="44" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
     </row>
     <row r="65" spans="18:19">
       <c r="R65" s="44" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="S65" s="44" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
     </row>
     <row r="66" spans="18:19">
       <c r="R66" s="44" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="S66" s="44" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
     </row>
     <row r="67" spans="18:19">
       <c r="R67" s="44" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="S67" s="44" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
     </row>
     <row r="68" spans="18:19">
       <c r="R68" s="44" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="S68" s="44" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
     </row>
     <row r="69" spans="18:19">
       <c r="R69" s="44" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="S69" s="44" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
     </row>
     <row r="70" spans="18:19">
       <c r="R70" s="44" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="S70" s="44" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
     </row>
     <row r="71" spans="18:19">
       <c r="R71" s="44" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="S71" s="44" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
     </row>
     <row r="72" spans="18:19">
       <c r="R72" s="44" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="S72" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
     </row>
     <row r="73" spans="18:19">
       <c r="R73" s="46" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="S73" s="46" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
     </row>
     <row r="74" spans="18:19">
       <c r="R74" s="44" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="S74" s="44" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="75" spans="18:19">
       <c r="R75" s="46" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="S75" s="46" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="76" spans="18:19">
       <c r="R76" s="44" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="S76" s="44" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
     </row>
     <row r="77" spans="18:19">
       <c r="R77" s="44" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="S77" s="44" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
     </row>
     <row r="78" spans="18:19">
       <c r="R78" s="46" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="S78" s="46" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
     </row>
     <row r="79" spans="18:19">
       <c r="R79" s="46" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="S79" s="46" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
     </row>
     <row r="80" spans="18:19">
       <c r="R80" s="44" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="S80" s="44" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
     </row>
     <row r="81" spans="18:19">
       <c r="R81" s="44" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="S81" s="44" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
     </row>
     <row r="82" spans="18:19">
       <c r="R82" s="44" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="S82" s="44" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="83" spans="18:19">
       <c r="R83" s="46" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="S83" s="46" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
     </row>
     <row r="84" spans="18:19">
       <c r="R84" s="46" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="S84" s="46" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="85" spans="18:19">
       <c r="R85" s="44" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="S85" s="44" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
     </row>
     <row r="86" spans="18:19">
       <c r="R86" s="44" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="S86" s="44" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
     </row>
     <row r="87" spans="18:19">
       <c r="R87" s="44" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="S87" s="44" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
     </row>
     <row r="88" spans="18:19">
       <c r="R88" s="44" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="S88" s="44" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
     </row>
     <row r="89" spans="18:19">
       <c r="R89" s="44" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="S89" s="44" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
     </row>
     <row r="90" spans="18:19">
       <c r="R90" s="44" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="S90" s="44" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="91" spans="18:19">
       <c r="R91" s="44" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="S91" s="44" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
     </row>
     <row r="92" spans="18:19">
       <c r="R92" s="44" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="S92" s="44" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
     </row>
     <row r="93" spans="18:19">
       <c r="R93" s="44" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="S93" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
     </row>
     <row r="94" spans="18:19">
       <c r="R94" s="44" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="S94" s="44" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
     </row>
     <row r="95" spans="18:19">
       <c r="R95" s="44" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="S95" s="44" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
     </row>
     <row r="96" spans="18:19">
       <c r="R96" s="44" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="S96" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
     </row>
     <row r="97" spans="18:19">
       <c r="R97" s="44" t="s">
-        <v>618</v>
+        <v>291</v>
       </c>
       <c r="S97" s="57" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="98" spans="18:19">
       <c r="R98" s="57" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="S98" s="32" t="s">
         <v>133</v>
@@ -60423,14 +60467,14 @@
     </row>
     <row r="99" spans="18:19">
       <c r="R99" s="44" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="S99" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="R2:S91">
+  <sortState ref="R2:S91">
     <sortCondition ref="R2:R91"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/appliances_usage.xlsx
+++ b/appliances_usage.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="-4485" yWindow="-21105" windowWidth="38400" windowHeight="19395" firstSheet="1" activeTab="1"/>
+    <workbookView xWindow="-4485" yWindow="-21105" windowWidth="38400" windowHeight="19395" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Usage" sheetId="5" state="hidden" r:id="rId1"/>
@@ -23,9 +23,8 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="3" r:id="rId5"/>
   </pivotCaches>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -889,9 +888,6 @@
     <t>coder</t>
   </si>
   <si>
-    <t>study_ID_purchaseprobability</t>
-  </si>
-  <si>
     <t>authors</t>
   </si>
   <si>
@@ -2253,6 +2249,9 @@
   </si>
   <si>
     <t>dishwasher</t>
+  </si>
+  <si>
+    <t>counterfactual</t>
   </si>
 </sst>
 </file>
@@ -34722,7 +34721,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:BJ18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="92">
     <pivotField showAll="0"/>
@@ -46585,7 +46584,7 @@
         <v>181</v>
       </c>
       <c r="B1" s="59" t="s">
-        <v>182</v>
+        <v>618</v>
       </c>
       <c r="C1" s="59" t="s">
         <v>1</v>
@@ -46594,10 +46593,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="60" t="s">
+        <v>182</v>
+      </c>
+      <c r="F1" s="61" t="s">
         <v>183</v>
-      </c>
-      <c r="F1" s="61" t="s">
-        <v>184</v>
       </c>
       <c r="G1" s="62" t="s">
         <v>4</v>
@@ -46627,19 +46626,19 @@
         <v>50</v>
       </c>
       <c r="P1" s="66" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q1" s="67" t="s">
         <v>185</v>
       </c>
-      <c r="Q1" s="67" t="s">
+      <c r="R1" s="67" t="s">
         <v>186</v>
       </c>
-      <c r="R1" s="67" t="s">
+      <c r="S1" s="67" t="s">
         <v>187</v>
       </c>
-      <c r="S1" s="67" t="s">
+      <c r="T1" s="68" t="s">
         <v>188</v>
-      </c>
-      <c r="T1" s="68" t="s">
-        <v>189</v>
       </c>
       <c r="U1" s="67" t="s">
         <v>53</v>
@@ -46651,7 +46650,7 @@
         <v>56</v>
       </c>
       <c r="X1" s="71" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Y1" s="72" t="s">
         <v>12</v>
@@ -46669,25 +46668,25 @@
         <v>16</v>
       </c>
       <c r="AD1" s="73" t="s">
+        <v>190</v>
+      </c>
+      <c r="AE1" s="73" t="s">
         <v>191</v>
       </c>
-      <c r="AE1" s="73" t="s">
+      <c r="AF1" s="73" t="s">
         <v>192</v>
       </c>
-      <c r="AF1" s="73" t="s">
+      <c r="AG1" s="73" t="s">
         <v>193</v>
-      </c>
-      <c r="AG1" s="73" t="s">
-        <v>194</v>
       </c>
       <c r="AH1" s="74" t="s">
         <v>17</v>
       </c>
       <c r="AI1" s="75" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AJ1" s="75" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AK1" s="75" t="s">
         <v>19</v>
@@ -46702,22 +46701,22 @@
         <v>22</v>
       </c>
       <c r="AO1" s="75" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AP1" s="75" t="s">
         <v>24</v>
       </c>
       <c r="AQ1" s="76" t="s">
+        <v>196</v>
+      </c>
+      <c r="AR1" s="59" t="s">
         <v>197</v>
       </c>
-      <c r="AR1" s="59" t="s">
+      <c r="AS1" s="59" t="s">
         <v>198</v>
       </c>
-      <c r="AS1" s="59" t="s">
+      <c r="AT1" s="59" t="s">
         <v>199</v>
-      </c>
-      <c r="AT1" s="59" t="s">
-        <v>200</v>
       </c>
       <c r="AU1" s="59" t="s">
         <v>27</v>
@@ -46735,13 +46734,13 @@
         <v>40</v>
       </c>
       <c r="AZ1" s="78" t="s">
+        <v>200</v>
+      </c>
+      <c r="BA1" s="79" t="s">
         <v>201</v>
       </c>
-      <c r="BA1" s="79" t="s">
+      <c r="BB1" s="80" t="s">
         <v>202</v>
-      </c>
-      <c r="BB1" s="80" t="s">
-        <v>203</v>
       </c>
       <c r="BC1" s="81" t="s">
         <v>31</v>
@@ -46774,40 +46773,40 @@
         <v>43</v>
       </c>
       <c r="BM1" s="84" t="s">
+        <v>203</v>
+      </c>
+      <c r="BN1" s="85" t="s">
         <v>204</v>
       </c>
-      <c r="BN1" s="85" t="s">
+      <c r="BO1" s="86" t="s">
         <v>205</v>
       </c>
-      <c r="BO1" s="86" t="s">
+      <c r="BP1" s="87" t="s">
         <v>206</v>
       </c>
-      <c r="BP1" s="87" t="s">
+      <c r="BQ1" s="88" t="s">
         <v>207</v>
       </c>
-      <c r="BQ1" s="88" t="s">
+      <c r="BR1" s="88" t="s">
         <v>208</v>
       </c>
-      <c r="BR1" s="88" t="s">
+      <c r="BS1" s="88" t="s">
         <v>209</v>
       </c>
-      <c r="BS1" s="88" t="s">
+      <c r="BT1" s="86" t="s">
         <v>210</v>
       </c>
-      <c r="BT1" s="86" t="s">
+      <c r="BU1" s="89" t="s">
         <v>211</v>
       </c>
-      <c r="BU1" s="89" t="s">
+      <c r="BV1" s="90" t="s">
         <v>212</v>
       </c>
-      <c r="BV1" s="90" t="s">
+      <c r="BW1" s="91" t="s">
         <v>213</v>
       </c>
-      <c r="BW1" s="91" t="s">
+      <c r="BX1" s="28" t="s">
         <v>214</v>
-      </c>
-      <c r="BX1" s="28" t="s">
-        <v>215</v>
       </c>
       <c r="BY1" s="92" t="s">
         <v>62</v>
@@ -46822,22 +46821,22 @@
         <v>65</v>
       </c>
       <c r="CC1" t="s">
+        <v>215</v>
+      </c>
+      <c r="CD1" t="s">
         <v>216</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CE1" s="28" t="s">
         <v>217</v>
       </c>
-      <c r="CE1" s="28" t="s">
+      <c r="CF1" s="92" t="s">
         <v>218</v>
       </c>
-      <c r="CF1" s="92" t="s">
+      <c r="CG1" s="93" t="s">
         <v>219</v>
       </c>
-      <c r="CG1" s="93" t="s">
+      <c r="CH1" s="93" t="s">
         <v>220</v>
-      </c>
-      <c r="CH1" s="93" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:86">
@@ -46852,22 +46851,22 @@
         <v>107</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F2" s="11">
         <v>2020</v>
       </c>
       <c r="G2" t="s">
+        <v>222</v>
+      </c>
+      <c r="H2" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="I2" s="18">
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
         <v>224</v>
-      </c>
-      <c r="I2" s="18">
-        <v>1</v>
-      </c>
-      <c r="J2" t="s">
-        <v>225</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>73</v>
@@ -46876,106 +46875,106 @@
         <v>5</v>
       </c>
       <c r="M2" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="N2" t="s">
         <v>226</v>
-      </c>
-      <c r="N2" t="s">
-        <v>227</v>
       </c>
       <c r="O2" t="s">
         <v>96</v>
       </c>
       <c r="P2" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q2" t="s">
         <v>228</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>229</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2" t="s">
         <v>230</v>
       </c>
-      <c r="S2">
-        <v>1</v>
-      </c>
-      <c r="T2" t="s">
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2" s="18" t="s">
+      <c r="W2" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="X2" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>1</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="s">
         <v>232</v>
       </c>
-      <c r="W2" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="X2" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>1</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-      <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="s">
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>1</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR2" t="s">
         <v>233</v>
       </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
-      <c r="AM2">
-        <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>0</v>
-      </c>
-      <c r="AO2">
-        <v>1</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR2" t="s">
+      <c r="AS2" t="s">
         <v>234</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AT2" t="s">
         <v>235</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>236</v>
       </c>
       <c r="AU2" s="21">
         <v>5.8000000000000003E-2</v>
@@ -47109,22 +47108,22 @@
         <v>107</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F3" s="11">
         <v>2020</v>
       </c>
       <c r="G3" t="s">
+        <v>222</v>
+      </c>
+      <c r="H3" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="I3" s="18">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
         <v>224</v>
-      </c>
-      <c r="I3" s="18">
-        <v>1</v>
-      </c>
-      <c r="J3" t="s">
-        <v>225</v>
       </c>
       <c r="K3" s="10" t="s">
         <v>73</v>
@@ -47133,106 +47132,106 @@
         <v>5</v>
       </c>
       <c r="M3" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="N3" t="s">
         <v>226</v>
-      </c>
-      <c r="N3" t="s">
-        <v>227</v>
       </c>
       <c r="O3" t="s">
         <v>96</v>
       </c>
       <c r="P3" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q3" t="s">
         <v>228</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>229</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3">
+        <v>1</v>
+      </c>
+      <c r="T3" t="s">
         <v>230</v>
       </c>
-      <c r="S3">
-        <v>1</v>
-      </c>
-      <c r="T3" t="s">
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3" s="18" t="s">
+      <c r="W3" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="X3" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>1</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="s">
         <v>232</v>
       </c>
-      <c r="W3" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="X3" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>1</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="s">
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>1</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR3" t="s">
         <v>233</v>
       </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AK3">
-        <v>0</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AO3">
-        <v>1</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR3" t="s">
+      <c r="AS3" t="s">
         <v>234</v>
       </c>
-      <c r="AS3" t="s">
+      <c r="AT3" t="s">
         <v>235</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>236</v>
       </c>
       <c r="AU3" s="21">
         <v>5.3999999999999999E-2</v>
@@ -47366,22 +47365,22 @@
         <v>107</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F4" s="11">
         <v>2020</v>
       </c>
       <c r="G4" t="s">
+        <v>222</v>
+      </c>
+      <c r="H4" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="I4" s="18">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
         <v>224</v>
-      </c>
-      <c r="I4" s="18">
-        <v>1</v>
-      </c>
-      <c r="J4" t="s">
-        <v>225</v>
       </c>
       <c r="K4" s="10" t="s">
         <v>73</v>
@@ -47390,106 +47389,106 @@
         <v>5</v>
       </c>
       <c r="M4" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="N4" t="s">
         <v>226</v>
-      </c>
-      <c r="N4" t="s">
-        <v>227</v>
       </c>
       <c r="O4" t="s">
         <v>96</v>
       </c>
       <c r="P4" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q4" t="s">
         <v>228</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>229</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4" t="s">
         <v>230</v>
       </c>
-      <c r="S4">
-        <v>1</v>
-      </c>
-      <c r="T4" t="s">
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4" s="18" t="s">
+      <c r="W4" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="X4" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="s">
         <v>232</v>
       </c>
-      <c r="W4" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="X4" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>1</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="s">
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>1</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR4" t="s">
         <v>233</v>
       </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AK4">
-        <v>0</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <v>1</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR4" t="s">
+      <c r="AS4" t="s">
         <v>234</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AT4" t="s">
         <v>235</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>236</v>
       </c>
       <c r="AU4" s="21">
         <v>5.3999999999999999E-2</v>
@@ -47623,22 +47622,22 @@
         <v>107</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F5" s="11">
         <v>2020</v>
       </c>
       <c r="G5" t="s">
+        <v>222</v>
+      </c>
+      <c r="H5" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="I5" s="18">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
         <v>224</v>
-      </c>
-      <c r="I5" s="18">
-        <v>1</v>
-      </c>
-      <c r="J5" t="s">
-        <v>225</v>
       </c>
       <c r="K5" s="10" t="s">
         <v>73</v>
@@ -47647,106 +47646,106 @@
         <v>5</v>
       </c>
       <c r="M5" s="18" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="N5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O5" t="s">
         <v>96</v>
       </c>
       <c r="P5" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q5" t="s">
         <v>228</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>229</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5" t="s">
         <v>230</v>
       </c>
-      <c r="S5">
-        <v>1</v>
-      </c>
-      <c r="T5" t="s">
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5" s="18" t="s">
+      <c r="W5" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="X5" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="s">
         <v>232</v>
       </c>
-      <c r="W5" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="X5" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>1</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="s">
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>1</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR5" t="s">
         <v>233</v>
       </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-      <c r="AI5">
-        <v>0</v>
-      </c>
-      <c r="AJ5">
-        <v>0</v>
-      </c>
-      <c r="AK5">
-        <v>0</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>0</v>
-      </c>
-      <c r="AO5">
-        <v>1</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR5" t="s">
+      <c r="AS5" t="s">
         <v>234</v>
       </c>
-      <c r="AS5" t="s">
+      <c r="AT5" t="s">
         <v>235</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>236</v>
       </c>
       <c r="AU5" s="21">
         <v>5.1999999999999998E-2</v>
@@ -47880,22 +47879,22 @@
         <v>107</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F6" s="11">
         <v>2020</v>
       </c>
       <c r="G6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H6" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="I6" s="18">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
         <v>224</v>
-      </c>
-      <c r="I6" s="18">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>225</v>
       </c>
       <c r="K6" s="10" t="s">
         <v>73</v>
@@ -47904,106 +47903,106 @@
         <v>5</v>
       </c>
       <c r="M6" s="18" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="N6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O6" t="s">
         <v>96</v>
       </c>
       <c r="P6" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q6" t="s">
         <v>228</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>229</v>
       </c>
-      <c r="R6" t="s">
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6" t="s">
         <v>230</v>
       </c>
-      <c r="S6">
-        <v>1</v>
-      </c>
-      <c r="T6" t="s">
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6" s="18" t="s">
+      <c r="W6" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="X6" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="s">
         <v>232</v>
       </c>
-      <c r="W6" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="X6" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y6">
-        <v>0</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>1</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="s">
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>1</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR6" t="s">
         <v>233</v>
       </c>
-      <c r="AH6">
-        <v>0</v>
-      </c>
-      <c r="AI6">
-        <v>0</v>
-      </c>
-      <c r="AJ6">
-        <v>0</v>
-      </c>
-      <c r="AK6">
-        <v>0</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>0</v>
-      </c>
-      <c r="AO6">
-        <v>1</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR6" t="s">
+      <c r="AS6" t="s">
         <v>234</v>
       </c>
-      <c r="AS6" t="s">
+      <c r="AT6" t="s">
         <v>235</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>236</v>
       </c>
       <c r="AU6" s="21">
         <v>5.6000000000000001E-2</v>
@@ -48137,22 +48136,22 @@
         <v>107</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F7" s="11">
         <v>2020</v>
       </c>
       <c r="G7" t="s">
+        <v>222</v>
+      </c>
+      <c r="H7" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="H7" s="22" t="s">
+      <c r="I7" s="18">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
         <v>224</v>
-      </c>
-      <c r="I7" s="18">
-        <v>1</v>
-      </c>
-      <c r="J7" t="s">
-        <v>225</v>
       </c>
       <c r="K7" s="10" t="s">
         <v>73</v>
@@ -48161,106 +48160,106 @@
         <v>5</v>
       </c>
       <c r="M7" s="18" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="N7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O7" t="s">
         <v>96</v>
       </c>
       <c r="P7" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q7" t="s">
         <v>228</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" t="s">
         <v>229</v>
       </c>
-      <c r="R7" t="s">
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7" t="s">
         <v>230</v>
       </c>
-      <c r="S7">
-        <v>1</v>
-      </c>
-      <c r="T7" t="s">
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7" s="18" t="s">
+      <c r="W7" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="X7" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="s">
         <v>232</v>
       </c>
-      <c r="W7" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="X7" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>1</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="s">
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>1</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR7" t="s">
         <v>233</v>
       </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <v>0</v>
-      </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>0</v>
-      </c>
-      <c r="AO7">
-        <v>1</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR7" t="s">
+      <c r="AS7" t="s">
         <v>234</v>
       </c>
-      <c r="AS7" t="s">
+      <c r="AT7" t="s">
         <v>235</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>236</v>
       </c>
       <c r="AU7" s="21">
         <v>4.4999999999999998E-2</v>
@@ -48394,22 +48393,22 @@
         <v>107</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F8" s="11">
         <v>2020</v>
       </c>
       <c r="G8" t="s">
+        <v>222</v>
+      </c>
+      <c r="H8" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="H8" s="22" t="s">
+      <c r="I8" s="18">
+        <v>1</v>
+      </c>
+      <c r="J8" t="s">
         <v>224</v>
-      </c>
-      <c r="I8" s="18">
-        <v>1</v>
-      </c>
-      <c r="J8" t="s">
-        <v>225</v>
       </c>
       <c r="K8" s="10" t="s">
         <v>73</v>
@@ -48418,106 +48417,106 @@
         <v>6</v>
       </c>
       <c r="M8" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="N8" t="s">
         <v>226</v>
-      </c>
-      <c r="N8" t="s">
-        <v>227</v>
       </c>
       <c r="O8" t="s">
         <v>96</v>
       </c>
       <c r="P8" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q8" t="s">
         <v>228</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
         <v>229</v>
       </c>
-      <c r="R8" t="s">
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8" t="s">
         <v>230</v>
       </c>
-      <c r="S8">
-        <v>1</v>
-      </c>
-      <c r="T8" t="s">
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8" s="18" t="s">
+      <c r="W8" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="X8" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="s">
         <v>232</v>
       </c>
-      <c r="W8" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="X8" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y8">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <v>1</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="s">
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>1</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR8" t="s">
         <v>233</v>
       </c>
-      <c r="AH8">
-        <v>0</v>
-      </c>
-      <c r="AI8">
-        <v>0</v>
-      </c>
-      <c r="AJ8">
-        <v>0</v>
-      </c>
-      <c r="AK8">
-        <v>0</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>0</v>
-      </c>
-      <c r="AO8">
-        <v>1</v>
-      </c>
-      <c r="AP8">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR8" t="s">
+      <c r="AS8" t="s">
         <v>234</v>
       </c>
-      <c r="AS8" t="s">
+      <c r="AT8" t="s">
         <v>235</v>
-      </c>
-      <c r="AT8" t="s">
-        <v>236</v>
       </c>
       <c r="AU8" s="21">
         <v>5.7000000000000002E-2</v>
@@ -48654,22 +48653,22 @@
         <v>107</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F9" s="11">
         <v>2020</v>
       </c>
       <c r="G9" t="s">
+        <v>222</v>
+      </c>
+      <c r="H9" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="H9" s="22" t="s">
+      <c r="I9" s="18">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
         <v>224</v>
-      </c>
-      <c r="I9" s="18">
-        <v>1</v>
-      </c>
-      <c r="J9" t="s">
-        <v>225</v>
       </c>
       <c r="K9" s="10" t="s">
         <v>73</v>
@@ -48678,106 +48677,106 @@
         <v>6</v>
       </c>
       <c r="M9" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="N9" t="s">
         <v>226</v>
-      </c>
-      <c r="N9" t="s">
-        <v>227</v>
       </c>
       <c r="O9" t="s">
         <v>96</v>
       </c>
       <c r="P9" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q9" t="s">
         <v>228</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="R9" t="s">
         <v>229</v>
       </c>
-      <c r="R9" t="s">
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9" t="s">
         <v>230</v>
       </c>
-      <c r="S9">
-        <v>1</v>
-      </c>
-      <c r="T9" t="s">
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9" s="18" t="s">
+      <c r="W9" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="X9" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="s">
         <v>232</v>
       </c>
-      <c r="W9" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="X9" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y9">
-        <v>0</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <v>1</v>
-      </c>
-      <c r="AB9">
-        <v>0</v>
-      </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="s">
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>1</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR9" t="s">
         <v>233</v>
       </c>
-      <c r="AH9">
-        <v>0</v>
-      </c>
-      <c r="AI9">
-        <v>0</v>
-      </c>
-      <c r="AJ9">
-        <v>0</v>
-      </c>
-      <c r="AK9">
-        <v>0</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>0</v>
-      </c>
-      <c r="AN9">
-        <v>0</v>
-      </c>
-      <c r="AO9">
-        <v>1</v>
-      </c>
-      <c r="AP9">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR9" t="s">
+      <c r="AS9" t="s">
         <v>234</v>
       </c>
-      <c r="AS9" t="s">
+      <c r="AT9" t="s">
         <v>235</v>
-      </c>
-      <c r="AT9" t="s">
-        <v>236</v>
       </c>
       <c r="AU9" s="21">
         <v>6.4000000000000001E-2</v>
@@ -48914,22 +48913,22 @@
         <v>107</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F10" s="11">
         <v>2020</v>
       </c>
       <c r="G10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H10" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="H10" s="22" t="s">
+      <c r="I10" s="18">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
         <v>224</v>
-      </c>
-      <c r="I10" s="18">
-        <v>1</v>
-      </c>
-      <c r="J10" t="s">
-        <v>225</v>
       </c>
       <c r="K10" s="10" t="s">
         <v>73</v>
@@ -48938,106 +48937,106 @@
         <v>6</v>
       </c>
       <c r="M10" s="18" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="N10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O10" t="s">
         <v>96</v>
       </c>
       <c r="P10" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q10" t="s">
         <v>228</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
         <v>229</v>
       </c>
-      <c r="R10" t="s">
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10" t="s">
         <v>230</v>
       </c>
-      <c r="S10">
-        <v>1</v>
-      </c>
-      <c r="T10" t="s">
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10" s="18" t="s">
+      <c r="W10" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="X10" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>1</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="s">
         <v>232</v>
       </c>
-      <c r="W10" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="X10" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y10">
-        <v>0</v>
-      </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10">
-        <v>1</v>
-      </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="s">
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>1</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR10" t="s">
         <v>233</v>
       </c>
-      <c r="AH10">
-        <v>0</v>
-      </c>
-      <c r="AI10">
-        <v>0</v>
-      </c>
-      <c r="AJ10">
-        <v>0</v>
-      </c>
-      <c r="AK10">
-        <v>0</v>
-      </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <v>0</v>
-      </c>
-      <c r="AN10">
-        <v>0</v>
-      </c>
-      <c r="AO10">
-        <v>1</v>
-      </c>
-      <c r="AP10">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR10" t="s">
+      <c r="AS10" t="s">
         <v>234</v>
       </c>
-      <c r="AS10" t="s">
+      <c r="AT10" t="s">
         <v>235</v>
-      </c>
-      <c r="AT10" t="s">
-        <v>236</v>
       </c>
       <c r="AU10" s="21">
         <v>6.5000000000000002E-2</v>
@@ -49174,22 +49173,22 @@
         <v>107</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F11" s="11">
         <v>2020</v>
       </c>
       <c r="G11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H11" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="H11" s="22" t="s">
+      <c r="I11" s="18">
+        <v>1</v>
+      </c>
+      <c r="J11" t="s">
         <v>224</v>
-      </c>
-      <c r="I11" s="18">
-        <v>1</v>
-      </c>
-      <c r="J11" t="s">
-        <v>225</v>
       </c>
       <c r="K11" s="10" t="s">
         <v>73</v>
@@ -49198,106 +49197,106 @@
         <v>6</v>
       </c>
       <c r="M11" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O11" t="s">
         <v>96</v>
       </c>
       <c r="P11" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q11" t="s">
         <v>228</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="R11" t="s">
         <v>229</v>
       </c>
-      <c r="R11" t="s">
+      <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11" t="s">
         <v>230</v>
       </c>
-      <c r="S11">
-        <v>1</v>
-      </c>
-      <c r="T11" t="s">
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11" s="18" t="s">
+      <c r="W11" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="X11" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>1</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="s">
         <v>232</v>
       </c>
-      <c r="W11" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="X11" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y11">
-        <v>0</v>
-      </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
-      <c r="AA11">
-        <v>1</v>
-      </c>
-      <c r="AB11">
-        <v>0</v>
-      </c>
-      <c r="AC11">
-        <v>0</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="s">
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>1</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR11" t="s">
         <v>233</v>
       </c>
-      <c r="AH11">
-        <v>0</v>
-      </c>
-      <c r="AI11">
-        <v>0</v>
-      </c>
-      <c r="AJ11">
-        <v>0</v>
-      </c>
-      <c r="AK11">
-        <v>0</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>0</v>
-      </c>
-      <c r="AN11">
-        <v>0</v>
-      </c>
-      <c r="AO11">
-        <v>1</v>
-      </c>
-      <c r="AP11">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR11" t="s">
+      <c r="AS11" t="s">
         <v>234</v>
       </c>
-      <c r="AS11" t="s">
+      <c r="AT11" t="s">
         <v>235</v>
-      </c>
-      <c r="AT11" t="s">
-        <v>236</v>
       </c>
       <c r="AU11" s="21">
         <v>7.8E-2</v>
@@ -49434,22 +49433,22 @@
         <v>107</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F12" s="11">
         <v>2020</v>
       </c>
       <c r="G12" t="s">
+        <v>222</v>
+      </c>
+      <c r="H12" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="I12" s="18">
+        <v>1</v>
+      </c>
+      <c r="J12" t="s">
         <v>224</v>
-      </c>
-      <c r="I12" s="18">
-        <v>1</v>
-      </c>
-      <c r="J12" t="s">
-        <v>225</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>73</v>
@@ -49458,106 +49457,106 @@
         <v>7</v>
       </c>
       <c r="M12" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O12" t="s">
         <v>96</v>
       </c>
       <c r="P12" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q12" t="s">
         <v>228</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="R12" t="s">
         <v>229</v>
       </c>
-      <c r="R12" t="s">
+      <c r="S12">
+        <v>1</v>
+      </c>
+      <c r="T12" t="s">
         <v>230</v>
       </c>
-      <c r="S12">
-        <v>1</v>
-      </c>
-      <c r="T12" t="s">
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12" s="18" t="s">
+      <c r="W12" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="X12" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>1</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="s">
         <v>232</v>
       </c>
-      <c r="W12" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="X12" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y12">
-        <v>0</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <v>1</v>
-      </c>
-      <c r="AB12">
-        <v>0</v>
-      </c>
-      <c r="AC12">
-        <v>0</v>
-      </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="s">
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>1</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR12" t="s">
         <v>233</v>
       </c>
-      <c r="AH12">
-        <v>0</v>
-      </c>
-      <c r="AI12">
-        <v>0</v>
-      </c>
-      <c r="AJ12">
-        <v>0</v>
-      </c>
-      <c r="AK12">
-        <v>0</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>0</v>
-      </c>
-      <c r="AO12">
-        <v>1</v>
-      </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR12" t="s">
+      <c r="AS12" t="s">
         <v>234</v>
       </c>
-      <c r="AS12" t="s">
+      <c r="AT12" t="s">
         <v>235</v>
-      </c>
-      <c r="AT12" t="s">
-        <v>236</v>
       </c>
       <c r="AU12" s="21">
         <v>7.8E-2</v>
@@ -49691,22 +49690,22 @@
         <v>107</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F13" s="11">
         <v>2020</v>
       </c>
       <c r="G13" t="s">
+        <v>222</v>
+      </c>
+      <c r="H13" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="I13" s="18">
+        <v>1</v>
+      </c>
+      <c r="J13" t="s">
         <v>224</v>
-      </c>
-      <c r="I13" s="18">
-        <v>1</v>
-      </c>
-      <c r="J13" t="s">
-        <v>225</v>
       </c>
       <c r="K13" s="10" t="s">
         <v>73</v>
@@ -49715,106 +49714,106 @@
         <v>7</v>
       </c>
       <c r="M13" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O13" t="s">
         <v>96</v>
       </c>
       <c r="P13" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q13" t="s">
         <v>228</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
         <v>229</v>
       </c>
-      <c r="R13" t="s">
+      <c r="S13">
+        <v>1</v>
+      </c>
+      <c r="T13" t="s">
         <v>230</v>
       </c>
-      <c r="S13">
-        <v>1</v>
-      </c>
-      <c r="T13" t="s">
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13" s="18" t="s">
+      <c r="W13" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="X13" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>1</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="s">
         <v>232</v>
       </c>
-      <c r="W13" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="X13" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y13">
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>1</v>
-      </c>
-      <c r="AB13">
-        <v>0</v>
-      </c>
-      <c r="AC13">
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="s">
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>1</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR13" t="s">
         <v>233</v>
       </c>
-      <c r="AH13">
-        <v>0</v>
-      </c>
-      <c r="AI13">
-        <v>0</v>
-      </c>
-      <c r="AJ13">
-        <v>0</v>
-      </c>
-      <c r="AK13">
-        <v>0</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>0</v>
-      </c>
-      <c r="AO13">
-        <v>1</v>
-      </c>
-      <c r="AP13">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR13" t="s">
+      <c r="AS13" t="s">
         <v>234</v>
       </c>
-      <c r="AS13" t="s">
+      <c r="AT13" t="s">
         <v>235</v>
-      </c>
-      <c r="AT13" t="s">
-        <v>236</v>
       </c>
       <c r="AU13" s="21">
         <v>6.9000000000000006E-2</v>
@@ -49950,16 +49949,16 @@
         <v>130</v>
       </c>
       <c r="E14" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F14">
         <v>2018</v>
       </c>
       <c r="G14" t="s">
+        <v>239</v>
+      </c>
+      <c r="H14" t="s">
         <v>240</v>
-      </c>
-      <c r="H14" t="s">
-        <v>241</v>
       </c>
       <c r="I14">
         <v>1</v>
@@ -49977,100 +49976,100 @@
         <v>120</v>
       </c>
       <c r="N14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O14" t="s">
         <v>81</v>
       </c>
       <c r="P14" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q14" t="s">
         <v>242</v>
       </c>
-      <c r="Q14" t="s">
+      <c r="R14" t="s">
+        <v>229</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14" t="s">
+        <v>230</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14" t="s">
+        <v>231</v>
+      </c>
+      <c r="W14" t="s">
+        <v>231</v>
+      </c>
+      <c r="X14" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="s">
         <v>243</v>
       </c>
-      <c r="R14" t="s">
-        <v>230</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14" t="s">
-        <v>231</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14" t="s">
-        <v>232</v>
-      </c>
-      <c r="W14" t="s">
-        <v>232</v>
-      </c>
-      <c r="X14" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y14">
-        <v>0</v>
-      </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0</v>
-      </c>
-      <c r="AC14">
-        <v>0</v>
-      </c>
-      <c r="AD14">
-        <v>0</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>1</v>
-      </c>
-      <c r="AG14" t="s">
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>1</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="s">
         <v>244</v>
       </c>
-      <c r="AH14">
-        <v>0</v>
-      </c>
-      <c r="AI14">
-        <v>0</v>
-      </c>
-      <c r="AJ14">
-        <v>1</v>
-      </c>
-      <c r="AK14">
-        <v>0</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-      <c r="AN14">
-        <v>0</v>
-      </c>
-      <c r="AO14">
-        <v>0</v>
-      </c>
-      <c r="AP14">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="s">
+      <c r="AR14" t="s">
+        <v>233</v>
+      </c>
+      <c r="AS14" t="s">
         <v>245</v>
-      </c>
-      <c r="AR14" t="s">
-        <v>234</v>
-      </c>
-      <c r="AS14" t="s">
-        <v>246</v>
       </c>
       <c r="AT14" t="s">
         <v>73</v>
@@ -50205,16 +50204,16 @@
         <v>130</v>
       </c>
       <c r="E15" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F15">
         <v>2018</v>
       </c>
       <c r="G15" t="s">
+        <v>239</v>
+      </c>
+      <c r="H15" t="s">
         <v>240</v>
-      </c>
-      <c r="H15" t="s">
-        <v>241</v>
       </c>
       <c r="I15">
         <v>1</v>
@@ -50229,103 +50228,103 @@
         <v>347</v>
       </c>
       <c r="M15" s="18" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="N15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O15" t="s">
         <v>81</v>
       </c>
       <c r="P15" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q15" t="s">
         <v>242</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="R15" t="s">
+        <v>229</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15" t="s">
+        <v>230</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15" t="s">
+        <v>231</v>
+      </c>
+      <c r="W15" t="s">
+        <v>231</v>
+      </c>
+      <c r="X15" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>1</v>
+      </c>
+      <c r="AG15" t="s">
         <v>243</v>
       </c>
-      <c r="R15" t="s">
-        <v>230</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15" t="s">
-        <v>231</v>
-      </c>
-      <c r="U15">
-        <v>0</v>
-      </c>
-      <c r="V15" t="s">
-        <v>232</v>
-      </c>
-      <c r="W15" t="s">
-        <v>232</v>
-      </c>
-      <c r="X15" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y15">
-        <v>0</v>
-      </c>
-      <c r="Z15">
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>0</v>
-      </c>
-      <c r="AC15">
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <v>0</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>1</v>
-      </c>
-      <c r="AG15" t="s">
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>1</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="s">
         <v>244</v>
       </c>
-      <c r="AH15">
-        <v>0</v>
-      </c>
-      <c r="AI15">
-        <v>0</v>
-      </c>
-      <c r="AJ15">
-        <v>1</v>
-      </c>
-      <c r="AK15">
-        <v>0</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>0</v>
-      </c>
-      <c r="AN15">
-        <v>0</v>
-      </c>
-      <c r="AO15">
-        <v>0</v>
-      </c>
-      <c r="AP15">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="s">
+      <c r="AR15" t="s">
+        <v>233</v>
+      </c>
+      <c r="AS15" t="s">
         <v>245</v>
-      </c>
-      <c r="AR15" t="s">
-        <v>234</v>
-      </c>
-      <c r="AS15" t="s">
-        <v>246</v>
       </c>
       <c r="AT15" t="s">
         <v>73</v>
@@ -50460,16 +50459,16 @@
         <v>130</v>
       </c>
       <c r="E16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F16">
         <v>2018</v>
       </c>
       <c r="G16" t="s">
+        <v>239</v>
+      </c>
+      <c r="H16" t="s">
         <v>240</v>
-      </c>
-      <c r="H16" t="s">
-        <v>241</v>
       </c>
       <c r="I16">
         <v>1</v>
@@ -50487,65 +50486,65 @@
         <v>120</v>
       </c>
       <c r="N16" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O16" t="s">
         <v>81</v>
       </c>
       <c r="P16" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q16" t="s">
         <v>242</v>
       </c>
-      <c r="Q16" t="s">
+      <c r="R16" t="s">
+        <v>229</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16" t="s">
+        <v>230</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16" t="s">
+        <v>231</v>
+      </c>
+      <c r="W16" t="s">
+        <v>231</v>
+      </c>
+      <c r="X16" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="s">
         <v>243</v>
       </c>
-      <c r="R16" t="s">
-        <v>230</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16" t="s">
-        <v>231</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16" t="s">
-        <v>232</v>
-      </c>
-      <c r="W16" t="s">
-        <v>232</v>
-      </c>
-      <c r="X16" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-      <c r="AC16">
-        <v>0</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>1</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>244</v>
-      </c>
       <c r="AH16">
         <v>0</v>
       </c>
@@ -50574,13 +50573,13 @@
         <v>0</v>
       </c>
       <c r="AQ16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AR16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AS16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AT16" t="s">
         <v>73</v>
@@ -50715,16 +50714,16 @@
         <v>130</v>
       </c>
       <c r="E17" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F17">
         <v>2018</v>
       </c>
       <c r="G17" t="s">
+        <v>239</v>
+      </c>
+      <c r="H17" t="s">
         <v>240</v>
-      </c>
-      <c r="H17" t="s">
-        <v>241</v>
       </c>
       <c r="I17">
         <v>1</v>
@@ -50739,68 +50738,68 @@
         <v>348</v>
       </c>
       <c r="M17" s="18" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="N17" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O17" t="s">
         <v>81</v>
       </c>
       <c r="P17" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q17" t="s">
         <v>242</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="R17" t="s">
+        <v>229</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17" t="s">
+        <v>230</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17" t="s">
+        <v>231</v>
+      </c>
+      <c r="W17" t="s">
+        <v>231</v>
+      </c>
+      <c r="X17" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>1</v>
+      </c>
+      <c r="AG17" t="s">
         <v>243</v>
       </c>
-      <c r="R17" t="s">
-        <v>230</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17" t="s">
-        <v>231</v>
-      </c>
-      <c r="U17">
-        <v>0</v>
-      </c>
-      <c r="V17" t="s">
-        <v>232</v>
-      </c>
-      <c r="W17" t="s">
-        <v>232</v>
-      </c>
-      <c r="X17" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
-      <c r="AC17">
-        <v>0</v>
-      </c>
-      <c r="AD17">
-        <v>0</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <v>1</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>244</v>
-      </c>
       <c r="AH17">
         <v>0</v>
       </c>
@@ -50829,13 +50828,13 @@
         <v>0</v>
       </c>
       <c r="AQ17" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AR17" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AS17" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AT17" t="s">
         <v>73</v>
@@ -50971,61 +50970,61 @@
         <v>137</v>
       </c>
       <c r="E18" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F18" s="100">
         <v>2015</v>
       </c>
       <c r="G18" t="s">
+        <v>250</v>
+      </c>
+      <c r="H18" t="s">
         <v>251</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" s="101">
+        <v>1</v>
+      </c>
+      <c r="J18" t="s">
         <v>252</v>
       </c>
-      <c r="I18" s="101">
-        <v>1</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="K18" s="100" t="s">
+        <v>73</v>
+      </c>
+      <c r="L18" t="s">
         <v>253</v>
       </c>
-      <c r="K18" s="100" t="s">
-        <v>73</v>
-      </c>
-      <c r="L18" t="s">
+      <c r="M18" s="18" t="s">
         <v>254</v>
       </c>
-      <c r="M18" s="18" t="s">
+      <c r="N18" t="s">
         <v>255</v>
-      </c>
-      <c r="N18" t="s">
-        <v>256</v>
       </c>
       <c r="O18" t="s">
         <v>81</v>
       </c>
       <c r="P18" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q18" t="s">
+        <v>228</v>
+      </c>
+      <c r="R18" t="s">
         <v>229</v>
       </c>
-      <c r="R18" t="s">
-        <v>230</v>
-      </c>
       <c r="S18">
         <v>0</v>
       </c>
       <c r="T18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="U18">
         <v>0</v>
       </c>
       <c r="V18" s="100" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="W18" s="100" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="X18" s="100" t="s">
         <v>73</v>
@@ -51055,46 +51054,46 @@
         <v>0</v>
       </c>
       <c r="AG18" s="101" t="s">
+        <v>256</v>
+      </c>
+      <c r="AH18" s="101">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="101">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="101">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="101">
+        <v>0</v>
+      </c>
+      <c r="AL18" s="101">
+        <v>1</v>
+      </c>
+      <c r="AM18" s="101">
+        <v>0</v>
+      </c>
+      <c r="AN18" s="101">
+        <v>0</v>
+      </c>
+      <c r="AO18" s="101">
+        <v>0</v>
+      </c>
+      <c r="AP18" s="101">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR18" t="s">
+        <v>233</v>
+      </c>
+      <c r="AS18" t="s">
         <v>257</v>
       </c>
-      <c r="AH18" s="101">
-        <v>0</v>
-      </c>
-      <c r="AI18" s="101">
-        <v>0</v>
-      </c>
-      <c r="AJ18" s="101">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="101">
-        <v>0</v>
-      </c>
-      <c r="AL18" s="101">
-        <v>1</v>
-      </c>
-      <c r="AM18" s="101">
-        <v>0</v>
-      </c>
-      <c r="AN18" s="101">
-        <v>0</v>
-      </c>
-      <c r="AO18" s="101">
-        <v>0</v>
-      </c>
-      <c r="AP18" s="101">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR18" t="s">
-        <v>234</v>
-      </c>
-      <c r="AS18" t="s">
-        <v>258</v>
-      </c>
       <c r="AT18" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AU18" s="21">
         <v>2.7799999999999998E-2</v>
@@ -51152,13 +51151,13 @@
         <v>73</v>
       </c>
       <c r="BM18" s="101" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BN18" s="101">
         <v>0.1</v>
       </c>
       <c r="BO18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BP18" s="103" t="s">
         <v>73</v>
@@ -51232,61 +51231,61 @@
         <v>137</v>
       </c>
       <c r="E19" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F19" s="100">
         <v>2015</v>
       </c>
       <c r="G19" t="s">
+        <v>250</v>
+      </c>
+      <c r="H19" t="s">
         <v>251</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" s="101">
+        <v>1</v>
+      </c>
+      <c r="J19" t="s">
         <v>252</v>
       </c>
-      <c r="I19" s="101">
-        <v>1</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="K19" s="100" t="s">
+        <v>73</v>
+      </c>
+      <c r="L19" t="s">
         <v>253</v>
       </c>
-      <c r="K19" s="100" t="s">
-        <v>73</v>
-      </c>
-      <c r="L19" t="s">
+      <c r="M19" s="18" t="s">
         <v>254</v>
       </c>
-      <c r="M19" s="18" t="s">
+      <c r="N19" t="s">
         <v>255</v>
-      </c>
-      <c r="N19" t="s">
-        <v>256</v>
       </c>
       <c r="O19" t="s">
         <v>81</v>
       </c>
       <c r="P19" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q19" t="s">
+        <v>228</v>
+      </c>
+      <c r="R19" t="s">
         <v>229</v>
       </c>
-      <c r="R19" t="s">
-        <v>230</v>
-      </c>
       <c r="S19">
         <v>0</v>
       </c>
       <c r="T19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="U19">
         <v>0</v>
       </c>
       <c r="V19" s="100" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="W19" s="100" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="X19" s="100" t="s">
         <v>73</v>
@@ -51316,46 +51315,46 @@
         <v>0</v>
       </c>
       <c r="AG19" s="101" t="s">
+        <v>256</v>
+      </c>
+      <c r="AH19" s="101">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="101">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="101">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="101">
+        <v>0</v>
+      </c>
+      <c r="AL19" s="101">
+        <v>1</v>
+      </c>
+      <c r="AM19" s="101">
+        <v>0</v>
+      </c>
+      <c r="AN19" s="101">
+        <v>0</v>
+      </c>
+      <c r="AO19" s="101">
+        <v>0</v>
+      </c>
+      <c r="AP19" s="101">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="s">
+        <v>260</v>
+      </c>
+      <c r="AR19" t="s">
+        <v>233</v>
+      </c>
+      <c r="AS19" t="s">
         <v>257</v>
       </c>
-      <c r="AH19" s="101">
-        <v>0</v>
-      </c>
-      <c r="AI19" s="101">
-        <v>0</v>
-      </c>
-      <c r="AJ19" s="101">
-        <v>0</v>
-      </c>
-      <c r="AK19" s="101">
-        <v>0</v>
-      </c>
-      <c r="AL19" s="101">
-        <v>1</v>
-      </c>
-      <c r="AM19" s="101">
-        <v>0</v>
-      </c>
-      <c r="AN19" s="101">
-        <v>0</v>
-      </c>
-      <c r="AO19" s="101">
-        <v>0</v>
-      </c>
-      <c r="AP19" s="101">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="s">
-        <v>261</v>
-      </c>
-      <c r="AR19" t="s">
-        <v>234</v>
-      </c>
-      <c r="AS19" t="s">
-        <v>258</v>
-      </c>
       <c r="AT19" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AU19">
         <v>5.4399999999999997E-2</v>
@@ -51413,13 +51412,13 @@
         <v>73</v>
       </c>
       <c r="BM19" s="101" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BN19" s="101">
         <v>0.1</v>
       </c>
       <c r="BO19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BP19" s="103" t="s">
         <v>73</v>
@@ -51493,61 +51492,61 @@
         <v>137</v>
       </c>
       <c r="E20" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F20" s="100">
         <v>2015</v>
       </c>
       <c r="G20" t="s">
+        <v>250</v>
+      </c>
+      <c r="H20" t="s">
         <v>251</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" s="101">
+        <v>1</v>
+      </c>
+      <c r="J20" t="s">
         <v>252</v>
       </c>
-      <c r="I20" s="101">
-        <v>1</v>
-      </c>
-      <c r="J20" t="s">
-        <v>253</v>
-      </c>
       <c r="K20" s="100" t="s">
         <v>73</v>
       </c>
       <c r="L20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="M20" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="N20" t="s">
         <v>255</v>
-      </c>
-      <c r="N20" t="s">
-        <v>256</v>
       </c>
       <c r="O20" t="s">
         <v>81</v>
       </c>
       <c r="P20" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q20" t="s">
+        <v>228</v>
+      </c>
+      <c r="R20" t="s">
         <v>229</v>
       </c>
-      <c r="R20" t="s">
-        <v>230</v>
-      </c>
       <c r="S20">
         <v>0</v>
       </c>
       <c r="T20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="U20">
         <v>0</v>
       </c>
       <c r="V20" s="100" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="W20" s="100" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="X20" s="100" t="s">
         <v>73</v>
@@ -51577,46 +51576,46 @@
         <v>0</v>
       </c>
       <c r="AG20" s="101" t="s">
+        <v>256</v>
+      </c>
+      <c r="AH20" s="101">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="101">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="101">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="101">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="101">
+        <v>1</v>
+      </c>
+      <c r="AM20" s="101">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="101">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="101">
+        <v>0</v>
+      </c>
+      <c r="AP20" s="101">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR20" t="s">
+        <v>233</v>
+      </c>
+      <c r="AS20" t="s">
         <v>257</v>
       </c>
-      <c r="AH20" s="101">
-        <v>0</v>
-      </c>
-      <c r="AI20" s="101">
-        <v>0</v>
-      </c>
-      <c r="AJ20" s="101">
-        <v>0</v>
-      </c>
-      <c r="AK20" s="101">
-        <v>0</v>
-      </c>
-      <c r="AL20" s="101">
-        <v>1</v>
-      </c>
-      <c r="AM20" s="101">
-        <v>0</v>
-      </c>
-      <c r="AN20" s="101">
-        <v>0</v>
-      </c>
-      <c r="AO20" s="101">
-        <v>0</v>
-      </c>
-      <c r="AP20" s="101">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR20" t="s">
-        <v>234</v>
-      </c>
-      <c r="AS20" t="s">
-        <v>258</v>
-      </c>
       <c r="AT20" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AU20" s="21">
         <v>5.4600000000000003E-2</v>
@@ -51674,13 +51673,13 @@
         <v>73</v>
       </c>
       <c r="BM20" s="101" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BN20" s="101">
         <v>0.1</v>
       </c>
       <c r="BO20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BP20" s="103" t="s">
         <v>73</v>
@@ -51754,61 +51753,61 @@
         <v>137</v>
       </c>
       <c r="E21" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F21" s="100">
         <v>2015</v>
       </c>
       <c r="G21" t="s">
+        <v>250</v>
+      </c>
+      <c r="H21" t="s">
         <v>251</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" s="101">
+        <v>1</v>
+      </c>
+      <c r="J21" t="s">
         <v>252</v>
       </c>
-      <c r="I21" s="101">
-        <v>1</v>
-      </c>
-      <c r="J21" t="s">
-        <v>253</v>
-      </c>
       <c r="K21" s="100" t="s">
         <v>73</v>
       </c>
       <c r="L21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="M21" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="N21" t="s">
         <v>255</v>
-      </c>
-      <c r="N21" t="s">
-        <v>256</v>
       </c>
       <c r="O21" t="s">
         <v>81</v>
       </c>
       <c r="P21" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q21" t="s">
+        <v>228</v>
+      </c>
+      <c r="R21" t="s">
         <v>229</v>
       </c>
-      <c r="R21" t="s">
-        <v>230</v>
-      </c>
       <c r="S21">
         <v>0</v>
       </c>
       <c r="T21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="U21">
         <v>0</v>
       </c>
       <c r="V21" s="100" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="W21" s="100" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="X21" s="100" t="s">
         <v>73</v>
@@ -51838,46 +51837,46 @@
         <v>0</v>
       </c>
       <c r="AG21" s="101" t="s">
+        <v>256</v>
+      </c>
+      <c r="AH21" s="101">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="101">
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="101">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="101">
+        <v>0</v>
+      </c>
+      <c r="AL21" s="101">
+        <v>1</v>
+      </c>
+      <c r="AM21" s="101">
+        <v>0</v>
+      </c>
+      <c r="AN21" s="101">
+        <v>0</v>
+      </c>
+      <c r="AO21" s="101">
+        <v>0</v>
+      </c>
+      <c r="AP21" s="101">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="s">
+        <v>260</v>
+      </c>
+      <c r="AR21" t="s">
+        <v>233</v>
+      </c>
+      <c r="AS21" t="s">
         <v>257</v>
       </c>
-      <c r="AH21" s="101">
-        <v>0</v>
-      </c>
-      <c r="AI21" s="101">
-        <v>0</v>
-      </c>
-      <c r="AJ21" s="101">
-        <v>0</v>
-      </c>
-      <c r="AK21" s="101">
-        <v>0</v>
-      </c>
-      <c r="AL21" s="101">
-        <v>1</v>
-      </c>
-      <c r="AM21" s="101">
-        <v>0</v>
-      </c>
-      <c r="AN21" s="101">
-        <v>0</v>
-      </c>
-      <c r="AO21" s="101">
-        <v>0</v>
-      </c>
-      <c r="AP21" s="101">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="s">
-        <v>261</v>
-      </c>
-      <c r="AR21" t="s">
-        <v>234</v>
-      </c>
-      <c r="AS21" t="s">
-        <v>258</v>
-      </c>
       <c r="AT21" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AU21" s="21">
         <v>4.19E-2</v>
@@ -51935,13 +51934,13 @@
         <v>73</v>
       </c>
       <c r="BM21" s="101" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BN21" s="101">
         <v>0.1</v>
       </c>
       <c r="BO21" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BP21" s="103" t="s">
         <v>73</v>
@@ -52012,16 +52011,16 @@
         <v>138</v>
       </c>
       <c r="E22" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F22" s="100">
         <v>1988</v>
       </c>
       <c r="G22" t="s">
+        <v>263</v>
+      </c>
+      <c r="H22" t="s">
         <v>264</v>
-      </c>
-      <c r="H22" t="s">
-        <v>265</v>
       </c>
       <c r="I22" s="101">
         <v>1</v>
@@ -52039,103 +52038,103 @@
         <v>93</v>
       </c>
       <c r="N22" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O22" t="s">
         <v>81</v>
       </c>
       <c r="P22" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q22" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="R22" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22" t="s">
+        <v>188</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22" s="100" t="s">
+        <v>231</v>
+      </c>
+      <c r="W22" s="100" t="s">
+        <v>231</v>
+      </c>
+      <c r="X22" s="100" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y22" s="101">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="101">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="101">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="101">
+        <v>1</v>
+      </c>
+      <c r="AC22" s="101">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="101">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="101">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="101">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="101" t="s">
         <v>266</v>
       </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22" t="s">
-        <v>189</v>
-      </c>
-      <c r="U22">
-        <v>0</v>
-      </c>
-      <c r="V22" s="100" t="s">
-        <v>232</v>
-      </c>
-      <c r="W22" s="100" t="s">
-        <v>232</v>
-      </c>
-      <c r="X22" s="100" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y22" s="101">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="101">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="101">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="101">
-        <v>1</v>
-      </c>
-      <c r="AC22" s="101">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="101">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="101">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="101">
-        <v>0</v>
-      </c>
-      <c r="AG22" s="101" t="s">
+      <c r="AH22" s="101">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="101">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="101">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="101">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="101">
+        <v>0</v>
+      </c>
+      <c r="AM22" s="101">
+        <v>0</v>
+      </c>
+      <c r="AN22" s="101">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="101">
+        <v>1</v>
+      </c>
+      <c r="AP22" s="101">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR22" t="s">
+        <v>233</v>
+      </c>
+      <c r="AS22" t="s">
         <v>267</v>
       </c>
-      <c r="AH22" s="101">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="101">
-        <v>0</v>
-      </c>
-      <c r="AJ22" s="101">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="101">
-        <v>0</v>
-      </c>
-      <c r="AL22" s="101">
-        <v>0</v>
-      </c>
-      <c r="AM22" s="101">
-        <v>0</v>
-      </c>
-      <c r="AN22" s="101">
-        <v>0</v>
-      </c>
-      <c r="AO22" s="101">
-        <v>1</v>
-      </c>
-      <c r="AP22" s="101">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR22" t="s">
-        <v>234</v>
-      </c>
-      <c r="AS22" t="s">
-        <v>268</v>
-      </c>
       <c r="AT22" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AU22" s="7">
         <v>0.01</v>
@@ -52200,7 +52199,7 @@
         <v>1</v>
       </c>
       <c r="BO22" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BP22" s="103" t="s">
         <v>73</v>
@@ -52271,16 +52270,16 @@
         <v>138</v>
       </c>
       <c r="E23" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F23" s="100">
         <v>1988</v>
       </c>
       <c r="G23" t="s">
+        <v>263</v>
+      </c>
+      <c r="H23" t="s">
         <v>264</v>
-      </c>
-      <c r="H23" t="s">
-        <v>265</v>
       </c>
       <c r="I23" s="101">
         <v>1</v>
@@ -52298,103 +52297,103 @@
         <v>93</v>
       </c>
       <c r="N23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O23" t="s">
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="R23" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23" t="s">
+        <v>188</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23" s="100" t="s">
+        <v>231</v>
+      </c>
+      <c r="W23" s="100" t="s">
+        <v>231</v>
+      </c>
+      <c r="X23" s="100" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y23" s="101">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="101">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="101">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="101">
+        <v>1</v>
+      </c>
+      <c r="AC23" s="101">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="101">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="101">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="101">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="101" t="s">
         <v>266</v>
       </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23" t="s">
-        <v>189</v>
-      </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23" s="100" t="s">
-        <v>232</v>
-      </c>
-      <c r="W23" s="100" t="s">
-        <v>232</v>
-      </c>
-      <c r="X23" s="100" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y23" s="101">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="101">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="101">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="101">
-        <v>1</v>
-      </c>
-      <c r="AC23" s="101">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="101">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="101">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="101">
-        <v>0</v>
-      </c>
-      <c r="AG23" s="101" t="s">
+      <c r="AH23" s="101">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="101">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="101">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="101">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="101">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="101">
+        <v>0</v>
+      </c>
+      <c r="AN23" s="101">
+        <v>0</v>
+      </c>
+      <c r="AO23" s="101">
+        <v>1</v>
+      </c>
+      <c r="AP23" s="101">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="s">
+        <v>268</v>
+      </c>
+      <c r="AR23" t="s">
+        <v>233</v>
+      </c>
+      <c r="AS23" t="s">
         <v>267</v>
       </c>
-      <c r="AH23" s="101">
-        <v>0</v>
-      </c>
-      <c r="AI23" s="101">
-        <v>0</v>
-      </c>
-      <c r="AJ23" s="101">
-        <v>0</v>
-      </c>
-      <c r="AK23" s="101">
-        <v>0</v>
-      </c>
-      <c r="AL23" s="101">
-        <v>0</v>
-      </c>
-      <c r="AM23" s="101">
-        <v>0</v>
-      </c>
-      <c r="AN23" s="101">
-        <v>0</v>
-      </c>
-      <c r="AO23" s="101">
-        <v>1</v>
-      </c>
-      <c r="AP23" s="101">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="s">
-        <v>269</v>
-      </c>
-      <c r="AR23" t="s">
-        <v>234</v>
-      </c>
-      <c r="AS23" t="s">
-        <v>268</v>
-      </c>
       <c r="AT23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AU23" s="7">
         <v>0.12</v>
@@ -52459,7 +52458,7 @@
         <v>1</v>
       </c>
       <c r="BO23" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BP23" s="103" t="s">
         <v>73</v>
@@ -52530,16 +52529,16 @@
         <v>139</v>
       </c>
       <c r="E24" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F24" s="100">
         <v>2013</v>
       </c>
       <c r="G24" t="s">
+        <v>270</v>
+      </c>
+      <c r="H24" s="123" t="s">
         <v>271</v>
-      </c>
-      <c r="H24" s="123" t="s">
-        <v>272</v>
       </c>
       <c r="I24" s="101">
         <v>1</v>
@@ -52557,103 +52556,103 @@
         <v>120</v>
       </c>
       <c r="N24" t="s">
+        <v>226</v>
+      </c>
+      <c r="O24" t="s">
+        <v>272</v>
+      </c>
+      <c r="P24" t="s">
         <v>227</v>
       </c>
-      <c r="O24" t="s">
+      <c r="Q24" t="s">
+        <v>228</v>
+      </c>
+      <c r="R24" t="s">
+        <v>229</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24" t="s">
+        <v>230</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24" s="100" t="s">
+        <v>231</v>
+      </c>
+      <c r="W24" s="100" t="s">
+        <v>231</v>
+      </c>
+      <c r="X24" s="100" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y24" s="101">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="101">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="101">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="101">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="101">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="101">
+        <v>1</v>
+      </c>
+      <c r="AE24" s="101">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="101">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="101" t="s">
         <v>273</v>
       </c>
-      <c r="P24" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>229</v>
-      </c>
-      <c r="R24" t="s">
-        <v>230</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24" t="s">
-        <v>231</v>
-      </c>
-      <c r="U24">
-        <v>0</v>
-      </c>
-      <c r="V24" s="100" t="s">
-        <v>232</v>
-      </c>
-      <c r="W24" s="100" t="s">
-        <v>232</v>
-      </c>
-      <c r="X24" s="100" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y24" s="101">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="101">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="101">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="101">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="101">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="101">
-        <v>1</v>
-      </c>
-      <c r="AE24" s="101">
-        <v>0</v>
-      </c>
-      <c r="AF24" s="101">
-        <v>0</v>
-      </c>
-      <c r="AG24" s="101" t="s">
+      <c r="AH24" s="101">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="101">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="101">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="101">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="101">
+        <v>0</v>
+      </c>
+      <c r="AM24" s="101">
+        <v>1</v>
+      </c>
+      <c r="AN24" s="101">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="101">
+        <v>0</v>
+      </c>
+      <c r="AP24" s="101">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR24" t="s">
+        <v>233</v>
+      </c>
+      <c r="AS24" t="s">
         <v>274</v>
       </c>
-      <c r="AH24" s="101">
-        <v>0</v>
-      </c>
-      <c r="AI24" s="101">
-        <v>0</v>
-      </c>
-      <c r="AJ24" s="101">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="101">
-        <v>0</v>
-      </c>
-      <c r="AL24" s="101">
-        <v>0</v>
-      </c>
-      <c r="AM24" s="101">
-        <v>1</v>
-      </c>
-      <c r="AN24" s="101">
-        <v>0</v>
-      </c>
-      <c r="AO24" s="101">
-        <v>0</v>
-      </c>
-      <c r="AP24" s="101">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR24" t="s">
-        <v>234</v>
-      </c>
-      <c r="AS24" t="s">
-        <v>275</v>
-      </c>
       <c r="AT24" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AU24" s="108">
         <v>0.77300000000000002</v>
@@ -52787,16 +52786,16 @@
         <v>139</v>
       </c>
       <c r="E25" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F25" s="100">
         <v>2013</v>
       </c>
       <c r="G25" t="s">
+        <v>270</v>
+      </c>
+      <c r="H25" t="s">
         <v>271</v>
-      </c>
-      <c r="H25" t="s">
-        <v>272</v>
       </c>
       <c r="I25" s="101">
         <v>1</v>
@@ -52811,68 +52810,68 @@
         <v>283</v>
       </c>
       <c r="M25" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="N25" t="s">
+        <v>226</v>
+      </c>
+      <c r="O25" t="s">
+        <v>272</v>
+      </c>
+      <c r="P25" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>228</v>
+      </c>
+      <c r="R25" t="s">
+        <v>229</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25" t="s">
+        <v>230</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25" s="100" t="s">
+        <v>231</v>
+      </c>
+      <c r="W25" s="100" t="s">
+        <v>231</v>
+      </c>
+      <c r="X25" s="100" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y25" s="101">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="101">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="101">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="101">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="101">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="101">
+        <v>1</v>
+      </c>
+      <c r="AE25" s="101">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="101">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="101" t="s">
         <v>276</v>
       </c>
-      <c r="N25" t="s">
-        <v>227</v>
-      </c>
-      <c r="O25" t="s">
-        <v>273</v>
-      </c>
-      <c r="P25" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>229</v>
-      </c>
-      <c r="R25" t="s">
-        <v>230</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25" t="s">
-        <v>231</v>
-      </c>
-      <c r="U25">
-        <v>0</v>
-      </c>
-      <c r="V25" s="100" t="s">
-        <v>232</v>
-      </c>
-      <c r="W25" s="100" t="s">
-        <v>232</v>
-      </c>
-      <c r="X25" s="100" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y25" s="101">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="101">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="101">
-        <v>0</v>
-      </c>
-      <c r="AB25" s="101">
-        <v>0</v>
-      </c>
-      <c r="AC25" s="101">
-        <v>0</v>
-      </c>
-      <c r="AD25" s="101">
-        <v>1</v>
-      </c>
-      <c r="AE25" s="101">
-        <v>0</v>
-      </c>
-      <c r="AF25" s="101">
-        <v>0</v>
-      </c>
-      <c r="AG25" s="101" t="s">
-        <v>277</v>
-      </c>
       <c r="AH25" s="101">
         <v>0</v>
       </c>
@@ -52904,13 +52903,13 @@
         <v>73</v>
       </c>
       <c r="AR25" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AS25" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AT25" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AU25" s="108">
         <v>0.84</v>
@@ -53044,16 +53043,16 @@
         <v>139</v>
       </c>
       <c r="E26" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F26" s="100">
         <v>2013</v>
       </c>
       <c r="G26" t="s">
+        <v>270</v>
+      </c>
+      <c r="H26" t="s">
         <v>271</v>
-      </c>
-      <c r="H26" t="s">
-        <v>272</v>
       </c>
       <c r="I26" s="101">
         <v>1</v>
@@ -53071,34 +53070,34 @@
         <v>120</v>
       </c>
       <c r="N26" t="s">
+        <v>226</v>
+      </c>
+      <c r="O26" t="s">
+        <v>272</v>
+      </c>
+      <c r="P26" t="s">
         <v>227</v>
       </c>
-      <c r="O26" t="s">
-        <v>273</v>
-      </c>
-      <c r="P26" t="s">
+      <c r="Q26" t="s">
         <v>228</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="R26" t="s">
         <v>229</v>
       </c>
-      <c r="R26" t="s">
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26" t="s">
         <v>230</v>
       </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26" t="s">
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26" s="100" t="s">
         <v>231</v>
       </c>
-      <c r="U26">
-        <v>0</v>
-      </c>
-      <c r="V26" s="100" t="s">
-        <v>232</v>
-      </c>
       <c r="W26" s="100" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="X26" s="100" t="s">
         <v>73</v>
@@ -53128,46 +53127,46 @@
         <v>0</v>
       </c>
       <c r="AG26" s="101" t="s">
+        <v>276</v>
+      </c>
+      <c r="AH26" s="101">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="101">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="101">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="101">
+        <v>0</v>
+      </c>
+      <c r="AL26" s="101">
+        <v>0</v>
+      </c>
+      <c r="AM26" s="101">
+        <v>1</v>
+      </c>
+      <c r="AN26" s="101">
+        <v>0</v>
+      </c>
+      <c r="AO26" s="101">
+        <v>0</v>
+      </c>
+      <c r="AP26" s="101">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR26" t="s">
+        <v>233</v>
+      </c>
+      <c r="AS26" t="s">
         <v>277</v>
       </c>
-      <c r="AH26" s="101">
-        <v>0</v>
-      </c>
-      <c r="AI26" s="101">
-        <v>0</v>
-      </c>
-      <c r="AJ26" s="101">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="101">
-        <v>0</v>
-      </c>
-      <c r="AL26" s="101">
-        <v>0</v>
-      </c>
-      <c r="AM26" s="101">
-        <v>1</v>
-      </c>
-      <c r="AN26" s="101">
-        <v>0</v>
-      </c>
-      <c r="AO26" s="101">
-        <v>0</v>
-      </c>
-      <c r="AP26" s="101">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR26" t="s">
-        <v>234</v>
-      </c>
-      <c r="AS26" t="s">
-        <v>278</v>
-      </c>
       <c r="AT26" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AU26" s="108">
         <v>1.0999999999999999E-2</v>
@@ -53301,16 +53300,16 @@
         <v>139</v>
       </c>
       <c r="E27" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F27" s="100">
         <v>2013</v>
       </c>
       <c r="G27" t="s">
+        <v>270</v>
+      </c>
+      <c r="H27" t="s">
         <v>271</v>
-      </c>
-      <c r="H27" t="s">
-        <v>272</v>
       </c>
       <c r="I27" s="101">
         <v>1</v>
@@ -53325,106 +53324,106 @@
         <v>283</v>
       </c>
       <c r="M27" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="N27" t="s">
+        <v>226</v>
+      </c>
+      <c r="O27" t="s">
+        <v>272</v>
+      </c>
+      <c r="P27" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>228</v>
+      </c>
+      <c r="R27" t="s">
+        <v>229</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27" t="s">
+        <v>230</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27" s="100" t="s">
+        <v>231</v>
+      </c>
+      <c r="W27" s="100" t="s">
+        <v>231</v>
+      </c>
+      <c r="X27" s="100" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y27" s="101">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="101">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="101">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="101">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="101">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="101">
+        <v>1</v>
+      </c>
+      <c r="AE27" s="101">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="101">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="101" t="s">
         <v>276</v>
       </c>
-      <c r="N27" t="s">
-        <v>227</v>
-      </c>
-      <c r="O27" t="s">
-        <v>273</v>
-      </c>
-      <c r="P27" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>229</v>
-      </c>
-      <c r="R27" t="s">
-        <v>230</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27" t="s">
-        <v>231</v>
-      </c>
-      <c r="U27">
-        <v>0</v>
-      </c>
-      <c r="V27" s="100" t="s">
-        <v>232</v>
-      </c>
-      <c r="W27" s="100" t="s">
-        <v>232</v>
-      </c>
-      <c r="X27" s="100" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y27" s="101">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="101">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="101">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="101">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="101">
-        <v>0</v>
-      </c>
-      <c r="AD27" s="101">
-        <v>1</v>
-      </c>
-      <c r="AE27" s="101">
-        <v>0</v>
-      </c>
-      <c r="AF27" s="101">
-        <v>0</v>
-      </c>
-      <c r="AG27" s="101" t="s">
+      <c r="AH27" s="101">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="101">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="101">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="101">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="101">
+        <v>0</v>
+      </c>
+      <c r="AM27" s="101">
+        <v>1</v>
+      </c>
+      <c r="AN27" s="101">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="101">
+        <v>0</v>
+      </c>
+      <c r="AP27" s="101">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR27" t="s">
+        <v>233</v>
+      </c>
+      <c r="AS27" t="s">
         <v>277</v>
       </c>
-      <c r="AH27" s="101">
-        <v>0</v>
-      </c>
-      <c r="AI27" s="101">
-        <v>0</v>
-      </c>
-      <c r="AJ27" s="101">
-        <v>0</v>
-      </c>
-      <c r="AK27" s="101">
-        <v>0</v>
-      </c>
-      <c r="AL27" s="101">
-        <v>0</v>
-      </c>
-      <c r="AM27" s="101">
-        <v>1</v>
-      </c>
-      <c r="AN27" s="101">
-        <v>0</v>
-      </c>
-      <c r="AO27" s="101">
-        <v>0</v>
-      </c>
-      <c r="AP27" s="101">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR27" t="s">
-        <v>234</v>
-      </c>
-      <c r="AS27" t="s">
-        <v>278</v>
-      </c>
       <c r="AT27" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AU27" s="108">
         <v>9.5000000000000001E-2</v>
@@ -53558,16 +53557,16 @@
         <v>140</v>
       </c>
       <c r="E28" s="94" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F28" s="94">
         <v>2016</v>
       </c>
       <c r="G28" s="58" t="s">
+        <v>279</v>
+      </c>
+      <c r="H28" s="94" t="s">
         <v>280</v>
-      </c>
-      <c r="H28" s="94" t="s">
-        <v>281</v>
       </c>
       <c r="I28" s="94">
         <v>1</v>
@@ -53585,103 +53584,103 @@
         <v>120</v>
       </c>
       <c r="N28" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O28" s="94" t="s">
         <v>124</v>
       </c>
       <c r="P28" s="94" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q28" s="94" t="s">
+        <v>281</v>
+      </c>
+      <c r="R28" s="94" t="s">
         <v>282</v>
       </c>
-      <c r="R28" s="94" t="s">
+      <c r="S28" s="94">
+        <v>0</v>
+      </c>
+      <c r="T28" s="94" t="s">
+        <v>230</v>
+      </c>
+      <c r="U28" s="94">
+        <v>0</v>
+      </c>
+      <c r="V28" s="94" t="s">
         <v>283</v>
       </c>
-      <c r="S28" s="94">
-        <v>0</v>
-      </c>
-      <c r="T28" s="94" t="s">
+      <c r="W28" s="94" t="s">
         <v>231</v>
       </c>
-      <c r="U28" s="94">
-        <v>0</v>
-      </c>
-      <c r="V28" s="94" t="s">
+      <c r="X28" s="94" t="s">
         <v>284</v>
       </c>
-      <c r="W28" s="94" t="s">
-        <v>232</v>
-      </c>
-      <c r="X28" s="94" t="s">
+      <c r="Y28" s="94">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="94">
+        <v>1</v>
+      </c>
+      <c r="AG28" s="94" t="s">
         <v>285</v>
       </c>
-      <c r="Y28" s="94">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AC28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AD28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AE28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AF28" s="94">
-        <v>1</v>
-      </c>
-      <c r="AG28" s="94" t="s">
+      <c r="AH28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="94">
+        <v>1</v>
+      </c>
+      <c r="AP28" s="94">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="94" t="s">
         <v>286</v>
       </c>
-      <c r="AH28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AI28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AJ28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AK28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AL28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AM28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AN28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AO28" s="94">
-        <v>1</v>
-      </c>
-      <c r="AP28" s="94">
-        <v>0</v>
-      </c>
-      <c r="AQ28" s="94" t="s">
+      <c r="AR28" s="94" t="s">
+        <v>233</v>
+      </c>
+      <c r="AS28" s="94" t="s">
         <v>287</v>
       </c>
-      <c r="AR28" s="94" t="s">
-        <v>234</v>
-      </c>
-      <c r="AS28" s="94" t="s">
-        <v>288</v>
-      </c>
       <c r="AT28" s="41" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AU28" s="113">
         <v>3.8109999999999999</v>
@@ -53818,16 +53817,16 @@
         <v>140</v>
       </c>
       <c r="E29" s="94" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F29" s="94">
         <v>2016</v>
       </c>
       <c r="G29" s="58" t="s">
+        <v>279</v>
+      </c>
+      <c r="H29" s="94" t="s">
         <v>280</v>
-      </c>
-      <c r="H29" s="94" t="s">
-        <v>281</v>
       </c>
       <c r="I29" s="94">
         <v>1</v>
@@ -53845,65 +53844,65 @@
         <v>120</v>
       </c>
       <c r="N29" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O29" s="94" t="s">
         <v>124</v>
       </c>
       <c r="P29" s="94" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q29" s="94" t="s">
+        <v>281</v>
+      </c>
+      <c r="R29" s="94" t="s">
         <v>282</v>
       </c>
-      <c r="R29" s="94" t="s">
+      <c r="S29" s="94">
+        <v>0</v>
+      </c>
+      <c r="T29" s="94" t="s">
+        <v>230</v>
+      </c>
+      <c r="U29" s="94">
+        <v>0</v>
+      </c>
+      <c r="V29" s="94" t="s">
         <v>283</v>
       </c>
-      <c r="S29" s="94">
-        <v>0</v>
-      </c>
-      <c r="T29" s="94" t="s">
+      <c r="W29" s="94" t="s">
         <v>231</v>
       </c>
-      <c r="U29" s="94">
-        <v>0</v>
-      </c>
-      <c r="V29" s="94" t="s">
+      <c r="X29" s="94" t="s">
         <v>284</v>
       </c>
-      <c r="W29" s="94" t="s">
-        <v>232</v>
-      </c>
-      <c r="X29" s="94" t="s">
+      <c r="Y29" s="94">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="94">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="94">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="94">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="94">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="94">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="94">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="94">
+        <v>1</v>
+      </c>
+      <c r="AG29" s="94" t="s">
         <v>285</v>
       </c>
-      <c r="Y29" s="94">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="94">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="94">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="94">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="94">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="94">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="94">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="94">
-        <v>1</v>
-      </c>
-      <c r="AG29" s="94" t="s">
-        <v>286</v>
-      </c>
       <c r="AH29" s="94">
         <v>0</v>
       </c>
@@ -53932,16 +53931,16 @@
         <v>0</v>
       </c>
       <c r="AQ29" s="94" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AR29" s="94" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AS29" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AT29" s="41" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AU29" s="113">
         <v>1.9039999999999999</v>
@@ -54078,16 +54077,16 @@
         <v>140</v>
       </c>
       <c r="E30" s="94" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F30" s="94">
         <v>2016</v>
       </c>
       <c r="G30" s="58" t="s">
+        <v>279</v>
+      </c>
+      <c r="H30" s="94" t="s">
         <v>280</v>
-      </c>
-      <c r="H30" s="94" t="s">
-        <v>281</v>
       </c>
       <c r="I30" s="94">
         <v>1</v>
@@ -54105,65 +54104,65 @@
         <v>120</v>
       </c>
       <c r="N30" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O30" s="94" t="s">
         <v>124</v>
       </c>
       <c r="P30" s="94" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q30" s="94" t="s">
+        <v>281</v>
+      </c>
+      <c r="R30" s="94" t="s">
         <v>282</v>
       </c>
-      <c r="R30" s="94" t="s">
+      <c r="S30" s="94">
+        <v>0</v>
+      </c>
+      <c r="T30" s="94" t="s">
+        <v>230</v>
+      </c>
+      <c r="U30" s="94">
+        <v>0</v>
+      </c>
+      <c r="V30" s="94" t="s">
         <v>283</v>
       </c>
-      <c r="S30" s="94">
-        <v>0</v>
-      </c>
-      <c r="T30" s="94" t="s">
+      <c r="W30" s="94" t="s">
         <v>231</v>
       </c>
-      <c r="U30" s="94">
-        <v>0</v>
-      </c>
-      <c r="V30" s="94" t="s">
+      <c r="X30" s="94" t="s">
         <v>284</v>
       </c>
-      <c r="W30" s="94" t="s">
-        <v>232</v>
-      </c>
-      <c r="X30" s="94" t="s">
+      <c r="Y30" s="94">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="94">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="94">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="94">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="94">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="94">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="94">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="94">
+        <v>1</v>
+      </c>
+      <c r="AG30" s="94" t="s">
         <v>285</v>
       </c>
-      <c r="Y30" s="94">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="94">
-        <v>0</v>
-      </c>
-      <c r="AA30" s="94">
-        <v>0</v>
-      </c>
-      <c r="AB30" s="94">
-        <v>0</v>
-      </c>
-      <c r="AC30" s="94">
-        <v>0</v>
-      </c>
-      <c r="AD30" s="94">
-        <v>0</v>
-      </c>
-      <c r="AE30" s="94">
-        <v>0</v>
-      </c>
-      <c r="AF30" s="94">
-        <v>1</v>
-      </c>
-      <c r="AG30" s="94" t="s">
-        <v>286</v>
-      </c>
       <c r="AH30" s="94">
         <v>0</v>
       </c>
@@ -54192,16 +54191,16 @@
         <v>0</v>
       </c>
       <c r="AQ30" s="94" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AR30" s="94" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AS30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AT30" s="41" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AU30" s="113">
         <v>6.681</v>
@@ -54338,13 +54337,13 @@
         <v>148</v>
       </c>
       <c r="E31" s="96" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F31" s="94">
         <v>2016</v>
       </c>
       <c r="G31" s="97" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H31" s="94" t="s">
         <v>177</v>
@@ -54365,34 +54364,34 @@
         <v>93</v>
       </c>
       <c r="N31" s="94" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O31" s="94" t="s">
         <v>81</v>
       </c>
       <c r="P31" s="94" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q31" s="94" t="s">
+        <v>228</v>
+      </c>
+      <c r="R31" s="94" t="s">
         <v>229</v>
       </c>
-      <c r="R31" s="94" t="s">
-        <v>230</v>
-      </c>
       <c r="S31" s="94">
         <v>0</v>
       </c>
       <c r="T31" s="94" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="U31" s="94">
         <v>0</v>
       </c>
       <c r="V31" s="94" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="W31" s="94" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="X31" s="94" t="s">
         <v>180</v>
@@ -54452,16 +54451,16 @@
         <v>0</v>
       </c>
       <c r="AQ31" s="94" t="s">
+        <v>293</v>
+      </c>
+      <c r="AR31" s="94" t="s">
+        <v>233</v>
+      </c>
+      <c r="AS31" s="94" t="s">
         <v>294</v>
       </c>
-      <c r="AR31" s="94" t="s">
-        <v>234</v>
-      </c>
-      <c r="AS31" s="94" t="s">
-        <v>295</v>
-      </c>
       <c r="AT31" s="94" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AU31" s="98">
         <v>3.5900000000000001E-2</v>
@@ -54517,13 +54516,13 @@
         <v>73</v>
       </c>
       <c r="BM31" s="94" t="s">
+        <v>295</v>
+      </c>
+      <c r="BN31" t="s">
+        <v>73</v>
+      </c>
+      <c r="BO31" t="s">
         <v>296</v>
-      </c>
-      <c r="BN31" t="s">
-        <v>73</v>
-      </c>
-      <c r="BO31" t="s">
-        <v>297</v>
       </c>
       <c r="BP31" s="94" t="s">
         <v>73</v>
@@ -54596,7 +54595,7 @@
         <v>150</v>
       </c>
       <c r="E32" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F32">
         <v>2014</v>
@@ -54623,34 +54622,34 @@
         <v>120</v>
       </c>
       <c r="N32" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O32" t="s">
         <v>131</v>
       </c>
       <c r="P32" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q32" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="R32" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="S32">
         <v>0</v>
       </c>
       <c r="T32" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="U32">
         <v>0</v>
       </c>
       <c r="V32" s="94" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="W32" s="94" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="X32" s="94" t="s">
         <v>73</v>
@@ -54710,10 +54709,10 @@
         <v>0</v>
       </c>
       <c r="AQ32" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AR32" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AS32" s="94" t="s">
         <v>130</v>
@@ -54775,13 +54774,13 @@
         <v>73</v>
       </c>
       <c r="BM32" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="BN32" t="s">
         <v>73</v>
       </c>
       <c r="BO32" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BP32" t="s">
         <v>73</v>
@@ -54851,7 +54850,7 @@
         <v>150</v>
       </c>
       <c r="E33" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F33">
         <v>2014</v>
@@ -54878,34 +54877,34 @@
         <v>120</v>
       </c>
       <c r="N33" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O33" t="s">
         <v>131</v>
       </c>
       <c r="P33" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q33" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="R33" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="S33">
         <v>0</v>
       </c>
       <c r="T33" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="U33">
         <v>0</v>
       </c>
       <c r="V33" s="94" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="W33" s="94" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="X33" s="94" t="s">
         <v>73</v>
@@ -54965,10 +54964,10 @@
         <v>0</v>
       </c>
       <c r="AQ33" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AR33" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AS33" s="94" t="s">
         <v>130</v>
@@ -55030,13 +55029,13 @@
         <v>73</v>
       </c>
       <c r="BM33" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="BN33" t="s">
         <v>73</v>
       </c>
       <c r="BO33" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BP33" t="s">
         <v>73</v>
@@ -55106,7 +55105,7 @@
         <v>150</v>
       </c>
       <c r="E34" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F34">
         <v>2014</v>
@@ -55133,34 +55132,34 @@
         <v>120</v>
       </c>
       <c r="N34" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O34" t="s">
         <v>131</v>
       </c>
       <c r="P34" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q34" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="R34" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="S34">
         <v>0</v>
       </c>
       <c r="T34" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="U34">
         <v>0</v>
       </c>
       <c r="V34" s="94" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="W34" s="94" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="X34" s="94" t="s">
         <v>73</v>
@@ -55220,10 +55219,10 @@
         <v>0</v>
       </c>
       <c r="AQ34" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AR34" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AS34" s="94" t="s">
         <v>130</v>
@@ -55285,13 +55284,13 @@
         <v>73</v>
       </c>
       <c r="BM34" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="BN34" t="s">
         <v>73</v>
       </c>
       <c r="BO34" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BP34" t="s">
         <v>73</v>
@@ -55361,7 +55360,7 @@
         <v>150</v>
       </c>
       <c r="E35" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F35">
         <v>2014</v>
@@ -55388,34 +55387,34 @@
         <v>120</v>
       </c>
       <c r="N35" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O35" t="s">
         <v>131</v>
       </c>
       <c r="P35" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q35" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="R35" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="S35">
         <v>0</v>
       </c>
       <c r="T35" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="U35">
         <v>0</v>
       </c>
       <c r="V35" s="94" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="W35" s="94" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="X35" s="94" t="s">
         <v>73</v>
@@ -55475,10 +55474,10 @@
         <v>0</v>
       </c>
       <c r="AQ35" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AR35" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AS35" s="94" t="s">
         <v>130</v>
@@ -55540,13 +55539,13 @@
         <v>73</v>
       </c>
       <c r="BM35" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="BN35" t="s">
         <v>73</v>
       </c>
       <c r="BO35" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BP35" t="s">
         <v>73</v>
@@ -55607,7 +55606,7 @@
     </row>
     <row r="36" spans="1:86" ht="18" customHeight="1">
       <c r="A36" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C36" s="106">
         <v>3049</v>
@@ -55616,16 +55615,16 @@
         <v>313</v>
       </c>
       <c r="E36" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F36">
         <v>2014</v>
       </c>
       <c r="G36" t="s">
+        <v>302</v>
+      </c>
+      <c r="H36" t="s">
         <v>303</v>
-      </c>
-      <c r="H36" t="s">
-        <v>304</v>
       </c>
       <c r="I36">
         <v>1</v>
@@ -55634,7 +55633,7 @@
         <v>2013</v>
       </c>
       <c r="K36" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L36">
         <v>514</v>
@@ -55643,100 +55642,100 @@
         <v>120</v>
       </c>
       <c r="N36" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O36" t="s">
+        <v>305</v>
+      </c>
+      <c r="P36" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>228</v>
+      </c>
+      <c r="R36" t="s">
+        <v>282</v>
+      </c>
+      <c r="S36">
+        <v>1</v>
+      </c>
+      <c r="T36" t="s">
+        <v>230</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36" t="s">
+        <v>231</v>
+      </c>
+      <c r="W36" t="s">
+        <v>283</v>
+      </c>
+      <c r="X36" t="s">
         <v>306</v>
       </c>
-      <c r="P36" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>229</v>
-      </c>
-      <c r="R36" t="s">
-        <v>283</v>
-      </c>
-      <c r="S36">
-        <v>1</v>
-      </c>
-      <c r="T36" t="s">
-        <v>231</v>
-      </c>
-      <c r="U36">
-        <v>0</v>
-      </c>
-      <c r="V36" t="s">
-        <v>232</v>
-      </c>
-      <c r="W36" t="s">
-        <v>284</v>
-      </c>
-      <c r="X36" t="s">
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>1</v>
+      </c>
+      <c r="AC36">
+        <v>0</v>
+      </c>
+      <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH36">
+        <v>1</v>
+      </c>
+      <c r="AI36">
+        <v>0</v>
+      </c>
+      <c r="AJ36">
+        <v>0</v>
+      </c>
+      <c r="AK36">
+        <v>1</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>0</v>
+      </c>
+      <c r="AN36">
+        <v>1</v>
+      </c>
+      <c r="AO36">
+        <v>1</v>
+      </c>
+      <c r="AP36" s="18">
+        <v>1</v>
+      </c>
+      <c r="AQ36" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR36" t="s">
+        <v>233</v>
+      </c>
+      <c r="AS36" t="s">
         <v>307</v>
-      </c>
-      <c r="Y36">
-        <v>0</v>
-      </c>
-      <c r="Z36">
-        <v>0</v>
-      </c>
-      <c r="AA36">
-        <v>0</v>
-      </c>
-      <c r="AB36">
-        <v>1</v>
-      </c>
-      <c r="AC36">
-        <v>0</v>
-      </c>
-      <c r="AD36">
-        <v>0</v>
-      </c>
-      <c r="AE36">
-        <v>0</v>
-      </c>
-      <c r="AF36">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="s">
-        <v>73</v>
-      </c>
-      <c r="AH36">
-        <v>1</v>
-      </c>
-      <c r="AI36">
-        <v>0</v>
-      </c>
-      <c r="AJ36">
-        <v>0</v>
-      </c>
-      <c r="AK36">
-        <v>1</v>
-      </c>
-      <c r="AL36">
-        <v>0</v>
-      </c>
-      <c r="AM36">
-        <v>0</v>
-      </c>
-      <c r="AN36">
-        <v>1</v>
-      </c>
-      <c r="AO36">
-        <v>1</v>
-      </c>
-      <c r="AP36" s="18">
-        <v>1</v>
-      </c>
-      <c r="AQ36" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR36" t="s">
-        <v>234</v>
-      </c>
-      <c r="AS36" t="s">
-        <v>308</v>
       </c>
       <c r="AT36" t="s">
         <v>73</v>
@@ -55770,7 +55769,7 @@
         <v>73</v>
       </c>
       <c r="BE36" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="BF36" t="s">
         <v>73</v>
@@ -55794,7 +55793,7 @@
         <v>73</v>
       </c>
       <c r="BM36" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="BN36" t="s">
         <v>73</v>
@@ -55865,7 +55864,7 @@
     </row>
     <row r="37" spans="1:86" ht="18" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C37" s="106">
         <v>3050</v>
@@ -55874,16 +55873,16 @@
         <v>313</v>
       </c>
       <c r="E37" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F37">
         <v>2014</v>
       </c>
       <c r="G37" t="s">
+        <v>302</v>
+      </c>
+      <c r="H37" t="s">
         <v>303</v>
-      </c>
-      <c r="H37" t="s">
-        <v>304</v>
       </c>
       <c r="I37">
         <v>1</v>
@@ -55892,7 +55891,7 @@
         <v>2013</v>
       </c>
       <c r="K37" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L37">
         <v>514</v>
@@ -55901,100 +55900,100 @@
         <v>120</v>
       </c>
       <c r="N37" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O37" t="s">
+        <v>305</v>
+      </c>
+      <c r="P37" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>228</v>
+      </c>
+      <c r="R37" t="s">
+        <v>282</v>
+      </c>
+      <c r="S37">
+        <v>1</v>
+      </c>
+      <c r="T37" t="s">
+        <v>230</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37" t="s">
+        <v>231</v>
+      </c>
+      <c r="W37" t="s">
+        <v>283</v>
+      </c>
+      <c r="X37" t="s">
         <v>306</v>
       </c>
-      <c r="P37" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>229</v>
-      </c>
-      <c r="R37" t="s">
-        <v>283</v>
-      </c>
-      <c r="S37">
-        <v>1</v>
-      </c>
-      <c r="T37" t="s">
-        <v>231</v>
-      </c>
-      <c r="U37">
-        <v>0</v>
-      </c>
-      <c r="V37" t="s">
-        <v>232</v>
-      </c>
-      <c r="W37" t="s">
-        <v>284</v>
-      </c>
-      <c r="X37" t="s">
+      <c r="Y37">
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+      <c r="AA37">
+        <v>0</v>
+      </c>
+      <c r="AB37">
+        <v>1</v>
+      </c>
+      <c r="AC37">
+        <v>0</v>
+      </c>
+      <c r="AD37">
+        <v>0</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH37">
+        <v>1</v>
+      </c>
+      <c r="AI37">
+        <v>0</v>
+      </c>
+      <c r="AJ37">
+        <v>0</v>
+      </c>
+      <c r="AK37">
+        <v>1</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>0</v>
+      </c>
+      <c r="AN37">
+        <v>1</v>
+      </c>
+      <c r="AO37">
+        <v>1</v>
+      </c>
+      <c r="AP37" s="18">
+        <v>1</v>
+      </c>
+      <c r="AQ37" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR37" t="s">
+        <v>233</v>
+      </c>
+      <c r="AS37" t="s">
         <v>307</v>
-      </c>
-      <c r="Y37">
-        <v>0</v>
-      </c>
-      <c r="Z37">
-        <v>0</v>
-      </c>
-      <c r="AA37">
-        <v>0</v>
-      </c>
-      <c r="AB37">
-        <v>1</v>
-      </c>
-      <c r="AC37">
-        <v>0</v>
-      </c>
-      <c r="AD37">
-        <v>0</v>
-      </c>
-      <c r="AE37">
-        <v>0</v>
-      </c>
-      <c r="AF37">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="s">
-        <v>73</v>
-      </c>
-      <c r="AH37">
-        <v>1</v>
-      </c>
-      <c r="AI37">
-        <v>0</v>
-      </c>
-      <c r="AJ37">
-        <v>0</v>
-      </c>
-      <c r="AK37">
-        <v>1</v>
-      </c>
-      <c r="AL37">
-        <v>0</v>
-      </c>
-      <c r="AM37">
-        <v>0</v>
-      </c>
-      <c r="AN37">
-        <v>1</v>
-      </c>
-      <c r="AO37">
-        <v>1</v>
-      </c>
-      <c r="AP37" s="18">
-        <v>1</v>
-      </c>
-      <c r="AQ37" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR37" t="s">
-        <v>234</v>
-      </c>
-      <c r="AS37" t="s">
-        <v>308</v>
       </c>
       <c r="AT37" t="s">
         <v>73</v>
@@ -56028,7 +56027,7 @@
         <v>73</v>
       </c>
       <c r="BE37" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="BF37" t="s">
         <v>73</v>
@@ -56052,7 +56051,7 @@
         <v>73</v>
       </c>
       <c r="BM37" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="BN37" t="s">
         <v>73</v>
@@ -56416,203 +56415,203 @@
     </row>
     <row r="2" spans="1:62">
       <c r="A2" s="119" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:62">
       <c r="A4" s="119" t="s">
+        <v>311</v>
+      </c>
+      <c r="B4" t="s">
         <v>312</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>313</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>314</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>315</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>316</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>317</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>318</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>319</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>320</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>321</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>322</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>323</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>324</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>325</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>326</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>327</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>328</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>329</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>330</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>331</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>332</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>333</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>334</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>335</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>336</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>337</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>338</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>339</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>340</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>341</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>342</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AG4" t="s">
         <v>343</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AH4" t="s">
         <v>344</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AI4" t="s">
         <v>345</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AJ4" t="s">
         <v>346</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AK4" t="s">
         <v>347</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AL4" t="s">
         <v>348</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AM4" t="s">
         <v>349</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AN4" t="s">
         <v>350</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AO4" t="s">
         <v>351</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AP4" t="s">
         <v>352</v>
       </c>
-      <c r="AP4" t="s">
+      <c r="AQ4" t="s">
         <v>353</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="AR4" t="s">
         <v>354</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="AS4" t="s">
         <v>355</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AT4" t="s">
         <v>356</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AU4" t="s">
         <v>357</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AV4" t="s">
         <v>358</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AW4" t="s">
         <v>359</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AX4" t="s">
         <v>360</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="AY4" t="s">
         <v>361</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="AZ4" t="s">
         <v>362</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="BA4" t="s">
         <v>363</v>
       </c>
-      <c r="BA4" t="s">
+      <c r="BB4" t="s">
         <v>364</v>
       </c>
-      <c r="BB4" t="s">
+      <c r="BC4" t="s">
         <v>365</v>
       </c>
-      <c r="BC4" t="s">
+      <c r="BD4" t="s">
         <v>366</v>
       </c>
-      <c r="BD4" t="s">
+      <c r="BE4" t="s">
         <v>367</v>
       </c>
-      <c r="BE4" t="s">
+      <c r="BF4" t="s">
         <v>368</v>
       </c>
-      <c r="BF4" t="s">
+      <c r="BG4" t="s">
         <v>369</v>
       </c>
-      <c r="BG4" t="s">
+      <c r="BH4" t="s">
         <v>370</v>
       </c>
-      <c r="BH4" t="s">
+      <c r="BI4" t="s">
         <v>371</v>
       </c>
-      <c r="BI4" t="s">
+      <c r="BJ4" t="s">
         <v>372</v>
-      </c>
-      <c r="BJ4" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="5" spans="1:62">
       <c r="A5" s="120" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -56982,7 +56981,7 @@
     </row>
     <row r="7" spans="1:62">
       <c r="A7" s="120" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -57546,7 +57545,7 @@
     </row>
     <row r="10" spans="1:62">
       <c r="A10" s="120" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B10">
         <v>23</v>
@@ -57734,7 +57733,7 @@
     </row>
     <row r="11" spans="1:62">
       <c r="A11" s="120" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -57922,7 +57921,7 @@
     </row>
     <row r="12" spans="1:62">
       <c r="A12" s="120" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -58110,7 +58109,7 @@
     </row>
     <row r="13" spans="1:62">
       <c r="A13" s="120" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B13">
         <v>6</v>
@@ -58298,7 +58297,7 @@
     </row>
     <row r="14" spans="1:62">
       <c r="A14" s="120" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B14">
         <v>6</v>
@@ -58486,7 +58485,7 @@
     </row>
     <row r="15" spans="1:62">
       <c r="A15" s="120" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -58674,7 +58673,7 @@
     </row>
     <row r="16" spans="1:62">
       <c r="A16" s="120" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B16">
         <v>22</v>
@@ -59050,7 +59049,7 @@
     </row>
     <row r="18" spans="1:62">
       <c r="A18" s="120" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B18">
         <v>144</v>
@@ -59257,13 +59256,13 @@
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="B1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>385</v>
       </c>
       <c r="D1" t="s">
         <v>10</v>
@@ -59275,10 +59274,10 @@
         <v>9</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1" s="38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I1" s="39" t="s">
         <v>28</v>
@@ -59287,25 +59286,25 @@
         <v>7</v>
       </c>
       <c r="K1" s="39" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L1" s="39" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M1" s="39" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>50</v>
       </c>
       <c r="O1" s="39" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P1" s="42" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="R1" s="39" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S1" s="39" t="s">
         <v>4</v>
@@ -59316,10 +59315,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D2" t="s">
         <v>112</v>
@@ -59331,40 +59330,40 @@
         <v>93</v>
       </c>
       <c r="G2" s="26" t="s">
+        <v>387</v>
+      </c>
+      <c r="H2" t="s">
         <v>388</v>
-      </c>
-      <c r="H2" t="s">
-        <v>389</v>
       </c>
       <c r="I2" t="s">
         <v>80</v>
       </c>
       <c r="J2" t="s">
+        <v>389</v>
+      </c>
+      <c r="K2" t="s">
+        <v>231</v>
+      </c>
+      <c r="L2" t="s">
         <v>390</v>
       </c>
-      <c r="K2" t="s">
-        <v>232</v>
-      </c>
-      <c r="L2" t="s">
-        <v>391</v>
-      </c>
       <c r="M2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="N2" t="s">
         <v>81</v>
       </c>
       <c r="O2" t="s">
+        <v>391</v>
+      </c>
+      <c r="P2" s="41" t="s">
         <v>392</v>
       </c>
-      <c r="P2" s="41" t="s">
+      <c r="R2" s="47" t="s">
         <v>393</v>
       </c>
-      <c r="R2" s="47" t="s">
+      <c r="S2" s="47" t="s">
         <v>394</v>
-      </c>
-      <c r="S2" s="47" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="31.5">
@@ -59372,55 +59371,55 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I3" t="s">
         <v>86</v>
       </c>
       <c r="J3" t="s">
+        <v>397</v>
+      </c>
+      <c r="K3" t="s">
+        <v>283</v>
+      </c>
+      <c r="L3" t="s">
         <v>398</v>
       </c>
-      <c r="K3" t="s">
-        <v>284</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>399</v>
-      </c>
-      <c r="M3" t="s">
-        <v>400</v>
       </c>
       <c r="N3" t="s">
         <v>148</v>
       </c>
       <c r="O3" t="s">
+        <v>400</v>
+      </c>
+      <c r="P3" s="41" t="s">
+        <v>235</v>
+      </c>
+      <c r="R3" s="46" t="s">
         <v>401</v>
       </c>
-      <c r="P3" s="41" t="s">
-        <v>236</v>
-      </c>
-      <c r="R3" s="46" t="s">
+      <c r="S3" s="46" t="s">
         <v>402</v>
-      </c>
-      <c r="S3" s="46" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="47.25">
@@ -59428,69 +59427,69 @@
         <v>73</v>
       </c>
       <c r="B4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C4" t="s">
         <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4" t="s">
+        <v>403</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>310</v>
+      </c>
+      <c r="H4" t="s">
         <v>404</v>
       </c>
-      <c r="G4" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="J4" t="s">
         <v>405</v>
       </c>
-      <c r="J4" t="s">
+      <c r="L4" t="s">
+        <v>229</v>
+      </c>
+      <c r="M4" t="s">
+        <v>227</v>
+      </c>
+      <c r="N4" t="s">
         <v>406</v>
       </c>
-      <c r="L4" t="s">
-        <v>230</v>
-      </c>
-      <c r="M4" t="s">
-        <v>228</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>407</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" s="41" t="s">
         <v>408</v>
       </c>
-      <c r="P4" s="41" t="s">
-        <v>409</v>
-      </c>
       <c r="R4" s="44" t="s">
+        <v>249</v>
+      </c>
+      <c r="S4" s="44" t="s">
         <v>250</v>
-      </c>
-      <c r="S4" s="44" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="47.25">
       <c r="D5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F5" t="s">
         <v>120</v>
       </c>
       <c r="G5" s="40" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H5" t="s">
+        <v>409</v>
+      </c>
+      <c r="J5" s="41" t="s">
         <v>410</v>
       </c>
-      <c r="J5" s="41" t="s">
+      <c r="L5" t="s">
         <v>411</v>
-      </c>
-      <c r="L5" t="s">
-        <v>412</v>
       </c>
       <c r="M5" t="s">
         <v>73</v>
@@ -59499,71 +59498,71 @@
         <v>124</v>
       </c>
       <c r="O5" s="41" t="s">
+        <v>412</v>
+      </c>
+      <c r="P5" t="s">
+        <v>73</v>
+      </c>
+      <c r="R5" s="46" t="s">
         <v>413</v>
       </c>
-      <c r="P5" t="s">
-        <v>73</v>
-      </c>
-      <c r="R5" s="46" t="s">
+      <c r="S5" s="46" t="s">
         <v>414</v>
-      </c>
-      <c r="S5" s="46" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="D6" s="41" t="s">
+        <v>415</v>
+      </c>
+      <c r="F6" t="s">
         <v>416</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
+        <v>228</v>
+      </c>
+      <c r="J6" t="s">
         <v>417</v>
       </c>
-      <c r="H6" t="s">
-        <v>229</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="L6" t="s">
         <v>418</v>
       </c>
-      <c r="L6" t="s">
+      <c r="N6" t="s">
+        <v>305</v>
+      </c>
+      <c r="O6" t="s">
+        <v>73</v>
+      </c>
+      <c r="R6" s="46" t="s">
         <v>419</v>
       </c>
-      <c r="N6" t="s">
-        <v>306</v>
-      </c>
-      <c r="O6" t="s">
-        <v>73</v>
-      </c>
-      <c r="R6" s="46" t="s">
+      <c r="S6" s="46" t="s">
         <v>420</v>
-      </c>
-      <c r="S6" s="46" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="F7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J7" s="41" t="s">
+        <v>421</v>
+      </c>
+      <c r="L7" t="s">
+        <v>282</v>
+      </c>
+      <c r="N7" t="s">
         <v>422</v>
       </c>
-      <c r="L7" t="s">
-        <v>283</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
         <v>423</v>
       </c>
-      <c r="O7" t="s">
+      <c r="R7" s="46" t="s">
         <v>424</v>
       </c>
-      <c r="R7" s="46" t="s">
+      <c r="S7" s="46" t="s">
         <v>425</v>
-      </c>
-      <c r="S7" s="46" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -59571,39 +59570,39 @@
         <v>107</v>
       </c>
       <c r="J8" s="41" t="s">
+        <v>426</v>
+      </c>
+      <c r="L8" t="s">
+        <v>423</v>
+      </c>
+      <c r="N8" t="s">
         <v>427</v>
       </c>
-      <c r="L8" t="s">
-        <v>424</v>
-      </c>
-      <c r="N8" t="s">
+      <c r="R8" s="46" t="s">
         <v>428</v>
       </c>
-      <c r="R8" s="46" t="s">
+      <c r="S8" s="46" t="s">
         <v>429</v>
-      </c>
-      <c r="S8" s="46" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="F9" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L9" t="s">
+        <v>430</v>
+      </c>
+      <c r="N9" t="s">
         <v>431</v>
       </c>
-      <c r="N9" t="s">
+      <c r="R9" s="44" t="s">
         <v>432</v>
       </c>
-      <c r="R9" s="44" t="s">
+      <c r="S9" s="44" t="s">
         <v>433</v>
-      </c>
-      <c r="S9" s="44" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -59611,81 +59610,81 @@
         <v>155</v>
       </c>
       <c r="J10" t="s">
+        <v>434</v>
+      </c>
+      <c r="L10" t="s">
+        <v>265</v>
+      </c>
+      <c r="N10" t="s">
         <v>435</v>
       </c>
-      <c r="L10" t="s">
-        <v>266</v>
-      </c>
-      <c r="N10" t="s">
+      <c r="R10" s="44" t="s">
         <v>436</v>
       </c>
-      <c r="R10" s="44" t="s">
+      <c r="S10" s="44" t="s">
         <v>437</v>
-      </c>
-      <c r="S10" s="44" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="11" spans="1:19">
       <c r="F11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J11" t="s">
+        <v>438</v>
+      </c>
+      <c r="N11" t="s">
         <v>439</v>
       </c>
-      <c r="N11" t="s">
+      <c r="R11" s="44" t="s">
         <v>440</v>
       </c>
-      <c r="R11" s="44" t="s">
+      <c r="S11" s="44" t="s">
         <v>441</v>
-      </c>
-      <c r="S11" s="44" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="F12" t="s">
+        <v>442</v>
+      </c>
+      <c r="J12" t="s">
+        <v>73</v>
+      </c>
+      <c r="N12" t="s">
         <v>443</v>
       </c>
-      <c r="J12" t="s">
-        <v>73</v>
-      </c>
-      <c r="N12" t="s">
+      <c r="R12" s="44" t="s">
         <v>444</v>
       </c>
-      <c r="R12" s="44" t="s">
+      <c r="S12" s="44" t="s">
         <v>445</v>
-      </c>
-      <c r="S12" s="44" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="13" spans="1:19">
       <c r="F13" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="N13" t="s">
         <v>96</v>
       </c>
       <c r="R13" s="46" t="s">
+        <v>446</v>
+      </c>
+      <c r="S13" s="46" t="s">
         <v>447</v>
-      </c>
-      <c r="S13" s="46" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="14" spans="1:19">
       <c r="F14" s="41" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="N14" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="R14" s="44" t="s">
+        <v>269</v>
+      </c>
+      <c r="S14" s="44" t="s">
         <v>270</v>
-      </c>
-      <c r="S14" s="44" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -59693,52 +59692,52 @@
         <v>155</v>
       </c>
       <c r="N15" t="s">
+        <v>449</v>
+      </c>
+      <c r="R15" s="46" t="s">
         <v>450</v>
       </c>
-      <c r="R15" s="46" t="s">
+      <c r="S15" s="46" t="s">
         <v>451</v>
-      </c>
-      <c r="S15" s="46" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="F16" s="41" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N16" t="s">
         <v>156</v>
       </c>
       <c r="R16" s="46" t="s">
+        <v>453</v>
+      </c>
+      <c r="S16" s="46" t="s">
         <v>454</v>
-      </c>
-      <c r="S16" s="46" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="17" spans="6:19">
       <c r="F17" s="41" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N17" t="s">
+        <v>455</v>
+      </c>
+      <c r="R17" s="44" t="s">
         <v>456</v>
       </c>
-      <c r="R17" s="44" t="s">
+      <c r="S17" s="44" t="s">
         <v>457</v>
-      </c>
-      <c r="S17" s="44" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="18" spans="6:19">
       <c r="F18" s="41" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="N18" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="R18" s="46" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="S18" s="46" t="s">
         <v>127</v>
@@ -59746,142 +59745,142 @@
     </row>
     <row r="19" spans="6:19">
       <c r="F19" s="41" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N19" t="s">
+        <v>459</v>
+      </c>
+      <c r="R19" s="44" t="s">
         <v>460</v>
       </c>
-      <c r="R19" s="44" t="s">
+      <c r="S19" t="s">
         <v>461</v>
-      </c>
-      <c r="S19" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="20" spans="6:19">
       <c r="F20" s="41" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="N20" t="s">
+        <v>462</v>
+      </c>
+      <c r="R20" s="46" t="s">
         <v>463</v>
       </c>
-      <c r="R20" s="46" t="s">
+      <c r="S20" s="46" t="s">
         <v>464</v>
-      </c>
-      <c r="S20" s="46" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="21" spans="6:19">
       <c r="F21" s="41" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="N21" t="s">
+        <v>465</v>
+      </c>
+      <c r="R21" s="44" t="s">
         <v>466</v>
       </c>
-      <c r="R21" s="44" t="s">
+      <c r="S21" s="44" t="s">
         <v>467</v>
-      </c>
-      <c r="S21" s="44" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="22" spans="6:19">
       <c r="F22" s="41" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N22" t="s">
         <v>138</v>
       </c>
       <c r="R22" s="46" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="S22" s="46" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="23" spans="6:19">
       <c r="F23" s="41" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="N23" t="s">
+        <v>469</v>
+      </c>
+      <c r="R23" s="44" t="s">
         <v>470</v>
       </c>
-      <c r="R23" s="44" t="s">
+      <c r="S23" s="44" t="s">
         <v>471</v>
-      </c>
-      <c r="S23" s="44" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="24" spans="6:19">
       <c r="F24" s="41" t="s">
+        <v>472</v>
+      </c>
+      <c r="N24" t="s">
         <v>473</v>
       </c>
-      <c r="N24" t="s">
+      <c r="R24" s="44" t="s">
         <v>474</v>
       </c>
-      <c r="R24" s="44" t="s">
+      <c r="S24" s="44" t="s">
         <v>475</v>
-      </c>
-      <c r="S24" s="44" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="25" spans="6:19">
       <c r="F25" s="41" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="N25" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="R25" s="44" t="s">
+        <v>476</v>
+      </c>
+      <c r="S25" s="44" t="s">
         <v>477</v>
-      </c>
-      <c r="S25" s="44" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="26" spans="6:19">
       <c r="F26" s="41" t="s">
+        <v>478</v>
+      </c>
+      <c r="N26" t="s">
         <v>479</v>
       </c>
-      <c r="N26" t="s">
+      <c r="R26" s="44" t="s">
         <v>480</v>
       </c>
-      <c r="R26" s="44" t="s">
+      <c r="S26" s="44" t="s">
         <v>481</v>
-      </c>
-      <c r="S26" s="44" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="27" spans="6:19">
       <c r="F27" s="41" t="s">
+        <v>482</v>
+      </c>
+      <c r="N27" t="s">
         <v>483</v>
       </c>
-      <c r="N27" t="s">
+      <c r="R27" s="44" t="s">
         <v>484</v>
       </c>
-      <c r="R27" s="44" t="s">
+      <c r="S27" s="44" t="s">
         <v>485</v>
-      </c>
-      <c r="S27" s="44" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="28" spans="6:19">
       <c r="F28" s="41" t="s">
+        <v>486</v>
+      </c>
+      <c r="N28" t="s">
         <v>487</v>
       </c>
-      <c r="N28" t="s">
+      <c r="R28" s="44" t="s">
         <v>488</v>
       </c>
-      <c r="R28" s="44" t="s">
+      <c r="S28" s="44" t="s">
         <v>489</v>
-      </c>
-      <c r="S28" s="44" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="29" spans="6:19">
@@ -59889,27 +59888,27 @@
         <v>172</v>
       </c>
       <c r="N29" t="s">
+        <v>490</v>
+      </c>
+      <c r="R29" s="44" t="s">
         <v>491</v>
       </c>
-      <c r="R29" s="44" t="s">
+      <c r="S29" s="44" t="s">
         <v>492</v>
-      </c>
-      <c r="S29" s="44" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="30" spans="6:19">
       <c r="F30" s="41" t="s">
+        <v>493</v>
+      </c>
+      <c r="N30" t="s">
         <v>494</v>
       </c>
-      <c r="N30" t="s">
+      <c r="R30" s="44" t="s">
         <v>495</v>
       </c>
-      <c r="R30" s="44" t="s">
+      <c r="S30" s="44" t="s">
         <v>496</v>
-      </c>
-      <c r="S30" s="44" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="31" spans="6:19">
@@ -59917,21 +59916,21 @@
         <v>174</v>
       </c>
       <c r="R31" s="44" t="s">
+        <v>497</v>
+      </c>
+      <c r="S31" s="44" t="s">
         <v>498</v>
-      </c>
-      <c r="S31" s="44" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="32" spans="6:19">
       <c r="N32" t="s">
+        <v>499</v>
+      </c>
+      <c r="R32" s="44" t="s">
         <v>500</v>
       </c>
-      <c r="R32" s="44" t="s">
+      <c r="S32" s="44" t="s">
         <v>501</v>
-      </c>
-      <c r="S32" s="44" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="33" spans="14:19">
@@ -59939,95 +59938,95 @@
         <v>131</v>
       </c>
       <c r="R33" s="44" t="s">
+        <v>502</v>
+      </c>
+      <c r="S33" s="44" t="s">
         <v>503</v>
-      </c>
-      <c r="S33" s="44" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="34" spans="14:19">
       <c r="R34" s="44" t="s">
+        <v>504</v>
+      </c>
+      <c r="S34" s="44" t="s">
         <v>505</v>
-      </c>
-      <c r="S34" s="44" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="35" spans="14:19">
       <c r="R35" s="44" t="s">
+        <v>506</v>
+      </c>
+      <c r="S35" s="44" t="s">
         <v>507</v>
-      </c>
-      <c r="S35" s="44" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="36" spans="14:19">
       <c r="R36" s="44" t="s">
+        <v>508</v>
+      </c>
+      <c r="S36" s="44" t="s">
         <v>509</v>
-      </c>
-      <c r="S36" s="44" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="37" spans="14:19">
       <c r="R37" s="46" t="s">
+        <v>510</v>
+      </c>
+      <c r="S37" s="46" t="s">
         <v>511</v>
-      </c>
-      <c r="S37" s="46" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="38" spans="14:19">
       <c r="R38" s="46" t="s">
+        <v>512</v>
+      </c>
+      <c r="S38" s="46" t="s">
         <v>513</v>
-      </c>
-      <c r="S38" s="46" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="39" spans="14:19">
       <c r="R39" s="46" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="S39" s="46" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="40" spans="14:19">
       <c r="R40" s="44" t="s">
+        <v>515</v>
+      </c>
+      <c r="S40" s="44" t="s">
         <v>516</v>
-      </c>
-      <c r="S40" s="44" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="41" spans="14:19">
       <c r="R41" s="44" t="s">
+        <v>517</v>
+      </c>
+      <c r="S41" s="44" t="s">
         <v>518</v>
-      </c>
-      <c r="S41" s="44" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="42" spans="14:19">
       <c r="R42" s="46" t="s">
+        <v>519</v>
+      </c>
+      <c r="S42" s="46" t="s">
         <v>520</v>
-      </c>
-      <c r="S42" s="46" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="43" spans="14:19">
       <c r="R43" s="46" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="S43" s="46" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="44" spans="14:19">
       <c r="R44" s="44" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="S44" s="17" t="s">
         <v>117</v>
@@ -60035,431 +60034,431 @@
     </row>
     <row r="45" spans="14:19">
       <c r="R45" s="46" t="s">
+        <v>523</v>
+      </c>
+      <c r="S45" s="46" t="s">
         <v>524</v>
-      </c>
-      <c r="S45" s="46" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="46" spans="14:19">
       <c r="R46" s="44" t="s">
+        <v>525</v>
+      </c>
+      <c r="S46" s="44" t="s">
         <v>526</v>
-      </c>
-      <c r="S46" s="44" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="47" spans="14:19">
       <c r="R47" s="46" t="s">
+        <v>527</v>
+      </c>
+      <c r="S47" s="46" t="s">
         <v>528</v>
-      </c>
-      <c r="S47" s="46" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="48" spans="14:19">
       <c r="R48" s="44" t="s">
+        <v>529</v>
+      </c>
+      <c r="S48" s="44" t="s">
         <v>530</v>
-      </c>
-      <c r="S48" s="44" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="49" spans="18:19">
       <c r="R49" s="44" t="s">
+        <v>531</v>
+      </c>
+      <c r="S49" s="44" t="s">
         <v>532</v>
-      </c>
-      <c r="S49" s="44" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="50" spans="18:19">
       <c r="R50" s="44" t="s">
+        <v>533</v>
+      </c>
+      <c r="S50" s="44" t="s">
         <v>534</v>
-      </c>
-      <c r="S50" s="44" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="51" spans="18:19">
       <c r="R51" s="44" t="s">
+        <v>221</v>
+      </c>
+      <c r="S51" s="44" t="s">
         <v>222</v>
-      </c>
-      <c r="S51" s="44" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="52" spans="18:19">
       <c r="R52" s="44" t="s">
+        <v>535</v>
+      </c>
+      <c r="S52" s="44" t="s">
         <v>536</v>
-      </c>
-      <c r="S52" s="44" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="53" spans="18:19">
       <c r="R53" s="44" t="s">
+        <v>537</v>
+      </c>
+      <c r="S53" s="17" t="s">
         <v>538</v>
-      </c>
-      <c r="S53" s="17" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="54" spans="18:19">
       <c r="R54" s="44" t="s">
+        <v>539</v>
+      </c>
+      <c r="S54" s="44" t="s">
         <v>540</v>
-      </c>
-      <c r="S54" s="44" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="55" spans="18:19">
       <c r="R55" s="44" t="s">
+        <v>541</v>
+      </c>
+      <c r="S55" s="44" t="s">
         <v>542</v>
-      </c>
-      <c r="S55" s="44" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="56" spans="18:19">
       <c r="R56" s="44" t="s">
+        <v>543</v>
+      </c>
+      <c r="S56" s="44" t="s">
         <v>544</v>
-      </c>
-      <c r="S56" s="44" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="57" spans="18:19">
       <c r="R57" s="44" t="s">
+        <v>545</v>
+      </c>
+      <c r="S57" s="44" t="s">
         <v>546</v>
-      </c>
-      <c r="S57" s="44" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="58" spans="18:19">
       <c r="R58" s="44" t="s">
+        <v>547</v>
+      </c>
+      <c r="S58" s="44" t="s">
         <v>548</v>
-      </c>
-      <c r="S58" s="44" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="59" spans="18:19">
       <c r="R59" s="44" t="s">
+        <v>278</v>
+      </c>
+      <c r="S59" s="44" t="s">
         <v>279</v>
-      </c>
-      <c r="S59" s="44" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="60" spans="18:19">
       <c r="R60" s="44" t="s">
+        <v>549</v>
+      </c>
+      <c r="S60" s="44" t="s">
         <v>550</v>
-      </c>
-      <c r="S60" s="44" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="61" spans="18:19">
       <c r="R61" s="44" t="s">
+        <v>551</v>
+      </c>
+      <c r="S61" s="44" t="s">
         <v>552</v>
-      </c>
-      <c r="S61" s="44" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="62" spans="18:19">
       <c r="R62" s="44" t="s">
+        <v>553</v>
+      </c>
+      <c r="S62" s="44" t="s">
         <v>554</v>
-      </c>
-      <c r="S62" s="44" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="63" spans="18:19">
       <c r="R63" s="44" t="s">
+        <v>555</v>
+      </c>
+      <c r="S63" s="44" t="s">
         <v>556</v>
-      </c>
-      <c r="S63" s="44" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="64" spans="18:19">
       <c r="R64" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="S64" s="44" t="s">
         <v>558</v>
-      </c>
-      <c r="S64" s="44" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="65" spans="18:19">
       <c r="R65" s="44" t="s">
+        <v>559</v>
+      </c>
+      <c r="S65" s="44" t="s">
         <v>560</v>
-      </c>
-      <c r="S65" s="44" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="66" spans="18:19">
       <c r="R66" s="44" t="s">
+        <v>561</v>
+      </c>
+      <c r="S66" s="44" t="s">
         <v>562</v>
-      </c>
-      <c r="S66" s="44" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="67" spans="18:19">
       <c r="R67" s="44" t="s">
+        <v>563</v>
+      </c>
+      <c r="S67" s="44" t="s">
         <v>564</v>
-      </c>
-      <c r="S67" s="44" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="68" spans="18:19">
       <c r="R68" s="44" t="s">
+        <v>565</v>
+      </c>
+      <c r="S68" s="44" t="s">
         <v>566</v>
-      </c>
-      <c r="S68" s="44" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="69" spans="18:19">
       <c r="R69" s="44" t="s">
+        <v>567</v>
+      </c>
+      <c r="S69" s="44" t="s">
         <v>568</v>
-      </c>
-      <c r="S69" s="44" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="70" spans="18:19">
       <c r="R70" s="44" t="s">
+        <v>569</v>
+      </c>
+      <c r="S70" s="44" t="s">
         <v>570</v>
-      </c>
-      <c r="S70" s="44" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="71" spans="18:19">
       <c r="R71" s="44" t="s">
+        <v>571</v>
+      </c>
+      <c r="S71" s="44" t="s">
         <v>572</v>
-      </c>
-      <c r="S71" s="44" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="72" spans="18:19">
       <c r="R72" s="44" t="s">
+        <v>573</v>
+      </c>
+      <c r="S72" t="s">
         <v>574</v>
-      </c>
-      <c r="S72" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="73" spans="18:19">
       <c r="R73" s="46" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="S73" s="46" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="74" spans="18:19">
       <c r="R74" s="44" t="s">
+        <v>262</v>
+      </c>
+      <c r="S74" s="44" t="s">
         <v>263</v>
-      </c>
-      <c r="S74" s="44" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="75" spans="18:19">
       <c r="R75" s="46" t="s">
+        <v>576</v>
+      </c>
+      <c r="S75" s="46" t="s">
         <v>577</v>
-      </c>
-      <c r="S75" s="46" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="76" spans="18:19">
       <c r="R76" s="44" t="s">
+        <v>578</v>
+      </c>
+      <c r="S76" s="44" t="s">
         <v>579</v>
-      </c>
-      <c r="S76" s="44" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="77" spans="18:19">
       <c r="R77" s="44" t="s">
+        <v>580</v>
+      </c>
+      <c r="S77" s="44" t="s">
         <v>581</v>
-      </c>
-      <c r="S77" s="44" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="78" spans="18:19">
       <c r="R78" s="46" t="s">
+        <v>582</v>
+      </c>
+      <c r="S78" s="46" t="s">
         <v>583</v>
-      </c>
-      <c r="S78" s="46" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="79" spans="18:19">
       <c r="R79" s="46" t="s">
+        <v>584</v>
+      </c>
+      <c r="S79" s="46" t="s">
         <v>585</v>
-      </c>
-      <c r="S79" s="46" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="80" spans="18:19">
       <c r="R80" s="44" t="s">
+        <v>586</v>
+      </c>
+      <c r="S80" s="44" t="s">
         <v>587</v>
-      </c>
-      <c r="S80" s="44" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="81" spans="18:19">
       <c r="R81" s="44" t="s">
+        <v>588</v>
+      </c>
+      <c r="S81" s="44" t="s">
         <v>589</v>
-      </c>
-      <c r="S81" s="44" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="82" spans="18:19">
       <c r="R82" s="44" t="s">
+        <v>238</v>
+      </c>
+      <c r="S82" s="44" t="s">
         <v>239</v>
-      </c>
-      <c r="S82" s="44" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="83" spans="18:19">
       <c r="R83" s="46" t="s">
+        <v>590</v>
+      </c>
+      <c r="S83" s="46" t="s">
         <v>591</v>
-      </c>
-      <c r="S83" s="46" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="84" spans="18:19">
       <c r="R84" s="46" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="S84" s="46" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="85" spans="18:19">
       <c r="R85" s="44" t="s">
+        <v>592</v>
+      </c>
+      <c r="S85" s="44" t="s">
         <v>593</v>
-      </c>
-      <c r="S85" s="44" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="86" spans="18:19">
       <c r="R86" s="44" t="s">
+        <v>594</v>
+      </c>
+      <c r="S86" s="44" t="s">
         <v>595</v>
-      </c>
-      <c r="S86" s="44" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="87" spans="18:19">
       <c r="R87" s="44" t="s">
+        <v>596</v>
+      </c>
+      <c r="S87" s="44" t="s">
         <v>597</v>
-      </c>
-      <c r="S87" s="44" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="88" spans="18:19">
       <c r="R88" s="44" t="s">
+        <v>598</v>
+      </c>
+      <c r="S88" s="44" t="s">
         <v>599</v>
-      </c>
-      <c r="S88" s="44" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="89" spans="18:19">
       <c r="R89" s="44" t="s">
+        <v>600</v>
+      </c>
+      <c r="S89" s="44" t="s">
         <v>601</v>
-      </c>
-      <c r="S89" s="44" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="90" spans="18:19">
       <c r="R90" s="44" t="s">
+        <v>301</v>
+      </c>
+      <c r="S90" s="44" t="s">
         <v>302</v>
-      </c>
-      <c r="S90" s="44" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="91" spans="18:19">
       <c r="R91" s="44" t="s">
+        <v>602</v>
+      </c>
+      <c r="S91" s="44" t="s">
         <v>603</v>
-      </c>
-      <c r="S91" s="44" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="92" spans="18:19">
       <c r="R92" s="44" t="s">
+        <v>604</v>
+      </c>
+      <c r="S92" s="44" t="s">
         <v>605</v>
-      </c>
-      <c r="S92" s="44" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="93" spans="18:19">
       <c r="R93" s="44" t="s">
+        <v>606</v>
+      </c>
+      <c r="S93" t="s">
         <v>607</v>
-      </c>
-      <c r="S93" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="94" spans="18:19">
       <c r="R94" s="44" t="s">
+        <v>608</v>
+      </c>
+      <c r="S94" s="44" t="s">
         <v>609</v>
-      </c>
-      <c r="S94" s="44" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="95" spans="18:19">
       <c r="R95" s="44" t="s">
+        <v>610</v>
+      </c>
+      <c r="S95" s="44" t="s">
         <v>611</v>
-      </c>
-      <c r="S95" s="44" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="96" spans="18:19">
       <c r="R96" s="44" t="s">
+        <v>612</v>
+      </c>
+      <c r="S96" t="s">
         <v>613</v>
-      </c>
-      <c r="S96" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="97" spans="18:19">
       <c r="R97" s="44" t="s">
+        <v>290</v>
+      </c>
+      <c r="S97" s="57" t="s">
         <v>291</v>
-      </c>
-      <c r="S97" s="57" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="98" spans="18:19">
       <c r="R98" s="57" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="S98" s="32" t="s">
         <v>133</v>
@@ -60467,10 +60466,10 @@
     </row>
     <row r="99" spans="18:19">
       <c r="R99" s="44" t="s">
+        <v>615</v>
+      </c>
+      <c r="S99" t="s">
         <v>616</v>
-      </c>
-      <c r="S99" t="s">
-        <v>617</v>
       </c>
     </row>
   </sheetData>
